--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -489,7 +489,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-12</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1833,64 +1833,20 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - كحلي</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>بحث تقديري</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>wjhtektelecome</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أخضر</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>149.01 ر.س</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>بحث تقديري</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>alwan7</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>50.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -43,7 +43,7 @@
       <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +63,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,6 +109,9 @@
       <alignment vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -489,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-13</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -741,70 +749,70 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, iblackstores</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>194.01 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, iblackstores</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>9.96 ر.س</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>39.48 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>56.75 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -824,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -863,992 +871,1410 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>mokab</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>اوتلت مكعب</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>29.0 ر.س</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>mokab</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>اوتلت مكعب</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>5.0 ر.س</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>اكسسوارات ايفون 18</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>9.0 ر.س</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>اكسسوارات ايفون 18</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>9.0 ر.س</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>99.0 ر.س</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>119.0 ر.س</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>79.0 ر.س</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>9.96 ر.س</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>159.0 ر.س</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>129.0 ر.س</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>209.0 ر.س</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>179.0 ر.س</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>179.0 ر.س</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>149.0 ر.س</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>349.0 ر.س</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>129.0 ر.س</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>49.0 ر.س</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>149.0 ر.س</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>79.0 ر.س</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - برتقالي</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>iblackstores</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>جودا - بطاريات AAA القابلة للشحن</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>58.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>السعر: من الأقل إلى الأعلى</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>9.01 ر.س</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>iblackstores</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>58.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>جودا - شاحن سمارت للبطاريات الذكيه AA\AAA</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>139.02 ر.س</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>iblackstores</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>58.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>جودا - باور برو بطاريات قابلة للشحن 3600mWh</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>79.01 ر.س</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>iblackstores</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>جودا - منصة جودا بيك 4 منافذ تايب سي بقوة 240 واط - اسود</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>299.03 ر.س</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>بحث تقديري</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>iblackstores</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>جودا -شاحن سيارة كار فليكس 60 واط مع كابل مدمج بمنفذين USB-C و USB-A - أسود</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>79.01 ر.س</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>بحث تقديري</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>iblackstores</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>جودا - شاحن جداري بقوة 20 واط بمنفذ تايب سي - اسود</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>49.01 ر.س</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>بحث تقديري</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>iblackstores</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>جودا - شاحن سيارة بقوة 60 واط بمنفذين تايب سي - اسود</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>69.01 ر.س</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>بحث تقديري</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>iblackstores</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>149.01 ر.س</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>149.01 ر.س</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>alwan7</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>50.0 ر.س</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ميت باد 11.5 S بشاشة بيبر مات فائقة الوضوح وذاكرة 12 جيجابايت + 256 جيجابايت وبطارية 8800 ميلي امبير في الساعة وشحن فائق السرعة بقوة 40 واط مع لوحة مفاتيح قابلة للفصل من هواوي، رمادي</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>1799.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>3299.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>اونر تابلت باد في 9 (11.5 انش، واي فاي) 2024 سعة تخزين 256 جيجا، ذاكرة رام 8 جيجا، اندرويد 15 (رمادي)</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>1799.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت باد 7، 11.2 انش، 8+128 جيجا، رمادي، بطارية 8850mAh، شحن تيربو 45 واط، هايبر ايه اي (الشاحن غير متضمن)</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>1046.11 ر.س</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>1348.41 ر.س</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ريدمي باد 2 بذاكرة رام 4 جيجابايت وذاكرة روم 128 جيجابايت، لافندر أرجواني</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>740.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد اس اي 11 انش 4+128 جيجا رمادي، شاشة فل فيو وبطارية كبيرة السعة (مجددة)</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>549.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>تابلت شاومي ريدمي باد 2، 11 انش، 6 جيجا، 128 جيجا، واي فاي، هايبر او اس، اخضر مينت</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>991.44 ر.س</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد 12 × 2025 شاشة بيبر ميت 2.8K 12 بوصة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس ولوحة مفاتيح مرفقة (استخدام اللغة العربية غير مؤكد)، هواوي كير لمدة عام، (أبيض)</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>1999.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>3599.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>1289.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت باد ميني 12GB+512GB - تابلت 8.8 انش 3K 165Hz، الأبعاد 9400+، 7500mAh 67 واط، 13MP+8MP، هايبر او اس، اسود (مع الشاحن متضمن)</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>2682.22 ر.س</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت ريدمي باد 2 8 جيجابايت + 256 جيجابايت - رمادي - شاشة LCD 11 بوصة - 90 هرتز - بطارية 9000 مللي أمبير في الساعة - شاحن متضمن</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>1060.36 ر.س</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ون بلس باد 3، سناب دراجون 8 ايليت، معدل تحديث 144 هرتز، واي فاي (ستورم بلو، 12 جيجابايت + 256 جيجابايت)</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>3152.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت باد ميني 8+256GB، معالج ديمنستي 9400+، شاشة فائقة النعومة 8.8 انش 165Hz، بطارية بسعة كبيرة 7500mAh، واي فاي، ارجواني</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>2347.42 ر.س</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-14</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-15</t>
         </is>
       </c>
     </row>
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, iblackstores</t>
+          <t>aletawiksa, iblackstores, amazon_sa</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>194.01 ر.س</t>
+          <t>553.02 ر.س</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -795,11 +795,11 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, iblackstores</t>
+          <t>aletawiksa, iblackstores, amazon_sa</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>56.75 ر.س</t>
+          <t>59.09 ر.س</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>تابلت ميت باد 11.5 S بشاشة بيبر مات فائقة الوضوح وذاكرة 12 جيجابايت + 256 جيجابايت وبطارية 8800 ميلي امبير في الساعة وشحن فائق السرعة بقوة 40 واط مع لوحة مفاتيح قابلة للفصل من هواوي، رمادي</t>
+          <t>زد تي اي جوال A35e ثنائي شرائح الاتصال بذاكرة رام 2+4 جيجابايت وذاكرة داخلية 64 جيجابايت ويدعم تقنية 4G من بليد - اصدار الشرق الاوسط</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>1799.0 ر.س</t>
+          <t>309.0 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
+          <t>جوال سامسونج جالكسي A16، ذكي يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجابايت، تخزين 128 جيجابايت، أسود (إصدار المملكة العربية السعودية)</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>3299.0 ر.س</t>
+          <t>540.0 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>اونر تابلت باد في 9 (11.5 انش، واي فاي) 2024 سعة تخزين 256 جيجا، ذاكرة رام 8 جيجا، اندرويد 15 (رمادي)</t>
+          <t>جوال ذكي جالكسي A16، يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجا، ذاكرة تخزين 128 جيجا من سامسونج، رمادي (إصدار المملكة العربية السعودية)</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>1799.0 ر.س</t>
+          <t>549.0 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>شاومي تابلت باد 7، 11.2 انش، 8+128 جيجا، رمادي، بطارية 8850mAh، شحن تيربو 45 واط، هايبر ايه اي (الشاحن غير متضمن)</t>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>1046.11 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>1348.41 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>تابلت ريدمي باد 2 بذاكرة رام 4 جيجابايت وذاكرة روم 128 جيجابايت، لافندر أرجواني</t>
+          <t>جوال موتورولا G06 4G، ذاكرة وصول عشوائية 4+8 جيجابايت، وذاكرة داخلية 128 جيجابايت، ومعالج ام تي كيه هيليو G81 اكستريم، وشاشة 6.88 بوصة فائقة الدقة 120 هرتز، نظام اندرويد 15، لون بانتون تابيستري</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>740.0 ر.س</t>
+          <t>449.0 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>هواوي تابلت ميت باد اس اي 11 انش 4+128 جيجا رمادي، شاشة فل فيو وبطارية كبيرة السعة (مجددة)</t>
+          <t>جوال سامسونج جالكسي A17 ال تي اي، ثنائي شرائح اتصال، سعة 128 جيجا توسع حتى 2 تيرا، اندرويد 14 وذاكرة رام 4 جيجابايت، معالج اكسينوس وشاشة اموليد 6.7 بوصة بدقة 1080x2220، معدل تحديث 90 هرتز، لون أسود</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>549.0 ر.س</t>
+          <t>618.0 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>تابلت شاومي ريدمي باد 2، 11 انش، 6 جيجا، 128 جيجا، واي فاي، هايبر او اس، اخضر مينت</t>
+          <t>جوال A7 برو بذاكرة رام 4 جيجا وذاكرة روم 128 جيجا، لون أسود من ريدمي</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>991.44 ر.س</t>
+          <t>489.98 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>تابلت هواوي ميت باد 12 × 2025 شاشة بيبر ميت 2.8K 12 بوصة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس ولوحة مفاتيح مرفقة (استخدام اللغة العربية غير مؤكد)، هواوي كير لمدة عام، (أبيض)</t>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>1999.0 ر.س</t>
+          <t>82.95 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB</t>
+          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>3599.0 ر.س</t>
+          <t>139.99 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
+          <t>فيجير باور بانك 20000 مللي امبير في الساعة، شاحن محمول رفيع مع كيبلات متعددة مدمجة، بطارية شحن سريع عالية السعة مع شاشة عرض رقمية لايفون وسامسونج والجوالات - اسود</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>1289.0 ر.س</t>
+          <t>95.99 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>شاومي تابلت باد ميني 12GB+512GB - تابلت 8.8 انش 3K 165Hz، الأبعاد 9400+، 7500mAh 67 واط، 13MP+8MP، هايبر او اس، اسود (مع الشاحن متضمن)</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>2682.22 ر.س</t>
+          <t>198.82 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>شاومي تابلت ريدمي باد 2 8 جيجابايت + 256 جيجابايت - رمادي - شاشة LCD 11 بوصة - 90 هرتز - بطارية 9000 مللي أمبير في الساعة - شاحن متضمن</t>
+          <t>جوال هونر X5c، أزرق (تايدل بلو)</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>1060.36 ر.س</t>
+          <t>449.0 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>تابلت ون بلس باد 3، سناب دراجون 8 ايليت، معدل تحديث 144 هرتز، واي فاي (ستورم بلو، 12 جيجابايت + 256 جيجابايت)</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>3152.0 ر.س</t>
+          <t>138.87 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,15 +2264,675 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>شاومي تابلت باد ميني 8+256GB، معالج ديمنستي 9400+، شاشة فائقة النعومة 8.8 انش 165Hz، بطارية بسعة كبيرة 7500mAh، واي فاي، ارجواني</t>
+          <t>جوال ذكي اي تيل 4G A100c، ذاكرة تخزين 64 جيجابايت، اندرويد 14، ذاكرة رام 2 جيجابايت، يونيسوك T7100، شاشة LCD IPS مقاس 6.6 بوصة، دقة 1570x720، معدل تحديث 90 هرتز</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>2347.42 ر.س</t>
+          <t>369.0 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>449.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>447.27 ر.س</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب UG27PJ ليد 27 بوصة ومعدل تحديث 240Hz، لوحة IPS، استجابة 1 مل ثانية، دقة FHD (1920×1080)، سطوع 400 شمعة/م² من زد ايدج، حواف نحيفة، دعم فريسينك، منفذ(HDMI×2 وDP×2)، تثبت على الحائط، تدعم فيسا</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>519.19 ر.س</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>422.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب VG259QM5A بلوحة فاست اي بي اس FHD 24.5 بوصة، 240 هرتز، 0.3 مللي ثانية، جي-سينك وايه ام دي فري سينك بريميوم وELMB سينك، وألوان sRGB 99% ومركز ديسبلاي ويدجيت بالذكاء الاصطناعي من اسوس</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>699.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>549.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>AOC شاشة العاب 25G3ZM - 24.5 انش 240Hz FHD، ام بي ار تي 0.5 مللي ثانية، فري سينك بريميوم (1920x1080، HDMI 2.0 × 2، منفذ عرض 1.2 × 1، مخرج سماعة راس (3.5 ملم)) اسود/احمر</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>422.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب ليجن 24-10 23.8 بوصة FHD برو (لوحة IPS، 240هرتز، 0.5 مللي ثانية MPRT، HDMI 2.1، DP 1.4، HDR10)، حامل إمالة/دوران/رفع/محوري من لينوفو</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب منحنية مقاس 27 انش 280 هرتز FHD (1920x1080P) من ايسنو</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>499.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>490.56 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب منحنية 27 بوصة بدقة FHD 1080p 240Hz، لوحة IPS، وقت استجابة 0.5 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر، بدون إطار من ثلاث جهات، نحيفة للغاية، 100% sRGB، فلتر بلو لايت، DP، HDMI من فيوفيجن</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>529.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>281.51 ر.س</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب OLED من ماجيستي 27 بوصة 2K QHD | QD-OLED | 240Hz | 0.03ms | HDR400 | ‎120% sRGB | 10-Bit | G-SYNC &amp; FreeSync | HDMI 2.1 | DP | VESA | سماعات مدمجة | RGB خلفي | حامل مرن</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>1775.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب منحنية 32 بوصة، معدل تحديث 240 هرتز، دقة FHD 1080 بكسل 1500R HDR فري سينك، شاشة فائقة السرعة 1 مللي ثانية للاعب، تباين 3500:1 و2× منفذ HDMI 2.0، منفذ عرض 1.4 وUSB 2.0 من كيه تي سي، H32S17F</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>775.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>شاشة عرض للالعاب VX3219-PC-MHD منحنية قياس 32 انش بعرض HD 1080P،240Hz و1ms، تتضمن مكبرات صوت مزدوجة مدمجة بتزامن تكيفي و2 × HDMI ومنفذ عرض من فيوسونيك، بلون اسود، LED</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>599.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>38.49 ر.س</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>88.74 ر.س</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>45.85 ر.س</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>88.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>35.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>88.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>39.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>59.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>89.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>جوي رووم شاحن سيارة صغير JR-CCN05 30 واط USB-A USB-C يوفر شحن سريع وآمن، يشحن جهازين في وقت واحد - اسود</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>24.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>39.18 ر.س</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>75.88 ر.س</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>29.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 16 و15 وسامسونج S25 وS24 بـ3 منافذ بقدرة 145 واط مع شحن سريع وكابل قابل للسحب وحماية متعددة</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>149.65 ر.س</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-15</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-16</t>
         </is>
       </c>
     </row>
@@ -585,21 +585,21 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>al3bor-telecom</t>
+          <t>al3bor-telecom, amazon_sa</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>40.19 ر.س</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>271.71 ر.س</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -644,70 +644,70 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="C7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>11.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>38.46 ر.س</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="C8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>80.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>115.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -749,70 +749,70 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>aletawiksa, iblackstores, amazon_sa</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>553.02 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>608.62 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>aletawiksa, iblackstores, amazon_sa</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>9.96 ر.س</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>59.09 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>66.08 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>جودا -شاحن سيارة كار فليكس 60 واط مع كابل مدمج بمنفذين USB-C و USB-A - أسود</t>
+          <t>جودا - شاحن جداري بقوة 20 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>79.01 ر.س</t>
+          <t>49.01 ر.س</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن جداري بقوة 20 واط بمنفذ تايب سي - اسود</t>
+          <t>جودا -شاحن سيارة كار فليكس 60 واط مع كابل مدمج بمنفذين USB-C و USB-A - أسود</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>49.01 ر.س</t>
+          <t>79.01 ر.س</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>زد تي اي جوال A35e ثنائي شرائح الاتصال بذاكرة رام 2+4 جيجابايت وذاكرة داخلية 64 جيجابايت ويدعم تقنية 4G من بليد - اصدار الشرق الاوسط</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>309.0 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>جوال سامسونج جالكسي A16، ذكي يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجابايت، تخزين 128 جيجابايت، أسود (إصدار المملكة العربية السعودية)</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>540.0 ر.س</t>
+          <t>94.97 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>جوال ذكي جالكسي A16، يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجا، ذاكرة تخزين 128 جيجا من سامسونج، رمادي (إصدار المملكة العربية السعودية)</t>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>549.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>118.98 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
+          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>61.99 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>جوال موتورولا G06 4G، ذاكرة وصول عشوائية 4+8 جيجابايت، وذاكرة داخلية 128 جيجابايت، ومعالج ام تي كيه هيليو G81 اكستريم، وشاشة 6.88 بوصة فائقة الدقة 120 هرتز، نظام اندرويد 15، لون بانتون تابيستري</t>
+          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>449.0 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>جوال سامسونج جالكسي A17 ال تي اي، ثنائي شرائح اتصال، سعة 128 جيجا توسع حتى 2 تيرا، اندرويد 14 وذاكرة رام 4 جيجابايت، معالج اكسينوس وشاشة اموليد 6.7 بوصة بدقة 1080x2220، معدل تحديث 90 هرتز، لون أسود</t>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>618.0 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>جوال A7 برو بذاكرة رام 4 جيجا وذاكرة روم 128 جيجا، لون أسود من ريدمي</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>489.98 ر.س</t>
+          <t>198.82 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>82.95 ر.س</t>
+          <t>138.87 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو</t>
+          <t>باور بانك من يوجرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب A مع شحن سريع وحماية للهاتف واللابتوب 3 منافذ</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>139.99 ر.س</t>
+          <t>178.86 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>فيجير باور بانك 20000 مللي امبير في الساعة، شاحن محمول رفيع مع كيبلات متعددة مدمجة، بطارية شحن سريع عالية السعة مع شاشة عرض رقمية لايفون وسامسونج والجوالات - اسود</t>
+          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>95.99 ر.س</t>
+          <t>139.99 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>198.82 ر.س</t>
+          <t>189.0 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>جوال هونر X5c، أزرق (تايدل بلو)</t>
+          <t>بنك طاقة من انيو، شاحن محمول صغير بقدرة 22.5 واط وسعة 20000 ميلي أمبير، مزوّد بمدخل ومخرج USB-C، يدعم الشحن السريع PD 3.0 وQC 4.0، مع شاشة LED، لايفون 17 و16 و15 وسامسونج S25 وS24 وهواوي وهونر وغيرها</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>449.0 ر.س</t>
+          <t>111.14 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>138.87 ر.س</t>
+          <t>178.8 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>جوال ذكي اي تيل 4G A100c، ذاكرة تخزين 64 جيجابايت، اندرويد 14، ذاكرة رام 2 جيجابايت، يونيسوك T7100، شاشة LCD IPS مقاس 6.6 بوصة، دقة 1570x720، معدل تحديث 90 هرتز</t>
+          <t>شاحن محمول C سعة 20000 مللي أمبير، باور بانك 20K بمنفذ إدخال وإخراج نوع C ومنفذين A مع كيبل C إلى A مرفق لأجهزة ايفون وجالكسي وبيكسل وايباد وإيربودز والمزيد من بيلكن - رمادي سبيس</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>369.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+          <t>دار الأداب الهاربون والباقون</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>449.0 ر.س</t>
+          <t>98.0 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>447.27 ر.س</t>
+          <t>217.0 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب UG27PJ ليد 27 بوصة ومعدل تحديث 240Hz، لوحة IPS، استجابة 1 مل ثانية، دقة FHD (1920×1080)، سطوع 400 شمعة/م² من زد ايدج، حواف نحيفة، دعم فريسينك، منفذ(HDMI×2 وDP×2)، تثبت على الحائط، تدعم فيسا</t>
+          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>519.19 ر.س</t>
+          <t>40.19 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+          <t>بيلا فيتا جزمة هارب للنساء</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>422.98 ر.س</t>
+          <t>268.31 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب VG259QM5A بلوحة فاست اي بي اس FHD 24.5 بوصة، 240 هرتز، 0.3 مللي ثانية، جي-سينك وايه ام دي فري سينك بريميوم وELMB سينك، وألوان sRGB 99% ومركز ديسبلاي ويدجيت بالذكاء الاصطناعي من اسوس</t>
+          <t>رمح بلانتيك هاربون للصيد بالرمح بطول 104 سم وبهيكل من الالومنيوم الازرق مع قفازات، ألومنيوم عالي الجودة بطلاء مضاد للتآكل</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>699.0 ر.س</t>
+          <t>572.34 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>549.0 ر.س</t>
+          <t>291.0 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>AOC شاشة العاب 25G3ZM - 24.5 انش 240Hz FHD، ام بي ار تي 0.5 مللي ثانية، فري سينك بريميوم (1920x1080، HDMI 2.0 × 2، منفذ عرض 1.2 × 1، مخرج سماعة راس (3.5 ملم)) اسود/احمر</t>
+          <t>روبوتايم 3 دي بازل هارب</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>422.89 ر.س</t>
+          <t>204.52 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب ليجن 24-10 23.8 بوصة FHD برو (لوحة IPS، 240هرتز، 0.5 مللي ثانية MPRT، HDMI 2.1، DP 1.4، HDR10)، حامل إمالة/دوران/رفع/محوري من لينوفو</t>
+          <t>وايلد ريبابليك لعبة قطيفة من بوكيت كينز ايكو هارب، حيوان محشو، 5 انش، مصنوعة من مواد معاد تدويرها، صديقة للبيئة</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>499.0 ر.س</t>
+          <t>67.26 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>شاشة العاب منحنية مقاس 27 انش 280 هرتز FHD (1920x1080P) من ايسنو</t>
+          <t>سبيري حذاء رياضي هاربون كراش باك سهل الارتداء للرجال</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>499.95 ر.س</t>
+          <t>366.64 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+          <t>سبيري حذاء قارب هاربون للرجال</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>490.56 ر.س</t>
+          <t>330.36 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب منحنية 27 بوصة بدقة FHD 1080p 240Hz، لوحة IPS، وقت استجابة 0.5 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر، بدون إطار من ثلاث جهات، نحيفة للغاية، 100% sRGB، فلتر بلو لايت، DP، HDMI من فيوفيجن</t>
+          <t>سبيري حذاء قارب للرجال من هاربون، بيج داكن، مقاس 42 EU</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>529.0 ر.س</t>
+          <t>310.17 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+          <t>سبيري حذاء قارب هاربون للرجال، لون بيج داكن، مقاس 11.5</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>281.51 ر.س</t>
+          <t>354.82 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب OLED من ماجيستي 27 بوصة 2K QHD | QD-OLED | 240Hz | 0.03ms | HDR400 | ‎120% sRGB | 10-Bit | G-SYNC &amp; FreeSync | HDMI 2.1 | DP | VESA | سماعات مدمجة | RGB خلفي | حامل مرن</t>
+          <t>سبيري حذاء هاربون على شكل قارب للرجال، كحلي، مقاس 42 EU</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>1775.0 ر.س</t>
+          <t>277.5 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب منحنية 32 بوصة، معدل تحديث 240 هرتز، دقة FHD 1080 بكسل 1500R HDR فري سينك، شاشة فائقة السرعة 1 مللي ثانية للاعب، تباين 3500:1 و2× منفذ HDMI 2.0، منفذ عرض 1.4 وUSB 2.0 من كيه تي سي، H32S17F</t>
+          <t>Sperry Mens Harpoon Crushback Slip on Sneaker</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>775.99 ر.س</t>
+          <t>366.64 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>شاشة عرض للالعاب VX3219-PC-MHD منحنية قياس 32 انش بعرض HD 1080P،240Hz و1ms، تتضمن مكبرات صوت مزدوجة مدمجة بتزامن تكيفي و2 × HDMI ومنفذ عرض من فيوسونيك، بلون اسود، LED</t>
+          <t>سبيري حذاء قارب هاربون للرجال، رمادي، 8.5</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>599.9 ر.س</t>
+          <t>316.25 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>38.49 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>88.74 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>45.85 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>88.99 ر.س</t>
+          <t>112.0 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+          <t>نقطة وصول لاسلكية EAP650 اومادا واي فاي 6 AX3000 من تي بي لينك، تدعم شبكة</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>35.99 ر.س</t>
+          <t>364.35 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
+          <t>راوتر من تي بي لينك لكاميرات الأمن والمراقبة، بنطاق مفرد وإيثرنت، بسرعة 867 ميغابت في الثانية، مع التوصيل والتشغيل ومقاوم للعوامل الجوية، طراز بيم بريدج 5 UR كيت</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>88.89 ر.س</t>
+          <t>602.0 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+          <t>راوتر من تي بي-لينك أبيض لكاميرات IP والأجهزة الذكية، بنطاق مفرد وتقنية Wi-Fi، بسرعة 867 ميغابت في الثانية، مع نقل طويل المدى و MU-MIMO، طراز EAP211</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>39.9 ر.س</t>
+          <t>438.0 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>59.89 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+          <t>TP - لينك نقطة وصول لاسلكية تثبت بالسقف بسرعة 300 ميجابت في الثانية EAP115</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>89.99 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>جوي رووم شاحن سيارة صغير JR-CCN05 30 واط USB-A USB-C يوفر شحن سريع وآمن، يشحن جهازين في وقت واحد - اسود</t>
+          <t>TP - لينك TL-POE4824G - حاقن PoE</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>24.99 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+          <t>TP - لينك راوتر واي فاي خارجي 4G 300 ميجابت لكل ثانية من TL-MR100</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>222.51 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+          <t>TP - لينك راوتر خارجي MR402 خارجي 4G LTE من ارتشر، واي فاي AC1200Mbps ثنائي النطاق، مقاوم للماء IP65، دعم POE/DC، كات 4 حتى 150 ميجابت في الثانية، تقنية ون ميش، تركيب عمود/حائط، توصيل وتشغيل</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>39.18 ر.س</t>
+          <t>289.0 ر.س</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+          <t>TP - لينك مجموعة جسر EAP211، جسر لاسلكي من نقطة الى نقطة، 3 منافذ جيجابت، للاستخدام الخارجي والداخلي، نطاق طويل 1 كم، PtP &amp; PtMP، مدى طويل 1 كم، يعمل عبر الايثرنت او تيار مستمر، ادارة مركزية، تكوين</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>75.88 ر.س</t>
+          <t>438.0 ر.س</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+          <t>شاحن 17 فولت 1 امبير لمكبر الصوت اللاسلكي بوز ساوند لينك I II III 1 2 3</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>29.0 ر.س</t>
+          <t>68.48 ر.س</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -2924,15 +2924,1643 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>186.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>11.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>20.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>16.94 ر.س</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>11.79 ر.س</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>13.14 ر.س</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>106.08 ر.س</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه الكترونية ذكية قابلة للشحن عبر USB لغالونات وقوارير المياه | موزع مياه أوتوماتيكي محمول للمنزل والمكتب | لون اسود | ra206</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>12.21 ر.س</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من شوواي يدوي مطفي أزرق مصنوع من البلاستيك سعة 22.7 لتر</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>14.1 ر.س</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>13.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>يعمل الجهاز بضغط يصل إلى 26.1 PSI (حوالي 1.8 بار) وبقدرة كهربائية تبلغ 100 وات، مما يوفر أداءً فعالًا وقوة تشغيل مناسبة، مضخة مياه موفرة للطاقة 24 فولت مع محول 1/2 بوصة للاستحمام المنزلي وإمدادات</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>180.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>مضخة موزع مياه كهربائية، مضخة زجاجة مياه شرب أوتوماتيكية قابلة لاعادة الشحن بمنفذ USB لزجاجة عالمية سعة من 11.4 إلى 18.9 لتر، موزع للمكتب والمنزل والتخييم والمطبخ وما الى ذلك من مومنت</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>14.2 ر.س</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>29.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>15.66 ر.س</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>مجموعة رؤوس ضخ بديلة شاملة لموزعات الشراب متوافقة مع ابوريا وتوراني ودافينتشي ومونين (25 - 35 ملم، ابيض)، 2 قطع</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>13.5 ر.س</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>مضخة زجاجة مياه سعة 5 جالون موزع زجاجة مياه شحن يو اس بي مضخة مياه شرب اوتوماتيكية كهربائية محمولة مع مفتاح لزجاجة المياه</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>16.72 ر.س</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك مع 3 منافذ بي دي 20 واط 10000 مللي أمبير في الساعة من راف باور، شحن سريع PD/QC، شحن 3 أجهزة في وقت واحد، توافق عالمي لايفون 15/16 والمزيد، USB نوع C مزدوج + USB-A، تقنية اي سمارت</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>80.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>284.05 ر.س</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>159.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>159.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>139.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>118.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>94.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>109.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك في 9، شاحن محمول صغير 22.5 واط USB C 10000 مللي امبير في الساعة، حزمة بطارية شحن سريع بي دي، 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد رمادي</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>82.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>79.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك من أنكر فائق السرعة بسعة 25.000 مللي أمبير/الساعة وقوة 165 واط، لشحن 2 لابتوب، بطارية شحن سريع مع كابلات مدمجة وقابلة للطي، متوافق مع آيفون من سلسلة 16/15 وسامسونج وغيرها</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>298.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>محول جهد كهربائي 220 فولت إلى 110 فولت من ازوني، محول طاقة للسفر من 220 فولت إلى 110 فولت لأداة فرد الشعر والتلفزيون واللابتوب</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>55.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>محول جهد كهربائي 3000 واط 110 فولت/120 فولت/220 فولت/240 فولت من اليسم، محول طاقة تصاعدي / لأسفل مع حماية من قاطع الدائرة الكهربائية قابل لاعادة الضبط، مقبس عالمي مدمج للمنزل</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>499.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>جهاز اختبار بطارية السيارة 12 فولت 24 فولت، واختبار تحميل البطارية وعرض تيار بدء التشغيل على البارد رقميا محلل تلقائي دقيق اداة تشخيص البطارية مناسب للشاحنات والدراجات النارية من اياكام (من 8 إلى 30</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>75.34 ر.س</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>جهاز اختبار بطارية السيارة طراز BT600 قدرة 12 فولت 24 فولت مع طابعة، قياس التيار عند التشغيل البارد 100 إلى 2000 من توبدون، شاشة ملونة 3.5 بوصة، كيبل 1.8 م، متوفر تحديث البرامج</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>686.29 ر.س</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>مكيف هواء 12 فولت تيار مستمر، مكيف سقف قابل للتطبيق على الشاحنات والمركبات الترفيهية والحافلات والحفارات والمخيمات والمركبات الزراعية، مكيف هواء 12 فولت يعمل على البارد والساخن 24 فولت</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>1987.09 ر.س</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 220 فولت إلى تيار مستمر 12 فولت، محول بتيار 10 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>31.69 ر.س</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>جهاز اختبار رقمي اوتوماتيكي KW208 للبطارية بقوة 12 فولت / 100 -2000 امبير في درجات الحرارة الباردة للسيارة لاختبار المولد ونظام التشغيل والشحن مناسب للقوارب والدراجات البخارية والدفع الرباعي من كونوي</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>105.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه باردة ومضخة تفريغ الهواء مصغرة اي كيه 1856 بتيار مستمر وبجهد 6 فولت الى 12 فولت ار385 من جيكفن</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>38.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>وحدة تزويد طاقة تفاعلية 1000 فولت امبير من ارترونيك ارت، مزود طاقة غير منقطع 1000 فولت أمبير/600 واط، تنظيم جهد ايه في ار، موجة جيبية محاكاة، وظيفة التشغيل البارد، متوافق مع المولد</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>445.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>محول جهد كهربائي 2000 واط، 3000 واط، 110/120 فولت الى 220/240 فولت، حماية قاطع الدائرة، للاستخدام المنزلي (2000 واط)</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>400.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 500 فولت إلى تيار مستمر 12 فولت، محول بتيار 42 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>75.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>جهاز اختبار بطارية السيارة الرقمية وأداة تشخيص المولد من انسيل، سعة تحميل 100-2000 CCA، تحليل الشحن والتحريك للدراجة النارية والشاحنة والقارب والمركبة الترفيهية والبحرية وغيرها، 12 فولت، BA101</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>221.66 ر.س</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>لمبة من بونلوكس بتقنية LED بإضاءة أبيض دافئ و أبيض طبيعي و أبيض بارد، عبوة من قطعتين، بقوة 8 واط</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>38.44 ر.س</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>جهاز اختبار بطارية السيارة KW218 6 فولت 12 فولت 100-2000 سي سي ايه، جهاز اختبار تحميل بطارية السيارة ونظام شحن التحريك، محلل بطارية رقمي تلقائي للسيارة والشاحنات والدراجات النارية والقارب</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>105.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>بطاريات سوبر قلوية بجهد عالي من جي بي، طراز 23A بقوة 12 فولت (عبوة مكونة من 5 بطاريات)</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>22.69 ر.س</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>449.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>447.27 ر.س</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>422.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب UG27PJ ليد 27 بوصة ومعدل تحديث 240Hz، لوحة IPS، استجابة 1 مل ثانية، دقة FHD (1920×1080)، سطوع 400 شمعة/م² من زد ايدج، حواف نحيفة، دعم فريسينك، منفذ(HDMI×2 وDP×2)، تثبت على الحائط، تدعم فيسا</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>519.19 ر.س</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب VG259QM5A بلوحة فاست اي بي اس FHD 24.5 بوصة، 240 هرتز، 0.3 مللي ثانية، جي-سينك وايه ام دي فري سينك بريميوم وELMB سينك، وألوان sRGB 99% ومركز ديسبلاي ويدجيت بالذكاء الاصطناعي من اسوس</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>699.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>AOC شاشة العاب 25G3ZM - 24.5 انش 240Hz FHD، ام بي ار تي 0.5 مللي ثانية، فري سينك بريميوم (1920x1080، HDMI 2.0 × 2، منفذ عرض 1.2 × 1، مخرج سماعة راس (3.5 ملم)) اسود/احمر</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>380.6 ر.س</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>493.78 ر.س</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>549.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب منحنية 27 بوصة بدقة FHD 1080p 240Hz، لوحة IPS، وقت استجابة 0.5 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر، بدون إطار من ثلاث جهات، نحيفة للغاية، 100% sRGB، فلتر بلو لايت، DP، HDMI من فيوفيجن</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>529.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>شاشة عرض للالعاب VX3219-PC-MHD منحنية قياس 32 انش بعرض HD 1080P،240Hz و1ms، تتضمن مكبرات صوت مزدوجة مدمجة بتزامن تكيفي و2 × HDMI ومنفذ عرض من فيوسونيك، بلون اسود، LED</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>599.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب اي بي اس 27 بوصة 2K 240Hz بدقة رباعية عالية 2560 × 1440، سريعة 1ms جي تي جي 120% sRGB فري سينك بإضاءة خلفية RGB للاعبين الرياضات الإلكترونية ومكبرات صوت مدمجة من جاوفولك</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>749.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب سامسونج 27 انش، QHD (2560 × 1440)، معدل تحديث 240Hz، وقت استجابة 1 مللي ثانية، ذكي، اسود، كوانتوم دوت، HDR600، LS27BG650EMXUE</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>1272.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب OLED من ماجيستي 27 بوصة 2K QHD | QD-OLED | 240Hz | 0.03ms | HDR400 | ‎120% sRGB | 10-Bit | G-SYNC &amp; FreeSync | HDMI 2.1 | DP | VESA | سماعات مدمجة | RGB خلفي | حامل مرن</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>1775.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="20" customHeight="1">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>GAMEON GOESP27240IPS E-sports Series, Black Gaming Monitor 27 Inch, 1920x1080p FHD IPS Panel, 240Hz Refresh Rate, 0.5ms Response Time, Supports HDR 10, PS5</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>599.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>789.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>38.49 ر.س</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="20" customHeight="1">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>88.74 ر.س</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>45.85 ر.س</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>88.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="20" customHeight="1">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>35.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>88.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="20" customHeight="1">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>59.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="20" customHeight="1">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>39.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="20" customHeight="1">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>89.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>جوي رووم شاحن سيارة صغير JR-CCN05 30 واط USB-A USB-C يوفر شحن سريع وآمن، يشحن جهازين في وقت واحد - اسود</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>24.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="20" customHeight="1">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>39.18 ر.س</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
           <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 16 و15 وسامسونج S25 وS24 بـ3 منافذ بقدرة 145 واط مع شحن سريع وكابل قابل للسحب وحماية متعددة</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
+      <c r="C169" s="6" t="inlineStr">
         <is>
           <t>149.65 ر.س</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>75.88 ر.س</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B171" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>29.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D171" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-16</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-17</t>
         </is>
       </c>
     </row>
@@ -585,21 +585,21 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>al3bor-telecom, amazon_sa</t>
+          <t>al3bor-telecom</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>40.19 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>271.71 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -644,70 +644,70 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>11.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>38.46 ر.س</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>10.72 ر.س</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>38.06 ر.س</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>80.0 ر.س</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>115.0 ر.س</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -749,70 +749,70 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, iblackstores</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>194.01 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>شاحن سيارة جودا</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>شواحن سيارة</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>aletawiksa, iblackstores, amazon_sa</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>608.62 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>شاحن سيارة جودا</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>شواحن سيارة</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa, iblackstores, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>9.96 ر.س</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>66.08 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>75.4 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D171"/>
+  <dimension ref="A1:D142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>139.02 ر.س</t>
+          <t>96.01 ر.س</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>جودا -شاحن سيارة كار فليكس 60 واط مع كابل مدمج بمنفذين USB-C و USB-A - أسود</t>
+          <t>جودا - سمارت تشارج 45 واط شحن سريع مزدوج - اسود</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن سيارة بقوة 60 واط بمنفذين تايب سي - اسود</t>
+          <t>جودا -شاحن سيارة كار فليكس 60 واط مع كابل مدمج بمنفذين USB-C و USB-A - أسود</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>69.01 ر.س</t>
+          <t>79.01 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>جودا - شاحن سيارة بقوة 60 واط بمنفذين تايب سي - اسود</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>69.01 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1797,17 +1797,17 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -1929,17 +1929,17 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1951,22 +1951,22 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>94.97 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
+          <t>جوال سامسونج جالكسي A16، ذكي يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجابايت، تخزين 128 جيجابايت، أسود (إصدار المملكة العربية السعودية)</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>589.0 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>جوال ذكي جالكسي A16، يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجا، ذاكرة تخزين 128 جيجا من سامسونج، رمادي (إصدار المملكة العربية السعودية)</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>118.98 ر.س</t>
+          <t>549.0 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
+          <t>زد تي اي جوال A35e ثنائي شرائح الاتصال بذاكرة رام 2+4 جيجابايت وذاكرة داخلية 64 جيجابايت ويدعم تقنية 4G من بليد - اصدار الشرق الاوسط</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>61.99 ر.س</t>
+          <t>309.0 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
+          <t>جوال جالكسي ذكي A07 LTE بنظام أندرويد وذاكرة تخزين 64GB وذاكرة رام 4GB و6x تحديثات نظام التشغيل مع شاشة كبيرة ومعالج 6nm من سامسونج، أخضر (إصدار المملكة العربية السعودية)</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>449.99 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+          <t>جوال جالكسي ذكي A07 LTE بنظام أندرويد وذاكرة تخزين 64GB وذاكرة رام 4GB و6x تحديثات نظام التشغيل مع شاشة كبيرة ومعالج 6nm من سامسونج (إصدار المملكة العربية السعودية)</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>450.0 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+          <t>جوال A7 برو بذاكرة رام 4 جيجا وذاكرة روم 128 جيجا، لون أسود من ريدمي</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>198.82 ر.س</t>
+          <t>489.98 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+          <t>جوال سامسونج جالكسي A17 ال تي اي، ثنائي شرائح اتصال، سعة 128 جيجا توسع حتى 2 تيرا، اندرويد 14 وذاكرة رام 4 جيجابايت، معالج اكسينوس وشاشة اموليد 6.7 بوصة بدقة 1080x2220، معدل تحديث 90 هرتز، لون أسود</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>138.87 ر.س</t>
+          <t>627.0 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب A مع شحن سريع وحماية للهاتف واللابتوب 3 منافذ</t>
+          <t>جوال هونر X5c، أزرق (تايدل بلو)</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>178.86 ر.س</t>
+          <t>449.0 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو</t>
+          <t>جوال اكسبلور 1 للاستخدام الخارجي، جوال ذكي بشبكة الجيل الخامس 5G مقاوم للماء بنظام أندرويد 15، شاشة 6.78 بوصة بدقة 2.4 كيه، 12 جيجابايت+256 جيجابايت، بطارية 20000 ميلي أمبير/الساعة</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>139.99 ر.س</t>
+          <t>1790.0 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
+          <t>جوال A200 ثنائي شرائح الاتصال بذاكرة رام 3 جيجابايت وسعة 128 جيجابايت وشبكة الجيل الرابع 4G من ايتل، أزرق (Nightly Blue)</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>189.0 ر.س</t>
+          <t>430.0 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>بنك طاقة من انيو، شاحن محمول صغير بقدرة 22.5 واط وسعة 20000 ميلي أمبير، مزوّد بمدخل ومخرج USB-C، يدعم الشحن السريع PD 3.0 وQC 4.0، مع شاشة LED، لايفون 17 و16 و15 وسامسونج S25 وS24 وهواوي وهونر وغيرها</t>
+          <t>جوال ذكي اي تيل 4G A100c، ذاكرة تخزين 64 جيجابايت، اندرويد 14، ذاكرة رام 2 جيجابايت، يونيسوك T7100، شاشة LCD IPS مقاس 6.6 بوصة، دقة 1570x720، معدل تحديث 90 هرتز</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>111.14 ر.س</t>
+          <t>369.0 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000</t>
+          <t>جوال هونر ذكي X7e بطارية سيليكون كربون وشريحتين وشحن فائق 45 واط وشاشة 120Hz وكاميرا 50MP مدعومة بالذكاء الاصطناعي، بتصنيف IP64 لمقاومة المياه والغبار، ذاكرة رام 6GB وذاكرة تخزين 128GB، لون أزرق فاتح</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>178.8 ر.س</t>
+          <t>645.0 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>شاحن محمول C سعة 20000 مللي أمبير، باور بانك 20K بمنفذ إدخال وإخراج نوع C ومنفذين A مع كيبل C إلى A مرفق لأجهزة ايفون وجالكسي وبيكسل وايباد وإيربودز والمزيد من بيلكن - رمادي سبيس</t>
+          <t>جوال ريدمي A5 ثنائي شرائح الاتصال بذاكرة 4 جيجابايت وذاكرة داخلية 128 جيجابايت ويدعم تقنية 4G - النسخة العالمية</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>449.0 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>دار الأداب الهاربون والباقون</t>
+          <t>موتورولا جوال موتو G06 ثنائي شرائح الاتصال بذاكرة روم 256GB وذاكرة RAM 4GB (جي اس ام فقط | بدون سي دي ام ايه) هاتف ذكي 4G/LTE مفتوح من المصنع (بانتون تيندريل) - اصدار عالمي</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>98.0 ر.س</t>
+          <t>489.0 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>خلطة فيز 160 جم من هاريبو</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>217.0 ر.س</t>
+          <t>9.75 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
+          <t>حلوى بيريز من هاريبو، 160 جم</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>40.19 ر.س</t>
+          <t>8.99 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>بيلا فيتا جزمة هارب للنساء</t>
+          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>268.31 ر.س</t>
+          <t>7.95 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>رمح بلانتيك هاربون للصيد بالرمح بطول 104 سم وبهيكل من الالومنيوم الازرق مع قفازات، ألومنيوم عالي الجودة بطلاء مضاد للتآكل</t>
+          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>572.34 ر.س</t>
+          <t>8.99 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>291.0 ر.س</t>
+          <t>5.99 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>روبوتايم 3 دي بازل هارب</t>
+          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>204.52 ر.س</t>
+          <t>19.95 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>وايلد ريبابليك لعبة قطيفة من بوكيت كينز ايكو هارب، حيوان محشو، 5 انش، مصنوعة من مواد معاد تدويرها، صديقة للبيئة</t>
+          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>67.26 ر.س</t>
+          <t>14.5 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء رياضي هاربون كراش باك سهل الارتداء للرجال</t>
+          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>366.64 ر.س</t>
+          <t>16.48 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء قارب هاربون للرجال</t>
+          <t>حلوى هابي كولا من هاريبو، 80 جم</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>330.36 ر.س</t>
+          <t>6.0 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء قارب للرجال من هاربون، بيج داكن، مقاس 42 EU</t>
+          <t>حلوى جيلاتينية هاريبو جولد بيرز، 350 جم، عبوة من 5 قطع</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>310.17 ر.س</t>
+          <t>9.75 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء قارب هاربون للرجال، لون بيج داكن، مقاس 11.5</t>
+          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>354.82 ر.س</t>
+          <t>9.95 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء هاربون على شكل قارب للرجال، كحلي، مقاس 42 EU</t>
+          <t>بسكويت فيز هابي كولا من هاريبو 160 جم</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>277.5 ر.س</t>
+          <t>8.99 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Sperry Mens Harpoon Crushback Slip on Sneaker</t>
+          <t>حلوى هابي كولا من هاريبو، 200 جم</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>366.64 ر.س</t>
+          <t>15.12 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء قارب هاربون للرجال، رمادي، 8.5</t>
+          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>316.25 ر.س</t>
+          <t>15.0 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>توت هاريبو 150 جرام</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>9.5 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>112.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>راوتر من تي بي لينك لكاميرات الأمن والمراقبة، بنطاق مفرد وإيثرنت، بسرعة 867 ميغابت في الثانية، مع التوصيل والتشغيل ومقاوم للعوامل الجوية، طراز بيم بريدج 5 UR كيت</t>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>602.0 ر.س</t>
+          <t>112.0 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>راوتر من تي بي-لينك أبيض لكاميرات IP والأجهزة الذكية، بنطاق مفرد وتقنية Wi-Fi، بسرعة 867 ميغابت في الثانية، مع نقل طويل المدى و MU-MIMO، طراز EAP211</t>
+          <t>TP - لينك راوتر واي فاي خارجي 4G 300 ميجابت لكل ثانية من TL-MR100</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>438.0 ر.س</t>
+          <t>218.99 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
+          <t>راوتر من تي بي-لينك أبيض لكاميرات IP والأجهزة الذكية، بنطاق مفرد وتقنية Wi-Fi، بسرعة 867 ميغابت في الثانية، مع نقل طويل المدى و MU-MIMO، طراز EAP211</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>438.0 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك نقطة وصول لاسلكية تثبت بالسقف بسرعة 300 ميجابت في الثانية EAP115</t>
+          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE4824G - حاقن PoE</t>
+          <t>TP - لينك نقطة وصول لاسلكية تثبت بالسقف بسرعة 300 ميجابت في الثانية EAP115</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك راوتر واي فاي خارجي 4G 300 ميجابت لكل ثانية من TL-MR100</t>
+          <t>TP - لينك TL-POE4824G - حاقن PoE</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>222.51 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>68.48 ر.س</t>
+          <t>66.18 ر.س</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+          <t>شاحن 9 فولت متوافق مع كاميرا المراقبة تي بي لينك تابو C110 C200 C210</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>186.25 ر.س</t>
+          <t>97.55 ر.س</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>11.0 ر.س</t>
+          <t>186.25 ر.س</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>20.9 ر.س</t>
+          <t>11.0 ر.س</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>16.94 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>11.79 ر.س</t>
+          <t>17.66 ر.س</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>106.08 ر.س</t>
+          <t>11.79 ر.س</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه الكترونية ذكية قابلة للشحن عبر USB لغالونات وقوارير المياه | موزع مياه أوتوماتيكي محمول للمنزل والمكتب | لون اسود | ra206</t>
+          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>12.21 ر.س</t>
+          <t>106.08 ر.س</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من شوواي يدوي مطفي أزرق مصنوع من البلاستيك سعة 22.7 لتر</t>
+          <t>مضخة مياه الكترونية ذكية قابلة للشحن عبر USB لغالونات وقوارير المياه | موزع مياه أوتوماتيكي محمول للمنزل والمكتب | لون اسود | ra206</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>14.1 ر.س</t>
+          <t>12.21 ر.س</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+          <t>يعمل الجهاز بضغط يصل إلى 26.1 PSI (حوالي 1.8 بار) وبقدرة كهربائية تبلغ 100 وات، مما يوفر أداءً فعالًا وقوة تشغيل مناسبة، مضخة مياه موفرة للطاقة 24 فولت مع محول 1/2 بوصة للاستحمام المنزلي وإمدادات</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>13.75 ر.س</t>
+          <t>180.0 ر.س</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>يعمل الجهاز بضغط يصل إلى 26.1 PSI (حوالي 1.8 بار) وبقدرة كهربائية تبلغ 100 وات، مما يوفر أداءً فعالًا وقوة تشغيل مناسبة، مضخة مياه موفرة للطاقة 24 فولت مع محول 1/2 بوصة للاستحمام المنزلي وإمدادات</t>
+          <t>براد ماء من شوواي يدوي مطفي أزرق مصنوع من البلاستيك سعة 22.7 لتر</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>180.0 ر.س</t>
+          <t>14.1 ر.س</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>29.0 ر.س</t>
+          <t>13.75 ر.س</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
+          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>15.66 ر.س</t>
+          <t>29.0 ر.س</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>مجموعة رؤوس ضخ بديلة شاملة لموزعات الشراب متوافقة مع ابوريا وتوراني ودافينتشي ومونين (25 - 35 ملم، ابيض)، 2 قطع</t>
+          <t>مضخة زجاجة مياه سعة 5 جالون موزع زجاجة مياه شحن يو اس بي مضخة مياه شرب اوتوماتيكية كهربائية محمولة مع مفتاح لزجاجة المياه</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>13.5 ر.س</t>
+          <t>16.72 ر.س</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>مضخة زجاجة مياه سعة 5 جالون موزع زجاجة مياه شحن يو اس بي مضخة مياه شرب اوتوماتيكية كهربائية محمولة مع مفتاح لزجاجة المياه</t>
+          <t>منفاخ هواء من جودتول يدوي مع إبرة الكرة و محول الفوهة و خرطوم تمديد و مضخة يدوية يدوي</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>16.72 ر.س</t>
+          <t>10.72 ر.س</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك مع 3 منافذ بي دي 20 واط 10000 مللي أمبير في الساعة من راف باور، شحن سريع PD/QC، شحن 3 أجهزة في وقت واحد، توافق عالمي لايفون 15/16 والمزيد، USB نوع C مزدوج + USB-A، تقنية اي سمارت</t>
+          <t>مجموعة رؤوس ضخ بديلة شاملة لموزعات الشراب متوافقة مع ابوريا وتوراني ودافينتشي ومونين (25 - 35 ملم، ابيض)، 2 قطع</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>80.0 ر.س</t>
+          <t>14.0 ر.س</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+          <t>شاحن باور بانك مع 3 منافذ بي دي 20 واط 10000 مللي أمبير في الساعة من راف باور، شحن سريع PD/QC، شحن 3 أجهزة في وقت واحد، توافق عالمي لايفون 15/16 والمزيد، USB نوع C مزدوج + USB-A، تقنية اي سمارت</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>284.05 ر.س</t>
+          <t>80.0 ر.س</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>258.62 ر.س</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>150.0 ر.س</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>150.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>118.98 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>94.97 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>118.98 ر.س</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>باور بانك في 9، شاحن محمول صغير 22.5 واط USB C 10000 مللي امبير في الساعة، حزمة بطارية شحن سريع بي دي، 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد رمادي</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>94.97 ر.س</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+          <t>شاحن باور بانك من أنكر فائق السرعة بسعة 25.000 مللي أمبير/الساعة وقوة 165 واط، لشحن 2 لابتوب، بطارية شحن سريع مع كابلات مدمجة وقابلة للطي، متوافق مع آيفون من سلسلة 16/15 وسامسونج وغيرها</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>82.95 ر.س</t>
+          <t>298.0 ر.س</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
+          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك من أنكر فائق السرعة بسعة 25.000 مللي أمبير/الساعة وقوة 165 واط، لشحن 2 لابتوب، بطارية شحن سريع مع كابلات مدمجة وقابلة للطي، متوافق مع آيفون من سلسلة 16/15 وسامسونج وغيرها</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>298.0 ر.س</t>
+          <t>198.82 ر.س</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>محول جهد كهربائي 220 فولت إلى 110 فولت من ازوني، محول طاقة للسفر من 220 فولت إلى 110 فولت لأداة فرد الشعر والتلفزيون واللابتوب</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>55.99 ر.س</t>
+          <t>138.87 ر.س</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>محول جهد كهربائي 3000 واط 110 فولت/120 فولت/220 فولت/240 فولت من اليسم، محول طاقة تصاعدي / لأسفل مع حماية من قاطع الدائرة الكهربائية قابل لاعادة الضبط، مقبس عالمي مدمج للمنزل</t>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>499.99 ر.س</t>
+          <t>3299.0 ر.س</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>جهاز اختبار بطارية السيارة 12 فولت 24 فولت، واختبار تحميل البطارية وعرض تيار بدء التشغيل على البارد رقميا محلل تلقائي دقيق اداة تشخيص البطارية مناسب للشاحنات والدراجات النارية من اياكام (من 8 إلى 30</t>
+          <t>تابلت ميت باد 12 X 2025 شاشة بيبر بدقة 2.8K مقاس 12 بوصة 12+256 جيجابايت بطارية 10100 ميلي امبير شحن فائق 66 واط WPS مع اوفيس ولوحة مفاتيح داخل الصندوق من هواوي كير، لون أخضر</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>75.34 ر.س</t>
+          <t>2386.55 ر.س</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>جهاز اختبار بطارية السيارة طراز BT600 قدرة 12 فولت 24 فولت مع طابعة، قياس التيار عند التشغيل البارد 100 إلى 2000 من توبدون، شاشة ملونة 3.5 بوصة، كيبل 1.8 م، متوفر تحديث البرامج</t>
+          <t>اونر تابلت باد في 9 (11.5 انش، واي فاي) 2024 سعة تخزين 256 جيجا، ذاكرة رام 8 جيجا، اندرويد 15 (رمادي)</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>686.29 ر.س</t>
+          <t>1999.95 ر.س</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>مكيف هواء 12 فولت تيار مستمر، مكيف سقف قابل للتطبيق على الشاحنات والمركبات الترفيهية والحافلات والحفارات والمخيمات والمركبات الزراعية، مكيف هواء 12 فولت يعمل على البارد والساخن 24 فولت</t>
+          <t>تابلت هواوي ميت باد 12 × 2025 شاشة بيبر ميت 2.8K 12 بوصة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس ولوحة مفاتيح مرفقة (استخدام اللغة العربية غير مؤكد)، هواوي كير لمدة عام، (أبيض)</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>1987.09 ر.س</t>
+          <t>1999.0 ر.س</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 220 فولت إلى تيار مستمر 12 فولت، محول بتيار 10 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
+          <t>هواوي تابلت ميت باد 11.5 اس 2026 2.8K 144Hz فائق الوضوح، 12+256GB، شحن فائق 40 واط، واي فاي 6+، بلوتوث 5.2، جو بينت، كيبورد قابل للفصل، رمادي + ضمان ممتد لمدة عام</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>31.69 ر.س</t>
+          <t>1779.0 ر.س</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>جهاز اختبار رقمي اوتوماتيكي KW208 للبطارية بقوة 12 فولت / 100 -2000 امبير في درجات الحرارة الباردة للسيارة لاختبار المولد ونظام التشغيل والشحن مناسب للقوارب والدراجات البخارية والدفع الرباعي من كونوي</t>
+          <t>شاومي تابلت باد 7، 11.2 انش، 8+128 جيجا، رمادي، بطارية 8850mAh، شحن تيربو 45 واط، هايبر ايه اي (الشاحن غير متضمن)</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>105.0 ر.س</t>
+          <t>1070.06 ر.س</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه باردة ومضخة تفريغ الهواء مصغرة اي كيه 1856 بتيار مستمر وبجهد 6 فولت الى 12 فولت ار385 من جيكفن</t>
+          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>38.0 ر.س</t>
+          <t>1454.16 ر.س</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>وحدة تزويد طاقة تفاعلية 1000 فولت امبير من ارترونيك ارت، مزود طاقة غير منقطع 1000 فولت أمبير/600 واط، تنظيم جهد ايه في ار، موجة جيبية محاكاة، وظيفة التشغيل البارد، متوافق مع المولد</t>
+          <t>تابلت ريدمي باد 2 بذاكرة رام 4 جيجابايت وذاكرة روم 128 جيجابايت، لافندر أرجواني</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>445.0 ر.س</t>
+          <t>740.0 ر.س</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>محول جهد كهربائي 2000 واط، 3000 واط، 110/120 فولت الى 220/240 فولت، حماية قاطع الدائرة، للاستخدام المنزلي (2000 واط)</t>
+          <t>تابلت شاومي ريدمي باد 2، 11 انش، 6 جيجا، 128 جيجا، واي فاي، هايبر او اس، اخضر مينت</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>400.0 ر.س</t>
+          <t>991.44 ر.س</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 500 فولت إلى تيار مستمر 12 فولت، محول بتيار 42 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
+          <t>شاومي تابلت باد ميني 8+256GB، معالج ديمنستي 9400+، شاشة فائقة النعومة 8.8 انش 165Hz، بطارية بسعة كبيرة 7500mAh، واي فاي، ارجواني</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>75.3 ر.س</t>
+          <t>2304.82 ر.س</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>جهاز اختبار بطارية السيارة الرقمية وأداة تشخيص المولد من انسيل، سعة تحميل 100-2000 CCA، تحليل الشحن والتحريك للدراجة النارية والشاحنة والقارب والمركبة الترفيهية والبحرية وغيرها، 12 فولت، BA101</t>
+          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>221.66 ر.س</t>
+          <t>3599.0 ر.س</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>لمبة من بونلوكس بتقنية LED بإضاءة أبيض دافئ و أبيض طبيعي و أبيض بارد، عبوة من قطعتين، بقوة 8 واط</t>
+          <t>شاومي تابلت ريدمي باد 2 8 جيجابايت + 256 جيجابايت - رمادي - شاشة LCD 11 بوصة - 90 هرتز - بطارية 9000 مللي أمبير في الساعة - شاحن متضمن</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>38.44 ر.س</t>
+          <t>1060.36 ر.س</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>جهاز اختبار بطارية السيارة KW218 6 فولت 12 فولت 100-2000 سي سي ايه، جهاز اختبار تحميل بطارية السيارة ونظام شحن التحريك، محلل بطارية رقمي تلقائي للسيارة والشاحنات والدراجات النارية والقارب</t>
+          <t>تشو وي تابلت هاي 10 ماكس 33 سم 2880 × 1920 IPS، معالج انتل N150 (4C/4T، حتى 3.6Ghz)، 12GB DDR5، 512GB SSD، ويندوز 11 باد 3 في 1، واي فاي 6، كيبورد عربي</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>105.0 ر.س</t>
+          <t>2147.0 ر.س</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>بطاريات سوبر قلوية بجهد عالي من جي بي، طراز 23A بقوة 12 فولت (عبوة مكونة من 5 بطاريات)</t>
+          <t>تابلت هواوي ميت باد 10.4 انش بذاكرة روم 128GB وذاكرة RAM 4GB وواي فاي فقط (رمادي) - اصدار عالمي</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>22.69 ر.س</t>
+          <t>599.0 ر.س</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
@@ -3914,653 +3914,15 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+          <t>شاومي تابلت ريدمي باد 2 مي، 4GB + 128GB، ازرق سيان، ميديا تيك هيليو G100-الترا، شاشة 11 انش 2.5K 90Hz، بطارية 9000mAh، مع شاحن</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>449.0 ر.س</t>
+          <t>953.13 ر.س</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
-        </is>
-      </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>447.27 ر.س</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
-        </is>
-      </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>422.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب UG27PJ ليد 27 بوصة ومعدل تحديث 240Hz، لوحة IPS، استجابة 1 مل ثانية، دقة FHD (1920×1080)، سطوع 400 شمعة/م² من زد ايدج، حواف نحيفة، دعم فريسينك، منفذ(HDMI×2 وDP×2)، تثبت على الحائط، تدعم فيسا</t>
-        </is>
-      </c>
-      <c r="C145" s="6" t="inlineStr">
-        <is>
-          <t>519.19 ر.س</t>
-        </is>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب VG259QM5A بلوحة فاست اي بي اس FHD 24.5 بوصة، 240 هرتز، 0.3 مللي ثانية، جي-سينك وايه ام دي فري سينك بريميوم وELMB سينك، وألوان sRGB 99% ومركز ديسبلاي ويدجيت بالذكاء الاصطناعي من اسوس</t>
-        </is>
-      </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>699.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="20" customHeight="1">
-      <c r="A147" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B147" s="6" t="inlineStr">
-        <is>
-          <t>AOC شاشة العاب 25G3ZM - 24.5 انش 240Hz FHD، ام بي ار تي 0.5 مللي ثانية، فري سينك بريميوم (1920x1080، HDMI 2.0 × 2، منفذ عرض 1.2 × 1، مخرج سماعة راس (3.5 ملم)) اسود/احمر</t>
-        </is>
-      </c>
-      <c r="C147" s="6" t="inlineStr">
-        <is>
-          <t>380.6 ر.س</t>
-        </is>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B148" s="6" t="inlineStr">
-        <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
-        </is>
-      </c>
-      <c r="C148" s="6" t="inlineStr">
-        <is>
-          <t>493.78 ر.س</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B149" s="6" t="inlineStr">
-        <is>
-          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
-        </is>
-      </c>
-      <c r="C149" s="6" t="inlineStr">
-        <is>
-          <t>549.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D149" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب منحنية 27 بوصة بدقة FHD 1080p 240Hz، لوحة IPS، وقت استجابة 0.5 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر، بدون إطار من ثلاث جهات، نحيفة للغاية، 100% sRGB، فلتر بلو لايت، DP، HDMI من فيوفيجن</t>
-        </is>
-      </c>
-      <c r="C150" s="6" t="inlineStr">
-        <is>
-          <t>529.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="20" customHeight="1">
-      <c r="A151" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
-        <is>
-          <t>شاشة عرض للالعاب VX3219-PC-MHD منحنية قياس 32 انش بعرض HD 1080P،240Hz و1ms، تتضمن مكبرات صوت مزدوجة مدمجة بتزامن تكيفي و2 × HDMI ومنفذ عرض من فيوسونيك، بلون اسود، LED</t>
-        </is>
-      </c>
-      <c r="C151" s="6" t="inlineStr">
-        <is>
-          <t>599.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D151" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="20" customHeight="1">
-      <c r="A152" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب اي بي اس 27 بوصة 2K 240Hz بدقة رباعية عالية 2560 × 1440، سريعة 1ms جي تي جي 120% sRGB فري سينك بإضاءة خلفية RGB للاعبين الرياضات الإلكترونية ومكبرات صوت مدمجة من جاوفولك</t>
-        </is>
-      </c>
-      <c r="C152" s="6" t="inlineStr">
-        <is>
-          <t>749.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="20" customHeight="1">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب سامسونج 27 انش، QHD (2560 × 1440)، معدل تحديث 240Hz، وقت استجابة 1 مللي ثانية، ذكي، اسود، كوانتوم دوت، HDR600، LS27BG650EMXUE</t>
-        </is>
-      </c>
-      <c r="C153" s="6" t="inlineStr">
-        <is>
-          <t>1272.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D153" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="20" customHeight="1">
-      <c r="A154" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب OLED من ماجيستي 27 بوصة 2K QHD | QD-OLED | 240Hz | 0.03ms | HDR400 | ‎120% sRGB | 10-Bit | G-SYNC &amp; FreeSync | HDMI 2.1 | DP | VESA | سماعات مدمجة | RGB خلفي | حامل مرن</t>
-        </is>
-      </c>
-      <c r="C154" s="6" t="inlineStr">
-        <is>
-          <t>1775.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="20" customHeight="1">
-      <c r="A155" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B155" s="6" t="inlineStr">
-        <is>
-          <t>GAMEON GOESP27240IPS E-sports Series, Black Gaming Monitor 27 Inch, 1920x1080p FHD IPS Panel, 240Hz Refresh Rate, 0.5ms Response Time, Supports HDR 10, PS5</t>
-        </is>
-      </c>
-      <c r="C155" s="6" t="inlineStr">
-        <is>
-          <t>599.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D155" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="20" customHeight="1">
-      <c r="A156" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B156" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
-        </is>
-      </c>
-      <c r="C156" s="6" t="inlineStr">
-        <is>
-          <t>789.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="20" customHeight="1">
-      <c r="A157" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B157" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
-        </is>
-      </c>
-      <c r="C157" s="6" t="inlineStr">
-        <is>
-          <t>38.49 ر.س</t>
-        </is>
-      </c>
-      <c r="D157" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="20" customHeight="1">
-      <c r="A158" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>88.74 ر.س</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="20" customHeight="1">
-      <c r="A159" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>45.85 ر.س</t>
-        </is>
-      </c>
-      <c r="D159" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="20" customHeight="1">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C160" s="6" t="inlineStr">
-        <is>
-          <t>88.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D160" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="20" customHeight="1">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>35.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D161" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="20" customHeight="1">
-      <c r="A162" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
-        </is>
-      </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>88.89 ر.س</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="20" customHeight="1">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>59.89 ر.س</t>
-        </is>
-      </c>
-      <c r="D163" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="20" customHeight="1">
-      <c r="A164" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B164" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C164" s="6" t="inlineStr">
-        <is>
-          <t>39.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D164" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="20" customHeight="1">
-      <c r="A165" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B165" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C165" s="6" t="inlineStr">
-        <is>
-          <t>89.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D165" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="20" customHeight="1">
-      <c r="A166" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B166" s="6" t="inlineStr">
-        <is>
-          <t>جوي رووم شاحن سيارة صغير JR-CCN05 30 واط USB-A USB-C يوفر شحن سريع وآمن، يشحن جهازين في وقت واحد - اسود</t>
-        </is>
-      </c>
-      <c r="C166" s="6" t="inlineStr">
-        <is>
-          <t>24.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D166" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="20" customHeight="1">
-      <c r="A167" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>59.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D167" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="20" customHeight="1">
-      <c r="A168" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>39.18 ر.س</t>
-        </is>
-      </c>
-      <c r="D168" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="20" customHeight="1">
-      <c r="A169" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 16 و15 وسامسونج S25 وS24 بـ3 منافذ بقدرة 145 واط مع شحن سريع وكابل قابل للسحب وحماية متعددة</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>149.65 ر.س</t>
-        </is>
-      </c>
-      <c r="D169" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="20" customHeight="1">
-      <c r="A170" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B170" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C170" s="6" t="inlineStr">
-        <is>
-          <t>75.88 ر.س</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="20" customHeight="1">
-      <c r="A171" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B171" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
-        </is>
-      </c>
-      <c r="C171" s="6" t="inlineStr">
-        <is>
-          <t>29.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D171" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-17</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-18</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>10.72 ر.س</t>
+          <t>38.0 ر.س</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>38.06 ر.س</t>
+          <t>38.0 ر.س</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, iblackstores</t>
+          <t>aletawiksa, iblackstores, amazon_sa</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>194.01 ر.س</t>
+          <t>307.33 ر.س</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, iblackstores, amazon_sa</t>
+          <t>aletawiksa, amazon_sa</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>9.96 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>75.4 ر.س</t>
+          <t>109.5 ر.س</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D142"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1071,17 +1071,17 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>aletawiksa</t>
+          <t>al3bor-telecom</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>9.96 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
+          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
+          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
+          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>209.0 ر.س</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>209.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
+          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
+          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>349.0 ر.س</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
+          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>349.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
+          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
+          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>49.0 ر.س</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
+          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>49.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
+          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
+          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
+          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
+          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
+          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
+          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
+          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - برتقالي</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -1599,22 +1599,22 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>al3bor-telecom</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - برتقالي</t>
+          <t>جودا - بطاريات AAA القابلة للشحن</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>السعر: من الأقل إلى الأعلى</t>
+          <t>جودا - منصة جودا بيك 4 منافذ تايب سي بقوة 240 واط - اسود</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>9.01 ر.س</t>
+          <t>298.99 ر.س</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن سمارت للبطاريات الذكيه AA\AAA</t>
+          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>96.01 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>جودا - باور برو بطاريات قابلة للشحن 3600mWh</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>79.01 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1687,17 +1687,17 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>جودا - منصة جودا بيك 4 منافذ تايب سي بقوة 240 واط - اسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>299.03 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1709,17 +1709,17 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن جداري بقوة 20 واط بمنفذ تايب سي - اسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>49.01 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -1731,17 +1731,17 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>جودا - سمارت تشارج 45 واط شحن سريع مزدوج - اسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>79.01 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1753,17 +1753,17 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>جودا -شاحن سيارة كار فليكس 60 واط مع كابل مدمج بمنفذين USB-C و USB-A - أسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>79.01 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1775,17 +1775,17 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن سيارة بقوة 60 واط بمنفذين تايب سي - اسود</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>69.01 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1797,17 +1797,17 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1819,17 +1819,17 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1841,132 +1841,132 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>جوال سامسونج جالكسي A16، ذكي يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجابايت، تخزين 128 جيجابايت، أسود (إصدار المملكة العربية السعودية)</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>580.0 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>جوال ذكي جالكسي A16، يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجا، ذاكرة تخزين 128 جيجا من سامسونج، رمادي (إصدار المملكة العربية السعودية)</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>582.99 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>جوال اكسبلور 1 للاستخدام الخارجي، جوال ذكي بشبكة الجيل الخامس 5G مقاوم للماء بنظام أندرويد 15، شاشة 6.78 بوصة بدقة 2.4 كيه، 12 جيجابايت+256 جيجابايت، بطارية 20000 ميلي أمبير/الساعة</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>1790.0 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
+          <t>جوال جالكسي ذكي A07 LTE بنظام أندرويد وذاكرة تخزين 64GB وذاكرة رام 4GB و6x تحديثات نظام التشغيل مع شاشة كبيرة ومعالج 6nm من سامسونج، أخضر (إصدار المملكة العربية السعودية)</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>449.99 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
+          <t>زد تي اي جوال A35e ثنائي شرائح الاتصال بذاكرة رام 2+4 جيجابايت وذاكرة داخلية 64 جيجابايت ويدعم تقنية 4G من بليد - اصدار الشرق الاوسط</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>309.0 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>جوال سامسونج جالكسي A17 ال تي اي، ثنائي شرائح اتصال، سعة 128 جيجا توسع حتى 2 تيرا، اندرويد 14 وذاكرة رام 4 جيجابايت، معالج اكسينوس وشاشة اموليد 6.7 بوصة بدقة 1080x2220، معدل تحديث 90 هرتز، لون أسود</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>627.0 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+          <t>جوال A7 برو بذاكرة رام 4 جيجا وذاكرة روم 128 جيجا، لون أسود من ريدمي</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>489.98 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>جوال سامسونج جالكسي A16، ذكي يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجابايت، تخزين 128 جيجابايت، أسود (إصدار المملكة العربية السعودية)</t>
+          <t>جوال هونر X5c، أزرق (تايدل بلو)</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>589.0 ر.س</t>
+          <t>449.0 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>جوال ذكي جالكسي A16، يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجا، ذاكرة تخزين 128 جيجا من سامسونج، رمادي (إصدار المملكة العربية السعودية)</t>
+          <t>جوال تانك 1 متين 6.75 انش 120Hz FHD+ من شاندويليك، هاتف اتصال خارجي 12GB+256GB 20000mAh، هاتف ذكي 5G اندرويد 15 ان اف سي</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>549.0 ر.س</t>
+          <t>2090.0 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>زد تي اي جوال A35e ثنائي شرائح الاتصال بذاكرة رام 2+4 جيجابايت وذاكرة داخلية 64 جيجابايت ويدعم تقنية 4G من بليد - اصدار الشرق الاوسط</t>
+          <t>جوال سامسونج جالاكسي A57 الجيل الخامس 5G نظام أندرويد بسعة تخزين 256 جيجابايت ورام 8 جيجابايت بـ6 ترقيات لنظام التشغيلو شاشة كبيرة وكاميرا 50 ميجابكسل وعمر بطارية طويل، لون أزرق بحري (إصدار السعودية)</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>309.0 ر.س</t>
+          <t>1474.85 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>جوال جالكسي ذكي A07 LTE بنظام أندرويد وذاكرة تخزين 64GB وذاكرة رام 4GB و6x تحديثات نظام التشغيل مع شاشة كبيرة ومعالج 6nm من سامسونج، أخضر (إصدار المملكة العربية السعودية)</t>
+          <t>جوال هونر ذكي X7e بطارية سيليكون كربون وشريحتين وشحن فائق 45 واط وشاشة 120Hz وكاميرا 50MP مدعومة بالذكاء الاصطناعي، بتصنيف IP64 لمقاومة المياه والغبار، ذاكرة رام 6GB وذاكرة تخزين 128GB، لون أزرق فاتح</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>449.99 ر.س</t>
+          <t>645.0 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>جوال جالكسي ذكي A07 LTE بنظام أندرويد وذاكرة تخزين 64GB وذاكرة رام 4GB و6x تحديثات نظام التشغيل مع شاشة كبيرة ومعالج 6nm من سامسونج (إصدار المملكة العربية السعودية)</t>
+          <t>جوال ريدمي نوت 15 شبكة الجيل الخامس 5G ثنائي شرائح الاتصال بذاكرة رام 8 جيجابايت وذاكرة داخلية 256 جيجابايت - النسخة العالمية</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>450.0 ر.س</t>
+          <t>979.0 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>جوال A7 برو بذاكرة رام 4 جيجا وذاكرة روم 128 جيجا، لون أسود من ريدمي</t>
+          <t>جوال ايفون 12 ميني من ابل (64 جيجابايت) - لون أزرق (مجدد)</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>489.98 ر.س</t>
+          <t>650.0 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>جوال سامسونج جالكسي A17 ال تي اي، ثنائي شرائح اتصال، سعة 128 جيجا توسع حتى 2 تيرا، اندرويد 14 وذاكرة رام 4 جيجابايت، معالج اكسينوس وشاشة اموليد 6.7 بوصة بدقة 1080x2220، معدل تحديث 90 هرتز، لون أسود</t>
+          <t>جهاز عرض XP 2 من شاندوليك، هاتف ذكي 5G بالذكاء الاصطناعي، شاشة AMOLED 6.75 انش 3.2 كيه، كاميرا 50MP، 16GB + 1TB، 20000mAh، جوال خارجي متين</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>627.0 ر.س</t>
+          <t>3690.0 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>جوال هونر X5c، أزرق (تايدل بلو)</t>
+          <t>جوال متين تانك 1 من ال ام اتش تريد 6.78 انش 120Hz FHD + شاشة اتصال خارجية 16GB + 512GB 20000mAh، هاتف ذكي 5G اندرويد 15 ان اف سي</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>449.0 ر.س</t>
+          <t>2690.0 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>جوال اكسبلور 1 للاستخدام الخارجي، جوال ذكي بشبكة الجيل الخامس 5G مقاوم للماء بنظام أندرويد 15، شاشة 6.78 بوصة بدقة 2.4 كيه، 12 جيجابايت+256 جيجابايت، بطارية 20000 ميلي أمبير/الساعة</t>
+          <t>خلطة فيز 160 جم من هاريبو</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>1790.0 ر.س</t>
+          <t>9.75 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>جوال A200 ثنائي شرائح الاتصال بذاكرة رام 3 جيجابايت وسعة 128 جيجابايت وشبكة الجيل الرابع 4G من ايتل، أزرق (Nightly Blue)</t>
+          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>430.0 ر.س</t>
+          <t>17.95 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>جوال ذكي اي تيل 4G A100c، ذاكرة تخزين 64 جيجابايت، اندرويد 14، ذاكرة رام 2 جيجابايت، يونيسوك T7100، شاشة LCD IPS مقاس 6.6 بوصة، دقة 1570x720، معدل تحديث 90 هرتز</t>
+          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>369.0 ر.س</t>
+          <t>8.99 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>جوال هونر ذكي X7e بطارية سيليكون كربون وشريحتين وشحن فائق 45 واط وشاشة 120Hz وكاميرا 50MP مدعومة بالذكاء الاصطناعي، بتصنيف IP64 لمقاومة المياه والغبار، ذاكرة رام 6GB وذاكرة تخزين 128GB، لون أزرق فاتح</t>
+          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>645.0 ر.س</t>
+          <t>9.75 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>جوال ريدمي A5 ثنائي شرائح الاتصال بذاكرة 4 جيجابايت وذاكرة داخلية 128 جيجابايت ويدعم تقنية 4G - النسخة العالمية</t>
+          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>449.0 ر.س</t>
+          <t>15.23 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>موتورولا جوال موتو G06 ثنائي شرائح الاتصال بذاكرة روم 256GB وذاكرة RAM 4GB (جي اس ام فقط | بدون سي دي ام ايه) هاتف ذكي 4G/LTE مفتوح من المصنع (بانتون تيندريل) - اصدار عالمي</t>
+          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>489.0 ر.س</t>
+          <t>13.5 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>خلطة فيز 160 جم من هاريبو</t>
+          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>9.75 ر.س</t>
+          <t>7.5 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>حلوى بيريز من هاريبو، 160 جم</t>
+          <t>حلوى جيلاتينية هاريبو جولد بيرز، 350 جم، عبوة من 5 قطع</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>8.99 ر.س</t>
+          <t>9.75 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
+          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>7.95 ر.س</t>
+          <t>13.5 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
+          <t>بسكويت فيز هابي كولا من هاريبو 160 جم</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
+          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>5.99 ر.س</t>
+          <t>13.5 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
+          <t>حلوى هابي كولا من هاريبو، 80 جم</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>19.95 ر.س</t>
+          <t>7.95 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
+          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>14.5 ر.س</t>
+          <t>9.95 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
+          <t>توت هاريبو 150 جرام</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>16.48 ر.س</t>
+          <t>9.5 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 80 جم</t>
+          <t>حلوى هابي كولا من هاريبو، 200 جم</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>6.0 ر.س</t>
+          <t>15.22 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلاتينية هاريبو جولد بيرز، 350 جم، عبوة من 5 قطع</t>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>9.75 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>9.95 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>بسكويت فيز هابي كولا من هاريبو 160 جم</t>
+          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>8.99 ر.س</t>
+          <t>93.43 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 200 جم</t>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>15.12 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>15.0 ر.س</t>
+          <t>186.25 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>توت هاريبو 150 جرام</t>
+          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>9.5 ر.س</t>
+          <t>130.0 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>شاحن 17 فولت 1 امبير لمكبر الصوت اللاسلكي بوز ساوند لينك I II III 1 2 3</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>66.18 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+          <t>بطارية بديلة لجيه بي ال لينك 10، 3.7 فولت/3600 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>104.92 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
+          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>نقطة وصول لاسلكية EAP650 اومادا واي فاي 6 AX3000 من تي بي لينك، تدعم شبكة</t>
+          <t>شاحن 9 فولت متوافق مع كاميرا المراقبة تي بي لينك تابو C110 C200 C210</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>364.35 ر.س</t>
+          <t>97.55 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+          <t>شاحن مكبر صوت بلوتوث 12 فولت متوافق مع مكبر الصوت بوز ساوند لينك ميني اي اللاسلكي المحمول، سلك امدادات الطاقة (متوافق فقط مع بوز ساوند لينك ميني 1)</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>112.0 ر.س</t>
+          <t>106.78 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك راوتر واي فاي خارجي 4G 300 ميجابت لكل ثانية من TL-MR100</t>
+          <t>TP - لينك TL-POE4824G - حاقن PoE</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>218.99 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>راوتر من تي بي-لينك أبيض لكاميرات IP والأجهزة الذكية، بنطاق مفرد وتقنية Wi-Fi، بسرعة 867 ميغابت في الثانية، مع نقل طويل المدى و MU-MIMO، طراز EAP211</t>
+          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>438.0 ر.س</t>
+          <t>96.17 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
+          <t>محول طاقة ستيب اب بتيار مستمر 12 فولت/24 فولت الى 30 فولت لستارلينك ميني، محول معزز للادخال 9 فولت - 28 فولت مع فيوز لراوتر ستار لينك ميني ار في والشاحنة والسيارات البحرية والسفر</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>117.19 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك نقطة وصول لاسلكية تثبت بالسقف بسرعة 300 ميجابت في الثانية EAP115</t>
+          <t>شاحن باور بانك مع 3 منافذ بي دي 20 واط 10000 مللي أمبير في الساعة من راف باور، شحن سريع PD/QC، شحن 3 أجهزة في وقت واحد، توافق عالمي لايفون 15/16 والمزيد، USB نوع C مزدوج + USB-A، تقنية اي سمارت</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>80.0 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE4824G - حاقن PoE</t>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>258.62 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك راوتر خارجي MR402 خارجي 4G LTE من ارتشر، واي فاي AC1200Mbps ثنائي النطاق، مقاوم للماء IP65، دعم POE/DC، كات 4 حتى 150 ميجابت في الثانية، تقنية ون ميش، تركيب عمود/حائط، توصيل وتشغيل</t>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>289.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك مجموعة جسر EAP211، جسر لاسلكي من نقطة الى نقطة، 3 منافذ جيجابت، للاستخدام الخارجي والداخلي، نطاق طويل 1 كم، PtP &amp; PtMP، مدى طويل 1 كم، يعمل عبر الايثرنت او تيار مستمر، ادارة مركزية، تكوين</t>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>438.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>شاحن 17 فولت 1 امبير لمكبر الصوت اللاسلكي بوز ساوند لينك I II III 1 2 3</t>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>66.18 ر.س</t>
+          <t>150.0 ر.س</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>شاحن 9 فولت متوافق مع كاميرا المراقبة تي بي لينك تابو C110 C200 C210</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>97.55 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>186.25 ر.س</t>
+          <t>118.98 ر.س</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>11.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>20.9 ر.س</t>
+          <t>94.97 ر.س</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+          <t>باور بانك من يوجرين 10000 مللي امبير بمنفذ USB تايب-C مع شحن لاسلكي و سريع و مغناطيسي للهاتف الذكي بمنفذين رمادي</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>17.66 ر.س</t>
+          <t>118.99 ر.س</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>13.14 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>11.79 ر.س</t>
+          <t>82.95 ر.س</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
+          <t>باور بانك في 9، شاحن محمول صغير 22.5 واط USB C 10000 مللي امبير في الساعة، حزمة بطارية شحن سريع بي دي، 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد رمادي</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>106.08 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه الكترونية ذكية قابلة للشحن عبر USB لغالونات وقوارير المياه | موزع مياه أوتوماتيكي محمول للمنزل والمكتب | لون اسود | ra206</t>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>12.21 ر.س</t>
+          <t>79.96 ر.س</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>يعمل الجهاز بضغط يصل إلى 26.1 PSI (حوالي 1.8 بار) وبقدرة كهربائية تبلغ 100 وات، مما يوفر أداءً فعالًا وقوة تشغيل مناسبة، مضخة مياه موفرة للطاقة 24 فولت مع محول 1/2 بوصة للاستحمام المنزلي وإمدادات</t>
+          <t>جهاز اختبار بطارية السيارة 12 فولت 24 فولت، واختبار تحميل البطارية وعرض تيار بدء التشغيل على البارد رقميا محلل تلقائي دقيق اداة تشخيص البطارية مناسب للشاحنات والدراجات النارية من اياكام (من 8 إلى 30</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>180.0 ر.س</t>
+          <t>75.34 ر.س</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من شوواي يدوي مطفي أزرق مصنوع من البلاستيك سعة 22.7 لتر</t>
+          <t>محول جهد كهربائي 3000 واط 110 فولت/120 فولت/220 فولت/240 فولت من اليسم، محول طاقة تصاعدي / لأسفل مع حماية من قاطع الدائرة الكهربائية قابل لاعادة الضبط، مقبس عالمي مدمج للمنزل</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>14.1 ر.س</t>
+          <t>499.99 ر.س</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>مضخة موزع مياه كهربائية، مضخة زجاجة مياه شرب أوتوماتيكية قابلة لاعادة الشحن بمنفذ USB لزجاجة عالمية سعة من 11.4 إلى 18.9 لتر، موزع للمكتب والمنزل والتخييم والمطبخ وما الى ذلك من مومنت</t>
+          <t>جهاز اختبار بطارية السيارة طراز BT600 قدرة 12 فولت 24 فولت مع طابعة، قياس التيار عند التشغيل البارد 100 إلى 2000 من توبدون، شاشة ملونة 3.5 بوصة، كيبل 1.8 م، متوفر تحديث البرامج</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>14.2 ر.س</t>
+          <t>686.29 ر.س</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+          <t>مضخة مياه باردة ومضخة تفريغ الهواء مصغرة اي كيه 1856 بتيار مستمر وبجهد 6 فولت الى 12 فولت ار385 من جيكفن</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>13.75 ر.س</t>
+          <t>38.0 ر.س</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
+          <t>جهاز إمداد الطاقة من كولر ماستر إم دبليو إي برونز 750 V3 بقدرة 750 واط 230 فولت ATX 3.1 80 بلس برونز مروحة HDB 120 ملم، أسود</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>29.0 ر.س</t>
+          <t>239.0 ر.س</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>مضخة زجاجة مياه سعة 5 جالون موزع زجاجة مياه شحن يو اس بي مضخة مياه شرب اوتوماتيكية كهربائية محمولة مع مفتاح لزجاجة المياه</t>
+          <t>وحدة تزويد طاقة تفاعلية 1000 فولت امبير من ارترونيك ارت، مزود طاقة غير منقطع 1000 فولت أمبير/600 واط، تنظيم جهد ايه في ار، موجة جيبية محاكاة، وظيفة التشغيل البارد، متوافق مع المولد</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>16.72 ر.س</t>
+          <t>445.0 ر.س</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>منفاخ هواء من جودتول يدوي مع إبرة الكرة و محول الفوهة و خرطوم تمديد و مضخة يدوية يدوي</t>
+          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 220 فولت إلى تيار مستمر 12 فولت، محول بتيار 10 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>10.72 ر.س</t>
+          <t>42.79 ر.س</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>مجموعة رؤوس ضخ بديلة شاملة لموزعات الشراب متوافقة مع ابوريا وتوراني ودافينتشي ومونين (25 - 35 ملم، ابيض)، 2 قطع</t>
+          <t>جهاز اختبار رقمي اوتوماتيكي KW208 للبطارية بقوة 12 فولت / 100 -2000 امبير في درجات الحرارة الباردة للسيارة لاختبار المولد ونظام التشغيل والشحن مناسب للقوارب والدراجات البخارية والدفع الرباعي من كونوي</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>14.0 ر.س</t>
+          <t>105.0 ر.س</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك مع 3 منافذ بي دي 20 واط 10000 مللي أمبير في الساعة من راف باور، شحن سريع PD/QC، شحن 3 أجهزة في وقت واحد، توافق عالمي لايفون 15/16 والمزيد، USB نوع C مزدوج + USB-A، تقنية اي سمارت</t>
+          <t>محول جهد كهربائي 220 فولت إلى 110 فولت، محول طاقة للسفر 200 واط، محول خافض للجهد الكهربائي 220 فولت إلى 110 فولت لمكواة فرد الشعر وأجهزة التلفزيون واللابتوب من مابروتي</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>80.0 ر.س</t>
+          <t>57.99 ر.س</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+          <t>محول جهد كهربائي 2000 واط، 3000 واط، 110/120 فولت الى 220/240 فولت، حماية قاطع الدائرة، للاستخدام المنزلي (2000 واط)</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>258.62 ر.س</t>
+          <t>400.0 ر.س</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+          <t>جهاز اختبار بطارية السيارة الرقمية وأداة تشخيص المولد من انسيل، سعة تحميل 100-2000 CCA، تحليل الشحن والتحريك للدراجة النارية والشاحنة والقارب والمركبة الترفيهية والبحرية وغيرها، 12 فولت، BA101</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>150.0 ر.س</t>
+          <t>221.66 ر.س</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+          <t>محول جهد كهربائي 300W، 110V و120V و220V و240V، محول طاقة تصاعدي وتنازلي مع حماية من قاطع الدائرة الكهربائية قابلة لإعادة الضبط ومقبس عالمي مدمج للمنزل</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>159.99 ر.س</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 500 فولت إلى تيار مستمر 12 فولت، محول بتيار 42 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>96.09 ر.س</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>موزع مياه ساخن وبارد تحميل سفلي قائم على الارض 220-240 فولت مع ثلاجة من هوميكس - ابيض YLR-LW-2-5-100 باوند</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>396.0 ر.س</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -3430,499 +3430,15 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
+          <t>جهاز اختبار بطارية السيارة من ايكام، مقياس جهد رقمي للبطارية 12 فولت ومحلل نظام الشحن مع شاشة ال سي دي للدراجات النارية والسكوتر الكهربائي والقارب وسيارات الدفع الرباعي</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>18.04 ر.س</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>118.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>94.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>شاحن باور بانك من أنكر فائق السرعة بسعة 25.000 مللي أمبير/الساعة وقوة 165 واط، لشحن 2 لابتوب، بطارية شحن سريع مع كابلات مدمجة وقابلة للطي، متوافق مع آيفون من سلسلة 16/15 وسامسونج وغيرها</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>298.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>159.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>79.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>198.82 ر.س</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>138.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>3299.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>تابلت ميت باد 12 X 2025 شاشة بيبر بدقة 2.8K مقاس 12 بوصة 12+256 جيجابايت بطارية 10100 ميلي امبير شحن فائق 66 واط WPS مع اوفيس ولوحة مفاتيح داخل الصندوق من هواوي كير، لون أخضر</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>2386.55 ر.س</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>اونر تابلت باد في 9 (11.5 انش، واي فاي) 2024 سعة تخزين 256 جيجا، ذاكرة رام 8 جيجا، اندرويد 15 (رمادي)</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>1999.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد 12 × 2025 شاشة بيبر ميت 2.8K 12 بوصة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس ولوحة مفاتيح مرفقة (استخدام اللغة العربية غير مؤكد)، هواوي كير لمدة عام، (أبيض)</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>1999.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>هواوي تابلت ميت باد 11.5 اس 2026 2.8K 144Hz فائق الوضوح، 12+256GB، شحن فائق 40 واط، واي فاي 6+، بلوتوث 5.2، جو بينت، كيبورد قابل للفصل، رمادي + ضمان ممتد لمدة عام</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>1779.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت باد 7، 11.2 انش، 8+128 جيجا، رمادي، بطارية 8850mAh، شحن تيربو 45 واط، هايبر ايه اي (الشاحن غير متضمن)</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>1070.06 ر.س</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>1454.16 ر.س</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>تابلت ريدمي باد 2 بذاكرة رام 4 جيجابايت وذاكرة روم 128 جيجابايت، لافندر أرجواني</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>740.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>تابلت شاومي ريدمي باد 2، 11 انش، 6 جيجا، 128 جيجا، واي فاي، هايبر او اس، اخضر مينت</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>991.44 ر.س</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B137" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت باد ميني 8+256GB، معالج ديمنستي 9400+، شاشة فائقة النعومة 8.8 انش 165Hz، بطارية بسعة كبيرة 7500mAh، واي فاي، ارجواني</t>
-        </is>
-      </c>
-      <c r="C137" s="6" t="inlineStr">
-        <is>
-          <t>2304.82 ر.س</t>
-        </is>
-      </c>
-      <c r="D137" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>3599.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B139" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت ريدمي باد 2 8 جيجابايت + 256 جيجابايت - رمادي - شاشة LCD 11 بوصة - 90 هرتز - بطارية 9000 مللي أمبير في الساعة - شاحن متضمن</t>
-        </is>
-      </c>
-      <c r="C139" s="6" t="inlineStr">
-        <is>
-          <t>1060.36 ر.س</t>
-        </is>
-      </c>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>تشو وي تابلت هاي 10 ماكس 33 سم 2880 × 1920 IPS، معالج انتل N150 (4C/4T، حتى 3.6Ghz)، 12GB DDR5، 512GB SSD، ويندوز 11 باد 3 في 1، واي فاي 6، كيبورد عربي</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>2147.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد 10.4 انش بذاكرة روم 128GB وذاكرة RAM 4GB وواي فاي فقط (رمادي) - اصدار عالمي</t>
-        </is>
-      </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>599.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت ريدمي باد 2 مي، 4GB + 128GB، ازرق سيان، ميديا تيك هيليو G100-الترا، شاشة 11 انش 2.5K 90Hz، بطارية 9000mAh، مع شاحن</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>953.13 ر.س</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-18</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-19</t>
         </is>
       </c>
     </row>
@@ -585,21 +585,21 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>al3bor-telecom</t>
+          <t>al3bor-telecom, amazon_sa</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>40.19 ر.س</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>236.25 ر.س</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -644,70 +644,70 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>38.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>38.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>11.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>44.09 ر.س</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>80.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>115.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -749,70 +749,70 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa, iblackstores, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>aletawiksa, iblackstores</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>307.33 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>193.99 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>aletawiksa, amazon_sa</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>69.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>109.5 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>24.99 ر.س</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>61.24 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>جودا - بطاريات AAA القابلة للشحن</t>
+          <t>جودا - شاحن سمارت للبطاريات الذكيه AA\AAA</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>58.99 ر.س</t>
+          <t>95.99 ر.س</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>جودا - منصة جودا بيك 4 منافذ تايب سي بقوة 240 واط - اسود</t>
+          <t>جودا - بطاريات AAA القابلة للشحن</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>298.99 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>جودا - منصة جودا بيك 4 منافذ تايب سي بقوة 240 واط - اسود</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>58.99 ر.س</t>
+          <t>298.97 ر.س</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1687,17 +1687,17 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -1819,17 +1819,17 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1841,22 +1841,22 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>جوال سامسونج جالكسي A16، ذكي يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجابايت، تخزين 128 جيجابايت، أسود (إصدار المملكة العربية السعودية)</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>580.0 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>جوال ذكي جالكسي A16، يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجا، ذاكرة تخزين 128 جيجا من سامسونج، رمادي (إصدار المملكة العربية السعودية)</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>582.99 ر.س</t>
+          <t>324.99 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>جوال اكسبلور 1 للاستخدام الخارجي، جوال ذكي بشبكة الجيل الخامس 5G مقاوم للماء بنظام أندرويد 15، شاشة 6.78 بوصة بدقة 2.4 كيه، 12 جيجابايت+256 جيجابايت، بطارية 20000 ميلي أمبير/الساعة</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>1790.0 ر.س</t>
+          <t>371.75 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>جوال جالكسي ذكي A07 LTE بنظام أندرويد وذاكرة تخزين 64GB وذاكرة رام 4GB و6x تحديثات نظام التشغيل مع شاشة كبيرة ومعالج 6nm من سامسونج، أخضر (إصدار المملكة العربية السعودية)</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>449.99 ر.س</t>
+          <t>76.26 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>زد تي اي جوال A35e ثنائي شرائح الاتصال بذاكرة رام 2+4 جيجابايت وذاكرة داخلية 64 جيجابايت ويدعم تقنية 4G من بليد - اصدار الشرق الاوسط</t>
+          <t>سبيري حذاء رياضي هاربون كراش باك سهل الارتداء للرجال</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>309.0 ر.س</t>
+          <t>372.86 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>جوال سامسونج جالكسي A17 ال تي اي، ثنائي شرائح اتصال، سعة 128 جيجا توسع حتى 2 تيرا، اندرويد 14 وذاكرة رام 4 جيجابايت، معالج اكسينوس وشاشة اموليد 6.7 بوصة بدقة 1080x2220، معدل تحديث 90 هرتز، لون أسود</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>627.0 ر.س</t>
+          <t>308.28 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>جوال A7 برو بذاكرة رام 4 جيجا وذاكرة روم 128 جيجا، لون أسود من ريدمي</t>
+          <t>فستان كاجوال للنساء من هاربا، عبوة من قطعة واحدة، GR6356</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>489.98 ر.س</t>
+          <t>65.14 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>جوال هونر X5c، أزرق (تايدل بلو)</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>449.0 ر.س</t>
+          <t>328.33 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>جوال تانك 1 متين 6.75 انش 120Hz FHD+ من شاندويليك، هاتف اتصال خارجي 12GB+256GB 20000mAh، هاتف ذكي 5G اندرويد 15 ان اف سي</t>
+          <t>زي بويلر التنكري للرجال على شكل افارهول بتصميم مستوحى من زي السجين الهارب بلون برتقالي من سميفيز - مقاس S، البوليستر</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>2090.0 ر.س</t>
+          <t>146.91 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>جوال سامسونج جالاكسي A57 الجيل الخامس 5G نظام أندرويد بسعة تخزين 256 جيجابايت ورام 8 جيجابايت بـ6 ترقيات لنظام التشغيلو شاشة كبيرة وكاميرا 50 ميجابكسل وعمر بطارية طويل، لون أزرق بحري (إصدار السعودية)</t>
+          <t>فستان مطبوع عليه زهور وقبة مربعة وأكمام منفوخة بقصة ايه لاين للنساء من هاربا</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>1474.85 ر.س</t>
+          <t>64.81 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>جوال هونر ذكي X7e بطارية سيليكون كربون وشريحتين وشحن فائق 45 واط وشاشة 120Hz وكاميرا 50MP مدعومة بالذكاء الاصطناعي، بتصنيف IP64 لمقاومة المياه والغبار، ذاكرة رام 6GB وذاكرة تخزين 128GB، لون أزرق فاتح</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>645.0 ر.س</t>
+          <t>285.81 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>جوال ريدمي نوت 15 شبكة الجيل الخامس 5G ثنائي شرائح الاتصال بذاكرة رام 8 جيجابايت وذاكرة داخلية 256 جيجابايت - النسخة العالمية</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>979.0 ر.س</t>
+          <t>270.5 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>جوال ايفون 12 ميني من ابل (64 جيجابايت) - لون أزرق (مجدد)</t>
+          <t>دار الأداب الهاربون والباقون</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>650.0 ر.س</t>
+          <t>98.0 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>جهاز عرض XP 2 من شاندوليك، هاتف ذكي 5G بالذكاء الاصطناعي، شاشة AMOLED 6.75 انش 3.2 كيه، كاميرا 50MP، 16GB + 1TB، 20000mAh، جوال خارجي متين</t>
+          <t>بيلا فيتا جزمة هارب للنساء</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>3690.0 ر.س</t>
+          <t>251.61 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>جوال متين تانك 1 من ال ام اتش تريد 6.78 انش 120Hz FHD + شاشة اتصال خارجية 16GB + 512GB 20000mAh، هاتف ذكي 5G اندرويد 15 ان اف سي</t>
+          <t>روبوتايم 3 دي بازل هارب</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>2690.0 ر.س</t>
+          <t>202.8 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>خلطة فيز 160 جم من هاريبو</t>
+          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>9.75 ر.س</t>
+          <t>40.19 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>17.95 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>8.99 ر.س</t>
+          <t>18.04 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>9.75 ر.س</t>
+          <t>11.79 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>15.23 ر.س</t>
+          <t>13.14 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
+          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>13.5 ر.س</t>
+          <t>106.08 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>7.5 ر.س</t>
+          <t>11.0 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلاتينية هاريبو جولد بيرز، 350 جم، عبوة من 5 قطع</t>
+          <t>يعمل الجهاز بضغط يصل إلى 26.1 PSI (حوالي 1.8 بار) وبقدرة كهربائية تبلغ 100 وات، مما يوفر أداءً فعالًا وقوة تشغيل مناسبة، مضخة مياه موفرة للطاقة 24 فولت مع محول 1/2 بوصة للاستحمام المنزلي وإمدادات</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>9.75 ر.س</t>
+          <t>180.0 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
+          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>13.5 ر.س</t>
+          <t>29.0 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>بسكويت فيز هابي كولا من هاريبو 160 جم</t>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>8.99 ر.س</t>
+          <t>32.9 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>13.5 ر.س</t>
+          <t>11.25 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 80 جم</t>
+          <t>مضخة مياه كهربائية بشحن USB، مضخة مياه شرب محمولة متوافقة مع الزجاجات القياسية سعة 11 إلى 19 لتر، مناسبة للاستخدام في المنزل والمكتب وأساسية للتخييم من سكاي-تاتش</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>7.95 ر.س</t>
+          <t>25.9 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
+          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>9.95 ر.س</t>
+          <t>39.99 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>توت هاريبو 150 جرام</t>
+          <t>مضخة هواء محمولة من الصلب للدراجة الهوائية، متوافقة مع صمام بريستا وشرادر، مضخة إطارات الدراجة الصغيرة المدمجة، لون أزرق</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>9.5 ر.س</t>
+          <t>45.99 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 200 جم</t>
+          <t>استرو ايه اي منفاخ اطارات لاسلكي محمول 150 باوند لكل انش مربع</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>15.22 ر.س</t>
+          <t>119.99 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>مضخة موزع مياه كهربائية، مضخة زجاجة مياه شرب أوتوماتيكية قابلة لاعادة الشحن بمنفذ USB لزجاجة عالمية سعة من 11.4 إلى 18.9 لتر، موزع للمكتب والمنزل والتخييم والمطبخ وما الى ذلك من مومنت</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>22.0 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>38.49 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>93.43 ر.س</t>
+          <t>88.74 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>45.85 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>186.25 ر.س</t>
+          <t>88.99 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+          <t>جوي رووم شاحن سيارة صغير JR-CCN05 30 واط USB-A USB-C يوفر شحن سريع وآمن، يشحن جهازين في وقت واحد - اسود</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>130.0 ر.س</t>
+          <t>24.99 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>شاحن 17 فولت 1 امبير لمكبر الصوت اللاسلكي بوز ساوند لينك I II III 1 2 3</t>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>66.18 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لجيه بي ال لينك 10، 3.7 فولت/3600 مللي امبير في الساعة من زوفكوس</t>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>104.92 ر.س</t>
+          <t>89.99 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>59.89 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>شاحن 9 فولت متوافق مع كاميرا المراقبة تي بي لينك تابو C110 C200 C210</t>
+          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>97.55 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>شاحن مكبر صوت بلوتوث 12 فولت متوافق مع مكبر الصوت بوز ساوند لينك ميني اي اللاسلكي المحمول، سلك امدادات الطاقة (متوافق فقط مع بوز ساوند لينك ميني 1)</t>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>106.78 ر.س</t>
+          <t>39.18 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE4824G - حاقن PoE</t>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>39.9 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>96.17 ر.س</t>
+          <t>46.99 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>محول طاقة ستيب اب بتيار مستمر 12 فولت/24 فولت الى 30 فولت لستارلينك ميني، محول معزز للادخال 9 فولت - 28 فولت مع فيوز لراوتر ستار لينك ميني ار في والشاحنة والسيارات البحرية والسفر</t>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>117.19 ر.س</t>
+          <t>75.88 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك مع 3 منافذ بي دي 20 واط 10000 مللي أمبير في الساعة من راف باور، شحن سريع PD/QC، شحن 3 أجهزة في وقت واحد، توافق عالمي لايفون 15/16 والمزيد، USB نوع C مزدوج + USB-A، تقنية اي سمارت</t>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 16 و15 وسامسونج S25 وS24 بـ3 منافذ بقدرة 145 واط مع شحن سريع وكابل قابل للسحب وحماية متعددة</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>80.0 ر.س</t>
+          <t>149.65 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,609 +2836,15 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>258.62 ر.س</t>
+          <t>29.0 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>159.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>159.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>150.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>139.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>118.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>109.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>94.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يوجرين 10000 مللي امبير بمنفذ USB تايب-C مع شحن لاسلكي و سريع و مغناطيسي للهاتف الذكي بمنفذين رمادي</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>118.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>79.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>82.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك في 9، شاحن محمول صغير 22.5 واط USB C 10000 مللي امبير في الساعة، حزمة بطارية شحن سريع بي دي، 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد رمادي</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>79.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>جهاز اختبار بطارية السيارة 12 فولت 24 فولت، واختبار تحميل البطارية وعرض تيار بدء التشغيل على البارد رقميا محلل تلقائي دقيق اداة تشخيص البطارية مناسب للشاحنات والدراجات النارية من اياكام (من 8 إلى 30</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>75.34 ر.س</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>محول جهد كهربائي 3000 واط 110 فولت/120 فولت/220 فولت/240 فولت من اليسم، محول طاقة تصاعدي / لأسفل مع حماية من قاطع الدائرة الكهربائية قابل لاعادة الضبط، مقبس عالمي مدمج للمنزل</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>499.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>جهاز اختبار بطارية السيارة طراز BT600 قدرة 12 فولت 24 فولت مع طابعة، قياس التيار عند التشغيل البارد 100 إلى 2000 من توبدون، شاشة ملونة 3.5 بوصة، كيبل 1.8 م، متوفر تحديث البرامج</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>686.29 ر.س</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه باردة ومضخة تفريغ الهواء مصغرة اي كيه 1856 بتيار مستمر وبجهد 6 فولت الى 12 فولت ار385 من جيكفن</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>38.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>جهاز إمداد الطاقة من كولر ماستر إم دبليو إي برونز 750 V3 بقدرة 750 واط 230 فولت ATX 3.1 80 بلس برونز مروحة HDB 120 ملم، أسود</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>239.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>وحدة تزويد طاقة تفاعلية 1000 فولت امبير من ارترونيك ارت، مزود طاقة غير منقطع 1000 فولت أمبير/600 واط، تنظيم جهد ايه في ار، موجة جيبية محاكاة، وظيفة التشغيل البارد، متوافق مع المولد</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>445.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 220 فولت إلى تيار مستمر 12 فولت، محول بتيار 10 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>42.79 ر.س</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>جهاز اختبار رقمي اوتوماتيكي KW208 للبطارية بقوة 12 فولت / 100 -2000 امبير في درجات الحرارة الباردة للسيارة لاختبار المولد ونظام التشغيل والشحن مناسب للقوارب والدراجات البخارية والدفع الرباعي من كونوي</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>105.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>محول جهد كهربائي 220 فولت إلى 110 فولت، محول طاقة للسفر 200 واط، محول خافض للجهد الكهربائي 220 فولت إلى 110 فولت لمكواة فرد الشعر وأجهزة التلفزيون واللابتوب من مابروتي</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>57.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>محول جهد كهربائي 2000 واط، 3000 واط، 110/120 فولت الى 220/240 فولت، حماية قاطع الدائرة، للاستخدام المنزلي (2000 واط)</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>400.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>جهاز اختبار بطارية السيارة الرقمية وأداة تشخيص المولد من انسيل، سعة تحميل 100-2000 CCA، تحليل الشحن والتحريك للدراجة النارية والشاحنة والقارب والمركبة الترفيهية والبحرية وغيرها، 12 فولت، BA101</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>221.66 ر.س</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>محول جهد كهربائي 300W، 110V و120V و220V و240V، محول طاقة تصاعدي وتنازلي مع حماية من قاطع الدائرة الكهربائية قابلة لإعادة الضبط ومقبس عالمي مدمج للمنزل</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>159.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 500 فولت إلى تيار مستمر 12 فولت، محول بتيار 42 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>96.09 ر.س</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>موزع مياه ساخن وبارد تحميل سفلي قائم على الارض 220-240 فولت مع ثلاجة من هوميكس - ابيض YLR-LW-2-5-100 باوند</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>396.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>جهاز اختبار بطارية السيارة من ايكام، مقياس جهد رقمي للبطارية 12 فولت ومحلل نظام الشحن مع شاشة ال سي دي للدراجات النارية والسكوتر الكهربائي والقارب وسيارات الدفع الرباعي</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>18.04 ر.س</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-19</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -585,21 +585,21 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>al3bor-telecom, amazon_sa</t>
+          <t>al3bor-telecom</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>40.19 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>236.25 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -644,35 +644,35 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>11.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>44.09 ر.س</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -749,35 +749,35 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>aletawiksa, iblackstores</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>193.99 ر.س</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>aletawiksa, amazon_sa</t>
+          <t>aletawiksa</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>24.99 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>61.24 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1860,996 +1860,6 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>324.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>371.75 ر.س</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>76.26 ر.س</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>سبيري حذاء رياضي هاربون كراش باك سهل الارتداء للرجال</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>372.86 ر.س</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>308.28 ر.س</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>فستان كاجوال للنساء من هاربا، عبوة من قطعة واحدة، GR6356</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>65.14 ر.س</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>328.33 ر.س</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>زي بويلر التنكري للرجال على شكل افارهول بتصميم مستوحى من زي السجين الهارب بلون برتقالي من سميفيز - مقاس S، البوليستر</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>146.91 ر.س</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>فستان مطبوع عليه زهور وقبة مربعة وأكمام منفوخة بقصة ايه لاين للنساء من هاربا</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>64.81 ر.س</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>285.81 ر.س</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>270.5 ر.س</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>دار الأداب الهاربون والباقون</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>98.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>بيلا فيتا جزمة هارب للنساء</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>251.61 ر.س</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>روبوتايم 3 دي بازل هارب</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>202.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>40.19 ر.س</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>20.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>18.04 ر.س</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>11.79 ر.س</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>13.14 ر.س</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>106.08 ر.س</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>11.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>يعمل الجهاز بضغط يصل إلى 26.1 PSI (حوالي 1.8 بار) وبقدرة كهربائية تبلغ 100 وات، مما يوفر أداءً فعالًا وقوة تشغيل مناسبة، مضخة مياه موفرة للطاقة 24 فولت مع محول 1/2 بوصة للاستحمام المنزلي وإمدادات</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>180.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>29.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>32.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>11.25 ر.س</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه كهربائية بشحن USB، مضخة مياه شرب محمولة متوافقة مع الزجاجات القياسية سعة 11 إلى 19 لتر، مناسبة للاستخدام في المنزل والمكتب وأساسية للتخييم من سكاي-تاتش</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>25.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>39.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>مضخة هواء محمولة من الصلب للدراجة الهوائية، متوافقة مع صمام بريستا وشرادر، مضخة إطارات الدراجة الصغيرة المدمجة، لون أزرق</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>45.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>استرو ايه اي منفاخ اطارات لاسلكي محمول 150 باوند لكل انش مربع</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>119.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>مضخة موزع مياه كهربائية، مضخة زجاجة مياه شرب أوتوماتيكية قابلة لاعادة الشحن بمنفذ USB لزجاجة عالمية سعة من 11.4 إلى 18.9 لتر، موزع للمكتب والمنزل والتخييم والمطبخ وما الى ذلك من مومنت</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>22.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>38.49 ر.س</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>88.74 ر.س</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>45.85 ر.س</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>88.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>جوي رووم شاحن سيارة صغير JR-CCN05 30 واط USB-A USB-C يوفر شحن سريع وآمن، يشحن جهازين في وقت واحد - اسود</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>24.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>59.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>89.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>59.89 ر.س</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>39.18 ر.س</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>39.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>46.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>75.88 ر.س</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 16 و15 وسامسونج S25 وS24 بـ3 منافذ بقدرة 145 واط مع شحن سريع وكابل قابل للسحب وحماية متعددة</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>149.65 ر.س</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>29.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-20</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-21</t>
         </is>
       </c>
     </row>
@@ -644,70 +644,70 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>10.18 ر.س</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>46.37 ر.س</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>80.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>115.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -784,35 +784,35 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>69.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>69.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, iblackstores, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>20.78 ر.س</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>70.08 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>جودا - شاحن سيارة بقوة 60 واط بمنفذين تايب سي - اسود</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>68.99 ر.س</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1709,17 +1709,17 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -1841,22 +1841,2310 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
+          <t>wjhtektelecome</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>149.01 ر.س</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>بحث تقديري</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
           <t>alwan7</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>50.0 ر.س</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>139.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>94.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>99.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>61.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>109.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>118.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>171.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>134.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>198.81 ر.س</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>138.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يوجرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب A مع شحن سريع وحماية للهاتف واللابتوب 3 منافذ</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>178.86 ر.س</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>138.87 ر.س</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>178.94 ر.س</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>بطارية خارجية سعة 20000 ميلي امبير في الساعة مع كابل مدمج من كوكتيك - لون أسود</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>122.55 ر.س</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>82.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>14.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>9.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>خلطة فيز 160 جم من هاريبو</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>11.55 ر.س</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>6.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>12.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>12.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>حلوى بيريز من هاريبو، 160 جم</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>11.55 ر.س</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>6.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>14.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>6.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>12.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جيلاتينية هاريبو جولد بيرز، 350 جم، عبوة من 5 قطع</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>9.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>حلوى شامالو روبينو مارشميلو من هاريبو، 70 جم</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>6.5 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>12.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>10.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>40.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>نقطة وصول لاسلكية EAP650 اومادا واي فاي 6 AX3000 من تي بي لينك، تدعم شبكة</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>390.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>راوتر من تي بي-لينك أبيض لكاميرات IP والأجهزة الذكية، بنطاق مفرد وتقنية Wi-Fi، بسرعة 867 ميغابت في الثانية، مع نقل طويل المدى و MU-MIMO، طراز EAP211</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>438.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك راوتر واي فاي خارجي 4G 300 ميجابت لكل ثانية من TL-MR100</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>218.52 ر.س</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك موزع USB 3.0 مايكرو بي 7 منافذ مع محول طاقة 12 فولت/2.5 امبير وكابل USB 3.0 بطول 1 متر، شحن سريع 1.5 امبير، سرعة نقل بيانات 10 مرات، متوافق مع ويندوز وماك او اس اكس ولينكس (UH700)، اسود</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>136.69 ر.س</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE4824G - حاقن PoE</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك راوتر خارجي MR402 خارجي 4G LTE من ارتشر، واي فاي AC1200Mbps ثنائي النطاق، مقاوم للماء IP65، دعم POE/DC، كات 4 حتى 150 ميجابت في الثانية، تقنية ون ميش، تركيب عمود/حائط، توصيل وتشغيل</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>265.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك نقطة وصول لاسلكية تثبت بالسقف بسرعة 300 ميجابت في الثانية EAP115</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>125.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>شاحن 9 فولت متوافق مع كاميرا المراقبة تي بي لينك تابو C110 C200 C210</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>97.1 ر.س</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>شاحن 17 فولت 1 امبير لمكبر الصوت اللاسلكي بوز ساوند لينك I II III 1 2 3</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>66.18 ر.س</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>مضخة توزيع العطور من تول هاوس 12 قطعة، اداة نقل مضخة اعادة تعبئة السوائل، زجاجة بخاخ عطر قابلة لاعادة الملء للسفر، لللوشن وزيت الصابون</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>11.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>11.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>17.72 ر.س</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>17.76 ر.س</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>10.18 ر.س</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>11.78 ر.س</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>يعمل الجهاز بضغط يصل إلى 26.1 PSI (حوالي 1.8 بار) وبقدرة كهربائية تبلغ 100 وات، مما يوفر أداءً فعالًا وقوة تشغيل مناسبة، مضخة مياه موفرة للطاقة 24 فولت مع محول 1/2 بوصة للاستحمام المنزلي وإمدادات</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>180.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>146.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>11.24 ر.س</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>32.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه، موزع مياه قابل لإعادة الشحن مع شاحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 ل للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر من لوازم، 12.8 سم × 69 ملم</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>12.59 ر.س</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>مضخة توزيع المياه الاوتوماتيكية، مضخة مياه كهربائية قابلة للطي وقابلة لاعادة الشحن بمنفذ USB للاستخدام في المنزل او المكتب او المطبخ المنزلي</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>22.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه كهربائية بشحن USB، مضخة مياه شرب محمولة متوافقة مع الزجاجات القياسية سعة 11 إلى 19 لتر، مناسبة للاستخدام في المنزل والمكتب وأساسية للتخييم من سكاي-تاتش</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>21.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه شرب وموزع يدوي محمول تشغيل بالضغط اليدوي لزجاجات المياه خالية من البيسفينول ايه للسفر من لوازم، أزرق</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>10.18 ر.س</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>مضخة تعزيز ضغط المياه، مضخة اوتوماتيك بجهد 24 فولت لتعزيز ضغط دش الاستحمام، مضخة مياه منزلية قابلة للحمل بقوة 150 واط بمفتاح تدفق للحمام والمطبخ والمرحاض والحديقة من بيرفورلد</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>119.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك مع 3 منافذ بي دي 20 واط 10000 مللي أمبير في الساعة من راف باور، شحن سريع PD/QC، شحن 3 أجهزة في وقت واحد، توافق عالمي لايفون 15/16 والمزيد، USB نوع C مزدوج + USB-A، تقنية اي سمارت</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>80.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>263.11 ر.س</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>159.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>159.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>139.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>94.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>109.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>118.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>82.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>79.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك في 9، شاحن محمول صغير 22.5 واط USB C 10000 مللي امبير في الساعة، حزمة بطارية شحن سريع بي دي، 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد رمادي</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يوجرين 10000 مللي امبير بمنفذ USB تايب-C مع شحن لاسلكي و سريع و مغناطيسي للهاتف الذكي بمنفذين رمادي</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>118.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>1192.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>اونر تابلت باد في 9 (11.5 انش، واي فاي) 2024 سعة تخزين 256 جيجا، ذاكرة رام 8 جيجا، اندرويد 15 (رمادي)</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>1699.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ميت باد 12 X 2025 شاشة بيبر بدقة 2.8K مقاس 12 بوصة 12+256 جيجابايت بطارية 10100 ميلي امبير شحن فائق 66 واط WPS مع اوفيس ولوحة مفاتيح داخل الصندوق من هواوي كير، لون أخضر</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>1998.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد 11.5 اس 2026 2.8K 144Hz فائق الوضوح، 12+256GB، شحن فائق 40 واط، واي فاي 6+، بلوتوث 5.2، جو بينت، كيبورد قابل للفصل، رمادي + ضمان ممتد لمدة عام</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>1779.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>3299.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ميت باد 11.5 S بشاشة بيبر مات فائقة الوضوح وذاكرة 12 جيجابايت + 256 جيجابايت وبطارية 8800 ميلي امبير في الساعة وشحن فائق السرعة بقوة 40 واط مع لوحة مفاتيح قابلة للفصل من هواوي، رمادي</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>1773.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>1454.16 ر.س</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت باد 7، 11.2 انش، 8+128 جيجا، رمادي، بطارية 8850mAh، شحن تيربو 45 واط، هايبر ايه اي (الشاحن غير متضمن)</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>1070.1 ر.س</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد 12 × 2025 شاشة بيبر ميت 2.8K 12 بوصة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس ولوحة مفاتيح مرفقة (استخدام اللغة العربية غير مؤكد)، هواوي كير لمدة عام، (أبيض)</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>1999.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد 10.4 انش بذاكرة روم 128GB وذاكرة RAM 4GB وواي فاي فقط (رمادي) - اصدار عالمي</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>599.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>اونر تابلت باد X8a، واي فاي 11 انش، تخزين 64GB، بطارية 8300mAh، مكبر صوت رباعي، تصميم معدني رفيع، اندرويد 14، رمادي سبيس جديد</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>1153.01 ر.س</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>تابلت شاومي ريدمي باد 2، 11 انش، 6 جيجا، 128 جيجا، واي فاي، هايبر او اس، اخضر مينت</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>991.44 ر.س</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت باد ميني 8+256GB، معالج ديمنستي 9400+، شاشة فائقة النعومة 8.8 انش 165Hz، بطارية بسعة كبيرة 7500mAh، واي فاي، ارجواني</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>2304.82 ر.س</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>لينوفو نوت بوك ثينك باد T16 الجيل الرابع 22AW0065US بشاشة لمس 16 انش كوبيلوت + كمبيوتر نوت بوك - WUXGA - انتل كور الترا 5 سلسلة 2 236 فولت - 16 جيجا - 256 جيجا اس اس دي - كيبورد انجليزي - اسود</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>6334.79 ر.س</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>88.74 ر.س</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>45.85 ر.س</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>38.39 ر.س</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>88.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>35.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>20.78 ر.س</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>59.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>39.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>75.88 ر.س</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>39.18 ر.س</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>45.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 16 و15 وسامسونج S25 وS24 بـ3 منافذ بقدرة 145 واط مع شحن سريع وكابل قابل للسحب وحماية متعددة</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>149.65 ر.س</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-22</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -644,35 +644,35 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>10.18 ر.س</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>45.84 ر.س</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -714,35 +714,35 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>شاحن جودا فولت باد / VoltPad</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>شواحن جدارية</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>97.09 ر.س</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>97.09 ر.س</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -760,59 +760,59 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, iblackstores, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>484.1 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>شاحن سيارة جودا</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>شواحن سيارة</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa, iblackstores</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>194.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>شاحن سيارة جودا</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>شواحن سيارة</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>69.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>69.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>20.78 ر.س</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>61.53 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1838,6 +1838,1942 @@
         </is>
       </c>
     </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>9.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>12.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>14.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>خلطة فيز 160 جم من هاريبو</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>11.55 ر.س</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>6.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>12.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>حلوى بيريز من هاريبو، 160 جم</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>11.55 ر.س</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>14.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>12.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>12.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جيلاتينية هاريبو جولد بيرز، 350 جم، عبوة من 5 قطع</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>9.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>9.5 ر.س</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>6.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>حلوى بنكهة الكولا من هاريبو، وزن 250 جم</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>12.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>بسكويت فيز هابي كولا من هاريبو 160 جم</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>8.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>40.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>93.43 ر.س</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>186.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>130.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>شاحن 17 فولت 1 امبير لمكبر الصوت اللاسلكي بوز ساوند لينك I II III 1 2 3</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>66.18 ر.س</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك موزع USB 3.0 مايكرو بي 7 منافذ مع محول طاقة 12 فولت/2.5 امبير وكابل USB 3.0 بطول 1 متر، شحن سريع 1.5 امبير، سرعة نقل بيانات 10 مرات، متوافق مع ويندوز وماك او اس اكس ولينكس (UH700)، اسود</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>136.67 ر.س</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>106.18 ر.س</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>محول مقسم نشط POE من قطعتين، 48 فولت الى 12 فولت، متوافق مع IEEE 802.3af 10/100Mbps حتى 100 متر لكاميرا IP ونقطة الوصول اللاسلكية والهاتف عبر بروتوكول الإنترنت</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>45.2 ر.س</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>شاحن 9 فولت متوافق مع كاميرا المراقبة تي بي لينك تابو C110 C200 C210</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>97.09 ر.س</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>محول طاقة ستيب اب بتيار مستمر 12 فولت/24 فولت الى 30 فولت لستارلينك ميني، محول معزز للادخال 9 فولت - 28 فولت مع فيوز لراوتر ستار لينك ميني ار في والشاحنة والسيارات البحرية والسفر</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>117.19 ر.س</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>94.61 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>17.72 ر.س</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>17.15 ر.س</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>10.18 ر.س</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>11.78 ر.س</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>11.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>يعمل الجهاز بضغط يصل إلى 26.1 PSI (حوالي 1.8 بار) وبقدرة كهربائية تبلغ 100 وات، مما يوفر أداءً فعالًا وقوة تشغيل مناسبة، مضخة مياه موفرة للطاقة 24 فولت مع محول 1/2 بوصة للاستحمام المنزلي وإمدادات</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>180.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>146.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>22.23 ر.س</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>27.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>11.24 ر.س</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>استرو ايه اي منفاخ اطارات لاسلكي محمول 150 باوند لكل انش مربع</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>99.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>ضاغط هواء كهربائي محمول بعمر بطارية طويل مطور لعام 2024، منفاخ رقمي للكشف عن ضغط الإطارات مع ضوء LED (بحد أقصى 10 بار) بإيقاف تلقائي للسيارة والدراجة والكرة وغيرها من يوجرين</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>168.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>منفاخ هواء من يوماي أوتوماتيكي مع مضخة هواء بالون مصدر طاقة خارجي</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>38.17 ر.س</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>منفاخ هواء من جودتول يدوي مع إبرة الكرة و محول الفوهة و خرطوم تمديد و مضخة يدوية يدوي</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>10.72 ر.س</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>34.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ميت باد 11.5 S بشاشة بيبر مات فائقة الوضوح وذاكرة 12 جيجابايت + 256 جيجابايت وبطارية 8800 ميلي امبير في الساعة وشحن فائق السرعة بقوة 40 واط مع لوحة مفاتيح قابلة للفصل من هواوي، رمادي</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>1799.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>1243.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB C 12 فولت - 24 فولت، محول طاقة للابتوب 90 واط 65 واط متوافق مع لينوفو ثينك باد اتش بي ديل ايسر اسوس كروم بوك سامسونج ماك بوك برو/اير والمزيد من الاجهزة من النوع سي</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>101.91 ر.س</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد 12 × 2025 شاشة بيبر ميت 2.8K 12 بوصة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس ولوحة مفاتيح مرفقة (استخدام اللغة العربية غير مؤكد)، هواوي كير لمدة عام، (أبيض)</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>1999.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>3299.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>1454.16 ر.س</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد 11.5 بيبر مات اصدار واي فاي، شاشة فل فيو هواوي 120HZ مهدئة للعين، تصميم انيق للجسم الذهني، ذاكرة رام 8GB وذاكرة تخزين داخلية 256GB، رمادي سبيس</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>1449.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>تابلت شاومي ريدمي باد 2، 11 انش، 6 جيجا، 128 جيجا، واي فاي، هايبر او اس، اخضر مينت</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>978.04 ر.س</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>3599.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت باد 8 8GB/128GB، واي فاي 7، 11.2 انش 3.2 كيه، صوت دولبي اتموس، معالج سناب دراجون 870، بطارية 9200mAh (الشاحن غير متضمن)، رمادي</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>1732.26 ر.س</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت ريدمي باد 2 مي، 4GB + 128GB، ازرق سيان، ميديا تيك هيليو G100-الترا، شاشة 11 انش 2.5K 90Hz، بطارية 9000mAh، مع شاحن</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>953.13 ر.س</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>كيوكورا مرحل الملف اللولبي 12 فولت بادئ كهرومغناطيسي متين لاستبدال محرك اليخت البحري، اسود، وحدة واحدة</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>97.09 ر.س</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ون بلس باد 3، سناب دراجون 8 ايليت، معدل تحديث 144 هرتز، واي فاي (ستورم بلو، 12 جيجابايت + 256 جيجابايت)</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>3499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>399.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>599.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب منحنية 24 بوصة 240 هرتز FHD 1080p 1500R 1 مللي ثانية ومزامنة تكيفية وتباين 3000:1 ودعم HDR وHDMI 2.0 ومنفذ طاقة 1.4 بضوء أزرق منخفض وإمالة فيسا H24S17P من كيه تي سي</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>411.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب UG27PJ ليد 27 بوصة ومعدل تحديث 240Hz، لوحة IPS، استجابة 1 مل ثانية، دقة FHD (1920×1080)، سطوع 400 شمعة/م² من زد ايدج، حواف نحيفة، دعم فريسينك، منفذ(HDMI×2 وDP×2)، تثبت على الحائط، تدعم فيسا</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>519.19 ر.س</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>449.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>422.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>617.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>789.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>479.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>مبرد وحدة المعالجة المركزية السائل 240 RS ARGB نوتيلوس - 240 ملم AIO، منخفض الضوضاء، اتصال مباشر باللوحة الأم وتوصيل سلس - انتل LGA 1851/1700، AMD AM5/AM4 - 2 × مراوح RS120 ARGB متضمنة من كورسير، أسود</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>403.52 ر.س</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>مبرد سائل من سلسلة انيرجلو من سودوكو</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>265.24 ر.س</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>مبرد وحدة معالجة مركزية مائي فروزن نوت 240 ابيض ARGB من ثيرمال رايت، مواصفات مبرد وحدة معالجة مركزية 240 ابيض، مراوح PWM مزدوجة محامل S-FDB V2، مناسب لـAMD/AM4 AM5، انتل LGA 1700/1150/1151/1200/2011</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>240.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>مبرد وحدة المعالجة المركزية السائل للألعاب 240 - مراوح ARGB 2×120 ملم، آلية متشابكة منزلقة من جيجابايت، يدعم التوصيل المتسلسل، انتل LGA 1851 وAMD AM5</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>329.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>مروحة بانوراما اس اي 240 ايه ار جي بي وايت متكاملة قابلة للدوران 6.67 بوصة بشاشة اموليد منحنية ثلاثية الأبعاد بتأثير انامورفيك 240 ملم 260 واط TDP، مروحة انتل LGA 1851/1700/1200/115X AMD AM5/AM4</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>1199.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>36.47 ر.س</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>88.74 ر.س</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>45.85 ر.س</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>88.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>59.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>20.78 ر.س</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>35.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>39.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>جوي رووم شاحن سيارة صغير JR-CCN05 30 واط USB-A USB-C يوفر شحن سريع وآمن، يشحن جهازين في وقت واحد - اسود</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>24.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>75.88 ر.س</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>39.17 ر.س</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>45.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-23</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -585,21 +585,21 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>al3bor-telecom</t>
+          <t>al3bor-telecom, amazon_sa</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>35.0 ر.س</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>203.8 ر.س</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -644,175 +644,175 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>بطارية راف باور</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>بطاريات متنقلة</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>10.18 ر.س</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>45.84 ر.س</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>بطارية راف باور</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>بطاريات متنقلة</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>شاحن جودا فولت باد / VoltPad</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>شواحن جدارية</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>شاحن جودا فولت باد / VoltPad</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>شواحن جدارية</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>97.09 ر.س</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>97.09 ر.س</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>كيبل جودا 240 واط</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>كيابل شحن</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>aletawiksa, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>427.93 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>كيبل جودا 240 واط</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>كيابل شحن</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa, iblackstores, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>484.1 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>aletawiksa, amazon_sa</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>20.78 ر.س</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>61.53 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>69.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>106.97 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>جودا - بطاريات AAA القابلة للشحن</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>58.99 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1621,17 +1621,17 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>جودا - منصة جودا بيك 4 منافذ تايب سي بقوة 240 واط - اسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>298.99 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1643,17 +1643,17 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>58.99 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1665,17 +1665,17 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1753,17 +1753,17 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1775,66 +1775,66 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
+          <t>دار الأداب الهاربون والباقون</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>88.2 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
+          <t>روبوتايم 3 دي بازل هارب</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>202.91 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>35.0 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
@@ -1846,12 +1846,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>9.75 ر.س</t>
+          <t>205.0 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>12.95 ر.س</t>
+          <t>69.83 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
+          <t>ساعة منبه ران اواي المتدحرجة (الأصلية) من كلوكي، بصوت عال جدا الثقيل (روبوت غرفة النوم للكبار والأطفال) مضحكة، متدحرجة، هاربة، متحركة، قافزة (أزرق)</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>14.95 ر.س</t>
+          <t>151.2 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>خلطة فيز 160 جم من هاريبو</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>11.55 ر.س</t>
+          <t>275.0 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>6.95 ر.س</t>
+          <t>314.9 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
+          <t>ليجو سلسلة 25 - هاربي</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>12.95 ر.س</t>
+          <t>89.32 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>حلوى بيريز من هاريبو، 160 جم</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>11.55 ر.س</t>
+          <t>280.03 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
+          <t>هارمونيكا هارب هارموك ارمونيكا 24 فتحة فم، مفتاح احترافي سي متعدد الأصوات دياتونيك مع حافظة لموسيقى البوب والجاز الشعبي البلوز</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>14.95 ر.س</t>
+          <t>166.85 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>12.95 ر.س</t>
+          <t>299.0 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>12.95 ر.س</t>
+          <t>251.35 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلاتينية هاريبو جولد بيرز، 350 جم، عبوة من 5 قطع</t>
+          <t>فستان كاجوال للنساء من هاربا، عبوة من قطعة واحدة، GR6356</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>9.75 ر.س</t>
+          <t>65.14 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>9.5 ر.س</t>
+          <t>269.25 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>6.25 ر.س</t>
+          <t>278.06 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>حلوى بنكهة الكولا من هاريبو، وزن 250 جم</t>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>12.95 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>بسكويت فيز هابي كولا من هاريبو 160 جم</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>8.99 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>150.0 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>40.0 ر.س</t>
+          <t>79.96 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
+          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>119.0 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>93.43 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>186.25 ر.س</t>
+          <t>118.98 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>94.97 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>130.0 ر.س</t>
+          <t>82.95 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>شاحن 17 فولت 1 امبير لمكبر الصوت اللاسلكي بوز ساوند لينك I II III 1 2 3</t>
+          <t>باور بانك من يوجرين 10000 مللي امبير بمنفذ USB تايب-C مع شحن لاسلكي و سريع و مغناطيسي للهاتف الذكي بمنفذين رمادي</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>66.18 ر.س</t>
+          <t>118.99 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك موزع USB 3.0 مايكرو بي 7 منافذ مع محول طاقة 12 فولت/2.5 امبير وكابل USB 3.0 بطول 1 متر، شحن سريع 1.5 امبير، سرعة نقل بيانات 10 مرات، متوافق مع ويندوز وماك او اس اكس ولينكس (UH700)، اسود</t>
+          <t>شاحن باور بانك من أنكر فائق السرعة بسعة 25.000 مللي أمبير/الساعة وقوة 165 واط، لشحن 2 لابتوب، بطارية شحن سريع مع كابلات مدمجة وقابلة للطي، متوافق مع آيفون من سلسلة 16/15 وسامسونج وغيرها</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>136.67 ر.س</t>
+          <t>297.0 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
+          <t>تابلت هواوي ميت باد SE بشاشة 11 بوصة، ذاكرة 4+128 جيجابايت، مع قلم ام بن لايت، شاشة فول فيو وبطارية ذات سعة كبيرة مع ركن خاص بالأطفال</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>106.18 ر.س</t>
+          <t>703.0 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>محول مقسم نشط POE من قطعتين، 48 فولت الى 12 فولت، متوافق مع IEEE 802.3af 10/100Mbps حتى 100 متر لكاميرا IP ونقطة الوصول اللاسلكية والهاتف عبر بروتوكول الإنترنت</t>
+          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>45.2 ر.س</t>
+          <t>1243.0 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>شاحن 9 فولت متوافق مع كاميرا المراقبة تي بي لينك تابو C110 C200 C210</t>
+          <t>تابلت ميت باد 11.5 S بشاشة بيبر مات فائقة الوضوح وذاكرة 12 جيجابايت + 256 جيجابايت وبطارية 8800 ميلي امبير في الساعة وشحن فائق السرعة بقوة 40 واط مع لوحة مفاتيح قابلة للفصل من هواوي، رمادي</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>97.09 ر.س</t>
+          <t>1799.0 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>محول طاقة ستيب اب بتيار مستمر 12 فولت/24 فولت الى 30 فولت لستارلينك ميني، محول معزز للادخال 9 فولت - 28 فولت مع فيوز لراوتر ستار لينك ميني ار في والشاحنة والسيارات البحرية والسفر</t>
+          <t>شاحن سيارة USB C 12 فولت - 24 فولت، محول طاقة للابتوب 90 واط 65 واط متوافق مع لينوفو ثينك باد اتش بي ديل ايسر اسوس كروم بوك سامسونج ماك بوك برو/اير والمزيد من الاجهزة من النوع سي</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>117.19 ر.س</t>
+          <t>101.91 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>94.61 ر.س</t>
+          <t>3299.0 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+          <t>L23C3PE1 L23M3PE1 L23D3PE1 L23D3PE1 11.31 فولت 57 واط في الساعة متوافق مع لينوفو ايديا باد 5 2 في 1 14AHP9 83DR 16AHP9 83DS.</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>17.72 ر.س</t>
+          <t>243.0 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>17.15 ر.س</t>
+          <t>1454.16 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+          <t>روم تيك بطارية سيموس لجهاز لينوفو ثينك باد T430 T450S T460 T430I T430S - بطارية احتياطية للابتوب بيوس ار تي سي 3 فولت CR2032 T430 CMOS للوحة الام للكمبيوتر مع كيبل 2 سلك بدبوسين (عبوة واحدة)</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>10.18 ر.س</t>
+          <t>137.0 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+          <t>تابلت شاومي بوكو باد ام 1 واي فاي 8GB 256GB شاشة 12.1 انش 120Hz 12000mAh اسود (مع شاحن)</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>11.78 ر.س</t>
+          <t>1269.53 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>11.0 ر.س</t>
+          <t>3599.0 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>يعمل الجهاز بضغط يصل إلى 26.1 PSI (حوالي 1.8 بار) وبقدرة كهربائية تبلغ 100 وات، مما يوفر أداءً فعالًا وقوة تشغيل مناسبة، مضخة مياه موفرة للطاقة 24 فولت مع محول 1/2 بوصة للاستحمام المنزلي وإمدادات</t>
+          <t>هواوي تابلت ميت باد 11.5 اس 2026 2.8K 144Hz شاشة فائقة الوضوح، 12+256GB، شحن فائق 40 واط، واي فاي 6+، بلوتوث 5.2، جو بينت، كيبورد قابل للفصل، رمادي + ضمان ممتد لمدة عام</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>180.0 ر.س</t>
+          <t>2067.0 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
+          <t>تابلت ون بلس باد 3، سناب دراجون 8 ايليت، معدل تحديث 144 هرتز، واي فاي (ستورم بلو، 12 جيجابايت + 256 جيجابايت)</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>146.0 ر.س</t>
+          <t>3499.0 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
+          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>22.23 ر.س</t>
+          <t>399.0 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
+          <t>شاشة العاب منحنية 24 بوصة 240 هرتز FHD 1080p 1500R 1 مللي ثانية ومزامنة تكيفية وتباين 3000:1 ودعم HDR وHDMI 2.0 ومنفذ طاقة 1.4 بضوء أزرق منخفض وإمالة فيسا H24S17P من كيه تي سي</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>27.97 ر.س</t>
+          <t>411.99 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>11.24 ر.س</t>
+          <t>422.97 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>استرو ايه اي منفاخ اطارات لاسلكي محمول 150 باوند لكل انش مربع</t>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>99.98 ر.س</t>
+          <t>617.0 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>ضاغط هواء كهربائي محمول بعمر بطارية طويل مطور لعام 2024، منفاخ رقمي للكشف عن ضغط الإطارات مع ضوء LED (بحد أقصى 10 بار) بإيقاف تلقائي للسيارة والدراجة والكرة وغيرها من يوجرين</t>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>168.99 ر.س</t>
+          <t>448.98 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>منفاخ هواء من يوماي أوتوماتيكي مع مضخة هواء بالون مصدر طاقة خارجي</t>
+          <t>شاشة ألعاب UG27PJ ليد 27 بوصة ومعدل تحديث 240Hz، لوحة IPS، استجابة 1 مل ثانية، دقة FHD (1920×1080)، سطوع 400 شمعة/م² من زد ايدج، حواف نحيفة، دعم فريسينك، منفذ(HDMI×2 وDP×2)، تثبت على الحائط، تدعم فيسا</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>38.17 ر.س</t>
+          <t>519.19 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>منفاخ هواء من جودتول يدوي مع إبرة الكرة و محول الفوهة و خرطوم تمديد و مضخة يدوية يدوي</t>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>10.72 ر.س</t>
+          <t>291.82 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
+          <t>مبرد وحدة المعالجة المركزية السائل 240 RS ARGB نوتيلوس - 240 ملم AIO، منخفض الضوضاء، اتصال مباشر باللوحة الأم وتوصيل سلس - انتل LGA 1851/1700، AMD AM5/AM4 - 2 × مراوح RS120 ARGB متضمنة من كورسير، أسود</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>34.99 ر.س</t>
+          <t>390.0 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>تابلت ميت باد 11.5 S بشاشة بيبر مات فائقة الوضوح وذاكرة 12 جيجابايت + 256 جيجابايت وبطارية 8800 ميلي امبير في الساعة وشحن فائق السرعة بقوة 40 واط مع لوحة مفاتيح قابلة للفصل من هواوي، رمادي</t>
+          <t>مبرد وحدة المعالجة المركزية السائل ايوتا L24 BK 240 ملم AIO مع شاشة رقمية</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>1799.0 ر.س</t>
+          <t>289.99 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
+          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>1243.0 ر.س</t>
+          <t>789.98 ر.س</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة USB C 12 فولت - 24 فولت، محول طاقة للابتوب 90 واط 65 واط متوافق مع لينوفو ثينك باد اتش بي ديل ايسر اسوس كروم بوك سامسونج ماك بوك برو/اير والمزيد من الاجهزة من النوع سي</t>
+          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>101.91 ر.س</t>
+          <t>479.0 ر.س</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>تابلت هواوي ميت باد 12 × 2025 شاشة بيبر ميت 2.8K 12 بوصة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس ولوحة مفاتيح مرفقة (استخدام اللغة العربية غير مؤكد)، هواوي كير لمدة عام، (أبيض)</t>
+          <t>مبرد سائل من سلسلة انيرجلو من سودوكو</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>1999.0 ر.س</t>
+          <t>265.24 ر.س</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
+          <t>شاشة ألعاب KTC مقاس 24 بوصة 240 هرتز ودقة FHD 1080P، لوحة IPS سريعة، تقنية</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>3299.0 ر.س</t>
+          <t>494.99 ر.س</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
+          <t>مبرد وحدة المعالجة المركزية بالماء فروزن نوتي 240 اسود ARGB من ثيرمال رايت، المواصفات: مراوح بي دبليو ام مزدوجة، محامل اس- اف دي بي الاصدار2، مناسب لـ AMD/AM4 AM5، انتل LGA 1700/1150/1151/1200/2011</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>1454.16 ر.س</t>
+          <t>245.0 ر.س</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -2968,807 +2968,15 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>تابلت هواوي ميت باد 11.5 بيبر مات اصدار واي فاي، شاشة فل فيو هواوي 120HZ مهدئة للعين، تصميم انيق للجسم الذهني، ذاكرة رام 8GB وذاكرة تخزين داخلية 256GB، رمادي سبيس</t>
+          <t>شاشة ألعاب منحنية 24 بوصة 240 هرتز من كيه تي اس، شاشة كمبيوتر منحنية FHD 1500R 1080 بكسل، تباين 3000:1، مزامنة تكيفية، ام بي ار تي1، اتش دي ار مللي ثانية، منفذ عرض اتش دي ام اي، ضوء أزرق منخفض، إمالة</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>1449.0 ر.س</t>
+          <t>529.99 ر.س</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>تابلت شاومي ريدمي باد 2، 11 انش، 6 جيجا، 128 جيجا، واي فاي، هايبر او اس، اخضر مينت</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>978.04 ر.س</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>3599.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت باد 8 8GB/128GB، واي فاي 7، 11.2 انش 3.2 كيه، صوت دولبي اتموس، معالج سناب دراجون 870، بطارية 9200mAh (الشاحن غير متضمن)، رمادي</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>1732.26 ر.س</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت ريدمي باد 2 مي، 4GB + 128GB، ازرق سيان، ميديا تيك هيليو G100-الترا، شاشة 11 انش 2.5K 90Hz، بطارية 9000mAh، مع شاحن</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>953.13 ر.س</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>كيوكورا مرحل الملف اللولبي 12 فولت بادئ كهرومغناطيسي متين لاستبدال محرك اليخت البحري، اسود، وحدة واحدة</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>97.09 ر.س</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>تابلت ون بلس باد 3، سناب دراجون 8 ايليت، معدل تحديث 144 هرتز، واي فاي (ستورم بلو، 12 جيجابايت + 256 جيجابايت)</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>3499.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>399.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>599.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب منحنية 24 بوصة 240 هرتز FHD 1080p 1500R 1 مللي ثانية ومزامنة تكيفية وتباين 3000:1 ودعم HDR وHDMI 2.0 ومنفذ طاقة 1.4 بضوء أزرق منخفض وإمالة فيسا H24S17P من كيه تي سي</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>411.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب UG27PJ ليد 27 بوصة ومعدل تحديث 240Hz، لوحة IPS، استجابة 1 مل ثانية، دقة FHD (1920×1080)، سطوع 400 شمعة/م² من زد ايدج، حواف نحيفة، دعم فريسينك، منفذ(HDMI×2 وDP×2)، تثبت على الحائط، تدعم فيسا</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>519.19 ر.س</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>449.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>422.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>617.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>789.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>479.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>مبرد وحدة المعالجة المركزية السائل 240 RS ARGB نوتيلوس - 240 ملم AIO، منخفض الضوضاء، اتصال مباشر باللوحة الأم وتوصيل سلس - انتل LGA 1851/1700، AMD AM5/AM4 - 2 × مراوح RS120 ARGB متضمنة من كورسير، أسود</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>403.52 ر.س</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>مبرد سائل من سلسلة انيرجلو من سودوكو</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>265.24 ر.س</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>مبرد وحدة معالجة مركزية مائي فروزن نوت 240 ابيض ARGB من ثيرمال رايت، مواصفات مبرد وحدة معالجة مركزية 240 ابيض، مراوح PWM مزدوجة محامل S-FDB V2، مناسب لـAMD/AM4 AM5، انتل LGA 1700/1150/1151/1200/2011</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>240.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>499.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>مبرد وحدة المعالجة المركزية السائل للألعاب 240 - مراوح ARGB 2×120 ملم، آلية متشابكة منزلقة من جيجابايت، يدعم التوصيل المتسلسل، انتل LGA 1851 وAMD AM5</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>329.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>مروحة بانوراما اس اي 240 ايه ار جي بي وايت متكاملة قابلة للدوران 6.67 بوصة بشاشة اموليد منحنية ثلاثية الأبعاد بتأثير انامورفيك 240 ملم 260 واط TDP، مروحة انتل LGA 1851/1700/1200/115X AMD AM5/AM4</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>1199.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>36.47 ر.س</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>88.74 ر.س</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>45.85 ر.س</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>88.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>59.89 ر.س</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>20.78 ر.س</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>35.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>39.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>79.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>جوي رووم شاحن سيارة صغير JR-CCN05 30 واط USB-A USB-C يوفر شحن سريع وآمن، يشحن جهازين في وقت واحد - اسود</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>24.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>75.88 ر.س</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>59.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>39.17 ر.س</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>45.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-24</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-25</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>203.8 ر.س</t>
+          <t>217.17 ر.س</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -644,35 +644,35 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="C7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>10.18 ر.س</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>43.59 ر.س</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>aletawiksa, amazon_sa</t>
+          <t>aletawiksa, iblackstores, amazon_sa</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>427.93 ر.س</t>
+          <t>433.22 ر.س</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>20.78 ر.س</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>106.97 ر.س</t>
+          <t>73.72 ر.س</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>جودا - بطاريات AAA القابلة للشحن</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1621,17 +1621,17 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>جودا - منصة جودا بيك 4 منافذ تايب سي بقوة 240 واط - اسود</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>298.99 ر.س</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1643,17 +1643,17 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1665,17 +1665,17 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>بطارية جودا MagTack بقوة 35 واط (10000 مللي أمبير) مع كيبل Type-C مدمج - أسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1753,17 +1753,17 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1775,22 +1775,22 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>دار الأداب الهاربون والباقون</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>88.2 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>روبوتايم 3 دي بازل هارب</t>
+          <t>دار الأداب الهاربون والباقون</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>202.91 ر.س</t>
+          <t>88.2 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
+          <t>روبوتايم 3 دي بازل هارب</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>35.0 ر.س</t>
+          <t>202.91 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>بيلا فيتا جزمة هارب للنساء</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>69.83 ر.س</t>
+          <t>126.34 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>ساعة منبه ران اواي المتدحرجة (الأصلية) من كلوكي، بصوت عال جدا الثقيل (روبوت غرفة النوم للكبار والأطفال) مضحكة، متدحرجة، هاربة، متحركة، قافزة (أزرق)</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>151.2 ر.س</t>
+          <t>69.83 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>وايلد ريبابليك لعبة قطيفة من بوكيت كينز ايكو هارب، حيوان محشو، 5 انش، مصنوعة من مواد معاد تدويرها، صديقة للبيئة</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>275.0 ر.س</t>
+          <t>67.23 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>314.9 ر.س</t>
+          <t>35.0 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>ليجو سلسلة 25 - هاربي</t>
+          <t>سبيري حذاء رياضي هاربون كراش باك سهل الارتداء للرجال</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>89.32 ر.س</t>
+          <t>310.25 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>سبيري حذاء قارب هاربون للرجال، لون بيج داكن، مقاس 11.5</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>280.03 ر.س</t>
+          <t>354.87 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>هارمونيكا هارب هارموك ارمونيكا 24 فتحة فم، مفتاح احترافي سي متعدد الأصوات دياتونيك مع حافظة لموسيقى البوب والجاز الشعبي البلوز</t>
+          <t>سبيري حذاء قارب هاربون للرجال</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>166.85 ر.س</t>
+          <t>329.75 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>سبيري حذاء قارب للرجال من هاربون، بيج داكن، مقاس 42 EU</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>299.0 ر.س</t>
+          <t>290.74 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>سبيري حذاء هاربون على شكل قارب للرجال، كحلي، مقاس 42 EU</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>251.35 ر.س</t>
+          <t>272.15 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>فستان كاجوال للنساء من هاربا، عبوة من قطعة واحدة، GR6356</t>
+          <t>سبيري حذاء قارب هاربون للرجال، رمادي، 8.5</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>65.14 ر.س</t>
+          <t>292.3 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>Sperry Mens Harpoon Crushback Slip on Sneaker</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>269.25 ر.س</t>
+          <t>374.89 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+          <t>الدو صندل هاربا مفتوح عند الاصابع للنساء من 20 هاربا</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>278.06 ر.س</t>
+          <t>612.0 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>150.0 ر.س</t>
+          <t>93.43 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>79.96 ر.س</t>
+          <t>40.0 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>119.0 ر.س</t>
+          <t>186.25 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
+          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>130.0 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>118.98 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>بطارية بديلة لجيه بي ال لينك 10، 3.7 فولت/3600 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>94.97 ر.س</t>
+          <t>104.92 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>82.95 ر.س</t>
+          <t>106.18 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 10000 مللي امبير بمنفذ USB تايب-C مع شحن لاسلكي و سريع و مغناطيسي للهاتف الذكي بمنفذين رمادي</t>
+          <t>محول مقسم نشط POE من قطعتين، 48 فولت الى 12 فولت، متوافق مع IEEE 802.3af 10/100Mbps حتى 100 متر لكاميرا IP ونقطة الوصول اللاسلكية والهاتف عبر بروتوكول الإنترنت</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>118.99 ر.س</t>
+          <t>45.2 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك من أنكر فائق السرعة بسعة 25.000 مللي أمبير/الساعة وقوة 165 واط، لشحن 2 لابتوب، بطارية شحن سريع مع كابلات مدمجة وقابلة للطي، متوافق مع آيفون من سلسلة 16/15 وسامسونج وغيرها</t>
+          <t>شاحن 9 فولت متوافق مع كاميرا المراقبة تي بي لينك تابو C110 C200 C210</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>297.0 ر.س</t>
+          <t>97.09 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>تابلت هواوي ميت باد SE بشاشة 11 بوصة، ذاكرة 4+128 جيجابايت، مع قلم ام بن لايت، شاشة فول فيو وبطارية ذات سعة كبيرة مع ركن خاص بالأطفال</t>
+          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>703.0 ر.س</t>
+          <t>115.46 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
+          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>1243.0 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>تابلت ميت باد 11.5 S بشاشة بيبر مات فائقة الوضوح وذاكرة 12 جيجابايت + 256 جيجابايت وبطارية 8800 ميلي امبير في الساعة وشحن فائق السرعة بقوة 40 واط مع لوحة مفاتيح قابلة للفصل من هواوي، رمادي</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>1799.0 ر.س</t>
+          <t>17.15 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة USB C 12 فولت - 24 فولت، محول طاقة للابتوب 90 واط 65 واط متوافق مع لينوفو ثينك باد اتش بي ديل ايسر اسوس كروم بوك سامسونج ماك بوك برو/اير والمزيد من الاجهزة من النوع سي</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>101.91 ر.س</t>
+          <t>17.72 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>3299.0 ر.س</t>
+          <t>10.18 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>L23C3PE1 L23M3PE1 L23D3PE1 L23D3PE1 11.31 فولت 57 واط في الساعة متوافق مع لينوفو ايديا باد 5 2 في 1 14AHP9 83DR 16AHP9 83DS.</t>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>243.0 ر.س</t>
+          <t>11.78 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>1454.16 ر.س</t>
+          <t>11.0 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>روم تيك بطارية سيموس لجهاز لينوفو ثينك باد T430 T450S T460 T430I T430S - بطارية احتياطية للابتوب بيوس ار تي سي 3 فولت CR2032 T430 CMOS للوحة الام للكمبيوتر مع كيبل 2 سلك بدبوسين (عبوة واحدة)</t>
+          <t>يعمل الجهاز بضغط يصل إلى 26.1 PSI (حوالي 1.8 بار) وبقدرة كهربائية تبلغ 100 وات، مما يوفر أداءً فعالًا وقوة تشغيل مناسبة، مضخة مياه موفرة للطاقة 24 فولت مع محول 1/2 بوصة للاستحمام المنزلي وإمدادات</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>137.0 ر.س</t>
+          <t>180.0 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>تابلت شاومي بوكو باد ام 1 واي فاي 8GB 256GB شاشة 12.1 انش 120Hz 12000mAh اسود (مع شاحن)</t>
+          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>1269.53 ر.س</t>
+          <t>109.95 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB</t>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>3599.0 ر.س</t>
+          <t>27.97 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>هواوي تابلت ميت باد 11.5 اس 2026 2.8K 144Hz شاشة فائقة الوضوح، 12+256GB، شحن فائق 40 واط، واي فاي 6+، بلوتوث 5.2، جو بينت، كيبورد قابل للفصل، رمادي + ضمان ممتد لمدة عام</t>
+          <t>مضخة مياه كهربائية بشحن USB، مضخة مياه شرب محمولة متوافقة مع الزجاجات القياسية سعة 11 إلى 19 لتر، مناسبة للاستخدام في المنزل والمكتب وأساسية للتخييم من سكاي-تاتش</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>2067.0 ر.س</t>
+          <t>21.97 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>تابلت ون بلس باد 3، سناب دراجون 8 ايليت، معدل تحديث 144 هرتز، واي فاي (ستورم بلو، 12 جيجابايت + 256 جيجابايت)</t>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>3499.0 ر.س</t>
+          <t>11.24 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+          <t>استرو ايه اي منفاخ اطارات لاسلكي محمول 150 باوند لكل انش مربع</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>399.0 ر.س</t>
+          <t>99.98 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>شاشة العاب منحنية 24 بوصة 240 هرتز FHD 1080p 1500R 1 مللي ثانية ومزامنة تكيفية وتباين 3000:1 ودعم HDR وHDMI 2.0 ومنفذ طاقة 1.4 بضوء أزرق منخفض وإمالة فيسا H24S17P من كيه تي سي</t>
+          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>411.99 ر.س</t>
+          <t>22.23 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>422.97 ر.س</t>
+          <t>34.99 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+          <t>منفاخ هواء من يوماي أوتوماتيكي مع مضخة هواء بالون مصدر طاقة خارجي</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>617.0 ر.س</t>
+          <t>38.17 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+          <t>ضاغط هواء كهربائي محمول بعمر بطارية طويل مطور لعام 2024، منفاخ رقمي للكشف عن ضغط الإطارات مع ضوء LED (بحد أقصى 10 بار) بإيقاف تلقائي للسيارة والدراجة والكرة وغيرها من يوجرين</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>448.98 ر.س</t>
+          <t>168.99 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب UG27PJ ليد 27 بوصة ومعدل تحديث 240Hz، لوحة IPS، استجابة 1 مل ثانية، دقة FHD (1920×1080)، سطوع 400 شمعة/م² من زد ايدج، حواف نحيفة، دعم فريسينك، منفذ(HDMI×2 وDP×2)، تثبت على الحائط، تدعم فيسا</t>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>519.19 ر.س</t>
+          <t>260.12 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>291.82 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>مبرد وحدة المعالجة المركزية السائل 240 RS ARGB نوتيلوس - 240 ملم AIO، منخفض الضوضاء، اتصال مباشر باللوحة الأم وتوصيل سلس - انتل LGA 1851/1700، AMD AM5/AM4 - 2 × مراوح RS120 ARGB متضمنة من كورسير، أسود</t>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>390.0 ر.س</t>
+          <t>150.0 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>مبرد وحدة المعالجة المركزية السائل ايوتا L24 BK 240 ملم AIO مع شاشة رقمية</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>289.99 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>789.98 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
+          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>479.0 ر.س</t>
+          <t>119.0 ر.س</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>مبرد سائل من سلسلة انيرجلو من سودوكو</t>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>265.24 ر.س</t>
+          <t>79.96 ر.س</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب KTC مقاس 24 بوصة 240 هرتز ودقة FHD 1080P، لوحة IPS سريعة، تقنية</t>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>494.99 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>مبرد وحدة المعالجة المركزية بالماء فروزن نوتي 240 اسود ARGB من ثيرمال رايت، المواصفات: مراوح بي دبليو ام مزدوجة، محامل اس- اف دي بي الاصدار2، مناسب لـ AMD/AM4 AM5، انتل LGA 1700/1150/1151/1200/2011</t>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>245.0 ر.س</t>
+          <t>82.95 ر.س</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -2968,15 +2968,697 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>118.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>94.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>171.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك من أنكر فائق السرعة بسعة 25.000 مللي أمبير/الساعة وقوة 165 واط، لشحن 2 لابتوب، بطارية شحن سريع مع كابلات مدمجة وقابلة للطي، متوافق مع آيفون من سلسلة 16/15 وسامسونج وغيرها</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>297.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>399.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب منحنية 24 بوصة 240 هرتز FHD 1080p 1500R 1 مللي ثانية ومزامنة تكيفية وتباين 3000:1 ودعم HDR وHDMI 2.0 ومنفذ طاقة 1.4 بضوء أزرق منخفض وإمالة فيسا H24S17P من كيه تي سي</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>411.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>422.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>479.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>448.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب UG27PJ ليد 27 بوصة ومعدل تحديث 240Hz، لوحة IPS، استجابة 1 مل ثانية، دقة FHD (1920×1080)، سطوع 400 شمعة/م² من زد ايدج، حواف نحيفة، دعم فريسينك، منفذ(HDMI×2 وDP×2)، تثبت على الحائط، تدعم فيسا</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>519.19 ر.س</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>617.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>291.67 ر.س</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>789.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>مبرد وحدة المعالجة المركزية السائل 240 RS ARGB نوتيلوس - 240 ملم AIO، منخفض الضوضاء، اتصال مباشر باللوحة الأم وتوصيل سلس - انتل LGA 1851/1700، AMD AM5/AM4 - 2 × مراوح RS120 ARGB متضمنة من كورسير، أسود</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>403.52 ر.س</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>مبرد سائل من سلسلة انيرجلو من سودوكو</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>265.24 ر.س</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
           <t>شاشة ألعاب منحنية 24 بوصة 240 هرتز من كيه تي اس، شاشة كمبيوتر منحنية FHD 1500R 1080 بكسل، تباين 3000:1، مزامنة تكيفية، ام بي ار تي1، اتش دي ار مللي ثانية، منفذ عرض اتش دي ام اي، ضوء أزرق منخفض، إمالة</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
         <is>
           <t>529.99 ر.س</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>ساعة من كاسيو للجنسين بشاشة أنالوج و ديجيتال موديل ايه كيو-240</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>299.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>45.85 ر.س</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>88.74 ر.س</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>88.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>35.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>20.78 ر.س</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>39.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>59.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>45.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>75.88 ر.س</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>39.17 ر.س</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 16 و15 وسامسونج S25 وS24 بـ3 منافذ بقدرة 145 واط مع شحن سريع وكابل قابل للسحب وحماية متعددة</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>149.65 ر.س</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -43,7 +43,7 @@
       <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -63,11 +63,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,9 +104,6 @@
       <alignment vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -497,7 +489,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-27</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -749,35 +741,35 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa, iblackstores</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>aletawiksa</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>194.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -871,1322 +863,926 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>mokab</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>اوتلت مكعب</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>29.0 ر.س</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>mokab</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>اوتلت مكعب</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>5.0 ر.س</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>اكسسوارات ايفون 18</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>9.0 ر.س</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>اكسسوارات ايفون 18</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>9.0 ر.س</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>99.0 ر.س</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>119.0 ر.س</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>79.0 ر.س</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 سيليكون 60 واط تايب سي الى تايب سي 1 متر - وردي غامق</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>159.0 ر.س</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>129.0 ر.س</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>209.0 ر.س</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>179.0 ر.س</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>179.0 ر.س</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>149.0 ر.س</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>349.0 ر.س</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>129.0 ر.س</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>49.0 ر.س</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>149.0 ر.س</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>79.0 ر.س</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>iblackstores</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>جودا - بطاريات AAA القابلة للشحن</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>58.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>199.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>iblackstores</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>جودا - منصة جودا بيك 4 منافذ تايب سي بقوة 240 واط - اسود</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>298.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>wjhtektelecome</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>171.35 ر.س</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>iblackstores</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>58.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>wjhtektelecome</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>171.35 ر.س</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>iblackstores</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>199.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>wjhtektelecome</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>171.35 ر.س</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>wjhtektelecome</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>171.35 ر.س</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>alwan7</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>50.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>wjhtektelecome</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>171.35 ر.س</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>jarir</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>مايكل جوردن</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>39.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>wjhtektelecome</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>171.35 ر.س</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>jarir</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Item 1 of 2</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>37.08 ر.س</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>alwan7</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>50.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>jarir</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>How To Write</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>24.39 ر.س</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>jarir</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>مايكل جوردن</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>39.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>بحث تقديري</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>jarir</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>Item 1 of 2</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>37.08 ر.س</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>بحث تقديري</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>jarir</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>How To Write</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>24.39 ر.س</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>بحث تقديري</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>134.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>198.81 ر.س</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>171.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>جوال تانك 1 متين 6.75 انش 120Hz FHD+ من شاندويليك، هاتف اتصال خارجي 12GB+256GB 20000mAh، هاتف ذكي 5G اندرويد 15 ان اف سي</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>2090.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>82.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>99.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>جوال اكسبلور 1 للاستخدام الخارجي، جوال ذكي بشبكة الجيل الخامس 5G مقاوم للماء بنظام أندرويد 15، شاشة 6.78 بوصة بدقة 2.4 كيه، 12 جيجابايت+256 جيجابايت، بطارية 20000 ميلي أمبير/الساعة</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>1790.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>جوال تانك 1 متين 6.75 انش 120Hz FHD+ من شاندويليك، هاتف اتصال خارجي 12GB+256GB 20000mAh، هاتف ذكي 5G اندرويد 15 ان اف سي</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>2090.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>109.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>جهاز عرض XP 2 من شاندوليك، هاتف ذكي 5G بالذكاء الاصطناعي، شاشة AMOLED 6.75 انش 3.2 كيه، كاميرا 50MP، 16GB + 1TB، 20000mAh، جوال خارجي متين</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>3690.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>بنك طاقة من انيو، شاحن محمول صغير بقدرة 22.5 واط وسعة 20000 ميلي أمبير، مزوّد بمدخل ومخرج USB-C، يدعم الشحن السريع PD 3.0 وQC 4.0، مع شاشة LED، لايفون 17 و16 و15 وسامسونج S25 وS24 وهواوي وهونر وغيرها</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>111.14 ر.س</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>138.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك CP24 20000 مللي امبير في الساعة 40 واط سي سي سي مع كابلات مزدوجة</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>161.64 ر.س</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>جوال ذكي جالكسي A16، يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجا، ذاكرة تخزين 128 جيجا من سامسونج، رمادي (إصدار المملكة العربية السعودية)</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>585.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>فيجير باور بانك 20000 مللي امبير في الساعة، شاحن محمول رفيع مع كيبلات متعددة مدمجة، بطارية شحن سريع عالية السعة مع شاشة عرض رقمية لايفون وسامسونج والجوالات - اسود</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>95.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -43,7 +43,7 @@
       <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +63,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,6 +109,9 @@
       <alignment vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -489,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-28</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -776,35 +784,35 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>69.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>69.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>20.78 ر.س</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>64.18 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -824,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -863,926 +871,1542 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>mokab</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>اوتلت مكعب</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>29.0 ر.س</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>mokab</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>اوتلت مكعب</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>5.0 ر.س</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>اكسسوارات ايفون 18</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>9.0 ر.س</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>اكسسوارات ايفون 18</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>9.0 ر.س</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>99.0 ر.س</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>119.0 ر.س</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>79.0 ر.س</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>aletawiksa</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 سيليكون 60 واط تايب سي الى تايب سي 1 متر - وردي غامق</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>159.0 ر.س</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>129.0 ر.س</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>209.0 ر.س</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>179.0 ر.س</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>179.0 ر.س</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>149.0 ر.س</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>349.0 ر.س</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>129.0 ر.س</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>49.0 ر.س</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>149.0 ر.س</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>79.0 ر.س</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>109.0 ر.س</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>59.0 ر.س</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>al3bor-telecom</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>iblackstores</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>199.0 ر.س</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>wjhtektelecome</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>171.35 ر.س</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>alwan7</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>50.0 ر.س</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>jarir</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>مايكل جوردن</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>39.99 ر.س</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>jarir</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Item 1 of 2</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>37.08 ر.س</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>بحث تقديري</t>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>14.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>jarir</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>How To Write</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>24.39 ر.س</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>بحث تقديري</t>
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>8.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>11.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>12.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>6.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>خلطة فيز 160 جم من هاريبو</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>11.55 ر.س</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>حلوى بيريز من هاريبو، 160 جم</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>11.55 ر.س</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>11.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>9.5 ر.س</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>14.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>6.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>7.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>جيلي فيز على شكل ديدان من هاريبو، 70 جم</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>6.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>12.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جيلاتينية هاريبو جولد بيرز، 350 جم، عبوة من 5 قطع</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>11.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>45.85 ر.س</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>88.74 ر.س</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>20.78 ر.س</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>88.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>59.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>35.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>75.88 ر.س</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>39.17 ر.س</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>45.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>35.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 16 و15 وسامسونج S25 وS24 بـ3 منافذ بقدرة 145 واط مع شحن سريع وكابل قابل للسحب وحماية متعددة</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>149.65 ر.س</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع سامسونج وآيفون وهواوي P60 بـ 3 منافذ بقوة 130.0 واط مع شحن سريع وحماية متعددة</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>129.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-29</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -644,70 +644,70 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>10.18 ر.س</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>44.17 ر.س</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -749,35 +749,35 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>295.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -809,7 +809,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>64.18 ر.س</t>
+          <t>68.84 ر.س</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>14.95 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>8.99 ر.س</t>
+          <t>94.97 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
+          <t>شاحن باور بانك كيجو 20000 ميلي امبير في الساعة من جوي، أسود</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>11.96 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
+          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>12.95 ر.س</t>
+          <t>171.0 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>6.95 ر.س</t>
+          <t>198.81 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>خلطة فيز 160 جم من هاريبو</t>
+          <t>باور بانك CP24 20000 مللي امبير في الساعة 40 واط سي سي سي مع كابلات مزدوجة</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>11.55 ر.س</t>
+          <t>161.64 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>حلوى بيريز من هاريبو، 160 جم</t>
+          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>11.55 ر.س</t>
+          <t>61.99 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
+          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>11.96 ر.س</t>
+          <t>129.99 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>9.5 ر.س</t>
+          <t>138.87 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>14.95 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>6.95 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>7.25 ر.س</t>
+          <t>118.98 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>جيلي فيز على شكل ديدان من هاريبو، 70 جم</t>
+          <t>باور بانك في 10 20000 مللي امبير في الساعة 22.5 واط، شحن سريع، اصغر من معظم الشواحن 20 كلفن، باور بانك محمول مع كيبل مدمج، 4 مخارج وشاشة LED، مناسب للسفر لاجهزة ايفون وسامسونج وتابلت رمادي</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>6.95 ر.س</t>
+          <t>98.1 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
+          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>12.95 ر.س</t>
+          <t>229.0 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلاتينية هاريبو جولد بيرز، 350 جم، عبوة من 5 قطع</t>
+          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>11.75 ر.س</t>
+          <t>169.0 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>45.85 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>88.74 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>20.78 ر.س</t>
+          <t>115.19 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>88.99 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>59.89 ر.س</t>
+          <t>40.0 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>93.43 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>35.98 ر.س</t>
+          <t>186.25 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>79.96 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>75.88 ر.س</t>
+          <t>130.0 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>39.17 ر.س</t>
+          <t>105.94 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+          <t>TP - لينك موزع USB 3.0 مايكرو بي 7 منافذ مع محول طاقة 12 فولت/2.5 امبير وكابل USB 3.0 بطول 1 متر، شحن سريع 1.5 امبير، سرعة نقل بيانات 10 مرات، متوافق مع ويندوز وماك او اس اكس ولينكس (UH700)، اسود</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>45.0 ر.س</t>
+          <t>136.64 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
+          <t>شاحن 9 فولت متوافق مع كاميرا المراقبة تي بي لينك تابو C110 C200 C210</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>88.0 ر.س</t>
+          <t>96.86 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>35.8 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 16 و15 وسامسونج S25 وS24 بـ3 منافذ بقدرة 145 واط مع شحن سريع وكابل قابل للسحب وحماية متعددة</t>
+          <t>محول طاقة ستيب اب بتيار مستمر 12 فولت/24 فولت الى 30 فولت لستارلينك ميني، محول معزز للادخال 9 فولت - 28 فولت مع فيوز لراوتر ستار لينك ميني ار في والشاحنة والسيارات البحرية والسفر</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>149.65 ر.س</t>
+          <t>117.19 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,15 +2396,1313 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع سامسونج وآيفون وهواوي P60 بـ 3 منافذ بقوة 130.0 واط مع شحن سريع وحماية متعددة</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>129.89 ر.س</t>
+          <t>17.15 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>17.72 ر.س</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>11.78 ر.س</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>10.18 ر.س</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>106.15 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>22.23 ر.س</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه كهربائية محمولة مع شحن USB نوع سي، محرك مزدوج وتدفق سريع للمنزل والمكتب والتخييم والسيارة الترفيهية من كوزي تشارم، 19 لتر، أسود</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>64.5 ر.س</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>يعمل الجهاز بضغط يصل إلى 26.1 PSI (حوالي 1.8 بار) وبقدرة كهربائية تبلغ 100 وات، مما يوفر أداءً فعالًا وقوة تشغيل مناسبة، مضخة مياه موفرة للطاقة 24 فولت مع محول 1/2 بوصة للاستحمام المنزلي وإمدادات</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>180.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>24.5 ر.س</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>مضخة زجاجة مياه من كايبين، قابلة للطي، 3 اوضاع، 5 جالون، عبوة واحدة</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>29.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>11.24 ر.س</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>مضخة موزع مياه كهربائية محمولة لقوارير المياه بمضخات مزدوجة وقوة حصانية عالية ومخرجين للمياه، مزودة بواجهة شحن من النوع سي بمنفذ USB نوع سي، مناسبة للمكتب والمنزل والمطبخ من ار نيس، بلون أبيض</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>49.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>منفاخ هواء من يوماي أوتوماتيكي مع مضخة هواء بالون مصدر طاقة خارجي</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>38.17 ر.س</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه كهربائية بشحن USB، مضخة مياه شرب محمولة متوافقة مع الزجاجات القياسية سعة 11 إلى 19 لتر، مناسبة للاستخدام في المنزل والمكتب وأساسية للتخييم من سكاي-تاتش</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>21.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>منفاخ هواء من جودتول يدوي مع مضخة و إبرة و فوهة و خرطوم مرن يدوي</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>12.54 ر.س</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>263.11 ر.س</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>159.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>139.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>157.41 ر.س</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>119.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>109.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>94.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>82.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>171.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>198.81 ر.س</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك محمول 30000 ميلي امبير في الساعة، شحن سريع 20 واط، بي دي 18 واط، كيو سي 3.0، يو اس بي سي مع 4 مخارج و3 مداخل متوافق مع ايفون وايباد وسامسونج وهواوي والتابلت والمزيد من في ار يو ار سي</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>99.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>138.87 ر.س</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من باوليفانت 50000 مللي امبير ليثيوم بوليمر 12 ساعة شحن USB نوع C كابل مدمج وشحن سريع للهواتف الذكية 10 منافذ أسود</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>199.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>جهاز اختبار بطارية السيارة 12 فولت 24 فولت، واختبار تحميل البطارية وعرض تيار بدء التشغيل على البارد رقميا محلل تلقائي دقيق اداة تشخيص البطارية مناسب للشاحنات والدراجات النارية من اياكام (من 8 إلى 30</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>75.34 ر.س</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>وحدة تزويد طاقة تفاعلية 1000 فولت امبير من ارترونيك ارت، مزود طاقة غير منقطع 1000 فولت أمبير/600 واط، تنظيم جهد ايه في ار، موجة جيبية محاكاة، وظيفة التشغيل البارد، متوافق مع المولد</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>445.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>جهاز اختبار رقمي اوتوماتيكي KW208 للبطارية بقوة 12 فولت / 100 -2000 امبير في درجات الحرارة الباردة للسيارة لاختبار المولد ونظام التشغيل والشحن مناسب للقوارب والدراجات البخارية والدفع الرباعي من كونوي</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>105.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه باردة ومضخة تفريغ الهواء مصغرة اي كيه 1856 بتيار مستمر وبجهد 6 فولت الى 12 فولت ار385 من جيكفن</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>38.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>AUX نموذج عاكس هايبر كول بارد فقط 2 طن - 22000 وحدة حرارية بريطانية - كهربائي 220 فولت - 60 هرتز - 1 ساعة - واي فاي - وحدات داخلية وخارجية - ابيض - ATW24A2DI-CSA</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>2521.16 ر.س</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>جهاز اختبار بطارية السيارة طراز BT600 قدرة 12 فولت 24 فولت مع طابعة، قياس التيار عند التشغيل البارد 100 إلى 2000 من توبدون، شاشة ملونة 3.5 بوصة، كيبل 1.8 م، متوفر تحديث البرامج</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>715.12 ر.س</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>لمبة من بونلوكس بتقنية LED بإضاءة أبيض دافئ و أبيض طبيعي و أبيض بارد، عبوة من قطعتين، بقوة 8 واط</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>38.44 ر.س</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 500 فولت إلى تيار مستمر 12 فولت، محول بتيار 42 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>62.07 ر.س</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>جهاز جي اف سي اي لاختبار جهد خرج المقبس الكهربائي من هابو تيست مع عرض الجهد الكهربي 90-250 فولت، إختبار أوتوماتيك للدارات الكهربائية وكشف القطبية والتسرب HT107E</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>41.09 ر.س</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>محول جهد كهربائي 3000 واط 110 فولت/120 فولت/220 فولت/240 فولت من اليسم، محول طاقة تصاعدي / لأسفل مع حماية من قاطع الدائرة الكهربائية قابل لاعادة الضبط، مقبس عالمي مدمج للمنزل</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>399.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>موزع مياه ساخن وبارد تحميل سفلي قائم على الارض 220-240 فولت مع ثلاجة من هوميكس - ابيض YLR-LW-2-5-100 باوند</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>396.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>جهاز اختبار بطارية السيارة الرقمية وأداة تشخيص المولد من انسيل، سعة تحميل 100-2000 CCA، تحليل الشحن والتحريك للدراجة النارية والشاحنة والقارب والمركبة الترفيهية والبحرية وغيرها، 12 فولت، BA101</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>221.66 ر.س</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>مكيف هواء 12 فولت تيار مستمر، مكيف سقف قابل للتطبيق على الشاحنات والمركبات الترفيهية والحافلات والحفارات والمخيمات والمركبات الزراعية، مكيف هواء 12 فولت يعمل على البارد والساخن 24 فولت</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>1987.09 ر.س</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>جهاز قياس الجهد الكهربائي المحمول ار سي دي المتقدم من موريليان، فاحص الخرج الكهربائي للتيار المتردد دون تلامس/ بشاشة عرض ال سي دي لاضاءة الخلفية، فاحص فولت ～ على شكل قلم مع مؤئر تنبيه</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>63.27 ر.س</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>ايكام جهاز تحكم اوتوماتيكي بمضخة 220 فولت بمستشعر مياه HT 60 4 4 ضغط منخفض لبدء التشغيل الساخن والبارد من النحاس الاصفر G1 2 انش للتحكم التلقائي في الصنبور</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>41.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>45.85 ر.س</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>88.74 ر.س</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>20.78 ر.س</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>88.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>35.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>59.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>75.88 ر.س</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>39.17 ر.س</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>45.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>جوي رووم شاحن سيارة صغير JR-CCN05 30 واط USB-A USB-C يوفر شحن سريع وآمن، يشحن جهازين في وقت واحد - اسود</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>24.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 16 و15 وسامسونج S25 وS24 بـ3 منافذ بقدرة 145 واط مع شحن سريع وكابل قابل للسحب وحماية متعددة</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>149.65 ر.س</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>35.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-09-30</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>10.18 ر.س</t>
+          <t>38.0 ر.س</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>44.17 ر.س</t>
+          <t>159.66 ر.س</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -679,35 +679,35 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>150.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>150.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -774,7 +774,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>295.0 ر.س</t>
+          <t>474.81 ر.س</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>20.78 ر.س</t>
+          <t>29.0 ر.س</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>68.84 ر.س</t>
+          <t>64.17 ر.س</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D132"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>94.97 ر.س</t>
+          <t>198.81 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك كيجو 20000 ميلي امبير في الساعة من جوي، أسود</t>
+          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>189.0 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
+          <t>باور بانك سينجي ميني 20 بطارية 20,000mAh، شحن بقدرة 15 واط، ثلاث منافذ (2 نوع سي + 1 USB نوع ايه)، مدمج وسهل الحمل متوافق مع جي-تاج، أسود</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>171.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+          <t>شاحن باور بانك كيجو 20000 ميلي امبير في الساعة من جوي، أسود</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>198.81 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>باور بانك CP24 20000 مللي امبير في الساعة 40 واط سي سي سي مع كابلات مزدوجة</t>
+          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>161.64 ر.س</t>
+          <t>129.99 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>129.99 ر.س</t>
+          <t>138.87 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>138.87 ر.س</t>
+          <t>118.98 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+          <t>باور بانك CP24 20000 مللي امبير في الساعة 40 واط سي سي سي مع كابلات مزدوجة</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>118.98 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>باور بانك في 10 20000 مللي امبير في الساعة 22.5 واط، شحن سريع، اصغر من معظم الشواحن 20 كلفن، باور بانك محمول مع كيبل مدمج، 4 مخارج وشاشة LED، مناسب للسفر لاجهزة ايفون وسامسونج وتابلت رمادي</t>
+          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>98.1 ر.س</t>
+          <t>229.0 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
+          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>229.0 ر.س</t>
+          <t>169.0 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
+          <t>شاحن محمول C سعة 20000 مللي أمبير، باور بانك 20K بمنفذ إدخال وإخراج نوع C ومنفذين A مع كيبل C إلى A مرفق لأجهزة ايفون وجالكسي وبيكسل وايباد وإيربودز والمزيد من بيلكن - رمادي سبيس</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>169.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>17.95 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>11.96 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
+          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>115.19 ر.س</t>
+          <t>7.48 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
+          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>13.5 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+          <t>خلطة فيز 160 جم من هاريبو</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>40.0 ر.س</t>
+          <t>11.95 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
+          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>93.43 ر.س</t>
+          <t>11.25 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>186.25 ر.س</t>
+          <t>11.96 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>16.48 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+          <t>حلوى بيريز من هاريبو، 160 جم</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>130.0 ر.س</t>
+          <t>12.95 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
+          <t>حلوى جيلاتينية هاريبو جولد بيرز، 350 جم، عبوة من 5 قطع</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>105.94 ر.س</t>
+          <t>8.99 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك موزع USB 3.0 مايكرو بي 7 منافذ مع محول طاقة 12 فولت/2.5 امبير وكابل USB 3.0 بطول 1 متر، شحن سريع 1.5 امبير، سرعة نقل بيانات 10 مرات، متوافق مع ويندوز وماك او اس اكس ولينكس (UH700)، اسود</t>
+          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>136.64 ر.س</t>
+          <t>7.25 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>شاحن 9 فولت متوافق مع كاميرا المراقبة تي بي لينك تابو C110 C200 C210</t>
+          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>96.86 ر.س</t>
+          <t>7.5 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
+          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>12.96 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>محول طاقة ستيب اب بتيار مستمر 12 فولت/24 فولت الى 30 فولت لستارلينك ميني، محول معزز للادخال 9 فولت - 28 فولت مع فيوز لراوتر ستار لينك ميني ار في والشاحنة والسيارات البحرية والسفر</t>
+          <t>حلوى بنكهة الكولا من هاريبو، وزن 250 جم</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>117.19 ر.س</t>
+          <t>13.5 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>17.15 ر.س</t>
+          <t>13.5 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>17.72 ر.س</t>
+          <t>51.0 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>11.78 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>10.18 ر.س</t>
+          <t>51.0 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
+          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>106.15 ر.س</t>
+          <t>115.19 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>22.23 ر.س</t>
+          <t>40.0 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه كهربائية محمولة مع شحن USB نوع سي، محرك مزدوج وتدفق سريع للمنزل والمكتب والتخييم والسيارة الترفيهية من كوزي تشارم، 19 لتر، أسود</t>
+          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>64.5 ر.س</t>
+          <t>93.43 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>يعمل الجهاز بضغط يصل إلى 26.1 PSI (حوالي 1.8 بار) وبقدرة كهربائية تبلغ 100 وات، مما يوفر أداءً فعالًا وقوة تشغيل مناسبة، مضخة مياه موفرة للطاقة 24 فولت مع محول 1/2 بوصة للاستحمام المنزلي وإمدادات</t>
+          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>180.0 ر.س</t>
+          <t>130.0 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>24.5 ر.س</t>
+          <t>186.25 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>مضخة زجاجة مياه من كايبين، قابلة للطي، 3 اوضاع، 5 جالون، عبوة واحدة</t>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>29.99 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+          <t>بطارية بديلة لجيه بي ال لينك 10، 3.7 فولت/3600 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>11.24 ر.س</t>
+          <t>104.92 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>مضخة موزع مياه كهربائية محمولة لقوارير المياه بمضخات مزدوجة وقوة حصانية عالية ومخرجين للمياه، مزودة بواجهة شحن من النوع سي بمنفذ USB نوع سي، مناسبة للمكتب والمنزل والمطبخ من ار نيس، بلون أبيض</t>
+          <t>راوتر واي فاي 6 ثنائي النطاق AX3000 من تي بي لينك</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>49.3 ر.س</t>
+          <t>216.0 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>منفاخ هواء من يوماي أوتوماتيكي مع مضخة هواء بالون مصدر طاقة خارجي</t>
+          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>38.17 ر.س</t>
+          <t>105.94 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه كهربائية بشحن USB، مضخة مياه شرب محمولة متوافقة مع الزجاجات القياسية سعة 11 إلى 19 لتر، مناسبة للاستخدام في المنزل والمكتب وأساسية للتخييم من سكاي-تاتش</t>
+          <t>رييوبي رف بطارية 40 فولت من لينك STM819</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>21.97 ر.س</t>
+          <t>158.14 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>منفاخ هواء من جودتول يدوي مع مضخة و إبرة و فوهة و خرطوم مرن يدوي</t>
+          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>12.54 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+          <t>جهاز اختبار بطارية السيارة 12 فولت 24 فولت، واختبار تحميل البطارية وعرض تيار بدء التشغيل على البارد رقميا محلل تلقائي دقيق اداة تشخيص البطارية مناسب للشاحنات والدراجات النارية من اياكام (من 8 إلى 30</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>263.11 ر.س</t>
+          <t>75.34 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+          <t>وحدة تزويد طاقة تفاعلية 1000 فولت امبير من ارترونيك ارت، مزود طاقة غير منقطع 1000 فولت أمبير/600 واط، تنظيم جهد ايه في ار، موجة جيبية محاكاة، وظيفة التشغيل البارد، متوافق مع المولد</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>445.0 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+          <t>مضخة مياه باردة ومضخة تفريغ الهواء مصغرة اي كيه 1856 بتيار مستمر وبجهد 6 فولت الى 12 فولت ار385 من جيكفن</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>150.0 ر.س</t>
+          <t>38.0 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>جهاز اختبار رقمي اوتوماتيكي KW208 للبطارية بقوة 12 فولت / 100 -2000 امبير في درجات الحرارة الباردة للسيارة لاختبار المولد ونظام التشغيل والشحن مناسب للقوارب والدراجات البخارية والدفع الرباعي من كونوي</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>105.0 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+          <t>جهاز جي اف سي اي لاختبار جهد خرج المقبس الكهربائي من هابو تيست مع عرض الجهد الكهربي 90-250 فولت، إختبار أوتوماتيك للدارات الكهربائية وكشف القطبية والتسرب HT107E</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>157.41 ر.س</t>
+          <t>41.09 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
+          <t>محول جهد كهربائي 220 فولت الى 110 فولت، محول طاقة كهربائي، محول سفلي مع حماية من قاطع الدائرة الكهربائية القابلة لإعادة الضبط سهل التوصيل بمقابس الطاقة من هوماركت</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>119.0 ر.س</t>
+          <t>72.69 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
+          <t>لمبة من بونلوكس بتقنية LED بإضاءة أبيض دافئ و أبيض طبيعي و أبيض بارد، عبوة من قطعتين، بقوة 8 واط</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>79.96 ر.س</t>
+          <t>38.44 ر.س</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك محمول 20000 مللي امبير في الساعة 22.5 واط بحد أقصى 22.5 واط، شحن سريع USB نوع C، باور بانك نحيف مناسب للسفر، لايفون سلسلة 17/16، سامسونج S25/S24، هواوي، هونر والمزيد من انكر زولو</t>
+          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 220 فولت إلى تيار مستمر 12 فولت، محول بتيار 10 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>42.79 ر.س</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 500 فولت إلى تيار مستمر 12 فولت، محول بتيار 42 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>94.97 ر.س</t>
+          <t>101.8 ر.س</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+          <t>شاحن من ميتيكي بموصل دي سي برميلي، متوافق مع السماعات، بمنفذ واحد، 12 فولت 1 أمبير، قابس بريطاني</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>82.95 ر.س</t>
+          <t>19.97 ر.س</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
+          <t>جهاز اختبار بطارية السيارة طراز BT600 قدرة 12 فولت 24 فولت مع طابعة، قياس التيار عند التشغيل البارد 100 إلى 2000 من توبدون، شاشة ملونة 3.5 بوصة، كيبل 1.8 م، متوفر تحديث البرامج</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>171.0 ر.س</t>
+          <t>715.12 ر.س</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+          <t>بطارية اي-بلوك قابلة لإعادة الشحن 9 فولت من انسمان (قلوية، 17.5 × 26.5 × 48.5 ملم)</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>198.81 ر.س</t>
+          <t>9.99 ر.س</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>باور بانك محمول 30000 ميلي امبير في الساعة، شحن سريع 20 واط، بي دي 18 واط، كيو سي 3.0، يو اس بي سي مع 4 مخارج و3 مداخل متوافق مع ايفون وايباد وسامسونج وهواوي والتابلت والمزيد من في ار يو ار سي</t>
+          <t>محول جهد كهربائي 2000 واط، 3000 واط، 110/120 فولت الى 220/240 فولت، حماية قاطع الدائرة، للاستخدام المنزلي (2000 واط)</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>99.98 ر.س</t>
+          <t>400.0 ر.س</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+          <t>بطاريات سوبر قلوية بجهد عالي من جي بي، طراز 23A بقوة 12 فولت (عبوة مكونة من 5 بطاريات)</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>138.87 ر.س</t>
+          <t>22.69 ر.س</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من باوليفانت 50000 مللي امبير ليثيوم بوليمر 12 ساعة شحن USB نوع C كابل مدمج وشحن سريع للهواتف الذكية 10 منافذ أسود</t>
+          <t>ايكام جهاز تحكم اوتوماتيكي بمضخة 220 فولت بمستشعر مياه HT 60 4 4 ضغط منخفض لبدء التشغيل الساخن والبارد من النحاس الاصفر G1 2 انش للتحكم التلقائي في الصنبور</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>199.99 ر.س</t>
+          <t>41.99 ر.س</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>جهاز اختبار بطارية السيارة 12 فولت 24 فولت، واختبار تحميل البطارية وعرض تيار بدء التشغيل على البارد رقميا محلل تلقائي دقيق اداة تشخيص البطارية مناسب للشاحنات والدراجات النارية من اياكام (من 8 إلى 30</t>
+          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>75.34 ر.س</t>
+          <t>418.95 ر.س</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>وحدة تزويد طاقة تفاعلية 1000 فولت امبير من ارترونيك ارت، مزود طاقة غير منقطع 1000 فولت أمبير/600 واط، تنظيم جهد ايه في ار، موجة جيبية محاكاة، وظيفة التشغيل البارد، متوافق مع المولد</t>
+          <t>شاشة ألعاب VX2479A-HD-PRO، مقاس 24 بوصة، معدل تحديث 240 هرتز من فيوسونيك</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>445.0 ر.س</t>
+          <t>379.0 ر.س</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>جهاز اختبار رقمي اوتوماتيكي KW208 للبطارية بقوة 12 فولت / 100 -2000 امبير في درجات الحرارة الباردة للسيارة لاختبار المولد ونظام التشغيل والشحن مناسب للقوارب والدراجات البخارية والدفع الرباعي من كونوي</t>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>105.0 ر.س</t>
+          <t>445.78 ر.س</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه باردة ومضخة تفريغ الهواء مصغرة اي كيه 1856 بتيار مستمر وبجهد 6 فولت الى 12 فولت ار385 من جيكفن</t>
+          <t>شاشة ألعاب KTC مقاس 24 بوصة 240 هرتز ودقة FHD 1080P، لوحة IPS سريعة، تقنية</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>38.0 ر.س</t>
+          <t>549.99 ر.س</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>AUX نموذج عاكس هايبر كول بارد فقط 2 طن - 22000 وحدة حرارية بريطانية - كهربائي 220 فولت - 60 هرتز - 1 ساعة - واي فاي - وحدات داخلية وخارجية - ابيض - ATW24A2DI-CSA</t>
+          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>2521.16 ر.س</t>
+          <t>599.0 ر.س</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>جهاز اختبار بطارية السيارة طراز BT600 قدرة 12 فولت 24 فولت مع طابعة، قياس التيار عند التشغيل البارد 100 إلى 2000 من توبدون، شاشة ملونة 3.5 بوصة، كيبل 1.8 م، متوفر تحديث البرامج</t>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>715.12 ر.س</t>
+          <t>459.99 ر.س</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>لمبة من بونلوكس بتقنية LED بإضاءة أبيض دافئ و أبيض طبيعي و أبيض بارد، عبوة من قطعتين، بقوة 8 واط</t>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>38.44 ر.س</t>
+          <t>319.0 ر.س</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 500 فولت إلى تيار مستمر 12 فولت، محول بتيار 42 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>62.07 ر.س</t>
+          <t>617.0 ر.س</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>جهاز جي اف سي اي لاختبار جهد خرج المقبس الكهربائي من هابو تيست مع عرض الجهد الكهربي 90-250 فولت، إختبار أوتوماتيك للدارات الكهربائية وكشف القطبية والتسرب HT107E</t>
+          <t>شاشة العاب منحنية 24 بوصة 240 هرتز FHD 1080p 1500R 1 مللي ثانية ومزامنة تكيفية وتباين 3000:1 ودعم HDR وHDMI 2.0 ومنفذ طاقة 1.4 بضوء أزرق منخفض وإمالة فيسا H24S17P من كيه تي سي</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>41.09 ر.س</t>
+          <t>569.26 ر.س</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>محول جهد كهربائي 3000 واط 110 فولت/120 فولت/220 فولت/240 فولت من اليسم، محول طاقة تصاعدي / لأسفل مع حماية من قاطع الدائرة الكهربائية قابل لاعادة الضبط، مقبس عالمي مدمج للمنزل</t>
+          <t>شاشة ألعاب KTC مقاس 27 بوصة، معدل تحديث 240 هرتز، دقة FHD 1080 بكسل، لوحة IPS سريعة، تقنية مزامنة تكيفية وHDR، قاعدة قابلة لتعديل الارتفاع والدوران والإمالة، تدعم فيسا، منافذ HDMI/DP/USB، موديل H27F7</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>399.99 ر.س</t>
+          <t>667.0 ر.س</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>موزع مياه ساخن وبارد تحميل سفلي قائم على الارض 220-240 فولت مع ثلاجة من هوميكس - ابيض YLR-LW-2-5-100 باوند</t>
+          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>396.0 ر.س</t>
+          <t>899.99 ر.س</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>جهاز اختبار بطارية السيارة الرقمية وأداة تشخيص المولد من انسيل، سعة تحميل 100-2000 CCA، تحليل الشحن والتحريك للدراجة النارية والشاحنة والقارب والمركبة الترفيهية والبحرية وغيرها، 12 فولت، BA101</t>
+          <t>مبرد سائل من سلسلة انيرجلو من سودوكو</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>221.66 ر.س</t>
+          <t>265.24 ر.س</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>مكيف هواء 12 فولت تيار مستمر، مكيف سقف قابل للتطبيق على الشاحنات والمركبات الترفيهية والحافلات والحفارات والمخيمات والمركبات الزراعية، مكيف هواء 12 فولت يعمل على البارد والساخن 24 فولت</t>
+          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>1987.09 ر.س</t>
+          <t>499.0 ر.س</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>جهاز قياس الجهد الكهربائي المحمول ار سي دي المتقدم من موريليان، فاحص الخرج الكهربائي للتيار المتردد دون تلامس/ بشاشة عرض ال سي دي لاضاءة الخلفية، فاحص فولت ～ على شكل قلم مع مؤئر تنبيه</t>
+          <t>مبرد وحدة المعالجة المركزية بالماء فروزن نوتي 240 اسود ARGB من ثيرمال رايت، المواصفات: مراوح بي دبليو ام مزدوجة، محامل اس- اف دي بي الاصدار2، مناسب لـ AMD/AM4 AM5، انتل LGA 1700/1150/1151/1200/2011</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>63.27 ر.س</t>
+          <t>284.92 ر.س</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>ايكام جهاز تحكم اوتوماتيكي بمضخة 220 فولت بمستشعر مياه HT 60 4 4 ضغط منخفض لبدء التشغيل الساخن والبارد من النحاس الاصفر G1 2 انش للتحكم التلقائي في الصنبور</t>
+          <t>مبرد سائل لوحدة المعالجة المركزية 240 كور 2 من كولر ماستر، R9|U7|i7 بمضخة G9R مزدوجة ومرآة انفينيتي aRGB وأنبوب 40 سم ورادياتور 240 ملم ومروحة BWM 12 سم AMD رايزن AM5|4 انتل LGA 1851|1700</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>41.99 ر.س</t>
+          <t>399.0 ر.س</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>45.85 ر.س</t>
+          <t>88.74 ر.س</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>88.74 ر.س</t>
+          <t>36.47 ر.س</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>20.78 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>88.99 ر.س</t>
+          <t>35.98 ر.س</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>35.98 ر.س</t>
+          <t>88.99 ر.س</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>59.89 ر.س</t>
+          <t>75.88 ر.س</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>29.0 ر.س</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>75.88 ر.س</t>
+          <t>45.0 ر.س</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>79.96 ر.س</t>
+          <t>79.99 ر.س</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>39.17 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>45.0 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>جوي رووم شاحن سيارة صغير JR-CCN05 30 واط USB-A USB-C يوفر شحن سريع وآمن، يشحن جهازين في وقت واحد - اسود</t>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>24.99 ر.س</t>
+          <t>35.8 ر.س</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>88.0 ر.س</t>
+          <t>49.0 ر.س</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
@@ -3681,28 +3681,6 @@
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>35.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -57,17 +57,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-01</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -550,21 +550,21 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42.61 ر.س</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42.61 ر.س</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -585,94 +585,94 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>al3bor-telecom, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>35.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>225.43 ر.س</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>توصيلة جودا فولت لينك</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>توصيلات كهربائية</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>منتجات السيارة</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>179.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>179.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>توصيلة جودا فولت لينك</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>توصيلات كهربائية</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>منتجات السيارة</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>38.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>159.66 ر.س</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>806.02 ر.س</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>806.02 ر.س</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -690,129 +690,129 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>شاحن جودا فولت باد / VoltPad</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>شواحن جدارية</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>شاحن جودا فولت باد / VoltPad</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>شواحن جدارية</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>كيبل جودا 240 واط</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>كيابل شحن</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>aletawiksa, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>521.23 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>كيبل جودا 240 واط</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>كيابل شحن</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>شاحن سيارة جودا</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>شواحن سيارة</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>aletawiksa, amazon_sa</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>474.81 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>شاحن سيارة جودا</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>شواحن سيارة</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>29.0 ر.س</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>64.17 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>78.36 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>جودا - شاحن سمارت للبطاريات الذكيه AA\AAA</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>83.48 ر.س</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1621,17 +1621,17 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>جودا - بطارية بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>25.22 ر.س</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1643,17 +1643,17 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>جودا - كيبل تايب سي الى تايب سي سيليكون بقوة 60 واط بطول 1 متر - سماوي</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>16.52 ر.س</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1665,17 +1665,17 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>جودا - سلك قماشي تايب سي الى لايتنينق بقوة 60 واط بطول 1 متر - اسود</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>42.61 ر.س</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1687,17 +1687,17 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>جودا - شاحن جداري بقوة 20 واط بمنفذ تايب-سي - أسود</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>7.83 ر.س</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1709,17 +1709,17 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>جودا - شاحن جداري بقوة 20 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>42.61 ر.س</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -1731,17 +1731,17 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>مايكل جوردن</t>
+          <t>جودا - باور بانك NeoPower سعة 20000mAh بقوة 22.5 واط ومنفذين - أسود</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>39.99 ر.س</t>
+          <t>42.61 ر.س</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1753,154 +1753,154 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>198.81 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>باور بانك وشاحن محمول 20000 ميلي أمبير في الساعة مع كيبل USB-C مدمج وبطارية شحن سريع 87 واط لأجهزة ماك بوك وايفون 17/16 وسامسونج وسويتش وغيرها المزيد من انكر</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>189.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>باور بانك سينجي ميني 20 بطارية 20,000mAh، شحن بقدرة 15 واط، ثلاث منافذ (2 نوع سي + 1 USB نوع ايه)، مدمج وسهل الحمل متوافق مع جي-تاج، أسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك كيجو 20000 ميلي امبير في الساعة من جوي، أسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>شاحن محمول بقدرة 45 واط، أصغر باور بانك 20000 مللي امبير في الساعة مع كيبل USB-سي مدمج، شحن سريع USB نوع سي، شاحن جوال للسفر لايفون 16 15 سامسونج S25 S24 جوجل ايباد وغيرها من اي ان اي يو</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>129.99 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>jarir</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
+          <t>مايكل جوردن</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>61.99 ر.س</t>
+          <t>39.99 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>138.87 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>118.98 ر.س</t>
+          <t>189.0 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>باور بانك CP24 20000 مللي امبير في الساعة 40 واط سي سي سي مع كابلات مزدوجة</t>
+          <t>باور بانك سينجي ميني 20 بطارية 20,000mAh، شحن بقدرة 15 واط، ثلاث منافذ (2 نوع سي + 1 USB نوع ايه)، مدمج وسهل الحمل متوافق مع جي-تاج، أسود</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>باور بانك CP24 20000 مللي امبير في الساعة 40 واط سي سي سي مع كابلات مزدوجة</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>198.81 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
+          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>229.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
+          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>169.0 ر.س</t>
+          <t>61.99 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>شاحن محمول C سعة 20000 مللي أمبير، باور بانك 20K بمنفذ إدخال وإخراج نوع C ومنفذين A مع كيبل C إلى A مرفق لأجهزة ايفون وجالكسي وبيكسل وايباد وإيربودز والمزيد من بيلكن - رمادي سبيس</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>138.87 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>17.95 ر.س</t>
+          <t>118.98 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>11.96 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>7.48 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
+          <t>INIU Power Bank, 20000mAh 45W PD Fast Charging Small Portable Charger</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>13.5 ر.س</t>
+          <t>129.99 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>خلطة فيز 160 جم من هاريبو</t>
+          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>11.95 ر.س</t>
+          <t>229.0 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
+          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>11.25 ر.س</t>
+          <t>169.0 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
+          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>11.96 ر.س</t>
+          <t>169.0 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
+          <t>دار الأداب الهاربون والباقون</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>16.48 ر.س</t>
+          <t>94.74 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>حلوى بيريز من هاريبو، 160 جم</t>
+          <t>الهارب رواية اماراتية واقعية - خالد السلامي</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>12.95 ر.س</t>
+          <t>34.0 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلاتينية هاريبو جولد بيرز، 350 جم، عبوة من 5 قطع</t>
+          <t>روبوتايم 3 دي بازل هارب</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>8.99 ر.س</t>
+          <t>201.4 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
+          <t>وايلد ريبابليك لعبة قطيفة من بوكيت كينز ايكو هارب، حيوان محشو، 5 انش، مصنوعة من مواد معاد تدويرها، صديقة للبيئة</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>7.25 ر.س</t>
+          <t>67.72 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>7.5 ر.س</t>
+          <t>88.72 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>12.96 ر.س</t>
+          <t>69.83 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>حلوى بنكهة الكولا من هاريبو، وزن 250 جم</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>13.5 ر.س</t>
+          <t>324.96 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>13.5 ر.س</t>
+          <t>371.75 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>51.0 ر.س</t>
+          <t>35.0 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+          <t>سبيري حذاء قارب هاربون للرجال، لون بيج داكن، مقاس 11.5</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>359.1 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
+          <t>سبيري حذاء قارب هاربون للرجال</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>51.0 ر.س</t>
+          <t>343.64 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
+          <t>سبيري حذاء قارب للرجال من هاربون، بيج داكن، مقاس 42 EU</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>115.19 ر.س</t>
+          <t>299.76 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+          <t>سبيري حذاء هاربون على شكل قارب للرجال، كحلي، مقاس 42 EU</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>40.0 ر.س</t>
+          <t>279.86 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
+          <t>Sperry Mens Harpoon Crushback Slip on Sneaker</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>93.43 ر.س</t>
+          <t>374.89 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+          <t>سبيري حذاء قارب هاربون للرجال، رمادي، 8.5</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>130.0 ر.س</t>
+          <t>305.24 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>186.25 ر.س</t>
+          <t>263.11 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>182.8 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لجيه بي ال لينك 10، 3.7 فولت/3600 مللي امبير في الساعة من زوفكوس</t>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>104.92 ر.س</t>
+          <t>150.0 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>راوتر واي فاي 6 ثنائي النطاق AX3000 من تي بي لينك</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>216.0 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>105.94 ر.س</t>
+          <t>157.41 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>رييوبي رف بطارية 40 فولت من لينك STM819</t>
+          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>158.14 ر.س</t>
+          <t>119.0 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>79.96 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>جهاز اختبار بطارية السيارة 12 فولت 24 فولت، واختبار تحميل البطارية وعرض تيار بدء التشغيل على البارد رقميا محلل تلقائي دقيق اداة تشخيص البطارية مناسب للشاحنات والدراجات النارية من اياكام (من 8 إلى 30</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>75.34 ر.س</t>
+          <t>118.98 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>وحدة تزويد طاقة تفاعلية 1000 فولت امبير من ارترونيك ارت، مزود طاقة غير منقطع 1000 فولت أمبير/600 واط، تنظيم جهد ايه في ار، موجة جيبية محاكاة، وظيفة التشغيل البارد، متوافق مع المولد</t>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>445.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه باردة ومضخة تفريغ الهواء مصغرة اي كيه 1856 بتيار مستمر وبجهد 6 فولت الى 12 فولت ار385 من جيكفن</t>
+          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>38.0 ر.س</t>
+          <t>78.7 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>جهاز اختبار رقمي اوتوماتيكي KW208 للبطارية بقوة 12 فولت / 100 -2000 امبير في درجات الحرارة الباردة للسيارة لاختبار المولد ونظام التشغيل والشحن مناسب للقوارب والدراجات البخارية والدفع الرباعي من كونوي</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>105.0 ر.س</t>
+          <t>198.81 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>جهاز جي اف سي اي لاختبار جهد خرج المقبس الكهربائي من هابو تيست مع عرض الجهد الكهربي 90-250 فولت، إختبار أوتوماتيك للدارات الكهربائية وكشف القطبية والتسرب HT107E</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>41.09 ر.س</t>
+          <t>138.87 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>محول جهد كهربائي 220 فولت الى 110 فولت، محول طاقة كهربائي، محول سفلي مع حماية من قاطع الدائرة الكهربائية القابلة لإعادة الضبط سهل التوصيل بمقابس الطاقة من هوماركت</t>
+          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>72.69 ر.س</t>
+          <t>189.0 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>لمبة من بونلوكس بتقنية LED بإضاءة أبيض دافئ و أبيض طبيعي و أبيض بارد، عبوة من قطعتين، بقوة 8 واط</t>
+          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>38.44 ر.س</t>
+          <t>418.95 ر.س</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 220 فولت إلى تيار مستمر 12 فولت، محول بتيار 10 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
+          <t>ViewSonic VX2479A-HD-PRO 24” 240Hz Gaming Monitor</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>42.79 ر.س</t>
+          <t>379.0 ر.س</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 500 فولت إلى تيار مستمر 12 فولت، محول بتيار 42 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>101.8 ر.س</t>
+          <t>444.0 ر.س</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>شاحن من ميتيكي بموصل دي سي برميلي، متوافق مع السماعات، بمنفذ واحد، 12 فولت 1 أمبير، قابس بريطاني</t>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>19.97 ر.س</t>
+          <t>617.0 ر.س</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>جهاز اختبار بطارية السيارة طراز BT600 قدرة 12 فولت 24 فولت مع طابعة، قياس التيار عند التشغيل البارد 100 إلى 2000 من توبدون، شاشة ملونة 3.5 بوصة، كيبل 1.8 م، متوفر تحديث البرامج</t>
+          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>715.12 ر.س</t>
+          <t>599.0 ر.س</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>بطارية اي-بلوك قابلة لإعادة الشحن 9 فولت من انسمان (قلوية، 17.5 × 26.5 × 48.5 ملم)</t>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>9.99 ر.س</t>
+          <t>319.0 ر.س</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>محول جهد كهربائي 2000 واط، 3000 واط، 110/120 فولت الى 220/240 فولت، حماية قاطع الدائرة، للاستخدام المنزلي (2000 واط)</t>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>400.0 ر.س</t>
+          <t>459.99 ر.س</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>بطاريات سوبر قلوية بجهد عالي من جي بي، طراز 23A بقوة 12 فولت (عبوة مكونة من 5 بطاريات)</t>
+          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>22.69 ر.س</t>
+          <t>667.0 ر.س</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>ايكام جهاز تحكم اوتوماتيكي بمضخة 220 فولت بمستشعر مياه HT 60 4 4 ضغط منخفض لبدء التشغيل الساخن والبارد من النحاس الاصفر G1 2 انش للتحكم التلقائي في الصنبور</t>
+          <t>شاشة العاب منحنية 24 بوصة 240 هرتز FHD 1080p 1500R 1 مللي ثانية ومزامنة تكيفية وتباين 3000:1 ودعم HDR وHDMI 2.0 ومنفذ طاقة 1.4 بضوء أزرق منخفض وإمالة فيسا H24S17P من كيه تي سي</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>41.99 ر.س</t>
+          <t>569.26 ر.س</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>418.95 ر.س</t>
+          <t>899.99 ر.س</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب VX2479A-HD-PRO، مقاس 24 بوصة، معدل تحديث 240 هرتز من فيوسونيك</t>
+          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>379.0 ر.س</t>
+          <t>499.0 ر.س</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+          <t>KTC شاشة العاب منحنية 24 انش 240 هرتز، شاشة كمبيوتر FHD H24S17P</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>445.78 ر.س</t>
+          <t>529.99 ر.س</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب KTC مقاس 24 بوصة 240 هرتز ودقة FHD 1080P، لوحة IPS سريعة، تقنية</t>
+          <t>ساعة كوارتز وعرض أنالوج.</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>549.99 ر.س</t>
+          <t>84.27 ر.س</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
+          <t>بي كوايت مبرد مائي الكل في واحد 240 ملم من بيور لوب 3 لانظمة AMD/انتل كسر سرعة المعالج قليلا، 2X بيور وينجز 3 مراوح PWM عالية السرعة 120 ملم، ضغط ثابت عالي، مضخة PWM هادئة للغاية</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>599.0 ر.س</t>
+          <t>806.02 ر.س</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+          <t>شاحن من أنكر بتقنية USB، متوافق مع الهواتف المحمولة، بمنفذين من النوع C، بقدرة 30 واط لآيفون وسامسونج جالكسي وآيباد برو</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>459.99 ر.س</t>
+          <t>36.47 ر.س</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>319.0 ر.س</t>
+          <t>88.74 ر.س</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>617.0 ر.س</t>
+          <t>35.98 ر.س</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>شاشة العاب منحنية 24 بوصة 240 هرتز FHD 1080p 1500R 1 مللي ثانية ومزامنة تكيفية وتباين 3000:1 ودعم HDR وHDMI 2.0 ومنفذ طاقة 1.4 بضوء أزرق منخفض وإمالة فيسا H24S17P من كيه تي سي</t>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>569.26 ر.س</t>
+          <t>88.99 ر.س</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب KTC مقاس 27 بوصة، معدل تحديث 240 هرتز، دقة FHD 1080 بكسل، لوحة IPS سريعة، تقنية مزامنة تكيفية وHDR، قاعدة قابلة لتعديل الارتفاع والدوران والإمالة، تدعم فيسا، منافذ HDMI/DP/USB، موديل H27F7</t>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>667.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>899.99 ر.س</t>
+          <t>75.88 ر.س</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>مبرد سائل من سلسلة انيرجلو من سودوكو</t>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>265.24 ر.س</t>
+          <t>39.9 ر.س</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>499.0 ر.س</t>
+          <t>79.99 ر.س</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>مبرد وحدة المعالجة المركزية بالماء فروزن نوتي 240 اسود ARGB من ثيرمال رايت، المواصفات: مراوح بي دبليو ام مزدوجة، محامل اس- اف دي بي الاصدار2، مناسب لـ AMD/AM4 AM5، انتل LGA 1700/1150/1151/1200/2011</t>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>284.92 ر.س</t>
+          <t>45.0 ر.س</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>مبرد سائل لوحدة المعالجة المركزية 240 كور 2 من كولر ماستر، R9|U7|i7 بمضخة G9R مزدوجة ومرآة انفينيتي aRGB وأنبوب 40 سم ورادياتور 240 ملم ومروحة BWM 12 سم AMD رايزن AM5|4 انتل LGA 1851|1700</t>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>399.0 ر.س</t>
+          <t>29.0 ر.س</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>88.74 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة USB-C 30 واط بمنفذين من النوع C من انكر، شاحن سيارة لآيفون مع باور اي كيو 3.0، لآيفون 16/15/14/13/12 سلسلة سامسونج جالكسي S23/S22/S21، ايباد برو، ايربودز، هواوي والمزيد</t>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>36.47 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>49.0 ر.س</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
@@ -3452,235 +3452,15 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>35.98 ر.س</t>
+          <t>35.8 ر.س</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>88.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>75.88 ر.س</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>29.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>45.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>79.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>79.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة USB-C من انكر، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل للسحب، متوافق مع سلسلة ايفون 15/14، سامسونج S24/S23، ماك بوك برو/اير، ايباد، وغيرها من الأجهزة</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>35.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>49.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 16 و15 وسامسونج S25 وS24 بـ3 منافذ بقدرة 145 واط مع شحن سريع وكابل قابل للسحب وحماية متعددة</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>149.65 ر.س</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -57,17 +57,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-02</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -550,21 +550,21 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.61 ر.س</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>42.61 ر.س</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -585,21 +585,21 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>al3bor-telecom, amazon_sa</t>
+          <t>al3bor-telecom</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>35.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>225.43 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -609,70 +609,70 @@
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>توصيلة جودا فولت لينك</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>توصيلات كهربائية</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>806.02 ر.س</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>806.02 ر.س</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -690,21 +690,21 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>150.0 ر.س</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>150.0 ر.س</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -714,105 +714,105 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>شاحن جودا فولت باد / VoltPad</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>شواحن جدارية</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, iblackstores, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>512.21 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>شاحن سيارة جودا</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>شواحن سيارة</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>aletawiksa, amazon_sa</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>521.23 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>شاحن سيارة جودا</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>شواحن سيارة</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>29.0 ر.س</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>78.36 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>68.12 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن سمارت للبطاريات الذكيه AA\AAA</t>
+          <t>جودا - بطاريات AAA القابلة للشحن</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>83.48 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>جودا - بطارية بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
+          <t>جودا - منصة جودا بيك 4 منافذ تايب سي بقوة 240 واط - اسود</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>25.22 ر.س</t>
+          <t>298.99 ر.س</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>جودا - كيبل تايب سي الى تايب سي سيليكون بقوة 60 واط بطول 1 متر - سماوي</t>
+          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>16.52 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>جودا - سلك قماشي تايب سي الى لايتنينق بقوة 60 واط بطول 1 متر - اسود</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>42.61 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1687,17 +1687,17 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن جداري بقوة 20 واط بمنفذ تايب-سي - أسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>7.83 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1709,17 +1709,17 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن جداري بقوة 20 واط بمنفذ تايب سي - اسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>42.61 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -1731,17 +1731,17 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>جودا - باور بانك NeoPower سعة 20000mAh بقوة 22.5 واط ومنفذين - أسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>42.61 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1753,17 +1753,17 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1775,17 +1775,17 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1797,17 +1797,17 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>jarir</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>مايكل جوردن</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>39.99 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1819,88 +1819,88 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>418.95 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>ViewSonic VX2479A-HD-PRO 24” 240Hz Gaming Monitor</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>379.0 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>443.0 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>مايكل جوردن</t>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>39.99 ر.س</t>
+          <t>617.0 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>599.0 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>189.0 ر.س</t>
+          <t>459.99 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>باور بانك سينجي ميني 20 بطارية 20,000mAh، شحن بقدرة 15 واط، ثلاث منافذ (2 نوع سي + 1 USB نوع ايه)، مدمج وسهل الحمل متوافق مع جي-تاج، أسود</t>
+          <t>KTC 24 Inch 240Hz Curved Gaming Monitor, FHD 1080p 1500R 1ms Computer Monitor, Adaptive Sync, 3000:1 Contrast, HDR Support, HDMI 2.0 &amp; DP 1.4, Low Blue Light, Tilt, VESA, H24S17P</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>569.26 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>باور بانك CP24 20000 مللي امبير في الساعة 40 واط سي سي سي مع كابلات مزدوجة</t>
+          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>667.0 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>198.81 ر.س</t>
+          <t>389.0 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
+          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>899.99 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
+          <t>KTC شاشة العاب منحنية 24 انش 240 هرتز، شاشة كمبيوتر FHD H24S17P</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>61.99 ر.س</t>
+          <t>529.99 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor H27F7</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>138.87 ر.س</t>
+          <t>699.99 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>ساعة من كاسيو للجنسين بشاشة أنالوج و ديجيتال موديل ايه كيو-240</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>118.98 ر.س</t>
+          <t>329.21 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>ساعة كاسيو</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+          <t>بي كوايت مبرد مائي الكل في واحد 240 ملم من بيور لوب 3 لانظمة AMD/انتل كسر سرعة المعالج قليلا، 2X بيور وينجز 3 مراوح PWM عالية السرعة 120 ملم، ضغط ثابت عالي، مضخة PWM هادئة للغاية</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>806.02 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>INIU Power Bank, 20000mAh 45W PD Fast Charging Small Portable Charger</t>
+          <t>شاحن من أنكر بتقنية USB، متوافق مع الهواتف المحمولة، بمنفذين من النوع C، بقدرة 30 واط لآيفون وسامسونج جالكسي وآيباد برو</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>129.99 ر.س</t>
+          <t>36.47 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>229.0 ر.س</t>
+          <t>88.74 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000</t>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>169.0 ر.س</t>
+          <t>35.98 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>169.0 ر.س</t>
+          <t>88.99 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>دار الأداب الهاربون والباقون</t>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>94.74 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>الهارب رواية اماراتية واقعية - خالد السلامي</t>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>34.0 ر.س</t>
+          <t>79.96 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>روبوتايم 3 دي بازل هارب</t>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>201.4 ر.س</t>
+          <t>75.88 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>وايلد ريبابليك لعبة قطيفة من بوكيت كينز ايكو هارب، حيوان محشو، 5 انش، مصنوعة من مواد معاد تدويرها، صديقة للبيئة</t>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>67.72 ر.س</t>
+          <t>39.9 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>88.72 ر.س</t>
+          <t>29.0 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>69.83 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>324.96 ر.س</t>
+          <t>45.0 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>371.75 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>35.0 ر.س</t>
+          <t>35.8 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء قارب هاربون للرجال، لون بيج داكن، مقاس 11.5</t>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>359.1 ر.س</t>
+          <t>49.0 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,1005 +2462,15 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء قارب هاربون للرجال</t>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 16 و15 وسامسونج S25 وS24 بـ3 منافذ بقدرة 145 واط مع شحن سريع وكابل قابل للسحب وحماية متعددة</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>343.64 ر.س</t>
+          <t>149.65 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>سبيري حذاء قارب للرجال من هاربون، بيج داكن، مقاس 42 EU</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>299.76 ر.س</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>سبيري حذاء هاربون على شكل قارب للرجال، كحلي، مقاس 42 EU</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>279.86 ر.س</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>Sperry Mens Harpoon Crushback Slip on Sneaker</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>374.89 ر.س</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>سبيري حذاء قارب هاربون للرجال، رمادي، 8.5</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>305.24 ر.س</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>263.11 ر.س</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>182.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>150.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>139.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>157.41 ر.س</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>119.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>79.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>118.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>109.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>78.7 ر.س</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>198.81 ر.س</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>138.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>189.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>418.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>ViewSonic VX2479A-HD-PRO 24” 240Hz Gaming Monitor</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>379.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>444.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>617.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>599.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>319.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>459.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>667.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب منحنية 24 بوصة 240 هرتز FHD 1080p 1500R 1 مللي ثانية ومزامنة تكيفية وتباين 3000:1 ودعم HDR وHDMI 2.0 ومنفذ طاقة 1.4 بضوء أزرق منخفض وإمالة فيسا H24S17P من كيه تي سي</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>569.26 ر.س</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>899.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>499.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>KTC شاشة العاب منحنية 24 انش 240 هرتز، شاشة كمبيوتر FHD H24S17P</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>529.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>ساعة كوارتز وعرض أنالوج.</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>84.27 ر.س</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>بي كوايت مبرد مائي الكل في واحد 240 ملم من بيور لوب 3 لانظمة AMD/انتل كسر سرعة المعالج قليلا، 2X بيور وينجز 3 مراوح PWM عالية السرعة 120 ملم، ضغط ثابت عالي، مضخة PWM هادئة للغاية</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>806.02 ر.س</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بتقنية USB، متوافق مع الهواتف المحمولة، بمنفذين من النوع C، بقدرة 30 واط لآيفون وسامسونج جالكسي وآيباد برو</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>36.47 ر.س</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>88.74 ر.س</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>35.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>88.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>59.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>75.88 ر.س</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>39.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>79.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>45.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>29.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>79.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>49.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>35.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-03</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-04</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>806.02 ر.س</t>
+          <t>38.0 ر.س</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>806.02 ر.س</t>
+          <t>38.0 ر.س</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>512.21 ر.س</t>
+          <t>463.06 ر.س</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -784,35 +784,35 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>29.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>68.12 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>aletawiksa</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>69.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>69.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1824,12 +1824,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>418.95 ر.س</t>
+          <t>17.95 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>ViewSonic VX2479A-HD-PRO 24” 240Hz Gaming Monitor</t>
+          <t>حلوى شامالو روبينو مارشميلو من هاريبو، 70 جم</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>379.0 ر.س</t>
+          <t>7.95 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+          <t>خلطة فيز 160 جم من هاريبو</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>443.0 ر.س</t>
+          <t>11.95 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>617.0 ر.س</t>
+          <t>7.5 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
+          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>599.0 ر.س</t>
+          <t>11.95 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>459.99 ر.س</t>
+          <t>13.5 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>KTC 24 Inch 240Hz Curved Gaming Monitor, FHD 1080p 1500R 1ms Computer Monitor, Adaptive Sync, 3000:1 Contrast, HDR Support, HDMI 2.0 &amp; DP 1.4, Low Blue Light, Tilt, VESA, H24S17P</t>
+          <t>هاريبو جولد بيرز، 150 غرام، عبوة من قطعة واحدة</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>569.26 ر.س</t>
+          <t>9.44 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
+          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>667.0 ر.س</t>
+          <t>11.25 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>389.0 ر.س</t>
+          <t>17.0 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
+          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>899.99 ر.س</t>
+          <t>7.95 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>KTC شاشة العاب منحنية 24 انش 240 هرتز، شاشة كمبيوتر FHD H24S17P</t>
+          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>529.99 ر.س</t>
+          <t>11.95 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor H27F7</t>
+          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>699.99 ر.س</t>
+          <t>7.5 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>ساعة من كاسيو للجنسين بشاشة أنالوج و ديجيتال موديل ايه كيو-240</t>
+          <t>حلوى بيريز من هاريبو، 160 جم</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>329.21 ر.س</t>
+          <t>13.35 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>ساعة كاسيو</t>
+          <t>هاريبو جولد بيرز 160 جرام</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>11.95 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>بي كوايت مبرد مائي الكل في واحد 240 ملم من بيور لوب 3 لانظمة AMD/انتل كسر سرعة المعالج قليلا، 2X بيور وينجز 3 مراوح PWM عالية السرعة 120 ملم، ضغط ثابت عالي، مضخة PWM هادئة للغاية</t>
+          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>806.02 ر.س</t>
+          <t>12.96 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>شاحن من أنكر بتقنية USB، متوافق مع الهواتف المحمولة، بمنفذين من النوع C، بقدرة 30 واط لآيفون وسامسونج جالكسي وآيباد برو</t>
+          <t>جهاز اختبار رقمي اوتوماتيكي KW208 للبطارية بقوة 12 فولت / 100 -2000 امبير في درجات الحرارة الباردة للسيارة لاختبار المولد ونظام التشغيل والشحن مناسب للقوارب والدراجات البخارية والدفع الرباعي من كونوي</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>36.47 ر.س</t>
+          <t>105.0 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+          <t>وحدة تزويد طاقة تفاعلية 1000 فولت امبير من ارترونيك ارت، مزود طاقة غير منقطع 1000 فولت أمبير/600 واط، تنظيم جهد ايه في ار، موجة جيبية محاكاة، وظيفة التشغيل البارد، متوافق مع المولد</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>88.74 ر.س</t>
+          <t>445.0 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+          <t>مضخة مياه باردة ومضخة تفريغ الهواء مصغرة اي كيه 1856 بتيار مستمر وبجهد 6 فولت الى 12 فولت ار385 من جيكفن</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>35.98 ر.س</t>
+          <t>38.0 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+          <t>جهاز اختبار بطارية السيارة الرقمية وأداة تشخيص المولد من انسيل، سعة تحميل 100-2000 CCA، تحليل الشحن والتحريك للدراجة النارية والشاحنة والقارب والمركبة الترفيهية والبحرية وغيرها، 12 فولت، BA101</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>88.99 ر.س</t>
+          <t>221.66 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+          <t>لمبة من بونلوكس بتقنية LED بإضاءة أبيض دافئ و أبيض طبيعي و أبيض بارد، عبوة من قطعتين، بقوة 8 واط</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>38.44 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+          <t>Homarket 220V To 110V Voltage Converter,Electrical Power Transformer,Down Transformer Converter with Resettable Circuit Breaker Protection, Universal Socket</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>79.96 ر.س</t>
+          <t>72.69 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+          <t>موزع ماء ساخن وبارد بتصميم قائم على الأرض وسعة 16 لتر من نيكاي، بدون ثلاجة للتخزين، NWD1209TK</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>75.88 ر.س</t>
+          <t>255.0 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+          <t>جهاز اختبار بطارية السيارة طراز BT600 قدرة 12 فولت 24 فولت مع طابعة، قياس التيار عند التشغيل البارد 100 إلى 2000 من توبدون، شاشة ملونة 3.5 بوصة، كيبل 1.8 م، متوفر تحديث البرامج</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>39.9 ر.س</t>
+          <t>703.63 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+          <t>جهاز اختبار بطارية السيارة KW218 6 فولت 12 فولت 100-2000 سي سي ايه، جهاز اختبار تحميل بطارية السيارة ونظام شحن التحريك، محلل بطارية رقمي تلقائي للسيارة والشاحنات والدراجات النارية والقارب</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>29.0 ر.س</t>
+          <t>115.0 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
+          <t>محول جهد كهربائي 300W، 110V و120V و220V و240V، محول طاقة تصاعدي وتنازلي مع حماية من قاطع الدائرة الكهربائية قابلة لإعادة الضبط ومقبس عالمي مدمج للمنزل</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>159.99 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+          <t>محول جهد كهربائي اس تي 3000 واط 110 فولت/120 فولت/220 فولت/240 فولت، محول كهربائي لاعلى/اسفل، مع حماية قاطع دائرة كهربائية قابلة لاعادة الضبط، مقبس عالمي صغير الحجم</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>45.0 ر.س</t>
+          <t>499.99 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+          <t>شاحن من زوي بمنفذ USB لأجهزة 12 فولت 3 أمبير 36 واط، 8 منافذ، 10 واط، مع حماية من الجهد الزائد والتيار الزائد والدائرة القصيرة</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>24.99 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+          <t>محول طاقة 12 فولت 60 واط لشريط اضاءة LED ونظام كاميرا المراقبة سي سي تي في، محول جهد عالمي بتيار متردد وتيار مستمر قابل للتعديل 5 امبير</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>35.8 ر.س</t>
+          <t>42.26 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+          <t>بطارية اي-بلوك قابلة لإعادة الشحن 9 فولت من انسمان (قلوية، 17.5 × 26.5 × 48.5 ملم)</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>49.0 ر.س</t>
+          <t>9.99 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,15 +2462,345 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 16 و15 وسامسونج S25 وS24 بـ3 منافذ بقدرة 145 واط مع شحن سريع وكابل قابل للسحب وحماية متعددة</t>
+          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 220 فولت إلى تيار مستمر 12 فولت، محول بتيار 10 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>149.65 ر.س</t>
+          <t>46.5 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>ViewSonic VX2479A-HD-PRO 24” 240Hz Gaming Monitor</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>379.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>441.76 ر.س</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>617.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>599.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>489.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>شاشة من زد زد-ايدج عدد 1 LED بدقة 1920 × 1080 لون أسود</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>629.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>KTC 24 Inch 240Hz Curved Gaming Monitor, FHD 1080p 1500R 1ms Computer Monitor, Adaptive Sync, 3000:1 Contrast, HDR Support, HDMI 2.0 &amp; DP 1.4, Low Blue Light, Tilt, VESA, H24S17P</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>569.26 ر.س</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب منحنية 27 بوصة بدقة FHD 1080p 240Hz، لوحة IPS، وقت استجابة 0.5 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر، بدون إطار من ثلاث جهات، نحيفة للغاية، 100% sRGB، فلتر بلو لايت، DP، HDMI من فيوفيجن</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>529.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>389.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>667.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>899.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>مبرد سائل من سلسلة انيرجلو من سودوكو</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>265.24 ر.س</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>مبرد وحدة المعالجة المركزية اكوا اليت 240 V3 صف تبريد سائل بإضاءة ARGB ومراوح PWM مناسب لـ انتل LGA1150/1151/1155/1156/1200/2011/1700,AMD:AM4/AM5 من ثيرمال رايت، مبرد كمبيوتر ايه اي او، لون أبيض</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>245.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-04</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -644,35 +644,35 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>38.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>38.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, iblackstores, amazon_sa</t>
+          <t>aletawiksa, iblackstores</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>463.06 ر.س</t>
+          <t>194.0 ر.س</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
+          <t>سلك جودا من تايب سي الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز بدقة 4K بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
+          <t>سلك جودا من HDMI الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز 4K بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>شاحن جداري GaN VOLTDOCK 45 بقدرة 45 واط بمنفذ تايب سيمع سلك قابل للسحب مدمج تايب سي - أسود</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>سلك تايب سي الى تايب سي BEACON 100 مضيء جودا سيليكون نايلون مظفر بقوة 100 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
+          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
+          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>209.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
+          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
+          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
+          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
+          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>349.0 ر.س</t>
+          <t>209.0 ر.س</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
+          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>49.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
+          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>349.0 ر.س</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
+          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
+          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
+          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>49.0 ر.س</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
+          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
+          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - موف</t>
+          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - أخضر</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 تايب سي تايب سي سليكون 60 واط 1 متر - سماوي</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>سلك JODA ماج رول مغناطيسي بقوة 60 واط تايب سي الى تايب سي بطول 1.2 متر - كحلي</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1813,996 +1813,6 @@
       <c r="D46" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>17.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>حلوى شامالو روبينو مارشميلو من هاريبو، 70 جم</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>7.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>خلطة فيز 160 جم من هاريبو</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>11.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>7.5 ر.س</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>11.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>13.5 ر.س</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>هاريبو جولد بيرز، 150 غرام، عبوة من قطعة واحدة</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>9.44 ر.س</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>11.25 ر.س</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>17.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>7.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>11.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>7.5 ر.س</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>حلوى بيريز من هاريبو، 160 جم</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>13.35 ر.س</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>هاريبو جولد بيرز 160 جرام</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>11.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>12.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>جهاز اختبار رقمي اوتوماتيكي KW208 للبطارية بقوة 12 فولت / 100 -2000 امبير في درجات الحرارة الباردة للسيارة لاختبار المولد ونظام التشغيل والشحن مناسب للقوارب والدراجات البخارية والدفع الرباعي من كونوي</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>105.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>وحدة تزويد طاقة تفاعلية 1000 فولت امبير من ارترونيك ارت، مزود طاقة غير منقطع 1000 فولت أمبير/600 واط، تنظيم جهد ايه في ار، موجة جيبية محاكاة، وظيفة التشغيل البارد، متوافق مع المولد</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>445.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه باردة ومضخة تفريغ الهواء مصغرة اي كيه 1856 بتيار مستمر وبجهد 6 فولت الى 12 فولت ار385 من جيكفن</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>38.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>جهاز اختبار بطارية السيارة الرقمية وأداة تشخيص المولد من انسيل، سعة تحميل 100-2000 CCA، تحليل الشحن والتحريك للدراجة النارية والشاحنة والقارب والمركبة الترفيهية والبحرية وغيرها، 12 فولت، BA101</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>221.66 ر.س</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>لمبة من بونلوكس بتقنية LED بإضاءة أبيض دافئ و أبيض طبيعي و أبيض بارد، عبوة من قطعتين، بقوة 8 واط</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>38.44 ر.س</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>Homarket 220V To 110V Voltage Converter,Electrical Power Transformer,Down Transformer Converter with Resettable Circuit Breaker Protection, Universal Socket</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>72.69 ر.س</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>موزع ماء ساخن وبارد بتصميم قائم على الأرض وسعة 16 لتر من نيكاي، بدون ثلاجة للتخزين، NWD1209TK</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>255.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>جهاز اختبار بطارية السيارة طراز BT600 قدرة 12 فولت 24 فولت مع طابعة، قياس التيار عند التشغيل البارد 100 إلى 2000 من توبدون، شاشة ملونة 3.5 بوصة، كيبل 1.8 م، متوفر تحديث البرامج</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>703.63 ر.س</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>جهاز اختبار بطارية السيارة KW218 6 فولت 12 فولت 100-2000 سي سي ايه، جهاز اختبار تحميل بطارية السيارة ونظام شحن التحريك، محلل بطارية رقمي تلقائي للسيارة والشاحنات والدراجات النارية والقارب</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>115.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>محول جهد كهربائي 300W، 110V و120V و220V و240V، محول طاقة تصاعدي وتنازلي مع حماية من قاطع الدائرة الكهربائية قابلة لإعادة الضبط ومقبس عالمي مدمج للمنزل</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>159.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>محول جهد كهربائي اس تي 3000 واط 110 فولت/120 فولت/220 فولت/240 فولت، محول كهربائي لاعلى/اسفل، مع حماية قاطع دائرة كهربائية قابلة لاعادة الضبط، مقبس عالمي صغير الحجم</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>499.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من زوي بمنفذ USB لأجهزة 12 فولت 3 أمبير 36 واط، 8 منافذ، 10 واط، مع حماية من الجهد الزائد والتيار الزائد والدائرة القصيرة</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>24.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>محول طاقة 12 فولت 60 واط لشريط اضاءة LED ونظام كاميرا المراقبة سي سي تي في، محول جهد عالمي بتيار متردد وتيار مستمر قابل للتعديل 5 امبير</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>42.26 ر.س</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>بطارية اي-بلوك قابلة لإعادة الشحن 9 فولت من انسمان (قلوية، 17.5 × 26.5 × 48.5 ملم)</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>9.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>محول بمفتاح منظم، محول للكهرباء من تيار متردد 220 فولت إلى تيار مستمر 12 فولت، محول بتيار 10 امبير وجهد 120 واط لاشرطة الاضاءة والكاميرا والكمبيوتر وجهاز العرض والراديو من موريليان</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>46.5 ر.س</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>499.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>ViewSonic VX2479A-HD-PRO 24” 240Hz Gaming Monitor</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>379.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>441.76 ر.س</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>617.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>599.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>489.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>شاشة من زد زد-ايدج عدد 1 LED بدقة 1920 × 1080 لون أسود</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>629.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>KTC 24 Inch 240Hz Curved Gaming Monitor, FHD 1080p 1500R 1ms Computer Monitor, Adaptive Sync, 3000:1 Contrast, HDR Support, HDMI 2.0 &amp; DP 1.4, Low Blue Light, Tilt, VESA, H24S17P</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>569.26 ر.س</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب منحنية 27 بوصة بدقة FHD 1080p 240Hz، لوحة IPS، وقت استجابة 0.5 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر، بدون إطار من ثلاث جهات، نحيفة للغاية، 100% sRGB، فلتر بلو لايت، DP، HDMI من فيوفيجن</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>529.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>389.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>667.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>899.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>مبرد سائل من سلسلة انيرجلو من سودوكو</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>265.24 ر.س</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>مبرد وحدة المعالجة المركزية اكوا اليت 240 V3 صف تبريد سائل بإضاءة ARGB ومراوح PWM مناسب لـ انتل LGA1150/1151/1155/1156/1200/2011/1700,AMD:AM4/AM5 من ثيرمال رايت، مبرد كمبيوتر ايه اي او، لون أبيض</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>245.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>499.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-05</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -644,70 +644,70 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>11.32 ر.س</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>38.04 ر.س</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -760,59 +760,59 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, iblackstores, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>471.17 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>شاحن سيارة جودا</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>شواحن سيارة</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa, iblackstores</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>194.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>شاحن سيارة جودا</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>شواحن سيارة</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>69.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>69.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>28.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>81.21 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1816,6 +1816,1942 @@
         </is>
       </c>
     </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>jarir</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Jarir Reader</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>19.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>بحث تقديري</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>139.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>94.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>188.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>61.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>198.82 ر.س</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك سينجي ميني 20 بطارية 20,000mAh، شحن بقدرة 15 واط، ثلاث منافذ (2 نوع سي + 1 USB نوع ايه)، مدمج وسهل الحمل متوافق مع جي-تاج، أسود</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>138.87 ر.س</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>229.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>128.14 ر.س</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>INIU Power Bank, 20000mAh 45W PD Fast Charging Small Portable Charger</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>149.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك CP24 20000 مللي امبير في الساعة 40 واط سي سي سي مع كابلات مزدوجة</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>161.64 ر.س</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يوجرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب A مع شحن سريع وحماية للهاتف واللابتوب 3 منافذ</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>178.86 ر.س</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>99.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>178.94 ر.س</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>51.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>51.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>114.62 ر.س</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>40.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>186.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>93.43 ر.س</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>130.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>محول تيار مستمر 12 فولت/24 فولت الى 48 فولت من لينك جير لستارلينك ميني - محول جهد 96 واط مع حماية من الماء IP67 - منزل متنقل قارب سيارة تخييم (مع كيبل او مقبس) (مقبس (كيبل قابس)</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>178.49 ر.س</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك موزع USB 3.0 مايكرو بي 7 منافذ مع محول طاقة 12 فولت/2.5 امبير وكابل USB 3.0 بطول 1 متر، شحن سريع 1.5 امبير، سرعة نقل بيانات 10 مرات، متوافق مع ويندوز وماك او اس اكس ولينكس (UH700)، اسود</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>136.56 ر.س</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>105.83 ر.س</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>115.65 ر.س</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>رييوبي رف بطارية 40 فولت من لينك STM819</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>158.14 ر.س</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>20.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>13.1 ر.س</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>20.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>148.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>19.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>11.32 ر.س</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>24.5 ر.س</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>مضخة زجاجة مياه من كايبين، قابلة للطي، 3 اوضاع، 5 جالون، عبوة واحدة</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>34.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه محمولة، موزع مياه كهربائي عالمي سعة 19 لتر مع مفتاح تشغيل وشحن USB، للتخييم والمطبخ وورشة العمل والمرأب من كوفونج (لون أبيض، عبوة من قطعة واحدة)</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>19.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>مضخة تعزيز ضغط المياه، مضخة اوتوماتيك بجهد 24 فولت لتعزيز ضغط دش الاستحمام، مضخة مياه منزلية قابلة للحمل بقوة 150 واط بمفتاح تدفق للحمام والمطبخ والمرحاض والحديقة من بيرفورلد</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>119.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>مضخة موزع مياه من لوازم بتصميم حديث، براد ماء بشكل مستدير، مصنوع من ستانلس ستيل وبلاستيك، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>17.6 ر.س</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>15.16 ر.س</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>39.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>مضخة توزيع مياه كهربائية أوتوماتيكية مع منفذ USB، محمولة وسهلة الاستخدام، للتثبيت أعلى الجالون لزجاجات المياه بسعة من 7.5 إلى 19 لتر، قابلة لإعادة الشحن، للاستخدام في المنزل أو المكتب من مومنت، أبيض</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>16.61 ر.س</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>263.11 ر.س</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>182.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>141.67 ر.س</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>139.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>79.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>128.14 ر.س</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>89.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Anker Power Bank, 25,000mAh 165W Total Output Portable Charger for Laptops</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>291.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>94.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>159.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>78.7 ر.س</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>188.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>449.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>ViewSonic VX2479A-HD-PRO 24” 240Hz Gaming Monitor</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>399.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>549.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>474.78 ر.س</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>422.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>شاشة الألعاب الاحترافية UG25I بحجم 24.5 بوصة - 240Hz/1ms/فري سينك بريميوم - دقة وضوح FHD (1920x1080) - تصميم بدون إطار - تدعم DP و HDMI من زد ايدج</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>465.49 ر.س</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>389.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>617.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>KTC 24 Inch 240Hz Curved Gaming Monitor, FHD 1080p 1500R 1ms Computer Monitor, Adaptive Sync, 3000:1 Contrast, HDR Support, HDMI 2.0 &amp; DP 1.4, Low Blue Light, Tilt, VESA, H24S17P</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>569.26 ر.س</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>667.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>789.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>مبرد سائل من سلسلة انيرجلو من سودوكو</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>265.24 ر.س</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>KTC شاشة العاب منحنية 24 انش 240 هرتز، شاشة كمبيوتر FHD H24S17P</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>529.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>ساعة من كاسيو للجنسين بشاشة أنالوج و ديجيتال موديل ايه كيو-240</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>329.21 ر.س</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بتقنية USB، متوافق مع الهواتف المحمولة، بمنفذين من النوع C، بقدرة 30 واط لآيفون وسامسونج جالكسي وآيباد برو</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>36.47 ر.س</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>88.74 ر.س</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>46.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>59.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>39.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>75.87 ر.س</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>39.17 ر.س</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>28.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>48.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>129.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>35.79 ر.س</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من توكي بمنفذ USB متوافق مع ايفون 17/16/15 وسامسونج S26/S25 وايباد، 3 منافذ، 100 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>62.1 ر.س</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-06</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>11.32 ر.س</t>
+          <t>13.1 ر.س</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>38.04 ر.س</t>
+          <t>41.8 ر.س</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, iblackstores, amazon_sa</t>
+          <t>aletawiksa, iblackstores</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>471.17 ر.س</t>
+          <t>194.0 ر.س</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>28.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>81.21 ر.س</t>
+          <t>109.5 ر.س</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -873,17 +873,17 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>mokab</t>
+          <t>aletawiksa</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>اوتلت مكعب</t>
+          <t>اكسسوارات ايفون 18</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>29.0 ر.س</t>
+          <t>9.0 ر.س</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -895,17 +895,17 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>mokab</t>
+          <t>aletawiksa</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>اوتلت مكعب</t>
+          <t>اكسسوارات ايفون 18</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>5.0 ر.س</t>
+          <t>9.0 ر.س</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>اكسسوارات ايفون 18</t>
+          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>9.0 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>اكسسوارات ايفون 18</t>
+          <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>9.0 ر.س</t>
+          <t>119.0 ر.س</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
+          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
+          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>119.0 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
+          <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1027,17 +1027,17 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>aletawiksa</t>
+          <t>al3bor-telecom</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
+          <t>سلك جودا SLIP60 سيليكون 60 واط تايب سي الى تايب سي 1 متر - وردي غامق</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1049,17 +1049,17 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>aletawiksa</t>
+          <t>al3bor-telecom</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>سلك جودا من تايب سي الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز بدقة 4K بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 سيليكون 60 واط تايب سي الى تايب سي 1 متر - وردي غامق</t>
+          <t>سلك جودا من HDMI الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز 4K بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا من تايب سي الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز بدقة 4K بطول 2 متر - اسود</t>
+          <t>شاحن جداري GaN VOLTDOCK 45 بقدرة 45 واط بمنفذ تايب سيمع سلك قابل للسحب مدمج تايب سي - أسود</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا من HDMI الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز 4K بطول 2 متر - اسود</t>
+          <t>سلك تايب سي الى تايب سي BEACON 100 مضيء جودا سيليكون نايلون مظفر بقوة 100 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري GaN VOLTDOCK 45 بقدرة 45 واط بمنفذ تايب سيمع سلك قابل للسحب مدمج تايب سي - أسود</t>
+          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>سلك تايب سي الى تايب سي BEACON 100 مضيء جودا سيليكون نايلون مظفر بقوة 100 واط بطول 1.2 متر - ابيض</t>
+          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
+          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
+          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>209.0 ر.س</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>209.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
+          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
+          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>349.0 ر.س</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
+          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
+          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>349.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
+          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>49.0 ر.س</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
+          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
+          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>49.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
+          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -1555,44 +1555,44 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>al3bor-telecom</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
+          <t>جودا - بطاريات AAA القابلة للشحن</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>al3bor-telecom</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
+          <t>جودا - منصة جودا بيك 4 منافذ تايب سي بقوة 240 واط - اسود</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>298.99 ر.س</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>جودا - بطاريات AAA القابلة للشحن</t>
+          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>جودا - منصة جودا بيك 4 منافذ تايب سي بقوة 240 واط - اسود</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>298.99 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1643,17 +1643,17 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>58.99 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1665,17 +1665,17 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -1731,17 +1731,17 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1753,17 +1753,17 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>jarir</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>مايكل جوردن</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>39.99 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1775,17 +1775,17 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>jarir</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>Jarir Reader</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>19.99 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1797,44 +1797,44 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>مايكل جوردن</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>39.99 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Jarir Reader</t>
+          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>19.99 ر.س</t>
+          <t>188.99 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
@@ -1846,12 +1846,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>94.96 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>باور بانك CP24 20000 مللي امبير في الساعة 40 واط سي سي سي مع كابلات مزدوجة</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>94.96 ر.س</t>
+          <t>161.64 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
+          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>188.99 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>198.82 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>198.82 ر.س</t>
+          <t>138.87 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>باور بانك سينجي ميني 20 بطارية 20,000mAh، شحن بقدرة 15 واط، ثلاث منافذ (2 نوع سي + 1 USB نوع ايه)، مدمج وسهل الحمل متوافق مع جي-تاج، أسود</t>
+          <t>INIU Power Bank, 20000mAh 45W PD Fast Charging Small Portable Charger</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>134.99 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+          <t>باور بانك سينجي ميني 20 بطارية 20,000mAh، شحن بقدرة 15 واط، ثلاث منافذ (2 نوع سي + 1 USB نوع ايه)، مدمج وسهل الحمل متوافق مع جي-تاج، أسود</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>138.87 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>INIU Power Bank, 20000mAh 45W PD Fast Charging Small Portable Charger</t>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>149.99 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>باور بانك CP24 20000 مللي امبير في الساعة 40 واط سي سي سي مع كابلات مزدوجة</t>
+          <t>Anker Zolo Power Bank, 20,000mAh 22.5W Max Portable Charger, USB-C In and Out Fast Charging, Slim Travel Essential Phone Power Bank, For iPhone 17/16 Series, Samsung S25/S24, Huawei, Honor and More</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>161.64 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب A مع شحن سريع وحماية للهاتف واللابتوب 3 منافذ</t>
+          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>178.86 ر.س</t>
+          <t>169.0 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>178.94 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>51.0 ر.س</t>
+          <t>13.1 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>13.14 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
+          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>51.0 ر.س</t>
+          <t>148.0 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>114.62 ر.س</t>
+          <t>13.75 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>40.0 ر.س</t>
+          <t>24.5 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>186.25 ر.س</t>
+          <t>49.3 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
+          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>93.43 ر.س</t>
+          <t>29.0 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+          <t>مضخة مياه بسعة 5 جالون من كوزي تشارم، موزع مياه كهربائي محمول مع شحن USB نوع سي، محرك مزدوج، تدفق سريع، مثالي للمنزل والمكتب والتخييم والسيارة الترفيهية، اسود</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>130.0 ر.س</t>
+          <t>63.45 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+          <t>مضخة مياه محمولة، موزع مياه كهربائي عالمي سعة 19 لتر مع مفتاح تشغيل وشحن USB، للتخييم والمطبخ وورشة العمل والمرأب من كوفونج (لون أبيض، عبوة من قطعة واحدة)</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>19.0 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>محول تيار مستمر 12 فولت/24 فولت الى 48 فولت من لينك جير لستارلينك ميني - محول جهد 96 واط مع حماية من الماء IP67 - منزل متنقل قارب سيارة تخييم (مع كيبل او مقبس) (مقبس (كيبل قابس)</t>
+          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>178.49 ر.س</t>
+          <t>39.99 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك موزع USB 3.0 مايكرو بي 7 منافذ مع محول طاقة 12 فولت/2.5 امبير وكابل USB 3.0 بطول 1 متر، شحن سريع 1.5 امبير، سرعة نقل بيانات 10 مرات، متوافق مع ويندوز وماك او اس اكس ولينكس (UH700)، اسود</t>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>136.56 ر.س</t>
+          <t>15.0 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
+          <t>استرو ايه اي ضاغط هواء لنفخ الاطارات 12 فولت، مضخة اطارات السيارة الرقمية 150 باوند لكل انش مربع، ضغط اطارات مضبوط مسبقا وايقاف تلقائي، مضخة هواء كهربائية لاطارات السيارات والدراجات وغيرها من الاشياء</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>105.83 ر.س</t>
+          <t>99.99 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
+          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>115.65 ر.س</t>
+          <t>15.16 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>رييوبي رف بطارية 40 فولت من لينك STM819</t>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>158.14 ر.س</t>
+          <t>263.11 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>20.9 ر.س</t>
+          <t>141.67 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>13.1 ر.س</t>
+          <t>182.8 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>20.9 ر.س</t>
+          <t>150.0 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>148.0 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>19.25 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>11.32 ر.س</t>
+          <t>79.96 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>24.5 ر.س</t>
+          <t>128.14 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>مضخة زجاجة مياه من كايبين، قابلة للطي، 3 اوضاع، 5 جالون، عبوة واحدة</t>
+          <t>Anker Power Bank, 25,000mAh 165W Total Output Portable Charger for Laptops</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>34.99 ر.س</t>
+          <t>291.0 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه محمولة، موزع مياه كهربائي عالمي سعة 19 لتر مع مفتاح تشغيل وشحن USB، للتخييم والمطبخ وورشة العمل والمرأب من كوفونج (لون أبيض، عبوة من قطعة واحدة)</t>
+          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>19.0 ر.س</t>
+          <t>78.7 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>15.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>مضخة تعزيز ضغط المياه، مضخة اوتوماتيك بجهد 24 فولت لتعزيز ضغط دش الاستحمام، مضخة مياه منزلية قابلة للحمل بقوة 150 واط بمفتاح تدفق للحمام والمطبخ والمرحاض والحديقة من بيرفورلد</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>119.97 ر.س</t>
+          <t>198.82 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>مضخة موزع مياه من لوازم بتصميم حديث، براد ماء بشكل مستدير، مصنوع من ستانلس ستيل وبلاستيك، سعة 5.0 جالون</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>17.6 ر.س</t>
+          <t>94.96 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>15.16 ر.س</t>
+          <t>3299.0 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
+          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، WPS اوفيس (بدون قلم)، كيبورد وارد، هواوي كير حصري لمدة عام + (اخضر)</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>39.99 ر.س</t>
+          <t>2199.0 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>مضخة توزيع مياه كهربائية أوتوماتيكية مع منفذ USB، محمولة وسهلة الاستخدام، للتثبيت أعلى الجالون لزجاجات المياه بسعة من 7.5 إلى 19 لتر، قابلة لإعادة الشحن، للاستخدام في المنزل أو المكتب من مومنت، أبيض</t>
+          <t>بريمير جير بادئ تشغيل بدرجة احترافية PG-17703 متوافق مع/بديل لسيارة هوندا CR-V 1997-2001 31200-P3F-A51، DS4H1 12 فولت، دوران سي دبليو، 9 اسنان، 1.1 كيلو واط</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>16.61 ر.س</t>
+          <t>1028.85 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+          <t>HUAWEI MatePad SE 11'' 8+128GB Nebula Grey Tablet, FullView Display, Large Capacity Battery, 1-Year Amazon Exclusive Huawei Care+</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>263.11 ر.س</t>
+          <t>999.0 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+          <t>شاومي باد ميني، 8GB+256GB، 8.8 انش، 7500mAh، شاحن هايبر تشارج 67 واط، واي فاي 7، اسود (مع شاحن متضمن)</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>182.8 ر.س</t>
+          <t>2197.62 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+          <t>محول تيار متردد/تيار مستمر بجهد 8.5 فولت متوافق مع بيور-ويف من بادو CM-07 بادو بيوروايف، شاحن ومزود طاقة لاداة تدليك بيوروايف للجسم والوجه لاسلكية موديل FJ-SW08510000DU من ابرايت، أسود</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>150.0 ر.س</t>
+          <t>194.0 ر.س</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>141.67 ر.س</t>
+          <t>1454.16 ر.س</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بدون قلم، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس + هواوي كير لمدة عام واحد (ابيض)</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>1999.0 ر.س</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
+          <t>شاومي تابلت بوكو باد C1، 6+128GB 9.7 انش 2K 120Hz شاشة ضخمة شفافة 7600mAh بطارية سناب دراجون® 6s الجيل الثاني 4G الجيل الثاني، اصدار واي فاي، شاحن متضمن (اسود)</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>787.2 ر.س</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>ايه - بريميوم بادئ تشغيل متوافق مع دودج فيرنا 2004-2006 هونداي اكسنت 2001-2009 كيا ريو ريو 5 2006-2008 1.5 لتر/1.6 لتر 0.9 كيلو واط 12 فولت CW 8T</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>128.14 ر.س</t>
+          <t>522.42 ر.س</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
+          <t>شاومي تابلت باد ميني واي فاي ميديا تيك ديمنستي 9400+، 8.8 انش، شاشة 3K فائقة الوضوح، بطارية 7500mAh، شحن سريع 67 واط، 3008 × 1880، واي فاي 7، بلوتوث 5.4، 12GB + 512GB، اسود مع شاحن</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>89.99 ر.س</t>
+          <t>2632.38 ر.س</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Anker Power Bank, 25,000mAh 165W Total Output Portable Charger for Laptops</t>
+          <t>هواوي تابلت ميت باد 11.5 اس (2026)، شاشة فائقة الوضوح، 12GB + 256GB، بطارية 8800mAh، شحن فائق 40 واط، كيبورد قابل للفصل، اخضر</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>291.0 ر.س</t>
+          <t>1799.0 ر.س</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>تابلت شاومي ريدمي باد 2، 11 انش، 6 جيجا، 128 جيجا، واي فاي، هايبر او اس، اخضر مينت</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>94.96 ر.س</t>
+          <t>977.03 ر.س</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -3034,719 +3034,15 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
+          <t>شاحن محول تيار متردد/تيار مستمر 5 فولت 2 أمبير لبريستيجيو ملتي باد 8.0 PMP5780D PRIME DUO</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>75.99 ر.س</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>78.7 ر.س</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>188.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>449.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>ViewSonic VX2479A-HD-PRO 24” 240Hz Gaming Monitor</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>399.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>549.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>474.78 ر.س</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>422.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>شاشة الألعاب الاحترافية UG25I بحجم 24.5 بوصة - 240Hz/1ms/فري سينك بريميوم - دقة وضوح FHD (1920x1080) - تصميم بدون إطار - تدعم DP و HDMI من زد ايدج</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>465.49 ر.س</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>389.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>617.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>KTC 24 Inch 240Hz Curved Gaming Monitor, FHD 1080p 1500R 1ms Computer Monitor, Adaptive Sync, 3000:1 Contrast, HDR Support, HDMI 2.0 &amp; DP 1.4, Low Blue Light, Tilt, VESA, H24S17P</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>569.26 ر.س</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>667.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>789.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>مبرد سائل من سلسلة انيرجلو من سودوكو</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>265.24 ر.س</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>499.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>KTC شاشة العاب منحنية 24 انش 240 هرتز، شاشة كمبيوتر FHD H24S17P</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>529.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>ساعة من كاسيو للجنسين بشاشة أنالوج و ديجيتال موديل ايه كيو-240</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>329.21 ر.س</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بتقنية USB، متوافق مع الهواتف المحمولة، بمنفذين من النوع C، بقدرة 30 واط لآيفون وسامسونج جالكسي وآيباد برو</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>36.47 ر.س</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>88.74 ر.س</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>46.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>59.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>59.89 ر.س</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>39.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>75.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>79.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>39.17 ر.س</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>28.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>48.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>129.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>35.79 ر.س</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من توكي بمنفذ USB متوافق مع ايفون 17/16/15 وسامسونج S26/S25 وايباد، 3 منافذ، 100 واط، شحن سريع مع حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>62.1 ر.س</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -57,12 +57,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-07</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -550,199 +550,199 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>iblackstores</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>149.01 ر.س</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>149.01 ر.س</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>منصة جودا هاربو لشحن البطاريات</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>منصات ومحطات شحن</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>179.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>179.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>توصيلة جودا فولت لينك</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>توصيلات كهربائية</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>منصة جودا هاربو لشحن البطاريات</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>منصات ومحطات شحن</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>منتجات السيارة</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>179.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>179.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>13.1 ر.س</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>41.28 ر.س</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>توصيلة جودا فولت لينك</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>توصيلات كهربائية</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>بطارية راف باور</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>بطاريات متنقلة</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>شاحن جودا فولت باد / VoltPad</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>شواحن جدارية</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>منتجات السيارة</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>13.1 ر.س</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>41.8 ر.س</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>بطارية راف باور</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>بطاريات متنقلة</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>150.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>150.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>شاحن جودا فولت باد / VoltPad</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>شواحن جدارية</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, iblackstores</t>
+          <t>aletawiksa, iblackstores, amazon_sa</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>194.0 ر.س</t>
+          <t>442.73 ر.س</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>29.0 ر.س</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>109.5 ر.س</t>
+          <t>84.31 ر.س</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>جودا - بطاريات AAA القابلة للشحن</t>
+          <t>جودا - شاحن سمارت للبطاريات الذكيه AA\AAA</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>58.99 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>298.99 ر.س</t>
+          <t>299.01 ر.س</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن جداري بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>جودا - باور بانك NeoPower سعة 20000mAh بقوة 22.5 واط ومنفذين - أسود</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>58.99 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1753,44 +1753,44 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>مايكل جوردن</t>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>39.99 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Jarir Reader</t>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>19.99 ر.س</t>
+          <t>51.0 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>114.62 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>188.99 ر.س</t>
+          <t>51.0 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>94.96 ر.س</t>
+          <t>93.43 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>باور بانك CP24 20000 مللي امبير في الساعة 40 واط سي سي سي مع كابلات مزدوجة</t>
+          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>161.64 ر.س</t>
+          <t>130.0 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>186.25 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>198.82 ر.س</t>
+          <t>40.0 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>61.99 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+          <t>بطارية بديلة لجيه بي ال لينك 10، 3.7 فولت/3600 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>138.87 ر.س</t>
+          <t>104.92 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>INIU Power Bank, 20000mAh 45W PD Fast Charging Small Portable Charger</t>
+          <t>رييوبي رف بطارية 40 فولت من لينك STM819</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>134.99 ر.س</t>
+          <t>158.14 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>باور بانك سينجي ميني 20 بطارية 20,000mAh، شحن بقدرة 15 واط، ثلاث منافذ (2 نوع سي + 1 USB نوع ايه)، مدمج وسهل الحمل متوافق مع جي-تاج، أسود</t>
+          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>105.83 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
+          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>229.0 ر.س</t>
+          <t>115.62 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>محول امداد طاقة 12 فولت 0-3 امبير متوافق مع بي لينك / كامروي / تريجكي (مدخل تيار متردد 100-240 فولت، مخرج تيار مستمر 12 فولت 0-3 امبير 36 واط)، تيار مستمر عالمي ولراوتر كاميرا المراقبة</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>128.14 ر.س</t>
+          <t>164.98 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Anker Zolo Power Bank, 20,000mAh 22.5W Max Portable Charger, USB-C In and Out Fast Charging, Slim Travel Essential Phone Power Bank, For iPhone 17/16 Series, Samsung S25/S24, Huawei, Honor and More</t>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>13.1 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>169.0 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>20.9 ر.س</t>
+          <t>13.14 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>20.9 ر.س</t>
+          <t>49.3 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>13.1 ر.س</t>
+          <t>24.5 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>13.14 ر.س</t>
+          <t>148.0 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>مضخة تعزيز المياه، مضخة تعزيز ضغط مياه الاستحمام الاوتوماتيكية 24 فولت، مضخة معززة للمياه فائقة الصمت 150 واط مع مفتاح تدفق للحمام أو المرحاض أو المطبخ أو الحديقة</t>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>148.0 ر.س</t>
+          <t>13.75 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+          <t>ibsun Water Pressure Booster Pump, 26.1 PSI, 100W, Automatic</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>13.75 ر.س</t>
+          <t>180.0 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
+          <t>مضخة مياه محمولة، موزع مياه كهربائي عالمي سعة 19 لتر مع مفتاح تشغيل وشحن USB، للتخييم والمطبخ وورشة العمل والمرأب من كوفونج (لون أبيض، عبوة من قطعة واحدة)</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>24.5 ر.س</t>
+          <t>19.0 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
+          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>49.3 ر.س</t>
+          <t>29.0 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
+          <t>مضخة زجاجة مياه من كايبين، قابلة للطي، 3 اوضاع، 5 جالون، عبوة واحدة</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>29.0 ر.س</t>
+          <t>34.99 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه بسعة 5 جالون من كوزي تشارم، موزع مياه كهربائي محمول مع شحن USB نوع سي، محرك مزدوج، تدفق سريع، مثالي للمنزل والمكتب والتخييم والسيارة الترفيهية، اسود</t>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>63.45 ر.س</t>
+          <t>15.0 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه محمولة، موزع مياه كهربائي عالمي سعة 19 لتر مع مفتاح تشغيل وشحن USB، للتخييم والمطبخ وورشة العمل والمرأب من كوفونج (لون أبيض، عبوة من قطعة واحدة)</t>
+          <t>مضخة تعزيز ضغط المياه، مضخة اوتوماتيك بجهد 24 فولت لتعزيز ضغط دش الاستحمام، مضخة مياه منزلية قابلة للحمل بقوة 150 واط بمفتاح تدفق للحمام والمطبخ والمرحاض والحديقة من بيرفورلد</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>19.0 ر.س</t>
+          <t>119.97 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
+          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>39.99 ر.س</t>
+          <t>15.66 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>15.0 ر.س</t>
+          <t>263.11 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>استرو ايه اي ضاغط هواء لنفخ الاطارات 12 فولت، مضخة اطارات السيارة الرقمية 150 باوند لكل انش مربع، ضغط اطارات مضبوط مسبقا وايقاف تلقائي، مضخة هواء كهربائية لاطارات السيارات والدراجات وغيرها من الاشياء</t>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>99.99 ر.س</t>
+          <t>175.49 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>15.16 ر.س</t>
+          <t>150.0 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>263.11 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>141.67 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>182.8 ر.س</t>
+          <t>79.96 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+          <t>Anker Power Bank, 25,000mAh 165W Total Output Portable Charger for Laptops</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>150.0 ر.س</t>
+          <t>291.0 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
+          <t>يوجرين باور بانك 10000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 17/16، جالكسي S26U/S25U، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>79.96 ر.س</t>
+          <t>128.14 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>128.14 ر.س</t>
+          <t>78.7 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Anker Power Bank, 25,000mAh 165W Total Output Portable Charger for Laptops</t>
+          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>291.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>78.7 ر.س</t>
+          <t>198.82 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>3299.0 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، WPS اوفيس (بدون قلم)، كيبورد وارد، هواوي كير حصري لمدة عام + (اخضر)</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>198.82 ر.س</t>
+          <t>2199.0 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>HUAWEI MatePad SE 11'' 8+128GB Nebula Grey Tablet, FullView Display, Large Capacity Battery, 1-Year Amazon Exclusive Huawei Care+</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>94.96 ر.س</t>
+          <t>999.0 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
+          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>3299.0 ر.س</t>
+          <t>1454.16 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، WPS اوفيس (بدون قلم)، كيبورد وارد، هواوي كير حصري لمدة عام + (اخضر)</t>
+          <t>شاومي باد ميني، 8GB+256GB، 8.8 انش، 7500mAh، شاحن هايبر تشارج 67 واط، واي فاي 7، اسود (مع شاحن متضمن)</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>2199.0 ر.س</t>
+          <t>2172.6 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>HUAWEI MatePad SE 11'' 8+128GB Nebula Grey Tablet, FullView Display, Large Capacity Battery, 1-Year Amazon Exclusive Huawei Care+</t>
+          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بدون قلم، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس + هواوي كير لمدة عام واحد (ابيض)</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>999.0 ر.س</t>
+          <t>1999.0 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>شاومي باد ميني، 8GB+256GB، 8.8 انش، 7500mAh، شاحن هايبر تشارج 67 واط، واي فاي 7، اسود (مع شاحن متضمن)</t>
+          <t>بطارية ليبو 451848 3.7 فولت 250mAh 0.925Wh 1S 5C للالكترونيات بطارية ليثيوم بوليمر ايون قابلة لاعادة الشحن الهاتف الذكي - غير مناسبة للتحكم اللاسلكي 50×18×5 ملم (250mAh|451848)</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>2197.62 ر.س</t>
+          <t>99.93 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>محول تيار متردد/تيار مستمر بجهد 8.5 فولت متوافق مع بيور-ويف من بادو CM-07 بادو بيوروايف، شاحن ومزود طاقة لاداة تدليك بيوروايف للجسم والوجه لاسلكية موديل FJ-SW08510000DU من ابرايت، أسود</t>
+          <t>شاومي تابلت باد ميني واي فاي ميديا تيك ديمنستي 9400+، 8.8 انش، شاشة 3K فائقة الوضوح، بطارية 7500mAh، شحن سريع 67 واط، 3008 × 1880، واي فاي 7، بلوتوث 5.4، 12GB + 512GB، اسود مع شاحن</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>194.0 ر.س</t>
+          <t>2549.86 ر.س</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
+          <t>محول تيار متردد/تيار مستمر بجهد 8.5 فولت متوافق مع بيور-ويف من بادو CM-07 بادو بيوروايف، شاحن ومزود طاقة لاداة تدليك بيوروايف للجسم والوجه لاسلكية موديل FJ-SW08510000DU من ابرايت، أسود</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>1454.16 ر.س</t>
+          <t>194.0 ر.س</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بدون قلم، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس + هواوي كير لمدة عام واحد (ابيض)</t>
+          <t>ايه - بريميوم بادئ تشغيل متوافق مع دودج فيرنا 2004-2006 هونداي اكسنت 2001-2009 كيا ريو ريو 5 2006-2008 1.5 لتر/1.6 لتر 0.9 كيلو واط 12 فولت CW 8T</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>1999.0 ر.س</t>
+          <t>522.42 ر.س</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>787.2 ر.س</t>
+          <t>781.24 ر.س</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>ايه - بريميوم بادئ تشغيل متوافق مع دودج فيرنا 2004-2006 هونداي اكسنت 2001-2009 كيا ريو ريو 5 2006-2008 1.5 لتر/1.6 لتر 0.9 كيلو واط 12 فولت CW 8T</t>
+          <t>هواوي تابلت ميت باد 11.5 اس (2026)، شاشة فائقة الوضوح، 12GB + 256GB، بطارية 8800mAh، شحن فائق 40 واط، كيبورد قابل للفصل، اخضر</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>522.42 ر.س</t>
+          <t>1799.0 ر.س</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>شاومي تابلت باد ميني واي فاي ميديا تيك ديمنستي 9400+، 8.8 انش، شاشة 3K فائقة الوضوح، بطارية 7500mAh، شحن سريع 67 واط، 3008 × 1880، واي فاي 7، بلوتوث 5.4، 12GB + 512GB، اسود مع شاحن</t>
+          <t>تابلت شاومي ريدمي باد 2، 11 انش، 6 جيجا، 128 جيجا، واي فاي، هايبر او اس، اخضر مينت</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>2632.38 ر.س</t>
+          <t>977.03 ر.س</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>هواوي تابلت ميت باد 11.5 اس (2026)، شاشة فائقة الوضوح، 12GB + 256GB، بطارية 8800mAh، شحن فائق 40 واط، كيبورد قابل للفصل، اخضر</t>
+          <t>شاومي تابلت بوكو باد C1 6+128GB 9.7 انش 2K 120Hz شاشة صلبة شفافة 7600mAh (النوع) بطارية اصدار واي فاي شاحن متضمن (اسود)</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>1799.0 ر.س</t>
+          <t>903.39 ر.س</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>تابلت شاومي ريدمي باد 2، 11 انش، 6 جيجا، 128 جيجا، واي فاي، هايبر او اس، اخضر مينت</t>
+          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>977.03 ر.س</t>
+          <t>449.0 ر.س</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -3034,15 +3034,631 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>شاحن محول تيار متردد/تيار مستمر 5 فولت 2 أمبير لبريستيجيو ملتي باد 8.0 PMP5780D PRIME DUO</t>
+          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>75.99 ر.س</t>
+          <t>549.0 ر.س</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>فيوسونيك شاشة العاب VX2479A-HD-PRO 61 سم 240 هرتز</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>399.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240 هرتز FHD 1080p، لوحة VA، وقت استجابة 2 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر 3 جوانب بدون إطار نحيفة للغاية، 99% اس ار جي بي، فلتر للضوء الأزرق، HDMI وDP، لون أسود من فيوفيجن</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>419.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>464.56 ر.س</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>422.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>470.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>389.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>789.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>KTC شاشة العاب منحنية 61 سم 240Hz FHD 1080p 1500R 1 مللي ثانية، مزامنة تكيفية، تباين 3000:1، دعم HDR، HDMI 2.0 وDP 1.4، ضوء ازرق منخفض، امالة فيسا، H24S17P</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>459.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>567.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>مبرد سائل من سلسلة انيرجلو من سودوكو</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>265.24 ر.س</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>GAMEON GOESP27240IPS E-sports Series, Black Gaming Monitor 27 Inch, 1920x1080p FHD IPS Panel, 240Hz Refresh Rate, 0.5ms Response Time, Supports HDR 10, PS5</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>565.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>KTC شاشة العاب منحنية 24 انش 240 هرتز، شاشة كمبيوتر FHD H24S17P</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>529.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>88.74 ر.س</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بتقنية USB، متوافق مع الهواتف المحمولة، بمنفذين من النوع C، بقدرة 30 واط لآيفون وسامسونج جالكسي وآيباد برو</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>36.47 ر.س</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>35.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>58.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>59.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>39.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة لاسلكي وحامل جوال مغناطيسي، شحن سريع 15 واط، حامل تابلوه قابل للدوران 360 درجة، كوب شفط جل ومغناطيس N52، متوافق مع الاجهزة العالمية، تركيب سريع</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>89.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>75.87 ر.س</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>39.17 ر.س</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>48.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>29.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>129.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>35.79 ر.س</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-10</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -574,245 +574,245 @@
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>منصة جودا هاربو لشحن البطاريات</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>منصات ومحطات شحن</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>179.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>179.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>توصيلة جودا فولت لينك</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>توصيلات كهربائية</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>منتجات السيارة</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>بطارية راف باور</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>بطاريات متنقلة</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>شاحن جودا فولت باد / VoltPad</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>شواحن جدارية</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>كيبل جودا 240 واط</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>كيابل شحن</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, iblackstores, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>459.92 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>شاحن سيارة جودا</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>شواحن سيارة</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>al3bor-telecom, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>35.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>237.9 ر.س</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>توصيلة جودا فولت لينك</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>توصيلات كهربائية</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>منتجات السيارة</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>بطارية راف باور</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>بطاريات متنقلة</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>150.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>150.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>شاحن جودا فولت باد / VoltPad</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>شواحن جدارية</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>كيبل جودا 240 واط</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>كيابل شحن</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa, iblackstores, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>458.98 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>شاحن سيارة جودا</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>شواحن سيارة</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>aletawiksa, amazon_sa</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>28.0 ر.س</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>82.68 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>75.2 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا SLIP60 سيليكون 60 واط تايب سي الى تايب سي 1 متر - وردي غامق</t>
+          <t>بكج ثلاث اسلاك تايب سي الى تايب سي جودا JODA NeoFlow 60 ( 1م - 2م - 3م ) - أسود</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا من تايب سي الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز بدقة 4K بطول 2 متر - اسود</t>
+          <t>بطارية متنقلة 20 JODA NeoPower بقوة 22.5 واط بسعة 20000 ملي امبير بمنفذين تايب سي و منفذ يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا من HDMI الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز 4K بطول 2 متر - اسود</t>
+          <t>سلك جودا من تايب سي الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز بدقة 4K بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري GaN VOLTDOCK 45 بقدرة 45 واط بمنفذ تايب سيمع سلك قابل للسحب مدمج تايب سي - أسود</t>
+          <t>سلك جودا من HDMI الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز 4K بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>سلك تايب سي الى تايب سي BEACON 100 مضيء جودا سيليكون نايلون مظفر بقوة 100 واط بطول 1.2 متر - ابيض</t>
+          <t>شاحن جداري GaN VOLTDOCK 45 بقدرة 45 واط بمنفذ تايب سيمع سلك قابل للسحب مدمج تايب سي - أسود</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
+          <t>سلك تايب سي الى تايب سي BEACON 100 مضيء جودا سيليكون نايلون مظفر بقوة 100 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
+          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
+          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
+          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>209.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
+          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>209.0 ر.س</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
+          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>349.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
+          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>349.0 ر.س</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
+          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
+          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>49.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
+          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>49.0 ر.س</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
+          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
+          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
+          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - كحلي</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>جودا - جهاز تشغيل بطارية ومنفاخ هواء 4 في 1 بشاشة رقمية</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>299.01 ر.س</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1643,17 +1643,17 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -1731,17 +1731,17 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1753,17 +1753,17 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>مايكل جوردن</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>39.99 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1775,22 +1775,22 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>jarir</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>دار الأداب الهاربون والباقون</t>
+          <t>مايكل جوردن</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>94.74 ر.س</t>
+          <t>39.99 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>روبوتايم 3 دي بازل هارب</t>
+          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>201.09 ر.س</t>
+          <t>449.0 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>زي بويلر التنكري للرجال على شكل افارهول بتصميم مستوحى من زي السجين الهارب بلون برتقالي من سميفيز - مقاس S، البوليستر</t>
+          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>146.91 ر.س</t>
+          <t>549.0 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>فيوسونيك شاشة العاب VX2479A-HD-PRO 61 سم 240 هرتز</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>328.0 ر.س</t>
+          <t>399.0 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>275.0 ر.س</t>
+          <t>461.76 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>35.0 ر.س</t>
+          <t>422.97 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>وايلد ريبابليك لعبة قطيفة من بوكيت كينز ايكو هارب، حيوان محشو، 5 انش، مصنوعة من مواد معاد تدويرها، صديقة للبيئة</t>
+          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>67.0 ر.س</t>
+          <t>789.98 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء قارب هاربون للرجال</t>
+          <t>شاشة ألعاب 24 بوصة 240 هرتز FHD 1080p، لوحة VA، وقت استجابة 2 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر 3 جوانب بدون إطار نحيفة للغاية، 99% اس ار جي بي، فلتر للضوء الأزرق، HDMI وDP، لون أسود من فيوفيجن</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>314.65 ر.س</t>
+          <t>419.0 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء قارب للرجال من هاربون، بيج داكن، مقاس 42 EU</t>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>285.79 ر.س</t>
+          <t>389.0 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء قارب هاربون للرجال، لون بيج داكن، مقاس 11.5</t>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>358.24 ر.س</t>
+          <t>470.0 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء هاربون على شكل قارب للرجال، كحلي، مقاس 42 EU</t>
+          <t>KTC شاشة العاب منحنية 61 سم 240Hz FHD 1080p 1500R 1 مللي ثانية، مزامنة تكيفية، تباين 3000:1، دعم HDR، HDMI 2.0 وDP 1.4، ضوء ازرق منخفض، امالة فيسا، H24S17P</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>273.4 ر.س</t>
+          <t>459.99 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء قارب هاربون للرجال، رمادي، 8.5</t>
+          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>294.07 ر.س</t>
+          <t>567.0 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Sperry Mens Harpoon Crushback Slip on Sneaker</t>
+          <t>KTC شاشة العاب منحنية 24 انش 240 هرتز، شاشة كمبيوتر FHD H24S17P</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>375.62 ر.س</t>
+          <t>529.99 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>بيلا فيتا جزمة هارب للنساء</t>
+          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>255.88 ر.س</t>
+          <t>499.0 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>الدو صندل هاربا مفتوح عند الاصابع للنساء من 20 هاربا</t>
+          <t>مبرد سائل من سلسلة انيرجلو من سودوكو</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>612.0 ر.س</t>
+          <t>265.24 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+          <t>GAMEON GOESP27240IPS E-sports Series, Black Gaming Monitor 27 Inch, 1920x1080p FHD IPS Panel, 240Hz Refresh Rate, 0.5ms Response Time, Supports HDR 10, PS5</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>263.11 ر.س</t>
+          <t>565.0 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+          <t>شاحن من أنكر بتقنية USB، متوافق مع الهواتف المحمولة، بمنفذين من النوع C، بقدرة 30 واط لآيفون وسامسونج جالكسي وآيباد برو</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>141.67 ر.س</t>
+          <t>36.47 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>175.49 ر.س</t>
+          <t>35.98 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+          <t>شاحن سيارة لاسلكي وحامل جوال مغناطيسي، شحن سريع 15 واط، حامل تابلوه قابل للدوران 360 درجة، كوب شفط جل ومغناطيس N52، متوافق مع الاجهزة العالمية، تركيب سريع</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>150.0 ر.س</t>
+          <t>89.99 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>75.87 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>39.9 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>94.96 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>78.7 ر.س</t>
+          <t>39.17 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>138.87 ر.س</t>
+          <t>88.0 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>128.14 ر.س</t>
+          <t>68.98 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>198.82 ر.س</t>
+          <t>79.96 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Anker Zolo Power Bank, 20,000mAh 22.5W Max Portable Charger, USB-C In and Out Fast Charging, Slim Travel Essential Phone Power Bank, For iPhone 17/16 Series, Samsung S25/S24, Huawei, Honor and More</t>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>48.0 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 10000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 17/16، جالكسي S26U/S25U، ايباد، ايربودز</t>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>28.0 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>449.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع سامسونج وآيفون وهواوي P60 بـ 3 منافذ بقوة 130.0 واط مع شحن سريع وحماية متعددة</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>549.0 ر.س</t>
+          <t>129.89 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,609 +2440,15 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>فيوسونيك شاشة العاب VX2479A-HD-PRO 61 سم 240 هرتز</t>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>399.0 ر.س</t>
+          <t>35.79 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>789.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>462.78 ر.س</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>422.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240 هرتز FHD 1080p، لوحة VA، وقت استجابة 2 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر 3 جوانب بدون إطار نحيفة للغاية، 99% اس ار جي بي، فلتر للضوء الأزرق، HDMI وDP، لون أسود من فيوفيجن</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>419.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>389.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>470.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>مبرد سائل من سلسلة انيرجلو من سودوكو</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>265.24 ر.س</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>KTC شاشة العاب منحنية 61 سم 240Hz FHD 1080p 1500R 1 مللي ثانية، مزامنة تكيفية، تباين 3000:1، دعم HDR، HDMI 2.0 وDP 1.4، ضوء ازرق منخفض، امالة فيسا، H24S17P</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>459.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>567.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>KTC شاشة العاب منحنية 24 انش 240 هرتز، شاشة كمبيوتر FHD H24S17P</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>529.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>499.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>549.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بتقنية USB، متوافق مع الهواتف المحمولة، بمنفذين من النوع C، بقدرة 30 واط لآيفون وسامسونج جالكسي وآيباد برو</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>36.47 ر.س</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>35.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>58.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>75.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>59.89 ر.س</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة لاسلكي وحامل جوال مغناطيسي، شحن سريع 15 واط، حامل تابلوه قابل للدوران 360 درجة، كوب شفط جل ومغناطيس N52، متوافق مع الاجهزة العالمية، تركيب سريع</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>89.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>79.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>39.17 ر.س</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>39.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>68.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>48.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>28.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>129.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>35.79 ر.س</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-11</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, iblackstores, amazon_sa</t>
+          <t>aletawiksa, iblackstores</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>459.92 ر.س</t>
+          <t>194.0 ر.س</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -784,35 +784,35 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>28.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>75.2 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="C11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>aletawiksa</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>69.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>69.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1772,688 +1772,6 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>jarir</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>مايكل جوردن</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>39.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>بحث تقديري</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>449.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>549.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>فيوسونيك شاشة العاب VX2479A-HD-PRO 61 سم 240 هرتز</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>399.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>461.76 ر.س</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>422.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>789.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240 هرتز FHD 1080p، لوحة VA، وقت استجابة 2 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر 3 جوانب بدون إطار نحيفة للغاية، 99% اس ار جي بي، فلتر للضوء الأزرق، HDMI وDP، لون أسود من فيوفيجن</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>419.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>389.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>470.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>KTC شاشة العاب منحنية 61 سم 240Hz FHD 1080p 1500R 1 مللي ثانية، مزامنة تكيفية، تباين 3000:1، دعم HDR، HDMI 2.0 وDP 1.4، ضوء ازرق منخفض، امالة فيسا، H24S17P</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>459.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>567.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>KTC شاشة العاب منحنية 24 انش 240 هرتز، شاشة كمبيوتر FHD H24S17P</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>529.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>499.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>مبرد سائل من سلسلة انيرجلو من سودوكو</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>265.24 ر.س</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>GAMEON GOESP27240IPS E-sports Series, Black Gaming Monitor 27 Inch, 1920x1080p FHD IPS Panel, 240Hz Refresh Rate, 0.5ms Response Time, Supports HDR 10, PS5</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>565.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بتقنية USB، متوافق مع الهواتف المحمولة، بمنفذين من النوع C، بقدرة 30 واط لآيفون وسامسونج جالكسي وآيباد برو</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>36.47 ر.س</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>35.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة لاسلكي وحامل جوال مغناطيسي، شحن سريع 15 واط، حامل تابلوه قابل للدوران 360 درجة، كوب شفط جل ومغناطيس N52، متوافق مع الاجهزة العالمية، تركيب سريع</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>89.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>75.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 15 و جالاكسي S24 و آيباد بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>39.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>58.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>39.17 ر.س</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>68.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>79.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>48.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>28.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>129.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع سامسونج وآيفون وهواوي P60 بـ 3 منافذ بقوة 130.0 واط مع شحن سريع وحماية متعددة</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>129.89 ر.س</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>35.79 ر.س</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-12</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -644,70 +644,70 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>13.1 ر.س</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>46.12 ر.س</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>160.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>160.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -784,35 +784,35 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>aletawiksa</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>69.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>69.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="C11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>28.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>80.31 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>جودا - باور بانك NeoPower سعة 20000mAh بقوة 22.5 واط ومنفذين - أسود</t>
+          <t>جودا - جهاز تشغيل بطارية ومنفاخ هواء 4 في 1 بشاشة رقمية</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>299.01 ر.س</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>جودا - جهاز تشغيل بطارية ومنفاخ هواء 4 في 1 بشاشة رقمية</t>
+          <t>جودا - باور بانك NeoPower سعة 20000mAh بقوة 22.5 واط ومنفذين - أسود</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>299.01 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1769,6 +1769,1282 @@
       <c r="D44" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>jarir</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>مايكل جوردن</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>39.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>بحث تقديري</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>51.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>40.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>51.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>85.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>114.51 ر.س</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>130.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>93.43 ر.س</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>186.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>رييوبي رف بطارية 40 فولت من لينك STM819</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>158.14 ر.س</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك موزع USB 3.0 مايكرو بي 7 منافذ مع محول طاقة 12 فولت/2.5 امبير وكابل USB 3.0 بطول 1 متر، شحن سريع 1.5 امبير، سرعة نقل بيانات 10 مرات، متوافق مع ويندوز وماك او اس اكس ولينكس (UH700)، اسود</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>144.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>115.62 ر.س</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>105.87 ر.س</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن PoE سلبي 48 فولت/18 واط TL-PoE4818G | محول جيجابت PoE | التوصيل والتشغيل | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>80.47 ر.س</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>20.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>13.1 ر.س</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>20.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>13.14 ر.س</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه محمولة، موزع مياه كهربائي عالمي سعة 19 لتر مع مفتاح تشغيل وشحن USB، للتخييم والمطبخ وورشة العمل والمرأب من كوفونج (لون أبيض، عبوة من قطعة واحدة)</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>19.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>49.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>24.5 ر.س</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>15.66 ر.س</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>مومنت مضخة توزيع مياه شرب كهربائية، مضخة زجاجة مياه اوتوماتيكية محمولة وقابلة لاعادة الشحن بمنفذ USB لاباريق المياه سعة 7.6-18.9 لتر للمكتب والمنزل والتخييم والمطبخ، ابيض</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>18.36 ر.س</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>نظام المياه المعباة في قوارير 3.8 لتر/الدقيقة مضخة مياه معباه في قوارير 2.8 بار نظام مضخة توزيع المياه مع انبوب PE 6 م</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>349.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>34.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>13.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>15.16 ر.س</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>مضخة موزع مياه من لوازم بتصميم حديث، براد ماء بشكل مستدير، مصنوع من ستانلس ستيل وبلاستيك، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>17.6 ر.س</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>15.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>250.78 ر.س</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>139.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>182.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>127.2 ر.س</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>160.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>82.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Anker Zolo Power Bank, 20,000mAh 22.5W Max Portable Charger, USB-C In and Out Fast Charging, Slim Travel Essential Phone Power Bank, For iPhone 17/16 Series, Samsung S25/S24, Huawei, Honor and More</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>109.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>119.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>128.14 ر.س</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>78.7 ر.س</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>159.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>113.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بتقنية USB، متوافق مع الهواتف المحمولة، بمنفذين من النوع C، بقدرة 30 واط لآيفون وسامسونج جالكسي وآيباد برو</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>36.47 ر.س</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>35.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>75.87 ر.س</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>58.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>88.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>48.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>49.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>28.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع سامسونج وآيفون وهواوي P60 بـ 3 منافذ بقوة 130.0 واط مع شحن سريع وحماية متعددة</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>129.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>35.79 ر.س</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>85.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>AstroAI Jump Starter Portable Car Jump Starter 12V Car Battery Charger</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>254.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>88.74 ر.س</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-13</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>13.1 ر.س</t>
+          <t>11.0 ر.س</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>46.12 ر.س</t>
+          <t>70.84 ر.س</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -679,35 +679,35 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>160.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>160.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, iblackstores</t>
+          <t>aletawiksa, iblackstores, amazon_sa</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>194.0 ر.س</t>
+          <t>440.76 ر.س</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>80.31 ر.س</t>
+          <t>67.63 ر.س</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري GaN VOLTDOCK 45 بقدرة 45 واط بمنفذ تايب سيمع سلك قابل للسحب مدمج تايب سي - أسود</t>
+          <t>شاحن جداري جودا GaN VOLTDOCK 45 بقدرة 45 واط بمنفذ تايب سيمع سلك قابل للسحب مدمج تايب سي - أسود</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>51.0 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>40.0 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
+          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>51.0 ر.س</t>
+          <t>61.99 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>85.0 ر.س</t>
+          <t>188.99 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>114.51 ر.س</t>
+          <t>113.3 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+          <t>INIU Power Bank, 20000mAh 45W PD Fast Charging Small Portable Charger</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>130.0 ر.س</t>
+          <t>129.99 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
+          <t>باور بانك سينجي ميني 20 بطارية 20,000mAh، شحن بقدرة 15 واط، ثلاث منافذ (2 نوع سي + 1 USB نوع ايه)، مدمج وسهل الحمل متوافق مع جي-تاج، أسود</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>93.43 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>186.25 ر.س</t>
+          <t>229.0 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>198.82 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>رييوبي رف بطارية 40 فولت من لينك STM819</t>
+          <t>باور بانك من يوجرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب A مع شحن سريع وحماية للهاتف واللابتوب 3 منافذ</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>158.14 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك موزع USB 3.0 مايكرو بي 7 منافذ مع محول طاقة 12 فولت/2.5 امبير وكابل USB 3.0 بطول 1 متر، شحن سريع 1.5 امبير، سرعة نقل بيانات 10 مرات، متوافق مع ويندوز وماك او اس اكس ولينكس (UH700)، اسود</t>
+          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>144.0 ر.س</t>
+          <t>178.94 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>115.62 ر.س</t>
+          <t>154.0 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
+          <t>باور بانك CP24 20000 مللي امبير في الساعة 40 واط سي سي سي مع كابلات مزدوجة مدمجة من كوك تيك</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>105.87 ر.س</t>
+          <t>161.64 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE سلبي 48 فولت/18 واط TL-PoE4818G | محول جيجابت PoE | التوصيل والتشغيل | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط</t>
+          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>80.47 ر.س</t>
+          <t>169.0 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>20.9 ر.س</t>
+          <t>138.99 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>13.1 ر.س</t>
+          <t>51.0 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>20.9 ر.س</t>
+          <t>40.0 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>13.14 ر.س</t>
+          <t>85.0 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه محمولة، موزع مياه كهربائي عالمي سعة 19 لتر مع مفتاح تشغيل وشحن USB، للتخييم والمطبخ وورشة العمل والمرأب من كوفونج (لون أبيض، عبوة من قطعة واحدة)</t>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>19.0 ر.س</t>
+          <t>56.0 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>49.3 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
+          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>24.5 ر.س</t>
+          <t>114.54 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>15.66 ر.س</t>
+          <t>186.25 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>مومنت مضخة توزيع مياه شرب كهربائية، مضخة زجاجة مياه اوتوماتيكية محمولة وقابلة لاعادة الشحن بمنفذ USB لاباريق المياه سعة 7.6-18.9 لتر للمكتب والمنزل والتخييم والمطبخ، ابيض</t>
+          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>18.36 ر.س</t>
+          <t>93.43 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>نظام المياه المعباة في قوارير 3.8 لتر/الدقيقة مضخة مياه معباه في قوارير 2.8 بار نظام مضخة توزيع المياه مع انبوب PE 6 م</t>
+          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>349.99 ر.س</t>
+          <t>130.0 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
+          <t>بطارية بديلة لجيه بي ال لينك 10، 3.7 فولت/3600 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>34.99 ر.س</t>
+          <t>104.92 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+          <t>رييوبي رف بطارية 40 فولت من لينك STM819</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>13.75 ر.س</t>
+          <t>158.14 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
+          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>15.16 ر.س</t>
+          <t>105.87 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>مضخة موزع مياه من لوازم بتصميم حديث، براد ماء بشكل مستدير، مصنوع من ستانلس ستيل وبلاستيك، سعة 5.0 جالون</t>
+          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>17.6 ر.س</t>
+          <t>115.67 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>15.0 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>250.78 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>13.1 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>182.8 ر.س</t>
+          <t>13.14 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+          <t>مضخة مياه محمولة، موزع مياه كهربائي عالمي سعة 19 لتر مع مفتاح تشغيل وشحن USB، للتخييم والمطبخ وورشة العمل والمرأب من كوفونج (لون أبيض، عبوة من قطعة واحدة)</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>127.2 ر.س</t>
+          <t>19.0 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>160.0 ر.س</t>
+          <t>49.3 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>82.95 ر.س</t>
+          <t>24.5 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Anker Zolo Power Bank, 20,000mAh 22.5W Max Portable Charger, USB-C In and Out Fast Charging, Slim Travel Essential Phone Power Bank, For iPhone 17/16 Series, Samsung S25/S24, Huawei, Honor and More</t>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>13.75 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>119.0 ر.س</t>
+          <t>11.0 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>نظام المياه المعباة في قوارير 3.8 لتر/الدقيقة مضخة مياه معباه في قوارير 2.8 بار نظام مضخة توزيع المياه مع انبوب PE 6 م</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>128.14 ر.س</t>
+          <t>349.99 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
+          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>78.7 ر.س</t>
+          <t>15.16 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
+          <t>ibsun Water Pressure Booster Pump, 26.1 PSI, 100W, Automatic</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>79.96 ر.س</t>
+          <t>180.0 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
+          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>15.66 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>113.3 ر.س</t>
+          <t>29.0 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>شاحن من أنكر بتقنية USB، متوافق مع الهواتف المحمولة، بمنفذين من النوع C، بقدرة 30 واط لآيفون وسامسونج جالكسي وآيباد برو</t>
+          <t>مومنت مضخة توزيع مياه شرب كهربائية، مضخة زجاجة مياه اوتوماتيكية محمولة وقابلة لاعادة الشحن بمنفذ USB لاباريق المياه سعة 7.6-18.9 لتر للمكتب والمنزل والتخييم والمطبخ، ابيض</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>36.47 ر.س</t>
+          <t>18.36 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>35.98 ر.س</t>
+          <t>1279.0 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+          <t>بطارية محمولة 14.8 فولت 47 واط ساعة/3180mAh/8 خلايا 45N1704 45N1705 45N1706 متوافقة مع لينوفو ثينك باد S1 يوجا/ثينك باد يوجا 12 S1-S240 S1-120</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>75.87 ر.س</t>
+          <t>230.0 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+          <t>جهاز نانو كيه في ام فل من سيبيد، RISC-V IP كيه في ام مع مؤشر زر شاشة OLED، تحكم في طاقة ATX، تشغيل عن بعد 5 فولت، منفذ تسلسلي مزدوج HDMI USB شبكة 100 متر، لادارة الخادم عن بعد واعداد BIOS، اسود</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>58.99 ر.س</t>
+          <t>403.24 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+          <t>HUAWEI MatePad SE 11'' 8+128GB Nebula Grey Tablet, FullView Display, Large Capacity Battery, 1-Year Amazon Exclusive Huawei Care+</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>88.99 ر.س</t>
+          <t>863.29 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
+          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، WPS اوفيس (بدون قلم)، كيبورد وارد، هواوي كير حصري لمدة عام + (اخضر)</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>88.0 ر.س</t>
+          <t>2199.0 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>48.0 ر.س</t>
+          <t>3299.0 ر.س</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+          <t>بطارية ليبو 451848 3.7 فولت 250mAh 0.925Wh 1S 5C للالكترونيات بطارية ليثيوم بوليمر ايون قابلة لاعادة الشحن الهاتف الذكي - غير مناسبة للتحكم اللاسلكي 50×18×5 ملم (250mAh|451848)</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>79.96 ر.س</t>
+          <t>93.35 ر.س</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+          <t>تابلت هواوي ميت باد 10.4 انش بذاكرة روم 128GB وذاكرة RAM 4GB وواي فاي فقط (رمادي) - اصدار عالمي</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>49.0 ر.س</t>
+          <t>599.0 ر.س</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>28.0 ر.س</t>
+          <t>1454.16 ر.س</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع سامسونج وآيفون وهواوي P60 بـ 3 منافذ بقوة 130.0 واط مع شحن سريع وحماية متعددة</t>
+          <t>جوال شاومي ريدمي باد 2 بسعة 4 جيجابايت و128 جيجابايت بشاشة 11 بوصة، رمادي (الشاحن متضمن)</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>129.89 ر.س</t>
+          <t>904.03 ر.س</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+          <t>هواوي تابلت ميديا باد ام 1 - 8 انش (واي فاي + بلوتوث، 8 جيجا، 1 جيجا رام، اندرويد 4.2.2 جيلي بين)، رمادي</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>35.79 ر.س</t>
+          <t>460.67 ر.س</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة</t>
+          <t>Xiaomi Redmi Pad 2 4 + 128 GB Large Tablet, Grey, Display 11 Inches, Charger Included</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>85.0 ر.س</t>
+          <t>888.65 ر.س</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>AstroAI Jump Starter Portable Car Jump Starter 12V Car Battery Charger</t>
+          <t>بريك بادي مجموعة بطارية مباشرة 12 فولت 39305، اسود</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>254.95 ر.س</t>
+          <t>465.0 ر.س</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -3034,15 +3034,653 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>88.74 ر.س</t>
+          <t>449.0 ر.س</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>549.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>فيوسونيك شاشة العاب VX2479A-HD-PRO 61 سم 240 هرتز</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>399.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>549.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>458.78 ر.س</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>422.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>789.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240 هرتز FHD 1080p، لوحة VA، وقت استجابة 2 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر 3 جوانب بدون إطار نحيفة للغاية، 99% اس ار جي بي، فلتر للضوء الأزرق، HDMI وDP، لون أسود من فيوفيجن</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>399.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>389.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>470.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>GAMEON GOESP27240IPS E-sports Series, Black Gaming Monitor 27 Inch, 1920x1080p FHD IPS Panel, 240Hz Refresh Rate, 0.5ms Response Time, Supports HDR 10, PS5</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>565.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>KTC شاشة العاب منحنية 61 سم 240Hz FHD 1080p 1500R 1 مللي ثانية، مزامنة تكيفية، تباين 3000:1، دعم HDR، HDMI 2.0 وDP 1.4، ضوء ازرق منخفض، امالة فيسا، H24S17P</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>459.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>مبرد وحدة المعالجة المركزية السائل نيكسورا 240 من سودوكو: مبرد وحدة المعالجة المركزية AIO 240 ملم مع مضخة PWM ورأس مضخة ARGB - تبريد مائي مع مراوح اف دي بي لانتل LGA 1851/1700/1200/115X AMD AM5/AM4 - اسود</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>349.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>567.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>45.84 ر.س</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>35.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>75.87 ر.س</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>58.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>88.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>48.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>79.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>28.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>49.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع سامسونج وآيفون وهواوي P60 بـ 3 منافذ بقوة 130.0 واط مع شحن سريع وحماية متعددة</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>129.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>35.79 ر.س</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>79.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>AstroAI Jump Starter Portable Car Jump Starter 12V Car Battery Charger</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>254.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>85.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-14</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-15</t>
         </is>
       </c>
     </row>
@@ -574,70 +574,70 @@
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>منصة جودا هاربو لشحن البطاريات</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>منصات ومحطات شحن</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>179.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>179.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>al3bor-telecom, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>35.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>202.12 ر.س</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>توصيلة جودا فولت لينك</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>توصيلات كهربائية</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -669,7 +669,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>70.84 ر.س</t>
+          <t>48.33 ر.س</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -679,140 +679,140 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>شاحن جودا فولت باد / VoltPad</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>شواحن جدارية</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa, iblackstores, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>aletawiksa, iblackstores</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>440.76 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>194.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>28.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>67.63 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="C11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>aletawiksa</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>69.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>69.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1665,17 +1665,17 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>saada</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>توصيلة جودا 5 منافذ 5 متر 2990W مع حماية SASO + شاحن اورايمو باور كيوب 202 20 واط ميني تايب سي مع كيبل</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>80.0 ر.س</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -1753,17 +1753,17 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1775,17 +1775,17 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>مايكل جوردن</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>39.99 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1797,44 +1797,44 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>jarir</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>مايكل جوردن</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>39.99 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>jarir</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
+          <t>آنا كارنينا</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>12.99 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
@@ -1846,12 +1846,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
+          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>61.99 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>188.99 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>جوال تانك 1 متين 6.75 انش 120Hz FHD+ من شاندويليك، هاتف اتصال خارجي 12GB+256GB 20000mAh، هاتف ذكي 5G اندرويد 15 ان اف سي</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>113.3 ر.س</t>
+          <t>2090.0 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>INIU Power Bank, 20000mAh 45W PD Fast Charging Small Portable Charger</t>
+          <t>جوال تانك 1 متين 6.75 انش 120Hz FHD+ من شاندويليك، هاتف اتصال خارجي 12GB+256GB 20000mAh، هاتف ذكي 5G اندرويد 15 ان اف سي</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>129.99 ر.س</t>
+          <t>2090.0 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>باور بانك سينجي ميني 20 بطارية 20,000mAh، شحن بقدرة 15 واط، ثلاث منافذ (2 نوع سي + 1 USB نوع ايه)، مدمج وسهل الحمل متوافق مع جي-تاج، أسود</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>198.82 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>229.0 ر.س</t>
+          <t>154.0 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+          <t>جوال اكسبلور 1 للاستخدام الخارجي، جوال ذكي بشبكة الجيل الخامس 5G مقاوم للماء بنظام أندرويد 15، شاشة 6.78 بوصة بدقة 2.4 كيه، 12 جيجابايت+256 جيجابايت، بطارية 20000 ميلي أمبير/الساعة</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>198.82 ر.س</t>
+          <t>1790.0 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب A مع شحن سريع وحماية للهاتف واللابتوب 3 منافذ</t>
+          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>178.94 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج</t>
+          <t>جوال سامسونج جالكسي A16، ذكي يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجابايت، تخزين 128 جيجابايت، أسود (إصدار المملكة العربية السعودية)</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>178.94 ر.س</t>
+          <t>588.93 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+          <t>جوال هونر تشويس T10 بشبكة الجيل الرابع 4G، شاشة عالية الدقة HD مقاس 6.75 بوصة، ترجمة فورية متزامنة بالذكاء الاصطناعي، كاميرات 13 + 5 ميجابكسل، ثنائي شرائح الاتصال، ذاكرة 4 + 64 جيجابايت، فضي</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>154.0 ر.س</t>
+          <t>389.0 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>باور بانك CP24 20000 مللي امبير في الساعة 40 واط سي سي سي مع كابلات مزدوجة مدمجة من كوك تيك</t>
+          <t>فيجير باور بانك 20000 مللي امبير في الساعة، شاحن محمول رفيع مع كيبلات متعددة مدمجة، بطارية شحن سريع عالية السعة مع شاشة عرض رقمية لايفون وسامسونج والجوالات - اسود</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>161.64 ر.س</t>
+          <t>95.99 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000</t>
+          <t>باور بانك في 9، شاحن محمول صغير 22.5 واط USB C 10000 مللي امبير في الساعة، حزمة بطارية شحن سريع بي دي، 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد - بينك</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>169.0 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
+          <t>باور بانك من يوجرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب A مع شحن سريع وحماية للهاتف واللابتوب 3 منافذ</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>138.99 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>جوال هونر X5c، أزرق (تايدل بلو)</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>51.0 ر.س</t>
+          <t>444.51 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+          <t>جوال سامسونج جالكسي A17 ال تي اي، ثنائي شرائح اتصال، سعة 128 جيجا توسع حتى 2 تيرا، اندرويد 14 وذاكرة رام 4 جيجابايت، معالج اكسينوس وشاشة اموليد 6.7 بوصة بدقة 1080x2220، معدل تحديث 90 هرتز، لون أسود</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>40.0 ر.س</t>
+          <t>660.0 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+          <t>دار الأداب الهاربون والباقون</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>85.0 ر.س</t>
+          <t>94.6 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
+          <t>زي بويلر التنكري للرجال على شكل افارهول بتصميم مستوحى من زي السجين الهارب بلون برتقالي من سميفيز - مقاس S، البوليستر</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>56.0 ر.س</t>
+          <t>146.91 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+          <t>Aireo Sports Pickleball Paddles | Carbon Fiber 3K Kevlar Enhancing Ball Control, Improved Spin | Falcon Pro Harpy Eagle Series | Thermoforming Construction for PRO Player, USAPA Standards</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>306.11 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
+          <t>روبوتايم 3 دي بازل هارب</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>114.54 ر.س</t>
+          <t>201.51 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>186.25 ر.س</t>
+          <t>106.62 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>93.43 ر.س</t>
+          <t>69.83 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>130.0 ر.س</t>
+          <t>35.0 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لجيه بي ال لينك 10، 3.7 فولت/3600 مللي امبير في الساعة من زوفكوس</t>
+          <t>وايلد ريبابليك لعبة قطيفة من بوكيت كينز ايكو هارب، حيوان محشو، 5 انش، مصنوعة من مواد معاد تدويرها، صديقة للبيئة</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>104.92 ر.س</t>
+          <t>67.0 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>رييوبي رف بطارية 40 فولت من لينك STM819</t>
+          <t>سبيري حذاء قارب هاربون للرجال</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>158.14 ر.س</t>
+          <t>348.66 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
+          <t>سبيري حذاء قارب للرجال من هاربون، بيج داكن، مقاس 42 EU</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>105.87 ر.س</t>
+          <t>284.88 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
+          <t>سبيري حذاء قارب هاربون للرجال، لون بيج داكن، مقاس 11.5</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>115.67 ر.س</t>
+          <t>344.51 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+          <t>سبيري حذاء هاربون على شكل قارب للرجال، كحلي، مقاس 42 EU</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>20.9 ر.س</t>
+          <t>285.35 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+          <t>سبيري حذاء قارب هاربون للرجال، رمادي، 8.5</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>20.9 ر.س</t>
+          <t>295.92 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+          <t>Sperry Mens Harpoon Crushback Slip on Sneaker</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>13.1 ر.س</t>
+          <t>375.62 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+          <t>بيلا فيتا حذاء برقبة للنساء من هارب</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>13.14 ر.س</t>
+          <t>281.29 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه محمولة، موزع مياه كهربائي عالمي سعة 19 لتر مع مفتاح تشغيل وشحن USB، للتخييم والمطبخ وورشة العمل والمرأب من كوفونج (لون أبيض، عبوة من قطعة واحدة)</t>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>19.0 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>49.3 ر.س</t>
+          <t>51.0 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>24.5 ر.س</t>
+          <t>40.0 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>13.75 ر.س</t>
+          <t>114.54 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>11.0 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>نظام المياه المعباة في قوارير 3.8 لتر/الدقيقة مضخة مياه معباه في قوارير 2.8 بار نظام مضخة توزيع المياه مع انبوب PE 6 م</t>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>349.99 ر.س</t>
+          <t>186.25 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>15.16 ر.س</t>
+          <t>56.0 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>ibsun Water Pressure Booster Pump, 26.1 PSI, 100W, Automatic</t>
+          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>180.0 ر.س</t>
+          <t>130.0 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
+          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>15.66 ر.س</t>
+          <t>93.43 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
+          <t>راوتر ايه اكس 3000 بتقنية توصيل واي فاي 6 من تي بي-لينك، معيار اتصال لاسلكي 802.11ax، منفذ جيجابت، ثنائي التردد، يدعم VPN الخادم و المستخدم، مناسب لاجهزة من النوع ون ميش، (طراز Archer AX55)، أسود</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>29.0 ر.س</t>
+          <t>209.0 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>مومنت مضخة توزيع مياه شرب كهربائية، مضخة زجاجة مياه اوتوماتيكية محمولة وقابلة لاعادة الشحن بمنفذ USB لاباريق المياه سعة 7.6-18.9 لتر للمكتب والمنزل والتخييم والمطبخ، ابيض</t>
+          <t>رييوبي رف بطارية 40 فولت من لينك STM819</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>18.36 ر.س</t>
+          <t>158.14 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
+          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>1279.0 ر.س</t>
+          <t>105.87 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>بطارية محمولة 14.8 فولت 47 واط ساعة/3180mAh/8 خلايا 45N1704 45N1705 45N1706 متوافقة مع لينوفو ثينك باد S1 يوجا/ثينك باد يوجا 12 S1-S240 S1-120</t>
+          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>230.0 ر.س</t>
+          <t>115.67 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>جهاز نانو كيه في ام فل من سيبيد، RISC-V IP كيه في ام مع مؤشر زر شاشة OLED، تحكم في طاقة ATX، تشغيل عن بعد 5 فولت، منفذ تسلسلي مزدوج HDMI USB شبكة 100 متر، لادارة الخادم عن بعد واعداد BIOS، اسود</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>403.24 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>HUAWEI MatePad SE 11'' 8+128GB Nebula Grey Tablet, FullView Display, Large Capacity Battery, 1-Year Amazon Exclusive Huawei Care+</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>863.29 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، WPS اوفيس (بدون قلم)، كيبورد وارد، هواوي كير حصري لمدة عام + (اخضر)</t>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>2199.0 ر.س</t>
+          <t>13.1 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>3299.0 ر.س</t>
+          <t>13.14 ر.س</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>بطارية ليبو 451848 3.7 فولت 250mAh 0.925Wh 1S 5C للالكترونيات بطارية ليثيوم بوليمر ايون قابلة لاعادة الشحن الهاتف الذكي - غير مناسبة للتحكم اللاسلكي 50×18×5 ملم (250mAh|451848)</t>
+          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>93.35 ر.س</t>
+          <t>49.3 ر.س</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>تابلت هواوي ميت باد 10.4 انش بذاكرة روم 128GB وذاكرة RAM 4GB وواي فاي فقط (رمادي) - اصدار عالمي</t>
+          <t>نظام المياه المعباة في قوارير 3.8 لتر/الدقيقة مضخة مياه معباه في قوارير 2.8 بار نظام مضخة توزيع المياه مع انبوب PE 6 م</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>599.0 ر.س</t>
+          <t>349.99 ر.س</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
+          <t>مومنت مضخة توزيع مياه شرب كهربائية، مضخة زجاجة مياه اوتوماتيكية محمولة وقابلة لاعادة الشحن بمنفذ USB لاباريق المياه سعة 7.6-18.9 لتر للمكتب والمنزل والتخييم والمطبخ، ابيض</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>1454.16 ر.س</t>
+          <t>20.4 ر.س</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>جوال شاومي ريدمي باد 2 بسعة 4 جيجابايت و128 جيجابايت بشاشة 11 بوصة، رمادي (الشاحن متضمن)</t>
+          <t>مضخة مياه محمولة، موزع مياه كهربائي عالمي سعة 19 لتر مع مفتاح تشغيل وشحن USB، للتخييم والمطبخ وورشة العمل والمرأب من كوفونج (لون أبيض، عبوة من قطعة واحدة)</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>904.03 ر.س</t>
+          <t>19.0 ر.س</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>هواوي تابلت ميديا باد ام 1 - 8 انش (واي فاي + بلوتوث، 8 جيجا، 1 جيجا رام، اندرويد 4.2.2 جيلي بين)، رمادي</t>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>460.67 ر.س</t>
+          <t>24.5 ر.س</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Xiaomi Redmi Pad 2 4 + 128 GB Large Tablet, Grey, Display 11 Inches, Charger Included</t>
+          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>888.65 ر.س</t>
+          <t>15.16 ر.س</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>بريك بادي مجموعة بطارية مباشرة 12 فولت 39305، اسود</t>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>465.0 ر.س</t>
+          <t>13.75 ر.س</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>449.0 ر.س</t>
+          <t>15.66 ر.س</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>549.0 ر.س</t>
+          <t>11.0 ر.س</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>فيوسونيك شاشة العاب VX2479A-HD-PRO 61 سم 240 هرتز</t>
+          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>399.0 ر.س</t>
+          <t>34.99 ر.س</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -3100,587 +3100,15 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
+          <t>ibsun Water Pressure Booster Pump, 26.1 PSI, 100W, Automatic</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>549.0 ر.س</t>
+          <t>180.0 ر.س</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>458.78 ر.س</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>422.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>789.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240 هرتز FHD 1080p، لوحة VA، وقت استجابة 2 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر 3 جوانب بدون إطار نحيفة للغاية، 99% اس ار جي بي، فلتر للضوء الأزرق، HDMI وDP، لون أسود من فيوفيجن</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>399.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>389.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>470.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>GAMEON GOESP27240IPS E-sports Series, Black Gaming Monitor 27 Inch, 1920x1080p FHD IPS Panel, 240Hz Refresh Rate, 0.5ms Response Time, Supports HDR 10, PS5</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>565.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>KTC شاشة العاب منحنية 61 سم 240Hz FHD 1080p 1500R 1 مللي ثانية، مزامنة تكيفية، تباين 3000:1، دعم HDR، HDMI 2.0 وDP 1.4، ضوء ازرق منخفض، امالة فيسا، H24S17P</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>459.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>مبرد وحدة المعالجة المركزية السائل نيكسورا 240 من سودوكو: مبرد وحدة المعالجة المركزية AIO 240 ملم مع مضخة PWM ورأس مضخة ARGB - تبريد مائي مع مراوح اف دي بي لانتل LGA 1851/1700/1200/115X AMD AM5/AM4 - اسود</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>349.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>567.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>مبرد سائل كراكين بلس 240 لوحدة المعالجة المركزية، رادياتور 240 ملم مع 2 مراوح F120P بشاشة LCD مربعة قابلة للتعديل مقاس 1.54 بوصة AMD® AM5 وAM4 انتل LGA 1851/1700 و1200/115X من نزكست- أسود</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>499.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>45.84 ر.س</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>35.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>75.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>58.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>88.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>48.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>79.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>28.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>49.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع سامسونج وآيفون وهواوي P60 بـ 3 منافذ بقوة 130.0 واط مع شحن سريع وحماية متعددة</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>129.89 ر.س</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>35.79 ر.س</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>79.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>AstroAI Jump Starter Portable Car Jump Starter 12V Car Battery Charger</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>254.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>85.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-15</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-16</t>
         </is>
       </c>
     </row>
@@ -574,70 +574,70 @@
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>منصة جودا هاربو لشحن البطاريات</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>منصات ومحطات شحن</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>al3bor-telecom, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>35.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>202.12 ر.س</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>179.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>179.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>توصيلة جودا فولت لينك</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>توصيلات كهربائية</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -679,140 +679,140 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>شاحن جودا فولت باد / VoltPad</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>شواحن جدارية</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>aletawiksa, iblackstores</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>89.0 ر.س</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>194.0 ر.س</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>شاحن سيارة جودا</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>شواحن سيارة</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>aletawiksa</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="C11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, wjhtektelecome</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>69.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>106.38 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -873,17 +873,17 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>aletawiksa</t>
+          <t>mokab</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>اكسسوارات ايفون 18</t>
+          <t>ضمان : 24 شهر</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>9.0 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -895,17 +895,17 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>aletawiksa</t>
+          <t>mokab</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>اكسسوارات ايفون 18</t>
+          <t>ضمان : 24 شهر</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>9.0 ر.س</t>
+          <t>379.01 ر.س</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -917,17 +917,17 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>aletawiksa</t>
+          <t>mokab</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
+          <t>ضمان : 24 شهر</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>79.01 ر.س</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
+          <t>اكسسوارات ايفون 18</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>119.0 ر.س</t>
+          <t>9.0 ر.س</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
+          <t>اكسسوارات ايفون 18</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>9.0 ر.س</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
+          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>119.0 ر.س</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1027,12 +1027,12 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>al3bor-telecom</t>
+          <t>aletawiksa</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>بكج ثلاث اسلاك تايب سي الى تايب سي جودا JODA NeoFlow 60 ( 1م - 2م - 3م ) - أسود</t>
+          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1049,17 +1049,17 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>al3bor-telecom</t>
+          <t>aletawiksa</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة 20 JODA NeoPower بقوة 22.5 واط بسعة 20000 ملي امبير بمنفذين تايب سي و منفذ يو اس بي - اسود</t>
+          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1071,17 +1071,17 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>al3bor-telecom</t>
+          <t>aletawiksa</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا من تايب سي الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز بدقة 4K بطول 2 متر - اسود</t>
+          <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا من HDMI الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز 4K بطول 2 متر - اسود</t>
+          <t>بكج ثلاث اسلاك تايب سي الى تايب سي جودا JODA NeoFlow 60 ( 1م - 2م - 3م ) - أسود</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا GaN VOLTDOCK 45 بقدرة 45 واط بمنفذ تايب سيمع سلك قابل للسحب مدمج تايب سي - أسود</t>
+          <t>بطارية متنقلة 20 JODA NeoPower بقوة 22.5 واط بسعة 20000 ملي امبير بمنفذين تايب سي و منفذ يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>سلك تايب سي الى تايب سي BEACON 100 مضيء جودا سيليكون نايلون مظفر بقوة 100 واط بطول 1.2 متر - ابيض</t>
+          <t>سلك جودا من تايب سي الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز بدقة 4K بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
+          <t>سلك جودا من HDMI الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز 4K بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
+          <t>شاحن جداري جودا GaN VOLTDOCK 45 بقدرة 45 واط بمنفذ تايب سيمع سلك قابل للسحب مدمج تايب سي - أسود</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>سلك تايب سي الى تايب سي BEACON 100 مضيء جودا سيليكون نايلون مظفر بقوة 100 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
+          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
+          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>209.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
+          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
+          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
+          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>209.0 ر.س</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>349.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
+          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
+          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>49.0 ر.س</t>
+          <t>349.0 ر.س</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
+          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
+          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
+          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>49.0 ر.س</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
+          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
+          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1555,66 +1555,66 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>al3bor-telecom</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن سمارت للبطاريات الذكيه AA\AAA</t>
+          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>al3bor-telecom</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>جودا - منصة جودا بيك 4 منافذ تايب سي بقوة 240 واط - اسود</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>299.01 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>al3bor-telecom</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>جودا - جهاز تشغيل بطارية ومنفاخ هواء 4 في 1 بشاشة رقمية</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>299.01 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>جودا - باور بانك NeoPower سعة 20000mAh بقوة 22.5 واط ومنفذين - أسود</t>
+          <t>جودا - شاحن سمارت للبطاريات الذكيه AA\AAA</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>جودا - منصة جودا بيك 4 منافذ تايب سي بقوة 240 واط - اسود</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>299.01 ر.س</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1665,17 +1665,17 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>saada</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>توصيلة جودا 5 منافذ 5 متر 2990W مع حماية SASO + شاحن اورايمو باور كيوب 202 20 واط ميني تايب سي مع كيبل</t>
+          <t>جودا - جهاز تشغيل بطارية ومنفاخ هواء 4 في 1 بشاشة رقمية</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>80.0 ر.س</t>
+          <t>299.01 ر.س</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1687,17 +1687,17 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>جودا - باور بانك NeoPower سعة 20000mAh بقوة 22.5 واط ومنفذين - أسود</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1709,17 +1709,17 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -1731,17 +1731,17 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>saada</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>توصيلة جودا 5 منافذ 5 متر 2990W مع حماية SASO + شاحن اورايمو باور كيوب 202 20 واط ميني تايب سي مع كيبل</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>80.0 ر.س</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>بكج السرعة من جودا اليابانية</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>195.99 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1775,17 +1775,17 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>بكج المنزل 6 منتجات اصلية من جودا اليابانية</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>195.99 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1797,17 +1797,17 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>مايكل جوردن</t>
+          <t>جودا - شاحن سيارة بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>39.99 ر.س</t>
+          <t>143.75 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1819,17 +1819,17 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>آنا كارنينا</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>12.99 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1841,132 +1841,132 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>جوال تانك 1 متين 6.75 انش 120Hz FHD+ من شاندويليك، هاتف اتصال خارجي 12GB+256GB 20000mAh، هاتف ذكي 5G اندرويد 15 ان اف سي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>2090.0 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>جوال تانك 1 متين 6.75 انش 120Hz FHD+ من شاندويليك، هاتف اتصال خارجي 12GB+256GB 20000mAh، هاتف ذكي 5G اندرويد 15 ان اف سي</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>2090.0 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>jarir</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+          <t>مايكل جوردن</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>198.82 ر.س</t>
+          <t>39.99 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>jarir</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+          <t>آنا كارنينا</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>154.0 ر.س</t>
+          <t>12.99 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>جوال اكسبلور 1 للاستخدام الخارجي، جوال ذكي بشبكة الجيل الخامس 5G مقاوم للماء بنظام أندرويد 15، شاشة 6.78 بوصة بدقة 2.4 كيه، 12 جيجابايت+256 جيجابايت، بطارية 20000 ميلي أمبير/الساعة</t>
+          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>1790.0 ر.س</t>
+          <t>15.44 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج</t>
+          <t>خلطة فيز 160 جم من هاريبو</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>178.94 ر.س</t>
+          <t>9.44 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>جوال سامسونج جالكسي A16، ذكي يعمل بنظام اندرويد، ثنائي شرائح الاتصال، ذاكرة رام 4 جيجابايت، تخزين 128 جيجابايت، أسود (إصدار المملكة العربية السعودية)</t>
+          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>588.93 ر.س</t>
+          <t>9.44 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>جوال هونر تشويس T10 بشبكة الجيل الرابع 4G، شاشة عالية الدقة HD مقاس 6.75 بوصة، ترجمة فورية متزامنة بالذكاء الاصطناعي، كاميرات 13 + 5 ميجابكسل، ثنائي شرائح الاتصال، ذاكرة 4 + 64 جيجابايت، فضي</t>
+          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>389.0 ر.س</t>
+          <t>9.44 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>فيجير باور بانك 20000 مللي امبير في الساعة، شاحن محمول رفيع مع كيبلات متعددة مدمجة، بطارية شحن سريع عالية السعة مع شاشة عرض رقمية لايفون وسامسونج والجوالات - اسود</t>
+          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>95.99 ر.س</t>
+          <t>10.7 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>باور بانك في 9، شاحن محمول صغير 22.5 واط USB C 10000 مللي امبير في الساعة، حزمة بطارية شحن سريع بي دي، 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد - بينك</t>
+          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>6.62 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب A مع شحن سريع وحماية للهاتف واللابتوب 3 منافذ</t>
+          <t>حلوى شامالو روبينو مارشميلو من هاريبو، 70 جم</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>6.09 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>جوال هونر X5c، أزرق (تايدل بلو)</t>
+          <t>حلوى بيريز من هاريبو، 160 جم</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>444.51 ر.س</t>
+          <t>8.99 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>جوال سامسونج جالكسي A17 ال تي اي، ثنائي شرائح اتصال، سعة 128 جيجا توسع حتى 2 تيرا، اندرويد 14 وذاكرة رام 4 جيجابايت، معالج اكسينوس وشاشة اموليد 6.7 بوصة بدقة 1080x2220، معدل تحديث 90 هرتز، لون أسود</t>
+          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>660.0 ر.س</t>
+          <t>9.44 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>دار الأداب الهاربون والباقون</t>
+          <t>حلوى إسفنجية من هاريبو، 80 جرام</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>94.6 ر.س</t>
+          <t>6.62 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>زي بويلر التنكري للرجال على شكل افارهول بتصميم مستوحى من زي السجين الهارب بلون برتقالي من سميفيز - مقاس S، البوليستر</t>
+          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>146.91 ر.س</t>
+          <t>7.51 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Aireo Sports Pickleball Paddles | Carbon Fiber 3K Kevlar Enhancing Ball Control, Improved Spin | Falcon Pro Harpy Eagle Series | Thermoforming Construction for PRO Player, USAPA Standards</t>
+          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>306.11 ر.س</t>
+          <t>6.62 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>روبوتايم 3 دي بازل هارب</t>
+          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>201.51 ر.س</t>
+          <t>11.55 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>هاريبو جولد بيرز، 150 غرام، عبوة من قطعة واحدة</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>106.62 ر.س</t>
+          <t>9.98 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
+          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>69.83 ر.س</t>
+          <t>14.7 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
+          <t>محول امداد طاقة تيار مستمر 9 فولت لكاميرا تابو تي بي لينك تابو C100 C100/A</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>35.0 ر.س</t>
+          <t>24.99 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>وايلد ريبابليك لعبة قطيفة من بوكيت كينز ايكو هارب، حيوان محشو، 5 انش، مصنوعة من مواد معاد تدويرها، صديقة للبيئة</t>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>67.0 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء قارب هاربون للرجال</t>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>348.66 ر.س</t>
+          <t>51.0 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء قارب للرجال من هاربون، بيج داكن، مقاس 42 EU</t>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>284.88 ر.س</t>
+          <t>56.0 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء قارب هاربون للرجال، لون بيج داكن، مقاس 11.5</t>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>344.51 ر.س</t>
+          <t>40.0 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء هاربون على شكل قارب للرجال، كحلي، مقاس 42 EU</t>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>285.35 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>سبيري حذاء قارب هاربون للرجال، رمادي، 8.5</t>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>295.92 ر.س</t>
+          <t>186.25 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Sperry Mens Harpoon Crushback Slip on Sneaker</t>
+          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>375.62 ر.س</t>
+          <t>114.54 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>بيلا فيتا حذاء برقبة للنساء من هارب</t>
+          <t>راوتر ايه اكس 3000 بتقنية توصيل واي فاي 6 من تي بي-لينك، معيار اتصال لاسلكي 802.11ax، منفذ جيجابت، ثنائي التردد، يدعم VPN الخادم و المستخدم، مناسب لاجهزة من النوع ون ميش، (طراز Archer AX55)، أسود</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>281.29 ر.س</t>
+          <t>209.0 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>130.0 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>51.0 ر.س</t>
+          <t>115.67 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+          <t>TP - لينك حاقن PoE سلبي 48 فولت/18 واط TL-PoE4818G | محول جيجابت PoE | التوصيل والتشغيل | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>40.0 ر.س</t>
+          <t>80.64 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
+          <t>راوتر لاسلكي ارتشر Be230 V1 من تي بي لينك - 4 منافذ (ارتشر Be230)</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>114.54 ر.س</t>
+          <t>349.0 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>186.25 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>56.0 ر.س</t>
+          <t>13.1 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>130.0 ر.س</t>
+          <t>13.14 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
+          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>93.43 ر.س</t>
+          <t>49.3 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>راوتر ايه اكس 3000 بتقنية توصيل واي فاي 6 من تي بي-لينك، معيار اتصال لاسلكي 802.11ax، منفذ جيجابت، ثنائي التردد، يدعم VPN الخادم و المستخدم، مناسب لاجهزة من النوع ون ميش، (طراز Archer AX55)، أسود</t>
+          <t>مضخة مياه محمولة، موزع مياه كهربائي عالمي سعة 19 لتر مع مفتاح تشغيل وشحن USB، للتخييم والمطبخ وورشة العمل والمرأب من كوفونج (لون أبيض، عبوة من قطعة واحدة)</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>209.0 ر.س</t>
+          <t>19.0 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>رييوبي رف بطارية 40 فولت من لينك STM819</t>
+          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>158.14 ر.س</t>
+          <t>15.16 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
+          <t>مومنت مضخة توزيع مياه شرب كهربائية، مضخة زجاجة مياه اوتوماتيكية محمولة وقابلة لاعادة الشحن بمنفذ USB لاباريق المياه سعة 7.6-18.9 لتر للمكتب والمنزل والتخييم والمطبخ، ابيض</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>105.87 ر.س</t>
+          <t>20.4 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
+          <t>نظام المياه المعباة في قوارير 3.8 لتر/الدقيقة مضخة مياه معباه في قوارير 2.8 بار نظام مضخة توزيع المياه مع انبوب PE 6 م</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>115.67 ر.س</t>
+          <t>349.99 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>20.9 ر.س</t>
+          <t>24.5 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>20.9 ر.س</t>
+          <t>13.75 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>13.1 ر.س</t>
+          <t>11.0 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>13.14 ر.س</t>
+          <t>15.66 ر.س</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
+          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>49.3 ر.س</t>
+          <t>34.99 ر.س</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -2902,213 +2902,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>نظام المياه المعباة في قوارير 3.8 لتر/الدقيقة مضخة مياه معباه في قوارير 2.8 بار نظام مضخة توزيع المياه مع انبوب PE 6 م</t>
+          <t>استرو ايه اي منفاخ اطارات لاسلكي محمول 150 باوند لكل انش مربع</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>349.99 ر.س</t>
+          <t>99.98 ر.س</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>مومنت مضخة توزيع مياه شرب كهربائية، مضخة زجاجة مياه اوتوماتيكية محمولة وقابلة لاعادة الشحن بمنفذ USB لاباريق المياه سعة 7.6-18.9 لتر للمكتب والمنزل والتخييم والمطبخ، ابيض</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>20.4 ر.س</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه محمولة، موزع مياه كهربائي عالمي سعة 19 لتر مع مفتاح تشغيل وشحن USB، للتخييم والمطبخ وورشة العمل والمرأب من كوفونج (لون أبيض، عبوة من قطعة واحدة)</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>19.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>24.5 ر.س</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>15.16 ر.س</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>13.75 ر.س</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>15.66 ر.س</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>11.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>34.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>ibsun Water Pressure Booster Pump, 26.1 PSI, 100W, Automatic</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>180.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-16</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-17</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>48.33 ر.س</t>
+          <t>32.96 ر.س</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -679,70 +679,70 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>160.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>160.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>شاحن جودا فولت باد / VoltPad</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>شواحن جدارية</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>100.75 ر.س</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>100.75 ر.س</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, iblackstores</t>
+          <t>aletawiksa, iblackstores, amazon_sa</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>194.0 ر.س</t>
+          <t>413.12 ر.س</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, wjhtektelecome</t>
+          <t>aletawiksa, wjhtektelecome, amazon_sa</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>28.0 ر.س</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>106.38 ر.س</t>
+          <t>82.95 ر.س</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1929,44 +1929,44 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>مايكل جوردن</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>39.99 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>آنا كارنينا</t>
+          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>12.99 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
+          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>15.44 ر.س</t>
+          <t>61.99 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>خلطة فيز 160 جم من هاريبو</t>
+          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>9.44 ر.س</t>
+          <t>188.99 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>9.44 ر.س</t>
+          <t>113.3 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
+          <t>INIU Power Bank, 20000mAh 45W PD Fast Charging Small Portable Charger</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>9.44 ر.س</t>
+          <t>129.99 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلي بنكهة الخوخ من هاريبو، 160 جرام</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>10.7 ر.س</t>
+          <t>198.82 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>6.62 ر.س</t>
+          <t>154.0 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>حلوى شامالو روبينو مارشميلو من هاريبو، 70 جم</t>
+          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>6.09 ر.س</t>
+          <t>229.0 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>حلوى بيريز من هاريبو، 160 جم</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>8.99 ر.س</t>
+          <t>128.14 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلي على شكل ديدان 160 جرام</t>
+          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>9.44 ر.س</t>
+          <t>169.0 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>حلوى إسفنجية من هاريبو، 80 جرام</t>
+          <t>باور بانك CP25 سعة 20000 مللي امبير في الساعة بقدرة 55 واط كحد اقصى مع كيبل USB-C مدمج من كوك تيك</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>6.62 ر.س</t>
+          <t>122.55 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>7.51 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
+          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>6.62 ر.س</t>
+          <t>138.9 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
+          <t>باور بانك CP24 20000 مللي امبير في الساعة 40 واط سي سي سي مع كابلات مزدوجة مدمجة من كوك تيك</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>11.55 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>هاريبو جولد بيرز، 150 غرام، عبوة من قطعة واحدة</t>
+          <t>محول امداد طاقة تيار مستمر 9 فولت لكاميرا تابو تي بي لينك تابو C100 C100/A</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>9.98 ر.س</t>
+          <t>24.99 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
+          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>14.7 ر.س</t>
+          <t>66.0 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>محول امداد طاقة تيار مستمر 9 فولت لكاميرا تابو تي بي لينك تابو C100 C100/A</t>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>24.99 ر.س</t>
+          <t>51.0 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>56.0 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>51.0 ر.س</t>
+          <t>40.0 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>56.0 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>40.0 ر.س</t>
+          <t>114.54 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>186.25 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+          <t>راوتر ايه اكس 3000 بتقنية توصيل واي فاي 6 من تي بي-لينك، معيار اتصال لاسلكي 802.11ax، منفذ جيجابت، ثنائي التردد، يدعم VPN الخادم و المستخدم، مناسب لاجهزة من النوع ون ميش، (طراز Archer AX55)، أسود</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>186.25 ر.س</t>
+          <t>209.0 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
+          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>114.54 ر.س</t>
+          <t>93.43 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>راوتر ايه اكس 3000 بتقنية توصيل واي فاي 6 من تي بي-لينك، معيار اتصال لاسلكي 802.11ax، منفذ جيجابت، ثنائي التردد، يدعم VPN الخادم و المستخدم، مناسب لاجهزة من النوع ون ميش، (طراز Archer AX55)، أسود</t>
+          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>209.0 ر.س</t>
+          <t>130.0 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>130.0 ر.س</t>
+          <t>112.87 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
+          <t>TP - لينك حاقن PoE سلبي 48 فولت/18 واط TL-PoE4818G | محول جيجابت PoE | التوصيل والتشغيل | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>115.67 ر.س</t>
+          <t>80.42 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE سلبي 48 فولت/18 واط TL-PoE4818G | محول جيجابت PoE | التوصيل والتشغيل | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>80.64 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>راوتر لاسلكي ارتشر Be230 V1 من تي بي لينك - 4 منافذ (ارتشر Be230)</t>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>349.0 ر.س</t>
+          <t>13.14 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>20.9 ر.س</t>
+          <t>13.1 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>13.1 ر.س</t>
+          <t>49.3 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+          <t>مضخة مياه محمولة، موزع مياه كهربائي عالمي سعة 19 لتر مع مفتاح تشغيل وشحن USB، للتخييم والمطبخ وورشة العمل والمرأب من كوفونج (لون أبيض، عبوة من قطعة واحدة)</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>13.14 ر.س</t>
+          <t>19.0 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
+          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>49.3 ر.س</t>
+          <t>15.16 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه محمولة، موزع مياه كهربائي عالمي سعة 19 لتر مع مفتاح تشغيل وشحن USB، للتخييم والمطبخ وورشة العمل والمرأب من كوفونج (لون أبيض، عبوة من قطعة واحدة)</t>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>19.0 ر.س</t>
+          <t>13.75 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>15.16 ر.س</t>
+          <t>24.5 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>مومنت مضخة توزيع مياه شرب كهربائية، مضخة زجاجة مياه اوتوماتيكية محمولة وقابلة لاعادة الشحن بمنفذ USB لاباريق المياه سعة 7.6-18.9 لتر للمكتب والمنزل والتخييم والمطبخ، ابيض</t>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>20.4 ر.س</t>
+          <t>11.0 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>نظام المياه المعباة في قوارير 3.8 لتر/الدقيقة مضخة مياه معباه في قوارير 2.8 بار نظام مضخة توزيع المياه مع انبوب PE 6 م</t>
+          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>349.99 ر.س</t>
+          <t>15.66 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
+          <t>مومنت مضخة توزيع مياه شرب كهربائية، مضخة زجاجة مياه اوتوماتيكية محمولة وقابلة لاعادة الشحن بمنفذ USB لاباريق المياه سعة 7.6-18.9 لتر للمكتب والمنزل والتخييم والمطبخ، ابيض</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>24.5 ر.س</t>
+          <t>18.36 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+          <t>استرو ايه اي منفاخ اطارات لاسلكي محمول 150 باوند لكل انش مربع</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>13.75 ر.س</t>
+          <t>99.98 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+          <t>ibsun Water Pressure Booster Pump, 26.1 PSI, 100W, Automatic</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>11.0 ر.س</t>
+          <t>180.0 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
+          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>15.66 ر.س</t>
+          <t>34.99 ر.س</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>34.99 ر.س</t>
+          <t>250.78 ر.س</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -2902,15 +2902,1225 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>استرو ايه اي منفاخ اطارات لاسلكي محمول 150 باوند لكل انش مربع</t>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>99.98 ر.س</t>
+          <t>127.2 ر.س</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>139.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>182.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>160.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>188.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>113.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>128.14 ر.س</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>78.7 ر.س</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>198.82 ر.س</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>159.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>154.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>119.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>1279.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>جهاز تابلت باد 10 بيبرمات مقاس 12.1 بوصة وواي فاي وذاكرة رام 8 جيجابايت وذاكرة 256 جيجابايت مع حافظة لوحة المفاتيح مجانية وقلم هونر تشويس من هونر- إصدار الشرق الأوسط</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>1449.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>ديوالت بطاريات ليثيوم ايون DCB135C من قطعتين 12 فولت 3 امبير / 5 امبير في الساعة ومجموعة شاحن بادئ التشغيل</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>807.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>شاومي ريدمي باد برو 5G (رمادي جرافيت RAM 8GB وتخزين 256GB) - شاشة 12.1 انش 2.5K | منصة موبايل سناب دراجون® الجيل السابع الجيل الثاني 4 نانومتر | معدل تحديث سلس 120Hz | مكبرات صوت رباعية مع دولبي اتموس</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>1400.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>محول USB C الى طرف رفيع، محول شحن سريع 100 واط PD3.0 لشاحن مربع الى طاقة نوع سي، متوافق مع ثينك باد، ماك بوك، كروم بوك، سويتش، اي اجهزة USB-C، مدخل 15-20 فولت تيار مستمر</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>29.15 ر.س</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>3299.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، WPS اوفيس (بدون قلم)، كيبورد وارد، هواوي كير حصري لمدة عام + (اخضر)</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>2199.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>بادئ تشغيل جديد متوافق مع/بديل لـ 0.6 كيلو واط، 12 فولت، 8 اسنان، دوران سي سي دبليو كوشمان تيرف تراكستر 12 فولت 19714 103-074 2702893 S-80193 M900397 M2T13481 31100-78A00 91-27-33ددد10</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>684.11 ر.س</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بدون قلم، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس + هواوي كير لمدة عام واحد (ابيض)</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>2199.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>جهاز هواوي ميت باد برو 12مقاس 12.2 بوصة بدقة 2800×1840 ذاكرة رام 12 جيجابايت وروم 512 جيجابايت وواي فاي وكيبورد (Morandi-W09DK) وثماني النواة وبطارية ليثيوم بوليمر لون أخضر</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>2549.05 ر.س</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>HUAWEI MatePad SE 11'' 8+128GB Nebula Grey Tablet, FullView Display, Large Capacity Battery, 1-Year Amazon Exclusive Huawei Care+</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>863.29 ر.س</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>شاحن بطارية للدراجة النارية 6 فولت/12 فولت بادئ الشحن التلقائي</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>100.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>1454.16 ر.س</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت ريدمي باد 2 8GB + 256GB، 11 انش، بطارية 9000mAh، اخضر (الشاحن متضمن)</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>1028.19 ر.س</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>445.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>549.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>فيوسونيك شاشة العاب VX2479A-HD-PRO 61 سم 240 هرتز</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>389.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>789.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>457.54 ر.س</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب تي يو اف VG27AQ5A-J من اسوس: 27 انش، كيو اتش دي (2560×1440)، 210 هرتز (او سي)، تقنية IPS سريعة، مزامنة ELMB، 0.3ms GTG (دقيقة)، مكبر صوت ستيريو، مركز عرض ويدجيت، اسود - اصدار قوس</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>799.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>422.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>كورسير مبرد سائل لوحدة المعالجة المركزية 240 RS ARGB AIO من نوتيلوس 240 ملم متوافق مع انتل LGA 1851/1700 وAMD AM5/AM4، يتضمن مروحتين RS120 ARGB - اسود</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>343.88 ر.س</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>مبرد وحدة المعالجة المركزية السائل نيكسورا 240 من سودوكو: مبرد وحدة المعالجة المركزية AIO 240 ملم مع مضخة PWM ورأس مضخة ARGB - تبريد مائي مع مراوح اف دي بي لانتل LGA 1851/1700/1200/115X AMD AM5/AM4 - اسود</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>167.52 ر.س</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>Ocypus Iota L24 BK 240mm AIO Liquid CPU Cooler with Temp Digital Display</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>299.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240 هرتز FHD 1080p، لوحة VA، وقت استجابة 2 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر 3 جوانب بدون إطار نحيفة للغاية، 99% اس ار جي بي، فلتر للضوء الأزرق، HDMI وDP، لون أسود من فيوفيجن</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>399.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>389.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>549.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>470.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب KTC مقاس 24 بوصة 240 هرتز ودقة FHD 1080P، لوحة IPS سريعة، تقنية</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>549.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>45.85 ر.س</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>35.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>58.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>88.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>75.87 ر.س</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>88.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>48.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>28.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع سامسونج وآيفون وهواوي P60 بـ 3 منافذ بقوة 130.0 واط مع شحن سريع وحماية متعددة</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>129.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>79.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>35.79 ر.س</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>79.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>49.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>AstroAI Jump Starter Portable Car Jump Starter 12V Car Battery Charger</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>254.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>85.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-17</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-18</t>
         </is>
       </c>
     </row>
@@ -644,105 +644,105 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>11.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>32.96 ر.س</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>160.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>160.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>شاحن جودا فولت باد / VoltPad</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>شواحن جدارية</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>100.75 ر.س</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>100.75 ر.س</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, iblackstores, amazon_sa</t>
+          <t>aletawiksa, iblackstores</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>413.12 ر.س</t>
+          <t>194.0 ر.س</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, wjhtektelecome, amazon_sa</t>
+          <t>aletawiksa, wjhtektelecome</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>28.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>82.95 ر.س</t>
+          <t>106.38 ر.س</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1731,17 +1731,17 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>saada</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>توصيلة جودا 5 منافذ 5 متر 2990W مع حماية SASO + شاحن اورايمو باور كيوب 202 20 واط ميني تايب سي مع كيبل</t>
+          <t>بكج السرعة من جودا اليابانية</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>80.0 ر.س</t>
+          <t>195.99 ر.س</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>بكج السرعة من جودا اليابانية</t>
+          <t>بكج المنزل 6 منتجات اصلية من جودا اليابانية</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>بكج المنزل 6 منتجات اصلية من جودا اليابانية</t>
+          <t>جودا - شاحن سيارة بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>195.99 ر.س</t>
+          <t>143.75 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن سيارة بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>143.75 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -1885,17 +1885,17 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1907,17 +1907,17 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>jarir</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>مايكل جوردن</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>39.99 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1929,22 +1929,22 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>amazon_sa</t>
+          <t>jarir</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>آنا كارنينا</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>12.99 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
+          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>61.99 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
+          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>188.99 ر.س</t>
+          <t>61.99 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>113.3 ر.س</t>
+          <t>188.99 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>198.82 ر.س</t>
+          <t>229.0 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>154.0 ر.س</t>
+          <t>82.95 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>229.0 ر.س</t>
+          <t>113.3 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>128.14 ر.س</t>
+          <t>198.82 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>169.0 ر.س</t>
+          <t>154.0 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>باور بانك CP25 سعة 20000 مللي امبير في الساعة بقدرة 55 واط كحد اقصى مع كيبل USB-C مدمج من كوك تيك</t>
+          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>122.55 ر.س</t>
+          <t>169.0 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+          <t>INIU Power Bank, Smallest 20000mAh 22.5W Fast Charging Portable Charger</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>111.14 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
+          <t>باور بانك CP25 سعة 20000 مللي امبير في الساعة بقدرة 55 واط كحد اقصى مع كيبل USB-C مدمج من كوك تيك</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>138.9 ر.س</t>
+          <t>122.55 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>باور بانك CP24 20000 مللي امبير في الساعة 40 واط سي سي سي مع كابلات مزدوجة مدمجة من كوك تيك</t>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,1863 +2264,15 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>محول امداد طاقة تيار مستمر 9 فولت لكاميرا تابو تي بي لينك تابو C100 C100/A</t>
+          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>24.99 ر.س</t>
+          <t>138.9 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك حاقن عبر الايثرنت | محول PoE 48 فولت تيار مستمر | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE4824G)</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>66.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>51.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>56.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>40.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>بطارية TBL-53A3000 لراوتر تي بي لينك M7450 M7650 واي فاي 2000 مللي امبير في الساعة 3.8 فولت</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>114.54 ر.س</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>186.25 ر.س</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>راوتر ايه اكس 3000 بتقنية توصيل واي فاي 6 من تي بي-لينك، معيار اتصال لاسلكي 802.11ax، منفذ جيجابت، ثنائي التردد، يدعم VPN الخادم و المستخدم، مناسب لاجهزة من النوع ون ميش، (طراز Archer AX55)، أسود</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>209.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>بطارية بديلة لبوز 423816 ساوند لينك مايكرو 3.7 فولت/3400 مللي امبير في الساعة من زوفكوس</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>93.43 ر.س</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>130.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>112.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>TP - لينك حاقن PoE سلبي 48 فولت/18 واط TL-PoE4818G | محول جيجابت PoE | التوصيل والتشغيل | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>80.42 ر.س</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>20.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>13.14 ر.س</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>20.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>13.1 ر.س</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>49.3 ر.س</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه محمولة، موزع مياه كهربائي عالمي سعة 19 لتر مع مفتاح تشغيل وشحن USB، للتخييم والمطبخ وورشة العمل والمرأب من كوفونج (لون أبيض، عبوة من قطعة واحدة)</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>19.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>15.16 ر.س</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>13.75 ر.س</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>24.5 ر.س</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>11.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>15.66 ر.س</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>مومنت مضخة توزيع مياه شرب كهربائية، مضخة زجاجة مياه اوتوماتيكية محمولة وقابلة لاعادة الشحن بمنفذ USB لاباريق المياه سعة 7.6-18.9 لتر للمكتب والمنزل والتخييم والمطبخ، ابيض</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>18.36 ر.س</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>استرو ايه اي منفاخ اطارات لاسلكي محمول 150 باوند لكل انش مربع</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>99.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>ibsun Water Pressure Booster Pump, 26.1 PSI, 100W, Automatic</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>180.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>34.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>250.78 ر.س</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>127.2 ر.س</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>139.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>182.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>160.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>188.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>113.3 ر.س</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>128.14 ر.س</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>78.7 ر.س</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>198.82 ر.س</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>159.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>154.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>119.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>1279.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>جهاز تابلت باد 10 بيبرمات مقاس 12.1 بوصة وواي فاي وذاكرة رام 8 جيجابايت وذاكرة 256 جيجابايت مع حافظة لوحة المفاتيح مجانية وقلم هونر تشويس من هونر- إصدار الشرق الأوسط</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>1449.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>ديوالت بطاريات ليثيوم ايون DCB135C من قطعتين 12 فولت 3 امبير / 5 امبير في الساعة ومجموعة شاحن بادئ التشغيل</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>807.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>شاومي ريدمي باد برو 5G (رمادي جرافيت RAM 8GB وتخزين 256GB) - شاشة 12.1 انش 2.5K | منصة موبايل سناب دراجون® الجيل السابع الجيل الثاني 4 نانومتر | معدل تحديث سلس 120Hz | مكبرات صوت رباعية مع دولبي اتموس</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>1400.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>محول USB C الى طرف رفيع، محول شحن سريع 100 واط PD3.0 لشاحن مربع الى طاقة نوع سي، متوافق مع ثينك باد، ماك بوك، كروم بوك، سويتش، اي اجهزة USB-C، مدخل 15-20 فولت تيار مستمر</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>29.15 ر.س</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>3299.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، WPS اوفيس (بدون قلم)، كيبورد وارد، هواوي كير حصري لمدة عام + (اخضر)</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>2199.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>بادئ تشغيل جديد متوافق مع/بديل لـ 0.6 كيلو واط، 12 فولت، 8 اسنان، دوران سي سي دبليو كوشمان تيرف تراكستر 12 فولت 19714 103-074 2702893 S-80193 M900397 M2T13481 31100-78A00 91-27-33ددد10</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>684.11 ر.س</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بدون قلم، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس + هواوي كير لمدة عام واحد (ابيض)</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>2199.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>جهاز هواوي ميت باد برو 12مقاس 12.2 بوصة بدقة 2800×1840 ذاكرة رام 12 جيجابايت وروم 512 جيجابايت وواي فاي وكيبورد (Morandi-W09DK) وثماني النواة وبطارية ليثيوم بوليمر لون أخضر</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>2549.05 ر.س</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>HUAWEI MatePad SE 11'' 8+128GB Nebula Grey Tablet, FullView Display, Large Capacity Battery, 1-Year Amazon Exclusive Huawei Care+</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>863.29 ر.س</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>شاحن بطارية للدراجة النارية 6 فولت/12 فولت بادئ الشحن التلقائي</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>100.75 ر.س</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>1454.16 ر.س</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت ريدمي باد 2 8GB + 256GB، 11 انش، بطارية 9000mAh، اخضر (الشاحن متضمن)</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>1028.19 ر.س</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>445.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>شاشة تي يو اف للألعاب سلسلة 5 VG279QM5A-J، 27 بوصة FHD (1920 × 1080) IPS سريع، 240 Hz، 0.3 مللي ثانية، AMD فري سينك بريميوم، انفيديا جي سينك، شاشة سوداء - إصدار ارارك من اسوس</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>549.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>فيوسونيك شاشة العاب VX2479A-HD-PRO 61 سم 240 هرتز</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>389.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب 27 انش 2K 240Hz IPS QHD (2560x1440) من كروا</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>789.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>457.54 ر.س</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>شاشة العاب تي يو اف VG27AQ5A-J من اسوس: 27 انش، كيو اتش دي (2560×1440)، 210 هرتز (او سي)، تقنية IPS سريعة، مزامنة ELMB، 0.3ms GTG (دقيقة)، مكبر صوت ستيريو، مركز عرض ويدجيت، اسود - اصدار قوس</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>799.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>422.97 ر.س</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>كورسير مبرد سائل لوحدة المعالجة المركزية 240 RS ARGB AIO من نوتيلوس 240 ملم متوافق مع انتل LGA 1851/1700 وAMD AM5/AM4، يتضمن مروحتين RS120 ARGB - اسود</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>343.88 ر.س</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>مبرد وحدة المعالجة المركزية السائل نيكسورا 240 من سودوكو: مبرد وحدة المعالجة المركزية AIO 240 ملم مع مضخة PWM ورأس مضخة ARGB - تبريد مائي مع مراوح اف دي بي لانتل LGA 1851/1700/1200/115X AMD AM5/AM4 - اسود</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>167.52 ر.س</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>Ocypus Iota L24 BK 240mm AIO Liquid CPU Cooler with Temp Digital Display</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>299.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240 هرتز FHD 1080p، لوحة VA، وقت استجابة 2 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر 3 جوانب بدون إطار نحيفة للغاية، 99% اس ار جي بي، فلتر للضوء الأزرق، HDMI وDP، لون أسود من فيوفيجن</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>399.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>389.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>549.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>470.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>شاشة ألعاب KTC مقاس 24 بوصة 240 هرتز ودقة FHD 1080P، لوحة IPS سريعة، تقنية</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>549.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B137" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C137" s="6" t="inlineStr">
-        <is>
-          <t>45.85 ر.س</t>
-        </is>
-      </c>
-      <c r="D137" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>35.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B139" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C139" s="6" t="inlineStr">
-        <is>
-          <t>58.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>88.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>75.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>88.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
-        </is>
-      </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>48.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
-        </is>
-      </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>28.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع سامسونج وآيفون وهواوي P60 بـ 3 منافذ بقوة 130.0 واط مع شحن سريع وحماية متعددة</t>
-        </is>
-      </c>
-      <c r="C145" s="6" t="inlineStr">
-        <is>
-          <t>129.89 ر.س</t>
-        </is>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>79.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="20" customHeight="1">
-      <c r="A147" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B147" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
-        </is>
-      </c>
-      <c r="C147" s="6" t="inlineStr">
-        <is>
-          <t>35.79 ر.س</t>
-        </is>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B148" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C148" s="6" t="inlineStr">
-        <is>
-          <t>79.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B149" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C149" s="6" t="inlineStr">
-        <is>
-          <t>49.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D149" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>AstroAI Jump Starter Portable Car Jump Starter 12V Car Battery Charger</t>
-        </is>
-      </c>
-      <c r="C150" s="6" t="inlineStr">
-        <is>
-          <t>254.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="20" customHeight="1">
-      <c r="A151" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C151" s="6" t="inlineStr">
-        <is>
-          <t>85.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D151" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-18</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -574,245 +574,245 @@
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>منصة جودا هاربو لشحن البطاريات</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>منصات ومحطات شحن</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>al3bor-telecom, amazon_sa</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>35.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>233.81 ر.س</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>توصيلة جودا فولت لينك</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>توصيلات كهربائية</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>منتجات السيارة</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>بطارية راف باور</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>بطاريات متنقلة</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>شاحن جودا فولت باد / VoltPad</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>شواحن جدارية</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>179.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>179.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>100.75 ر.س</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>100.75 ر.س</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>توصيلة جودا فولت لينك</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>توصيلات كهربائية</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>كيبل جودا 240 واط</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>كيابل شحن</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>aletawiksa, iblackstores</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>194.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>منتجات السيارة</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>بطارية راف باور</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>بطاريات متنقلة</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>شاحن جودا فولت باد / VoltPad</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>شواحن جدارية</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>كيبل جودا 240 واط</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>كيابل شحن</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>شاحن سيارة جودا</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>شواحن سيارة</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa, iblackstores</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>194.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>شاحن سيارة جودا</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>شواحن سيارة</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>aletawiksa, wjhtektelecome</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>106.38 ر.س</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -917,17 +917,17 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>mokab</t>
+          <t>aletawiksa</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>ضمان : 24 شهر</t>
+          <t>اكسسوارات ايفون 18</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>79.01 ر.س</t>
+          <t>9.0 ر.س</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>اكسسوارات ايفون 18</t>
+          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>9.0 ر.س</t>
+          <t>99.0 ر.س</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 22.5 واط بمنفذين يو اس بي و منفذ تايب سي - اسود</t>
+          <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>119.0 ر.س</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>قاعدة سياره مع شحن لاسلكي - 15 واط - من JODA - موديل MAGQ C1</t>
+          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>119.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 60 واط بطول 1 متر - اسود</t>
+          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>كيبل JODA نايلون تايب سي الى تايب سي بقوة 240 واط بطول 1 متر - اسود</t>
+          <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1071,17 +1071,17 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>aletawiksa</t>
+          <t>al3bor-telecom</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة JODA بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>بكج ثلاث اسلاك تايب سي الى تايب سي جودا JODA NeoFlow 60 ( 1م - 2م - 3م ) - أسود</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>بكج ثلاث اسلاك تايب سي الى تايب سي جودا JODA NeoFlow 60 ( 1م - 2م - 3م ) - أسود</t>
+          <t>بطارية متنقلة 20 JODA NeoPower بقوة 22.5 واط بسعة 20000 ملي امبير بمنفذين تايب سي و منفذ يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة 20 JODA NeoPower بقوة 22.5 واط بسعة 20000 ملي امبير بمنفذين تايب سي و منفذ يو اس بي - اسود</t>
+          <t>سلك جودا من تايب سي الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز بدقة 4K بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا من تايب سي الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز بدقة 4K بطول 2 متر - اسود</t>
+          <t>سلك جودا من HDMI الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز 4K بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا من HDMI الى HDMI الترا فيجن 60 هرتز بدقة 8K و 120 هرتز 4K بطول 2 متر - اسود</t>
+          <t>شاحن جداري جودا GaN VOLTDOCK 45 بقدرة 45 واط بمنفذ تايب سيمع سلك قابل للسحب مدمج تايب سي - أسود</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا GaN VOLTDOCK 45 بقدرة 45 واط بمنفذ تايب سيمع سلك قابل للسحب مدمج تايب سي - أسود</t>
+          <t>سلك تايب سي الى تايب سي BEACON 100 مضيء جودا سيليكون نايلون مظفر بقوة 100 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>89.0 ر.س</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>سلك تايب سي الى تايب سي BEACON 100 مضيء جودا سيليكون نايلون مظفر بقوة 100 واط بطول 1.2 متر - ابيض</t>
+          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>159.0 ر.س</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>فيش سفر جودا TwistGo 70 متعدد المداخل بقوة 70 واط لاكثر من 200 دولة</t>
+          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>159.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagZ 10 ماج سيف بسعة 10000 ملي امبير 15 واط شحن ماج سيف 20 واط منفذ PD</t>
+          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 100 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري جودا VoltLux بقوة 70 واط بمنفذ تايب سي ومنفذ يو اس بي مع سلك تايب سي مدمج 70 سم بشاشة رقمية - رمادي</t>
+          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA بسعة 10000 ملي امبير بقوة 20 واط بي دي 15 واط ماج سيف - اسود</t>
+          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>209.0 ر.س</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>منفاخ هواء إيرفولت بي بلس جودا بايقاف تلقائي ذكي وقوة هواء 150 PSI - أسود</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>209.0 ر.س</t>
+          <t>179.0 ر.س</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف أبيض</t>
+          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>منصة JODA هاربو 8 بطاريات ليثيوم - شفاف اسود</t>
+          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>توصيلة VOLTCORE6 جودا 6 منافذ طاقة و 3 منافذ تايب سي ومنفذ يو اس بي - اسود</t>
+          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>349.0 ر.س</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA رقيمة 27000 امبير W200 بكيبل تايب سي مدمج - اسود</t>
+          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>349.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري عالمي JODA TOUR 70 بقوة 70 واط بتقنية جان ثلاث منافذ تايب سي و منفذين يو اس بي - اسود</t>
+          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>129.0 ر.س</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>باور بانك جودا Halo 10 بقوة 22.5 واط بسعة 10000 ملي امبير سلك تايب سي مدمج 19 سم - برتقالي</t>
+          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>129.0 ر.س</t>
+          <t>49.0 ر.س</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا LUCID 60 تايب سي الى تايب سي بقوة 60 واط بطول 1.2 متر - ابيض</t>
+          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>49.0 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTCOIL 65 فولت كويل بقوة 65 واط بمنفذ تايب سي وسلك مدمج 70 سم</t>
+          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>149.0 ر.س</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>بطارية JODA MagTack بقوة 35 واط بسعة 10000 ملي امبير ماج سيف مثبت للجوال مع سلك مدمج تايب سي - أخضر</t>
+          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>149.0 ر.س</t>
+          <t>79.0 ر.س</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>سلك جودا تايب سي الى تايب سي فايبر  قماشي بقوة 60 بطول 2 متر - اسود</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>79.0 ر.س</t>
+          <t>109.0 ر.س</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - أبيض</t>
+          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -1599,22 +1599,22 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>al3bor-telecom</t>
+          <t>iblackstores</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>شاحن جداري JODA VOLTPOD45 بقدرة شحن 45 واط منفذين تايب سي - برتقالي</t>
+          <t>جودا - شاحن سمارت للبطاريات الذكيه AA\AAA</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>رابط مؤكد</t>
+          <t>بحث تقديري</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن سمارت للبطاريات الذكيه AA\AAA</t>
+          <t>جودا - منصة جودا بيك 4 منافذ تايب سي بقوة 240 واط - اسود</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>299.01 ر.س</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>جودا - منصة جودا بيك 4 منافذ تايب سي بقوة 240 واط - اسود</t>
+          <t>جودا - جهاز تشغيل بطارية ومنفاخ هواء 4 في 1 بشاشة رقمية</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>جودا - جهاز تشغيل بطارية ومنفاخ هواء 4 في 1 بشاشة رقمية</t>
+          <t>جودا - باور بانك NeoPower سعة 20000mAh بقوة 22.5 واط ومنفذين - أسود</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>299.01 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>جودا - باور بانك NeoPower سعة 20000mAh بقوة 22.5 واط ومنفذين - أسود</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1709,17 +1709,17 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>بكج السرعة من جودا اليابانية</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>195.99 ر.س</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>بكج السرعة من جودا اليابانية</t>
+          <t>بكج المنزل 6 منتجات اصلية من جودا اليابانية</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>بكج المنزل 6 منتجات اصلية من جودا اليابانية</t>
+          <t>جودا - شاحن سيارة بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>195.99 ر.س</t>
+          <t>143.75 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن سيارة بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>143.75 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -1863,17 +1863,17 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1885,17 +1885,17 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>jarir</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>مايكل جوردن</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>39.99 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>مايكل جوردن</t>
+          <t>آنا كارنينا</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>39.99 ر.س</t>
+          <t>12.99 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1929,22 +1929,22 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>آنا كارنينا</t>
+          <t>دار الأداب الهاربون والباقون</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>12.99 ر.س</t>
+          <t>94.6 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>سبيري حذاء هاربون على شكل قارب للرجال، كحلي، مقاس 42 EU</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>139.0 ر.س</t>
+          <t>285.69 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
+          <t>بيلا فيتا حذاء برقبة للنساء من هارب</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>283.45 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
+          <t>روبوتايم 3 دي بازل هارب</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>61.99 ر.س</t>
+          <t>201.33 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
+          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>188.99 ر.س</t>
+          <t>35.0 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>INIU Power Bank, 20000mAh 45W PD Fast Charging Small Portable Charger</t>
+          <t>وايلد ريبابليك لعبة قطيفة من بوكيت كينز ايكو هارب، حيوان محشو، 5 انش، مصنوعة من مواد معاد تدويرها، صديقة للبيئة</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>129.99 ر.س</t>
+          <t>67.48 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
+          <t>سبيري حذاء قارب هاربون للرجال</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>229.0 ر.س</t>
+          <t>348.39 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+          <t>سبيري حذاء رياضي هاربون كراش باك سهل الارتداء للرجال</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>82.95 ر.س</t>
+          <t>346.02 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>سبيري حذاء قارب للرجال من هاربون، بيج داكن، مقاس 42 EU</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>113.3 ر.س</t>
+          <t>285.52 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+          <t>سبيري حذاء قارب هاربون للرجال، لون بيج داكن، مقاس 11.5</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>198.82 ر.س</t>
+          <t>345.37 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+          <t>ليجو نينجاجو سي باوند: كول ان سكوبا جير مع مسدس هاربون</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>154.0 ر.س</t>
+          <t>184.0 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000</t>
+          <t>Sperry Mens Harpoon Crushback Slip on Sneaker</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>169.0 ر.س</t>
+          <t>353.57 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>INIU Power Bank, Smallest 20000mAh 22.5W Fast Charging Portable Charger</t>
+          <t>سبيري حذاء قارب هاربون للرجال، رمادي، 8.5</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>111.14 ر.س</t>
+          <t>289.36 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>باور بانك CP25 سعة 20000 مللي امبير في الساعة بقدرة 55 واط كحد اقصى مع كيبل USB-C مدمج من كوك تيك</t>
+          <t>الدو صندل هاربا مفتوح عند الاصابع للنساء من 20 هاربا</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>122.55 ر.س</t>
+          <t>263.0 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>1279.0 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,15 +2264,257 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
+          <t>ديوالت بطاريات ليثيوم ايون DCB135C من قطعتين 12 فولت 3 امبير / 5 امبير في الساعة ومجموعة شاحن بادئ التشغيل</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>138.9 ر.س</t>
+          <t>807.0 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد SE بشاشة 11 بوصة، ذاكرة 4+128 جيجابايت، مع قلم ام بن لايت، شاشة فول فيو وبطارية ذات سعة كبيرة مع ركن خاص بالأطفال</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>720.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هونر باد X8a 4+ واي فاي 128 جيجا مع غطاء حماية قلاب، رمادي</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>799.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، WPS اوفيس (بدون قلم)، كيبورد وارد، هواوي كير حصري لمدة عام + (اخضر)</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>2199.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>3299.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بدون قلم، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس + هواوي كير لمدة عام واحد (ابيض)</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>2199.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>جهاز هواوي ميت باد برو 12مقاس 12.2 بوصة بدقة 2800×1840 ذاكرة رام 12 جيجابايت وروم 512 جيجابايت وواي فاي وكيبورد (Morandi-W09DK) وثماني النواة وبطارية ليثيوم بوليمر لون أخضر</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>2549.05 ر.س</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>3299.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>HUAWEI MatePad SE 11'' 8+128GB Nebula Grey Tablet, FullView Display, Large Capacity Battery, 1-Year Amazon Exclusive Huawei Care+</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>863.29 ر.س</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>شاحن بطارية للدراجة النارية 6 فولت/12 فولت بادئ الشحن التلقائي</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>100.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>1454.16 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت ريدمي باد 2 8GB + 256GB شاشة 11 انش 2.5K 90Hz ميديا تيك هيليو G100 الترا جرين (الشاحن متضمن)</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>992.04 ر.س</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-19</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-20</t>
         </is>
       </c>
     </row>
@@ -574,245 +574,245 @@
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>منصة جودا هاربو لشحن البطاريات</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>منصات ومحطات شحن</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>179.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>179.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>توصيلة جودا فولت لينك</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>توصيلات كهربائية</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>منتجات السيارة</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>بطارية راف باور</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>بطاريات متنقلة</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>شاحن جودا فولت باد / VoltPad</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>شواحن جدارية</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>كيبل جودا 240 واط</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>كيابل شحن</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>al3bor-telecom, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>35.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>233.81 ر.س</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>aletawiksa, iblackstores</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>194.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>توصيلة جودا فولت لينك</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>توصيلات كهربائية</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>منتجات السيارة</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>بطارية راف باور</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>بطاريات متنقلة</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>شاحن جودا فولت باد / VoltPad</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>شواحن جدارية</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>100.75 ر.س</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>100.75 ر.س</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>كيبل جودا 240 واط</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>كيابل شحن</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>شاحن سيارة جودا</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>شواحن سيارة</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>aletawiksa, iblackstores</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>194.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>شاحن سيارة جودا</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>شواحن سيارة</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>aletawiksa, wjhtektelecome</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>69.0 ر.س</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>106.38 ر.س</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1926,600 +1926,6 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>دار الأداب الهاربون والباقون</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>94.6 ر.س</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>سبيري حذاء هاربون على شكل قارب للرجال، كحلي، مقاس 42 EU</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>285.69 ر.س</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>بيلا فيتا حذاء برقبة للنساء من هارب</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>283.45 ر.س</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>روبوتايم 3 دي بازل هارب</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>201.33 ر.س</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>عاكس رياح معدني عالمي للدراجات النارية من هاربو، حاجب رياح امامي مع حامل للدراجة النارية مقاس 5 انش - 7 انش</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>35.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>وايلد ريبابليك لعبة قطيفة من بوكيت كينز ايكو هارب، حيوان محشو، 5 انش، مصنوعة من مواد معاد تدويرها، صديقة للبيئة</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>67.48 ر.س</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>سبيري حذاء قارب هاربون للرجال</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>348.39 ر.س</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>سبيري حذاء رياضي هاربون كراش باك سهل الارتداء للرجال</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>346.02 ر.س</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>سبيري حذاء قارب للرجال من هاربون، بيج داكن، مقاس 42 EU</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>285.52 ر.س</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>سبيري حذاء قارب هاربون للرجال، لون بيج داكن، مقاس 11.5</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>345.37 ر.س</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>ليجو نينجاجو سي باوند: كول ان سكوبا جير مع مسدس هاربون</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>184.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>Sperry Mens Harpoon Crushback Slip on Sneaker</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>353.57 ر.س</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>سبيري حذاء قارب هاربون للرجال، رمادي، 8.5</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>289.36 ر.س</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>الدو صندل هاربا مفتوح عند الاصابع للنساء من 20 هاربا</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>263.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>1279.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>ديوالت بطاريات ليثيوم ايون DCB135C من قطعتين 12 فولت 3 امبير / 5 امبير في الساعة ومجموعة شاحن بادئ التشغيل</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>807.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد SE بشاشة 11 بوصة، ذاكرة 4+128 جيجابايت، مع قلم ام بن لايت، شاشة فول فيو وبطارية ذات سعة كبيرة مع ركن خاص بالأطفال</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>720.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هونر باد X8a 4+ واي فاي 128 جيجا مع غطاء حماية قلاب، رمادي</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>799.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، WPS اوفيس (بدون قلم)، كيبورد وارد، هواوي كير حصري لمدة عام + (اخضر)</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>2199.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>3299.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بدون قلم، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس + هواوي كير لمدة عام واحد (ابيض)</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>2199.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>جهاز هواوي ميت باد برو 12مقاس 12.2 بوصة بدقة 2800×1840 ذاكرة رام 12 جيجابايت وروم 512 جيجابايت وواي فاي وكيبورد (Morandi-W09DK) وثماني النواة وبطارية ليثيوم بوليمر لون أخضر</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>2549.05 ر.س</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>3299.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>HUAWEI MatePad SE 11'' 8+128GB Nebula Grey Tablet, FullView Display, Large Capacity Battery, 1-Year Amazon Exclusive Huawei Care+</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>863.29 ر.س</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>شاحن بطارية للدراجة النارية 6 فولت/12 فولت بادئ الشحن التلقائي</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>100.75 ر.س</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>1454.16 ر.س</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت ريدمي باد 2 8GB + 256GB شاشة 11 انش 2.5K 90Hz ميديا تيك هيليو G100 الترا جرين (الشاحن متضمن)</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>992.04 ر.س</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -57,12 +57,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-20</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-21</t>
         </is>
       </c>
     </row>
@@ -550,94 +550,94 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>منصة جودا هاربو لشحن البطاريات</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>منصات ومحطات شحن</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>iblackstores</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>149.01 ر.س</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>149.01 ر.س</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>al3bor-telecom</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>179.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>179.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>منصة جودا هاربو لشحن البطاريات</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>منصات ومحطات شحن</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>al3bor-telecom</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>179.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>179.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>توصيلة جودا فولت لينك</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>توصيلات كهربائية</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -655,21 +655,21 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.0 ر.س</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35.8 ر.س</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -690,21 +690,21 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>160.0 ر.س</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>160.0 ر.س</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -725,21 +725,21 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100.75 ر.س</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100.75 ر.س</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, wjhtektelecome</t>
+          <t>aletawiksa, wjhtektelecome, amazon_sa</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>28.0 ر.س</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>106.38 ر.س</t>
+          <t>83.2 ر.س</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>379.01 ر.س</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>379.01 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>جودا - باور بانك NeoPower سعة 20000mAh بقوة 22.5 واط ومنفذين - أسود</t>
+          <t>الشحن والتوصيل والرسوم الجمركية</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>199.0 ر.س</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1687,17 +1687,17 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>iblackstores</t>
+          <t>wjhtektelecome</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>الشحن والتوصيل والرسوم الجمركية</t>
+          <t>بكج السرعة من جودا اليابانية</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>199.0 ر.س</t>
+          <t>195.99 ر.س</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>بكج السرعة من جودا اليابانية</t>
+          <t>بكج المنزل 6 منتجات اصلية من جودا اليابانية</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>بكج المنزل 6 منتجات اصلية من جودا اليابانية</t>
+          <t>جودا - شاحن سيارة بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>195.99 ر.س</t>
+          <t>143.75 ر.س</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن سيارة بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>143.75 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -1841,17 +1841,17 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1863,17 +1863,17 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>jarir</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>مايكل جوردن</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>39.99 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>مايكل جوردن</t>
+          <t>آنا كارنينا</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>39.99 ر.س</t>
+          <t>12.99 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1907,22 +1907,2200 @@
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>آنا كارنينا</t>
+          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>12.99 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>A7 بدون كاميرا وبدون نظام تحديد المواقع، ذاكرة RAM 12GB (4GB + 8GB قابلة للتوسيع) روم 128GB، شاشة 6.67 انش HD+، شريحتين اتصال، بطارية 5000mAh، 4G، ان اف سي، اندرويد 16 - اسود كوزميك</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>838.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>جوال تانك 1 متين 6.75 انش 120Hz FHD+ من شاندويليك، هاتف اتصال خارجي 12GB+256GB 20000mAh، هاتف ذكي 5G اندرويد 15 ان اف سي</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>2090.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>هاتف HONOR X9d 5G، رام 12 جيجابايت+تخزين 256 جيجابايت، بطارية سيليكون كربون، كاميرا OIS 108 ميجابكسل، شاشة أموليد 6.79 بوصة 120 هرتز، شحن 66 واط، سناب دراجون 6 الجيل 4، بني محمر</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>1384.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>61.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>82.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>94.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>99.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>جوال تانك 1 متين 6.75 انش 120Hz FHD+ من شاندويليك، هاتف اتصال خارجي 12GB+256GB 20000mAh، هاتف ذكي 5G اندرويد 15 ان اف سي</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>2090.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>188.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>118.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>164.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>A100Cs اخضر فاتح 2+4GB RAM 64GB 4G - اصدار الشرق الاوسط</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>329.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>175.29 ر.س</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>299.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>14.4 ر.س</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>خلطة فيز 160 جم من هاريبو</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>11.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>حلوى شامالو روبينو مارشميلو من هاريبو، 70 جم</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>5.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>6.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>8.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>11.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>14.7 ر.س</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>7.15 ر.س</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>11.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>هاريبو جولد بيرز، 150 غرام، عبوة من قطعة واحدة</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>10.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>جيلي فيز على شكل ديدان من هاريبو، 70 جم</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>6.15 ر.س</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>11.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>هاريبو جولد بيرز 160 جرام</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>11.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جيلي فيز ورمز من هاريبو، وزن 160 جرام</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>11.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>6.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>محول امداد طاقة تيار مستمر 9 فولت لكاميرا تابو تي بي لينك تابو C100 C100/A</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>24.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>51.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>40.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>56.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>مفتاح واي فاي اي وي لينك من ارنيم بتيار مستمر 5 فولت 12 فولت 24 فولت 32 فولت وحدة ترحيل لاسلكية للتحكم في المنزل الذكي مع تطبيق الجوال وجهاز تحكم عن بعد ومؤقت اليكسا وجوجل هوم للتحكم الصوتي لنظام</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>48.49 ر.س</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>106.11 ر.س</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>186.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>130.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>112.73 ر.س</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن PoE سلبي 48 فولت/18 واط TL-PoE4818G | محول جيجابت PoE | التوصيل والتشغيل | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>80.42 ر.س</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-PD30G-M2 | محول PoE الى غير PoE | يقسم الطاقة والبيانات حتى 330 قدم | التوصيل والتشغيل | معتمد من UL | مخرج تيار مستمر 12 فولت/9 فولت/5 فولت</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>110.58 ر.س</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>20.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>20.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>13.1 ر.س</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>13.14 ر.س</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>15.16 ر.س</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>49.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>13.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة قوة حصانية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ (اسود)</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>50.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه بسعة 5 جالون من كوزي تشارم، موزع مياه كهربائي محمول مع شحن USB نوع سي، محرك مزدوج، تدفق سريع، مثالي للمنزل والمكتب والتخييم والسيارة الترفيهية، اسود</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>53.3 ر.س</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>24.5 ر.س</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>11.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>موزع ماء بمضخة محمولة مناسبة لجميع الاحجم من 3 و4 و5 جالون مع شاحن USB كهربائي ومفتاح ايقاف التشغيل التلقائي (اسود)</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>31.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>مضخة تعزيز المياه من دي ام جي، مضخة تعزيز ضغط المياه الاوتوماتيكية المحمولة 24 فولت، مضخة معززة للدش 150 واط مع مفتاح تدفق تلقائي، مضخة مياه ساخنة وباردة لمياه الصنبور والمرحاض ودش الحمام (ابيض)</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>125.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>ibsun Water Pressure Booster Pump, 26.1 PSI, 100W, Automatic</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>180.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>29.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>250.78 ر.س</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>141.51 ر.س</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>182.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>160.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>188.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>94.96 ر.س</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>119.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>78.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>59.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>82.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>Anker Power Bank, 25,000mAh 165W Total Output Portable Charger for Laptops</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>288.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>118.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>78.69 ر.س</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>1237.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>ديوالت بطاريات ليثيوم ايون DCB135C من قطعتين 12 فولت 3 امبير / 5 امبير في الساعة ومجموعة شاحن بادئ التشغيل</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>968.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>جهاز تابلت باد 10 بيبرمات مقاس 12.1 بوصة وواي فاي وذاكرة رام 8 جيجابايت وذاكرة 256 جيجابايت مع حافظة لوحة المفاتيح مجانية وقلم هونر تشويس من هونر- إصدار الشرق الأوسط</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>1449.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>شاحن بطارية للدراجة النارية 6 فولت/12 فولت بادئ الشحن التلقائي</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>100.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، WPS اوفيس (بدون قلم)، كيبورد وارد، هواوي كير حصري لمدة عام + (اخضر)</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>2199.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بدون قلم، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس + هواوي كير لمدة عام واحد (ابيض)</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>2199.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>3299.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>ماجيك باد 4 12+ 256 جيجابايت واي فاي مع كيبورد وقلم ستايلس (في علبة)، رمادي - اصدار الشرق الاوسط من اونر</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>3599.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>بادئ تشغيل 24 فولت من باهيلز QDJ2659K-P QDJ2659K</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>1927.68 ر.س</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>HUAWEI MatePad SE 11'' 8+128GB Nebula Grey Tablet, FullView Display, Large Capacity Battery, 1-Year Amazon Exclusive Huawei Care+</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>863.29 ر.س</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>3299.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>1454.16 ر.س</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>شاومي تابلت ريدمي باد 2 8GB + 256GB شاشة 11 انش 2.5K 90Hz ميديا تيك هيليو G100 الترا جرين (الشاحن متضمن)</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>992.04 ر.س</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>بريك بادي مجموعة بطارية مباشرة 12 فولت 39305، اسود</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>465.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>شاحن محول تيار متردد 5 فولت 2000 مللي امبير 2 امبير لفيوسونيك فيو باد 7e VS14359</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>75.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>45.85 ر.س</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>46.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>58.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>88.79 ر.س</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>75.87 ر.س</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>28.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>59.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>79.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>106.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>39.17 ر.س</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>48.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع سامسونج وآيفون وهواوي P60 بـ 3 منافذ بقوة 130.0 واط مع شحن سريع وحماية متعددة</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>129.88 ر.س</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>35.79 ر.س</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>68.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>139.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-21</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-22</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>35.8 ر.س</t>
+          <t>24.48 ر.س</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -679,35 +679,35 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>160.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>160.0 ر.س</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, wjhtektelecome, amazon_sa</t>
+          <t>aletawiksa, wjhtektelecome</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>28.0 ر.س</t>
+          <t>69.0 ر.س</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>83.2 ر.س</t>
+          <t>106.38 ر.س</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D150"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>379.01 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>379.01 ر.س</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>49.0 ر.س</t>
+          <t>29.0 ر.س</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>مايكل جوردن</t>
+          <t>آنا كارنينا</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>39.99 ر.س</t>
+          <t>12.99 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1885,22 +1885,22 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>آنا كارنينا</t>
+          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>12.99 ر.س</t>
+          <t>61.99 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>59.0 ر.س</t>
+          <t>94.96 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>A7 بدون كاميرا وبدون نظام تحديد المواقع، ذاكرة RAM 12GB (4GB + 8GB قابلة للتوسيع) روم 128GB، شاشة 6.67 انش HD+، شريحتين اتصال، بطارية 5000mAh، 4G، ان اف سي، اندرويد 16 - اسود كوزميك</t>
+          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>838.95 ر.س</t>
+          <t>59.0 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>جوال تانك 1 متين 6.75 انش 120Hz FHD+ من شاندويليك، هاتف اتصال خارجي 12GB+256GB 20000mAh، هاتف ذكي 5G اندرويد 15 ان اف سي</t>
+          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>2090.0 ر.س</t>
+          <t>188.98 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>هاتف HONOR X9d 5G، رام 12 جيجابايت+تخزين 256 جيجابايت، بطارية سيليكون كربون، كاميرا OIS 108 ميجابكسل، شاشة أموليد 6.79 بوصة 120 هرتز، شحن 66 واط، سناب دراجون 6 الجيل 4، بني محمر</t>
+          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>1384.95 ر.س</t>
+          <t>228.99 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>61.99 ر.س</t>
+          <t>138.99 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+          <t>باور بانك صغير محمول 20000 مللي امبير في الساعة 45 واط بي دي للشحن السريع</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>82.95 ر.س</t>
+          <t>149.99 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>Anker Power Bank, 25,000mAh 165W Total Output Portable Charger for Laptops</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>94.96 ر.س</t>
+          <t>288.0 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>باور بانك 20000 مللي امبير في الساعة 20 واط بي دي شحن سريع، شاحن محمول 6 في 1 مع 4 كابلات USB ولايتنينج مدمجة، 1 منفذ USB-A و1 نوع C، شاشة LED، حزمة بطارية عالية السعة للجوال والتابلت</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>99.0 ر.س</t>
+          <t>138.87 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>جوال تانك 1 متين 6.75 انش 120Hz FHD+ من شاندويليك، هاتف اتصال خارجي 12GB+256GB 20000mAh، هاتف ذكي 5G اندرويد 15 ان اف سي</t>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>2090.0 ر.س</t>
+          <t>82.95 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
+          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>188.98 ر.س</t>
+          <t>169.0 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>118.99 ر.س</t>
+          <t>138.99 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>164.0 ر.س</t>
+          <t>198.81 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>A100Cs اخضر فاتح 2+4GB RAM 64GB 4G - اصدار الشرق الاوسط</t>
+          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>329.99 ر.س</t>
+          <t>175.28 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج</t>
+          <t>باور بانك من يوجرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب A مع شحن سريع وحماية للهاتف واللابتوب 3 منافذ</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>175.29 ر.س</t>
+          <t>178.85 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>299.0 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>هاريبو ميجا بارتي ميكس من هاريبو، 200 جرام</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>14.4 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>خلطة فيز 160 جم من هاريبو</t>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>11.3 ر.س</t>
+          <t>13.1 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>حلوى شامالو روبينو مارشميلو من هاريبو، 70 جم</t>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>5.8 ر.س</t>
+          <t>13.14 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>حلوى على شكل توت هاريبو بيريز، 80 غرام</t>
+          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>6.3 ر.س</t>
+          <t>15.16 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>هاريبو جيلي خليط كاندي ستار، 160 جم</t>
+          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>8.99 ر.س</t>
+          <t>49.3 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>حلوى الكرز هابي من هاريبو جيلي، 160 جرام</t>
+          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة قوة حصانية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ (اسود)</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>11.3 ر.س</t>
+          <t>50.3 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>حلوى جولد بيرز من هاريبو، 200 جم</t>
+          <t>موزع ماء بمضخة محمولة مناسبة لجميع الاحجم من 3 و4 و5 جالون مع شاحن USB كهربائي ومفتاح ايقاف التشغيل التلقائي (اسود)</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>14.7 ر.س</t>
+          <t>31.99 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>جيلي وحلوى هاريبو هابي تشيريز - 80 جم</t>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>7.15 ر.س</t>
+          <t>24.5 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 160 جم</t>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>11.3 ر.س</t>
+          <t>11.0 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>هاريبو جولد بيرز، 150 غرام، عبوة من قطعة واحدة</t>
+          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>10.99 ر.س</t>
+          <t>15.66 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>جيلي فيز على شكل ديدان من هاريبو، 70 جم</t>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>6.15 ر.س</t>
+          <t>13.75 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>حلوى هابي كولا من هاريبو، 150 جرام</t>
+          <t>استرو ايه اي منفاخ اطارات لاسلكي محمول 150 باوند لكل انش مربع</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>11.95 ر.س</t>
+          <t>99.98 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>هاريبو جولد بيرز 160 جرام</t>
+          <t>مضخة مياه كهربائية محمولة قابلة للشحن بمنفذ USB لعدد 2 عبوة بتصميم محمول للشحن للمكتب والمنزل والتخييم والمطبخ وغيرها سعة 7.5 إلى 19 لتر من سكاي-تاتش أسود</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>11.3 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلي فيز ورمز من هاريبو، وزن 160 جرام</t>
+          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>11.3 ر.س</t>
+          <t>34.99 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>حلوى جيلاتينية فانتاسيا من هاريبو، 80 جرام</t>
+          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>6.3 ر.س</t>
+          <t>1111.0 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>محول امداد طاقة تيار مستمر 9 فولت لكاميرا تابو تي بي لينك تابو C100 C100/A</t>
+          <t>جهاز تابلت باد 10 بيبرمات مقاس 12.1 بوصة وواي فاي وذاكرة رام 8 جيجابايت وذاكرة 256 جيجابايت مع حافظة لوحة المفاتيح مجانية وقلم هونر تشويس من هونر- إصدار الشرق الأوسط</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>24.99 ر.س</t>
+          <t>1449.0 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>ديوالت بطاريات ليثيوم ايون DCB135C من قطعتين 12 فولت 3 امبير / 5 امبير في الساعة ومجموعة شاحن بادئ التشغيل</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>51.0 ر.س</t>
+          <t>968.0 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+          <t>تابلت هواوي ميت باد SE بشاشة 11 بوصة، ذاكرة 4+128 جيجابايت، مع قلم ام بن لايت، شاشة فول فيو وبطارية ذات سعة كبيرة مع ركن خاص بالأطفال</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>40.0 ر.س</t>
+          <t>720.0 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
+          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، WPS اوفيس (بدون قلم)، كيبورد وارد، هواوي كير حصري لمدة عام + (اخضر)</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>56.0 ر.س</t>
+          <t>2199.0 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>3299.0 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>مفتاح واي فاي اي وي لينك من ارنيم بتيار مستمر 5 فولت 12 فولت 24 فولت 32 فولت وحدة ترحيل لاسلكية للتحكم في المنزل الذكي مع تطبيق الجوال وجهاز تحكم عن بعد ومؤقت اليكسا وجوجل هوم للتحكم الصوتي لنظام</t>
+          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بدون قلم، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس + هواوي كير لمدة عام واحد (ابيض)</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>48.49 ر.س</t>
+          <t>2199.0 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
+          <t>شاحن بطارية للدراجة النارية 6 فولت/12 فولت بادئ الشحن التلقائي</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>106.11 ر.س</t>
+          <t>100.75 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+          <t>ماجيك باد 4 12+ 256 جيجابايت واي فاي مع كيبورد وقلم ستايلس (في علبة)، رمادي - اصدار الشرق الاوسط من اونر</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>186.25 ر.س</t>
+          <t>3599.0 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>130.0 ر.س</t>
+          <t>3299.0 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
+          <t>HUAWEI MatePad SE 11'' 8+128GB Nebula Grey Tablet, FullView Display, Large Capacity Battery, 1-Year Amazon Exclusive Huawei Care+</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>112.73 ر.س</t>
+          <t>863.29 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE سلبي 48 فولت/18 واط TL-PoE4818G | محول جيجابت PoE | التوصيل والتشغيل | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط</t>
+          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>80.42 ر.س</t>
+          <t>1391.84 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-PD30G-M2 | محول PoE الى غير PoE | يقسم الطاقة والبيانات حتى 330 قدم | التوصيل والتشغيل | معتمد من UL | مخرج تيار مستمر 12 فولت/9 فولت/5 فولت</t>
+          <t>اونر تابلت باد X8a، واي فاي 11 انش، تخزين 64GB، بطارية 8300mAh، مكبر صوت رباعي، تصميم معدني رفيع، اندرويد 14، رمادي سبيس جديد</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>110.58 ر.س</t>
+          <t>1030.96 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,1269 +2836,15 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
+          <t>شاومي تابلت ريدمي باد 2 8GB + 256GB شاشة 11 انش 2.5K 90Hz ميديا تيك هيليو G100 الترا جرين (الشاحن متضمن)</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>20.9 ر.س</t>
+          <t>992.04 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>20.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>13.1 ر.س</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>13.14 ر.س</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>15.16 ر.س</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>49.3 ر.س</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>13.75 ر.س</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة قوة حصانية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ (اسود)</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>50.3 ر.س</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه بسعة 5 جالون من كوزي تشارم، موزع مياه كهربائي محمول مع شحن USB نوع سي، محرك مزدوج، تدفق سريع، مثالي للمنزل والمكتب والتخييم والسيارة الترفيهية، اسود</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>53.3 ر.س</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>24.5 ر.س</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>11.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>موزع ماء بمضخة محمولة مناسبة لجميع الاحجم من 3 و4 و5 جالون مع شاحن USB كهربائي ومفتاح ايقاف التشغيل التلقائي (اسود)</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>31.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>مضخة تعزيز المياه من دي ام جي، مضخة تعزيز ضغط المياه الاوتوماتيكية المحمولة 24 فولت، مضخة معززة للدش 150 واط مع مفتاح تدفق تلقائي، مضخة مياه ساخنة وباردة لمياه الصنبور والمرحاض ودش الحمام (ابيض)</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>125.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>ibsun Water Pressure Booster Pump, 26.1 PSI, 100W, Automatic</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>180.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه شرب يدوية طراز RF7785 من رويالفورد</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>29.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>250.78 ر.س</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>141.51 ر.س</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>182.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>160.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>188.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>94.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>119.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>78.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>59.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>82.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>Anker Power Bank, 25,000mAh 165W Total Output Portable Charger for Laptops</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>288.8 ر.س</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>118.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>78.69 ر.س</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>1237.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>ديوالت بطاريات ليثيوم ايون DCB135C من قطعتين 12 فولت 3 امبير / 5 امبير في الساعة ومجموعة شاحن بادئ التشغيل</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>968.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>جهاز تابلت باد 10 بيبرمات مقاس 12.1 بوصة وواي فاي وذاكرة رام 8 جيجابايت وذاكرة 256 جيجابايت مع حافظة لوحة المفاتيح مجانية وقلم هونر تشويس من هونر- إصدار الشرق الأوسط</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>1449.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>شاحن بطارية للدراجة النارية 6 فولت/12 فولت بادئ الشحن التلقائي</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>100.75 ر.س</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، WPS اوفيس (بدون قلم)، كيبورد وارد، هواوي كير حصري لمدة عام + (اخضر)</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>2199.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بدون قلم، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس + هواوي كير لمدة عام واحد (ابيض)</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>2199.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>3299.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>ماجيك باد 4 12+ 256 جيجابايت واي فاي مع كيبورد وقلم ستايلس (في علبة)، رمادي - اصدار الشرق الاوسط من اونر</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>3599.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>بادئ تشغيل 24 فولت من باهيلز QDJ2659K-P QDJ2659K</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>1927.68 ر.س</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>HUAWEI MatePad SE 11'' 8+128GB Nebula Grey Tablet, FullView Display, Large Capacity Battery, 1-Year Amazon Exclusive Huawei Care+</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>863.29 ر.س</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>3299.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>1454.16 ر.س</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت ريدمي باد 2 8GB + 256GB شاشة 11 انش 2.5K 90Hz ميديا تيك هيليو G100 الترا جرين (الشاحن متضمن)</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>992.04 ر.س</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>بريك بادي مجموعة بطارية مباشرة 12 فولت 39305، اسود</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>465.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>شاحن محول تيار متردد 5 فولت 2000 مللي امبير 2 امبير لفيوسونيك فيو باد 7e VS14359</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>75.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>45.85 ر.س</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B137" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C137" s="6" t="inlineStr">
-        <is>
-          <t>46.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D137" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>58.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B139" s="6" t="inlineStr">
-        <is>
-          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
-        </is>
-      </c>
-      <c r="C139" s="6" t="inlineStr">
-        <is>
-          <t>88.79 ر.س</t>
-        </is>
-      </c>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>75.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
-        </is>
-      </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>28.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>59.89 ر.س</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>79.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
-        </is>
-      </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>106.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C145" s="6" t="inlineStr">
-        <is>
-          <t>39.17 ر.س</t>
-        </is>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
-        </is>
-      </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>48.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="20" customHeight="1">
-      <c r="A147" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B147" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع سامسونج وآيفون وهواوي P60 بـ 3 منافذ بقوة 130.0 واط مع شحن سريع وحماية متعددة</t>
-        </is>
-      </c>
-      <c r="C147" s="6" t="inlineStr">
-        <is>
-          <t>129.88 ر.س</t>
-        </is>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B148" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
-        </is>
-      </c>
-      <c r="C148" s="6" t="inlineStr">
-        <is>
-          <t>35.79 ر.س</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B149" s="6" t="inlineStr">
-        <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 وجالكسي S24 وS23، بمنفذين، 60 واط، شحن سريع مع حماية متعددة</t>
-        </is>
-      </c>
-      <c r="C149" s="6" t="inlineStr">
-        <is>
-          <t>68.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D149" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع سامسونج S24 و آيفون 15 و ماك بوك، 3 منافذ، 130.0 واط، شحن سريع و تصميم مدمج</t>
-        </is>
-      </c>
-      <c r="C150" s="6" t="inlineStr">
-        <is>
-          <t>139.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr">
         <is>
           <t>رابط مؤكد</t>
         </is>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-22</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -644,35 +644,35 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>11.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>24.48 ر.س</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -714,35 +714,35 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>شاحن جودا فولت باد / VoltPad</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>شواحن جدارية</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>100.75 ر.س</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>100.75 ر.س</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>149.01 ر.س</t>
+          <t>379.01 ر.س</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>379.01 ر.س</t>
+          <t>149.01 ر.س</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1879,974 +1879,6 @@
       <c r="D49" s="6" t="inlineStr">
         <is>
           <t>بحث تقديري</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>61.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>94.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>59.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>188.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>228.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>138.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك صغير محمول 20000 مللي امبير في الساعة 45 واط بي دي للشحن السريع</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>149.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>Anker Power Bank, 25,000mAh 165W Total Output Portable Charger for Laptops</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>288.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>138.87 ر.س</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>82.95 ر.س</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>169.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>138.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>198.81 ر.س</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>يوجرين بنك طاقة نيكسود بسعة 20000mAh وقوة 67 واط،شاحن محمول مزود بكابل مدمج</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>175.28 ر.س</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>باور بانك من يوجرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب A مع شحن سريع وحماية للهاتف واللابتوب 3 منافذ</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>178.85 ر.س</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>20.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>20.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>13.1 ر.س</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>13.14 ر.س</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>15.16 ر.س</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>49.3 ر.س</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة قوة حصانية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ (اسود)</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>50.3 ر.س</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>موزع ماء بمضخة محمولة مناسبة لجميع الاحجم من 3 و4 و5 جالون مع شاحن USB كهربائي ومفتاح ايقاف التشغيل التلقائي (اسود)</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>31.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>24.5 ر.س</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>11.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>15.66 ر.س</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>13.75 ر.س</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>استرو ايه اي منفاخ اطارات لاسلكي محمول 150 باوند لكل انش مربع</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>99.98 ر.س</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>مضخة مياه كهربائية محمولة قابلة للشحن بمنفذ USB لعدد 2 عبوة بتصميم محمول للشحن للمكتب والمنزل والتخييم والمطبخ وغيرها سعة 7.5 إلى 19 لتر من سكاي-تاتش أسود</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>20.9 ر.س</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>34.99 ر.س</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>ديوالت بطاريات ليثيوم ايون ماكس باور ستاك DCBP315-2C 20 فولت ومجموعة شاحن بادئ التشغيل (1.7 Ah/5 Ah)</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>1111.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>جهاز تابلت باد 10 بيبرمات مقاس 12.1 بوصة وواي فاي وذاكرة رام 8 جيجابايت وذاكرة 256 جيجابايت مع حافظة لوحة المفاتيح مجانية وقلم هونر تشويس من هونر- إصدار الشرق الأوسط</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>1449.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>ديوالت بطاريات ليثيوم ايون DCB135C من قطعتين 12 فولت 3 امبير / 5 امبير في الساعة ومجموعة شاحن بادئ التشغيل</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>968.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد SE بشاشة 11 بوصة، ذاكرة 4+128 جيجابايت، مع قلم ام بن لايت، شاشة فول فيو وبطارية ذات سعة كبيرة مع ركن خاص بالأطفال</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>720.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، WPS اوفيس (بدون قلم)، كيبورد وارد، هواوي كير حصري لمدة عام + (اخضر)</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>2199.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>3299.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بدون قلم، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس + هواوي كير لمدة عام واحد (ابيض)</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>2199.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>شاحن بطارية للدراجة النارية 6 فولت/12 فولت بادئ الشحن التلقائي</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>100.75 ر.س</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>ماجيك باد 4 12+ 256 جيجابايت واي فاي مع كيبورد وقلم ستايلس (في علبة)، رمادي - اصدار الشرق الاوسط من اونر</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>3599.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>تابلت هواوي ميت باد اير 12 بوصة بشاشة اوليد بيبر مات، بذاكرة 8 +256GB</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>3299.0 ر.س</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>HUAWEI MatePad SE 11'' 8+128GB Nebula Grey Tablet, FullView Display, Large Capacity Battery, 1-Year Amazon Exclusive Huawei Care+</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>863.29 ر.س</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت بوكو باد ام 1 8 جيجا + 256 جيجا 12.1 انش 120 هرتز 2.5 كيه شاشة سناب دراجون® الجيل الرابع 7 الجيل الرابع بطارية 12000mAh يدعم الشحن العكسي 27 واط مع شاحن 33 واط (اسود)</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>1391.84 ر.س</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>اونر تابلت باد X8a، واي فاي 11 انش، تخزين 64GB، بطارية 8300mAh، مكبر صوت رباعي، تصميم معدني رفيع، اندرويد 14، رمادي سبيس جديد</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>1030.96 ر.س</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>شاومي تابلت ريدمي باد 2 8GB + 256GB شاشة 11 انش 2.5K 90Hz ميديا تيك هيليو G100 الترا جرين (الشاحن متضمن)</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>992.04 ر.س</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-23</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-24</t>
         </is>
       </c>
     </row>
@@ -644,105 +644,105 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>167.52 ر.س</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>167.52 ر.س</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>159.5 ر.س</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>شاحن جودا فولت باد / VoltPad</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>شواحن جدارية</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>100.75 ر.س</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>100.75 ر.س</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -760,11 +760,11 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, iblackstores</t>
+          <t>aletawiksa, iblackstores, amazon_sa</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>194.0 ر.س</t>
+          <t>423.93 ر.س</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -795,21 +795,21 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>aletawiksa, wjhtektelecome</t>
+          <t>aletawiksa, wjhtektelecome, amazon_sa</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>69.0 ر.س</t>
+          <t>29.0 ر.س</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>106.38 ر.س</t>
+          <t>79.01 ر.س</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>بكج السرعة من جودا اليابانية</t>
+          <t>بكج المنزل 6 منتجات اصلية من جودا اليابانية</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>بكج المنزل 6 منتجات اصلية من جودا اليابانية</t>
+          <t>جودا - شاحن سيارة بقوة 30 واط بمنفذ تايب سي - اسود</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>195.99 ر.س</t>
+          <t>143.75 ر.س</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>جودا - شاحن سيارة بقوة 30 واط بمنفذ تايب سي - اسود</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>143.75 ر.س</t>
+          <t>171.35 ر.س</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - رمادي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10,000 مللي أمبير - ذهبي</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - أزرق</t>
+          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -1819,17 +1819,17 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>wjhtektelecome</t>
+          <t>alwan7</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>بطارية متنقلة جودا MagZ 10 (ماج سيف) بسعة 10000 مللي أمبير - برتقالي</t>
+          <t>الحقوق محفوظة | 2026 متجر الوان</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>171.35 ر.س</t>
+          <t>50.0 ر.س</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1841,17 +1841,17 @@
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>alwan7</t>
+          <t>jarir</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>الحقوق محفوظة | 2026 متجر الوان</t>
+          <t>آنا كارنينا</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>50.0 ر.س</t>
+          <t>12.99 ر.س</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1863,22 +1863,1518 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>jarir</t>
+          <t>amazon_sa</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>آنا كارنينا</t>
+          <t>محول امداد طاقة تيار مستمر 9 فولت لكاميرا تابو تي بي لينك تابو C100 C100/A</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>12.99 ر.س</t>
+          <t>24.99 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>بحث تقديري</t>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>51.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>40.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE2412G، محول PoE</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>56.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>186.25 ر.س</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>106.26 ر.س</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>130.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>66.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>67.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك TL-PD30G-M2 | محول PoE الى غير PoE | يقسم الطاقة والبيانات حتى 330 قدم | التوصيل والتشغيل | معتمد من UL | مخرج تيار مستمر 12 فولت/9 فولت/5 فولت</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>110.63 ر.س</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>TP - لينك EAP683 UR | اومادا واي فاي 6 AX6000 لاسلكي 2.5G يثبت على السقف | يدعم شبكة او اف دي ام ايه والتجوال السلس HE160 وMU-MIMO | SDN مدمج | الوصول السحابي وتطبيق اومادا | يعمل بتقنية PoE+</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>699.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>مكبر صوت ساوند لينك ميني 2 فولت من بوز (088772، 088789، 088796، 7.4 فولت، 3400mAh)</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>254.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>061384 061385 061386 063287/063287 بوز ساوند لينك ميني 1 1 بوز ساوند لينك ميني 1 1 بوز ساوند لينك ميني اي ون ون 7.4 فولت 2230 مللي امبير في الساعة 17 واط</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>252.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>141.51 ر.س</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>249.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>182.8 ر.س</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>138.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>89.9 ر.س</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>119.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>188.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>138.87 ر.س</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>118.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>78.69 ر.س</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>78.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>79.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>109.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>شاحن باور بانك RP-PB208 10000 مللي امبير في الساعة 30 واط بمنفذين وشاحن حائط 65 واط من راف باور، أسود</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>169.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>ديوالت بطاريات ليثيوم ايون DCB135C من قطعتين 12 فولت 3 امبير / 5 امبير في الساعة ومجموعة شاحن بادئ التشغيل</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>968.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>اونر تابلت باد X8a 11 انش 4GB RAM 128GB ROM سناب دراجون 680 4G ماجيك او اس</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>716.36 ر.س</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>3299.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، WPS اوفيس (بدون قلم)، كيبورد وارد، هواوي كير حصري لمدة عام + (اخضر)</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>2199.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بدون قلم، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس + هواوي كير لمدة عام واحد (ابيض)</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>2199.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>مجموعة بادئ راسبيري باي 4 بسعة 4 جيجابايت بلون اسود | مزود طاقة USB نوع سي 5 فولت 3 امبير | غطاء | مشتت حراري | راسبيري باي 4 موديل بي 4 ذاكرة رام 4 جيجابايت</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>636.39 ر.س</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>ماجيك باد 4 12+ 256 جيجابايت واي فاي مع كيبورد وقلم ستايلس (في علبة)، رمادي - اصدار الشرق الاوسط من اونر</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>3599.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>هواوي تابلت ميت باد 11.5 اس (2026)، شاشة فائقة الوضوح، 12GB + 256GB، بطارية 8800mAh، شحن فائق 40 واط، كيبورد قابل للفصل، رمادي</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>1599.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>شاحن بطارية للدراجة النارية 6 فولت/12 فولت بادئ الشحن التلقائي</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>100.75 ر.س</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>تابلت ميت باد برو بحجم 12.2 بوصة اتصال واي فاي فقط وبذاكرة 12 جيجابايت وتخزين 512 جيجابايت من هواوي، لون أسود</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>2534.31 ر.س</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>HUAWEI MatePad SE 11'' 8+128GB Nebula Grey Tablet, FullView Display, Large Capacity Battery, 1-Year Amazon Exclusive Huawei Care+</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>860.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240 هرتز FHD 1080p، لوحة VA، وقت استجابة 2 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر 3 جوانب بدون إطار نحيفة للغاية، 99% اس ار جي بي، فلتر للضوء الأزرق، HDMI وDP، لون أسود من فيوفيجن</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>399.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>509.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>422.97 ر.س</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>شاشة العاب تي يو اف VG27AQ5A-J من اسوس: 27 انش، كيو اتش دي (2560×1440)، 210 هرتز (او سي)، تقنية IPS سريعة، مزامنة ELMB، 0.3ms GTG (دقيقة)، مكبر صوت ستيريو، مركز عرض ويدجيت، اسود - اصدار قوس</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>849.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>مبرد وحدة المعالجة المركزية السائل نيكسورا 240 من سودوكو: مبرد وحدة المعالجة المركزية AIO 240 ملم مع مضخة PWM ورأس مضخة ARGB - تبريد مائي مع مراوح اف دي بي لانتل LGA 1851/1700/1200/115X AMD AM5/AM4 - اسود</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>167.52 ر.س</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>فيوسونيك شاشة العاب VX2479A-HD-PRO 61 سم 240 هرتز</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>499.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>472.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>كورسير مبرد سائل لوحدة المعالجة المركزية 240 RS ARGB AIO من نوتيلوس 240 ملم متوافق مع انتل LGA 1851/1700 وAMD AM5/AM4، يتضمن مروحتين RS120 ARGB - اسود</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>402.45 ر.س</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>389.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>GAMEON GOESP27240IPS E-sports Series, Black Gaming Monitor 27 Inch, 1920x1080p FHD IPS Panel, 240Hz Refresh Rate, 0.5ms Response Time, Supports HDR 10, PS5</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>565.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>567.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>549.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>KTC شاشة العاب منحنية 24 انش 240 هرتز، شاشة كمبيوتر FHD H24S17P</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>529.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>45.84 ر.س</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>35.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>88.98 ر.س</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>88.79 ر.س</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>75.87 ر.س</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>58.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة لاسلكي وحامل جوال مغناطيسي، شحن سريع 15 واط، حامل تابلوه قابل للدوران 360 درجة، كوب شفط جل ومغناطيس N52، متوافق مع الاجهزة العالمية، تركيب سريع</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>89.99 ر.س</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>59.89 ر.س</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>29.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>79.95 ر.س</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>48.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>39.17 ر.س</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع سامسونج وآيفون وهواوي P60 بـ 3 منافذ بقوة 130.0 واط مع شحن سريع وحماية متعددة</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>129.88 ر.س</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>شاحن سيارة USB C مع خاصية امداد الطاقة القابل للبرمجة 30 واط، يو اس بي، أسود</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>39.0 ر.س</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آبل آيفون XR بمنفذين 24.0 واط مع منافذ مزدوجة وتصميم مدمج ومقاوم للخدش</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>35.79 ر.س</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>رابط مؤكد</t>
         </is>
       </c>
     </row>

--- a/data/تقرير_المنافسين.xlsx
+++ b/data/تقرير_المنافسين.xlsx
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-24</t>
+          <t>تقرير رصد المنافسين — تيك تايم — 2026-10-25</t>
         </is>
       </c>
     </row>
@@ -585,21 +585,21 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>al3bor-telecom</t>
+          <t>al3bor-telecom, amazon_sa</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>67.24 ر.س</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>179.0 ر.س</t>
+          <t>219.68 ر.س</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -644,175 +644,175 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>مضخة هواء جودا AirVolt / مضخة بدون بطارية</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>منتجات السيارة</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>167.52 ر.س</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>167.52 ر.س</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>11.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>32.22 ر.س</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>بطارية راف باور</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>بطاريات متنقلة</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>amazon_sa</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>150.0 ر.س</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>159.5 ر.س</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>150.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>شاحن جودا فولت باد / VoltPad</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>شواحن جدارية</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>amazon_sa</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>100.75 ر.س</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>100.75 ر.س</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>كيبل جودا 240 واط</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>كيابل شحن</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>aletawiksa, iblackstores</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>89.0 ر.س</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>194.0 ر.س</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>شاحن سيارة جودا</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>شواحن سيارة</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>aletawiksa, iblackstores, amazon_sa</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>89.0 ر.س</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>423.93 ر.س</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>شاحن سيارة جودا</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>شواحن سيارة</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>aletawiksa, wjhtektelecome, amazon_sa</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>29.0 ر.س</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>79.01 ر.س</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>81.92 ر.س</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>تعذر الجلب (حظر مؤقت من جوجل، طبيعي أحيانًا)</t>
         </is>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>محول امداد طاقة تيار مستمر 9 فولت لكاميرا تابو تي بي لينك تابو C100 C100/A</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>24.99 ر.س</t>
+          <t>89.9 ر.س</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك حاقن PoE | محول PoE 24V DC PoE السلبي | منافذ جيجابت | حتى 100 متر (320 قدم) | تصميم قابل للتثبيت على الحائط (TL-PoE2412G)</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>51.0 ر.س</t>
+          <t>138.99 ر.س</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>موزع جيجابت بتقنية نل الطاقة عبر الايثرنت متوافق مع 802.3af من تي بي لينك TL-PoE10R، مخرج طاقة 5/9/12 فولت تيار مستمر، حتى 100 متر، محول طاقة وكيبل متضمنة</t>
+          <t>جوي باور بانك 20,000 مللي امبير في الساعة من كيجو - شحن متزامن للهواتف الذكية والتابلت واجهزة الالعاب والمزيد، شاحن محمول صغير الحجم مناسب للسفر، اسود</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>40.0 ر.س</t>
+          <t>53.0 ر.س</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE2412G، محول PoE</t>
+          <t>باور بانك 20000 مللي امبير في الساعة من ايوسويت - شاحن محمول سريع الشحن 22.5 واط مع شاشة LED رقمية، شحن متزامن من 3 اجهزة، متوافق مع ايفون 17/16/15، سامسونج S25/S24، هونر - اسود</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>56.0 ر.س</t>
+          <t>61.99 ر.س</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>محول وحاقن نقل الطاقة عبر الايثرنت 2.5 جيجابت من تي بي لينك TL-POE260S</t>
+          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>89.0 ر.س</t>
+          <t>188.98 ر.س</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 404600، ساوند لينك، ساوند لينك 2، ساوند لينك 3، ساوند لينك 2، ساوند لينك II، ساوند تاتش 20، 11.1 فولت/2200 مللي امبير في الساعة</t>
+          <t>باور بانك صغير محمول 20000 مللي امبير في الساعة 45 واط بي دي للشحن السريع</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>186.25 ر.س</t>
+          <t>129.99 ر.س</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>شاحن مكبر صوت بلوتوث 12 فولت لبوز ساوند لينك ميني اي هاي فاي</t>
+          <t>Anker Power Bank, 25,000mAh 165W Total Output Portable Charger for Laptops</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>106.26 ر.س</t>
+          <t>288.8 ر.س</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>بطارية بديلة لبوز 413295، ساوند لينك ميني، ساوند لينك ميني ون، 7.4 فولت/2600 مللي امبير في الساعة من زوفكوس</t>
+          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>130.0 ر.س</t>
+          <t>138.87 ر.س</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-POE4824G 48V محول PoE السلبي إيثرنت جيجابت</t>
+          <t>باور بانك من أنكر 20000 مللي أمبير 5 ساعات شحن بمنفذ USB-C شحن سريع و كابل مدمج للهاتف الذكي أزرق</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>66.0 ر.س</t>
+          <t>138.99 ر.س</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك وحدة ميني غب، IEEE 802.3z، CSMA/CD، TCP/IP، طول الموجة 850 نانومتر، مزود طاقة 3.3 فولت، 1.25 جيجابايت في الثانية، 9/125 ميكرومتر أحادي الطور (SM311LM)</t>
+          <t>يوجرين مجموعة طاقة ، تتضمن بنك طاقة 20000 مللي أمبير/ساعة 45 وات وشاحن USB C قابل للسحب وكابل USB C 60 وات وFineTrack ومجموعة شحن لأجهزة iPad/الهاتف/الساعة وما إلى ذلك، مثالية للأعمال والسفر</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>67.0 ر.س</t>
+          <t>228.99 ر.س</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك TL-PD30G-M2 | محول PoE الى غير PoE | يقسم الطاقة والبيانات حتى 330 قدم | التوصيل والتشغيل | معتمد من UL | مخرج تيار مستمر 12 فولت/9 فولت/5 فولت</t>
+          <t>انكر باور بانك (نسخة مطورة 2026) من زولو، شحن سريع 45 واط، بطارية 20,000</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>110.63 ر.س</t>
+          <t>169.0 ر.س</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>TP - لينك EAP683 UR | اومادا واي فاي 6 AX6000 لاسلكي 2.5G يثبت على السقف | يدعم شبكة او اف دي ام ايه والتجوال السلس HE160 وMU-MIMO | SDN مدمج | الوصول السحابي وتطبيق اومادا | يعمل بتقنية PoE+</t>
+          <t>INIU Power Bank, Smallest 20000mAh 22.5W Fast Charging Portable Charger</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>699.0 ر.س</t>
+          <t>111.14 ر.س</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>مكبر صوت ساوند لينك ميني 2 فولت من بوز (088772، 088789، 088796، 7.4 فولت، 3400mAh)</t>
+          <t>باور بانك من يوجرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب A مع شحن سريع وحماية للهاتف واللابتوب 3 منافذ</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>254.0 ر.س</t>
+          <t>178.85 ر.س</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>061384 061385 061386 063287/063287 بوز ساوند لينك ميني 1 1 بوز ساوند لينك ميني 1 1 بوز ساوند لينك ميني اي ون ون 7.4 فولت 2230 مللي امبير في الساعة 17 واط</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>252.0 ر.س</t>
+          <t>198.81 ر.س</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
+          <t>باور بانك CP25 سعة 20000 مللي امبير في الساعة بقدرة 55 واط كحد اقصى مع كيبل USB-C مدمج من كوك تيك</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>141.51 ر.س</t>
+          <t>139.0 ر.س</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
+          <t>دار الأداب الهاربون والباقون</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>249.0 ر.س</t>
+          <t>94.6 ر.س</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
+          <t>كودا هاربون دارت اند ليارد</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>182.8 ر.س</t>
+          <t>138.46 ر.س</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
+          <t>بيلا فيتا حذاء برقبة للنساء من هارب</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>138.99 ر.س</t>
+          <t>282.46 ر.س</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
+          <t>حذاء هاربون اوكسفورد للرجال من ستيف مادن</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>150.0 ر.س</t>
+          <t>77.72 ر.س</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
+          <t>روبوتايم 3 دي بازل هارب</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>89.9 ر.س</t>
+          <t>212.92 ر.س</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
+          <t>سلفيمار هاربون جيت 5 اينوكس، اسود، 17 سم</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>119.0 ر.س</t>
+          <t>67.24 ر.س</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
+          <t>وايلد ريبابليك لعبة قطيفة ناعمة على شكل جرو من هارب سيل، العاب كادلكينز المحبوبة، هدايا للاطفال 20 سم، ابيض</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>188.98 ر.س</t>
+          <t>81.05 ر.س</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يوجرين 20 امبير ليثيوم أيون بوليمر بمنفذ USB-C مع كابل مدمج و شحن سريع للهاتف الذكي و اللابتوب</t>
+          <t>وايلد ريبابليك لعبة قطيفة من بوكيت كينز ايكو هارب، حيوان محشو، 5 انش، مصنوعة من مواد معاد تدويرها، صديقة للبيئة</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>138.87 ر.س</t>
+          <t>108.34 ر.س</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
+          <t>سبيري حذاء قارب هاربون للرجال</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>118.99 ر.س</t>
+          <t>345.98 ر.س</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
+          <t>سبيري حذاء رياضي هاربون كراش باك سهل الارتداء للرجال</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>78.69 ر.س</t>
+          <t>346.37 ر.س</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
+          <t>سبيري حذاء قارب للرجال من هاربون، بيج داكن، مقاس 42 EU</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>78.99 ر.س</t>
+          <t>286.34 ر.س</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من إينيو 10000 مللي امبير بشحن 3 ساعات بمنفذ USB تايب-C مع شحن سريع للهواتف و التابلت باللون الأسود</t>
+          <t>سبيري حذاء قارب هاربون للرجال، لون بيج داكن، مقاس 11.5</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>79.95 ر.س</t>
+          <t>344.9 ر.س</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
+          <t>سبيري حذاء قارب هاربون للرجال، رمادي، 8.5</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>109.0 ر.س</t>
+          <t>290.92 ر.س</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>شاحن باور بانك RP-PB208 10000 مللي امبير في الساعة 30 واط بمنفذين وشاحن حائط 65 واط من راف باور، أسود</t>
+          <t>سبيري حذاء هاربون على شكل قارب للرجال، كحلي، مقاس 42 EU</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>169.0 ر.س</t>
+          <t>285.65 ر.س</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>ديوالت بطاريات ليثيوم ايون DCB135C من قطعتين 12 فولت 3 امبير / 5 امبير في الساعة ومجموعة شاحن بادئ التشغيل</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>968.0 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>اونر تابلت باد X8a 11 انش 4GB RAM 128GB ROM سناب دراجون 680 4G ماجيك او اس</t>
+          <t>مضخة مياه لوازم - 112 × 64 ملم - موزع مياه قابل لإعادة الشحن مع شحن USB نوع سي وفوهة من الفولاذ المقاوم للصدأ توافق زجاجة 14-23 لتر - مثالي للمنزل والمكتب والمطبخ والأماكن الخارجية والسفر</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>716.36 ر.س</t>
+          <t>13.1 ر.س</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>هواوي تابلت ميت باد اير 12 انش OLED بيبر مات 8+256 جيجا 10100 مللي امبير في</t>
+          <t>براد ماء من سكاي-تاتش محمول، لامع، أبيض، مصنوع من البلاستيك، سعة 5.0 جالون</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>3299.0 ر.س</t>
+          <t>20.9 ر.س</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بطارية 10100mAh، شحن فائق 66 واط، WPS اوفيس (بدون قلم)، كيبورد وارد، هواوي كير حصري لمدة عام + (اخضر)</t>
+          <t>مضخة مياه كهربائية لاسلكية قابلة لإعادة الشحن، أوتوماتيكية لزجاجات المياه سعة الجالون، مزودة بزر تشغيل ويمكن حملها، مناسبة للمطبخ والمنزل والمكتب والتخييم (لون أسود).</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>2199.0 ر.س</t>
+          <t>15.16 ر.س</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>تابلت هواوي ميت باد 12 X 2025 بشاشة 2.8K 12 انش غير لامعة، 12+256GB، بدون قلم، بطارية 10100mAh، شحن فائق 66 واط، دبليو بي اس اوفيس + هواوي كير لمدة عام واحد (ابيض)</t>
+          <t>ارنيس مضخة موزع مياه كهربائية، مضخات مزدوجة بقوة حصانية عالية، منافذ مياه مزدوجة، واجهة شحن من النوع سي، اباريق مضخة مياه كهربائية محمولة، شحن USB C، للمكتب والمنزل والمطبخ</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>2199.0 ر.س</t>
+          <t>49.3 ر.س</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>مجموعة بادئ راسبيري باي 4 بسعة 4 جيجابايت بلون اسود | مزود طاقة USB نوع سي 5 فولت 3 امبير | غطاء | مشتت حراري | راسبيري باي 4 موديل بي 4 ذاكرة رام 4 جيجابايت</t>
+          <t>مضخة مياه شرب من لوازم - موزع يدوي محمول يعمل بالضغط اليدوي لزجاجات المياه - خالية من البيسفينول ايه للسفر</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>636.39 ر.س</t>
+          <t>19.95 ر.س</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>ماجيك باد 4 12+ 256 جيجابايت واي فاي مع كيبورد وقلم ستايلس (في علبة)، رمادي - اصدار الشرق الاوسط من اونر</t>
+          <t>موزع ماء بمضخة محمولة مناسبة لجميع الاحجم من 3 و4 و5 جالون مع شاحن USB كهربائي ومفتاح ايقاف التشغيل التلقائي (اسود)</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>3599.0 ر.س</t>
+          <t>31.99 ر.س</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>هواوي تابلت ميت باد 11.5 اس (2026)، شاشة فائقة الوضوح، 12GB + 256GB، بطارية 8800mAh، شحن فائق 40 واط، كيبورد قابل للفصل، رمادي</t>
+          <t>مضخة موزع مياه من بادرايغ محمولة، براد ماء باللون الأبيض مصنوعة من سيليكون وستانلس ستيل وبلاستيك ABS، سعة 18.9 لتر</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>1599.0 ر.س</t>
+          <t>15.66 ر.س</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>شاحن بطارية للدراجة النارية 6 فولت/12 فولت بادئ الشحن التلقائي</t>
+          <t>مضخة هواء كهربائية اوتوماتيكية تيار مستمر 12 فولت - تيار متردد 230 فولت مع 3 مرفقات من جينيرك، DC12V-AC230V</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>100.75 ر.س</t>
+          <t>24.5 ر.س</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>تابلت ميت باد برو بحجم 12.2 بوصة اتصال واي فاي فقط وبذاكرة 12 جيجابايت وتخزين 512 جيجابايت من هواوي، لون أسود</t>
+          <t>مضخة يدوية مزدوجة وسريعة من انتيكس</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>2534.31 ر.س</t>
+          <t>11.0 ر.س</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>HUAWEI MatePad SE 11'' 8+128GB Nebula Grey Tablet, FullView Display, Large Capacity Battery, 1-Year Amazon Exclusive Huawei Care+</t>
+          <t>مضخة تعزيز المياه من دي ام جي، مضخة تعزيز ضغط المياه الاوتوماتيكية المحمولة 24 فولت، مضخة معززة للدش 150 واط مع مفتاح تدفق تلقائي، مضخة مياه ساخنة وباردة لمياه الصنبور والمرحاض ودش الحمام (ابيض)</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>860.0 ر.س</t>
+          <t>125.0 ر.س</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب من اسوس، سلسلة ألعاب تي يو اف 5، مقاس 23.8 بوصة، بدقة FHD (1920 × 1080) وتقنية فاست-اي بي اس مع 240 هرتز وزمن استجابة 0.3 ميلي ثانية وإضاءة ار جي بي 99%، إصدار انفينيارك موديل VG249QM5A-J</t>
+          <t>مضخة شفط يدوية محمولة وخفيفة الوزن ومتينة ذات التدفق العالي ومتعددة الأغراض لنقل السوائل والوقود والماء والزيت للمنزل والسيارة والحديقة والطوارئ من لوازم، قطعتان</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>499.0 ر.س</t>
+          <t>13.75 ر.س</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب 24 بوصة 240 هرتز FHD 1080p، لوحة VA، وقت استجابة 2 مللي ثانية، مزامنة تكيفية، شاشة كمبيوتر 3 جوانب بدون إطار نحيفة للغاية، 99% اس ار جي بي، فلتر للضوء الأزرق، HDMI وDP، لون أسود من فيوفيجن</t>
+          <t>مضخة زجاجة مياه الشرب من نيكومي، مضخة زجاجة مياه بشحن USB، مضخة مياه شرب اوتوماتيك، لزجاجة 3-5 جالون عالمية، موزع مياه محمول للاماكن الداخلية والخارجية (لون اسود)</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>399.0 ر.س</t>
+          <t>34.99 ر.س</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>كمبيوتر فيوسونيك VX2719 MHD للألعاب‏، شاشة منحنية FHD‏ 27 انش 1920×1080، 240Hz‏، 1 مللي في الثانية، منفذ صوت 3.5 ملم، HDMI 2.0 ×2، منفذ عرض: 1، مزامنة تكييفية، أسود، LED</t>
+          <t>استرو ايه اي منفاخ اطارات لاسلكي محمول 150 باوند لكل انش مربع</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>509.0 ر.س</t>
+          <t>99.98 ر.س</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب بدون إطار بحجم 24.5 بوصة وبمعدل تحديث 240 هرتز وزمن استجابة 1 مللي ثانية ودقة FHD 1920×1080 بتقنية IPS مع فري سينك، تدعم DP وHDM من زي-ايدج، طراز UG25</t>
+          <t>منفاخ هواء من إنتكس أوتوماتيكي مع 3 فوهات قابلة للتوصيل كهربائي سلكي</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>422.97 ر.س</t>
+          <t>57.37 ر.س</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>شاشة العاب تي يو اف VG27AQ5A-J من اسوس: 27 انش، كيو اتش دي (2560×1440)، 210 هرتز (او سي)، تقنية IPS سريعة، مزامنة ELMB، 0.3ms GTG (دقيقة)، مكبر صوت ستيريو، مركز عرض ويدجيت، اسود - اصدار قوس</t>
+          <t>راف بور باور بانك الترا بي دي بيونير 20000mAh، مخرج 100W كحد اقصى، شحن سريع ثنائي الاتجاه 70W، شاشة رقمية ذكية، شحن 4 أجهزة، شاحن محمول صغير للابتوب والتابلت والجوال الذكي - PB208ULTR</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>849.0 ر.س</t>
+          <t>244.59 ر.س</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>مبرد وحدة المعالجة المركزية السائل نيكسورا 240 من سودوكو: مبرد وحدة المعالجة المركزية AIO 240 ملم مع مضخة PWM ورأس مضخة ARGB - تبريد مائي مع مراوح اف دي بي لانتل LGA 1851/1700/1200/115X AMD AM5/AM4 - اسود</t>
+          <t>شاحن من رافباور بمنفذ USB متوافق مع آيفون 12 و13 و14 و15 بمنفذين بقوة 20 واط مع شحن سريع ولاسلكي ومغناطيسي وحامل قابل للطي</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>167.52 ر.س</t>
+          <t>141.51 ر.س</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>فيوسونيك شاشة العاب VX2479A-HD-PRO 61 سم 240 هرتز</t>
+          <t>باور بانك PB1229 20 واط 20000 ميلي امبير في الساعة مع شاحن سيارة VC1017 وكابل CB1021 نوع C إلى نوع C من راف باور، أسود</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>499.0 ر.س</t>
+          <t>150.0 ر.س</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>شاشة ألعاب 24 بوصة 240Hz، شاشة كمبيوتر 1080P مع لوحة IPS سريعة، HDR 400، مزامنة تكيفية، 1 مللي ثانية (ام بي ار تي)، 116% sRGB، منفذ عرض HDMI، العناية بالعين، حامل فيسا H24F7، أبيض H24F7</t>
+          <t>باور بانك بي دي بيونير 20000 مللي أمبير في الساعة مع كيبل USB-C مدمج من راف بور، شحن سريع 35 واط، منفذ مزدوج، حماية اي سمارت المتقدمة، PB1224-PRO</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>472.0 ر.س</t>
+          <t>182.8 ر.س</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>كورسير مبرد سائل لوحدة المعالجة المركزية 240 RS ARGB AIO من نوتيلوس 240 ملم متوافق مع انتل LGA 1851/1700 وAMD AM5/AM4، يتضمن مروحتين RS120 ARGB - اسود</t>
+          <t>انكر باور بانك من زولو، شاحن محمول عالي السرعة 20,000mAh 30 واط مع كيبل</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>402.45 ر.س</t>
+          <t>138.99 ر.س</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>مبرد مياه لوحدة المعالجة المركزية كور 240 RGB من ان زد اكس تي كراكين - مبرد 240 ملم - مروحة إطار واحد 240 ملم - متوافق مع انتل LGA 1851/1700/1200/115X وAMD AM5/AM4 - أسود</t>
+          <t>يوجرين باور بانك بسعة 20000mAh و22.5W ، يدعم الشحن السريع، وشاشة عرض رقمية</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>389.0 ر.س</t>
+          <t>89.9 ر.س</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>GAMEON GOESP27240IPS E-sports Series, Black Gaming Monitor 27 Inch, 1920x1080p FHD IPS Panel, 240Hz Refresh Rate, 0.5ms Response Time, Supports HDR 10, PS5</t>
+          <t>باور بانك من يو جرين 10 امبير ساعة بوقت شحن 2.3 ساعة بمنفذ USB-C و USB-A مع كابل مدمج و شحن سريع لسمارتفون و تابلت 3 منافذ</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>565.0 ر.س</t>
+          <t>119.0 ر.س</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>KTC 27 Inch Gaming Monitor 240Hz, FHD 1080p Fast IPS Computer Monitor with Adaptive Sync, HDR, Height Pivot Tilt Adjustable, Vesa Mount, HDMI/DP/USB, H27F7</t>
+          <t>يوجرين باور بانك 20000mAh 30 واط مع 3 منافذ (2 × USB-C وUSB-A) بطارية محمولة، شاشة رقمية، شاحن محمول سريع الشحن مع كابل لايفون 16، جالكسي S25U/S25/S24، ايباد، ايربودز</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>567.0 ر.س</t>
+          <t>118.99 ر.س</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>جيم اون شاشة العاب ميدنايت برو GOM24FHD240IPS 61 سم FHD 1920×1080 240Hz MPRT 0.5 مللي ثانية جاهزة لوحدة التحكم (PS5)، HDMI 2.1، DP 1.4، HDR10، 99% sRGB، فري سينك، مكبرات صوت، RGB، اسود</t>
+          <t>باور بانك من يو جرين 5000 ميلي امبير بمنفذ USB تايب-C مع شحن لاسلكي مغناطيسي و سريع للهاتف الذكي، أوف وايت</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>549.0 ر.س</t>
+          <t>78.99 ر.س</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>KTC شاشة العاب منحنية 24 انش 240 هرتز، شاشة كمبيوتر FHD H24S17P</t>
+          <t>باور بانك من أنكر 10000 مللي امبير بمنفذ USB-C مع شحن سريع و تصميم مدمج للهاتف الذكي و التابلت منفذ واحد أسود</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>529.99 ر.س</t>
+          <t>78.69 ر.س</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
+          <t>انكر باور بانك، شاحن محمول 20000mAh مع كيبل USB-C مدمج، حزمة بطارية شحن سريع 87 واط، لماك بوك، لابتوب، ايفون 17/16/15، سامسونج S25/S24/S23، هواوي، هونر والمزيد</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>45.84 ر.س</t>
+          <t>188.98 ر.س</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
+          <t>باور بانك من يو جرين 20000 مللي امبير ليثيوم أيون بمنفذ USB تايب-C شحن سريع مع شاشة ذكية للابتوب و السمارتفون 3 منافذ</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>35.98 ر.س</t>
+          <t>198.81 ر.س</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
+          <t>باور بانك من يوجرين 20000 مللي أمبير بوقت شحن 1.5 ساعة بمنفذ USB تايب A مع شحن سريع وحماية للهاتف واللابتوب 3 منافذ</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>88.98 ر.س</t>
+          <t>178.85 ر.س</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
+          <t>باور بانك في 9، شاحن محمول صغير 22.5 واط USB C 10000 مللي امبير في الساعة، حزمة بطارية شحن سريع بي دي، 3 مخارج شاحن موبايل متوافق مع ايفون وسامسونج وبيكسل وايربودز وايباد رمادي</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>88.79 ر.س</t>
+          <t>74.9 ر.س</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
+          <t>باور بانك من PDBEST بسعة 20 امبير بمنفذ USB-C و لايتنينج و مايكرو USB مع كابل مدمج و شحن سريع لهاتف ذكي و جهاز لوحي بـ 5 منافذ أسود</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>75.87 ر.س</t>
+          <t>109.99 ر.س</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 و15 و14 وسامسونج وآيباد، 3 منافذ، 30 واط، شحن سريع مع حماية متعددة</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>58.99 ر.س</t>
+          <t>45.84 ر.س</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة لاسلكي وحامل جوال مغناطيسي، شحن سريع 15 واط، حامل تابلوه قابل للدوران 360 درجة، كوب شفط جل ومغناطيس N52، متوافق مع الاجهزة العالمية، تركيب سريع</t>
+          <t>شاحن من إنيو بمنفذ USB و USB-C متوافق مع آيفون 13 برو ماكس وسامسونج، منفذين، 30 واط، شحن سريع وتصميم مدمج</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>89.99 ر.س</t>
+          <t>35.98 ر.س</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
+          <t>انكر شاحن سيارة USB C، شاحن سيارة سريع صغير للغاية 75 واط مع كيبل مدمج قابل</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>59.89 ر.س</t>
+          <t>88.79 ر.س</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من بروميت بمنفذ USB متوافق مع آيفون وأندرويد بمنفذين بقوة 20 واط مع شحن سريع وتوصيل الطاقة وكويك تشارج 3.0</t>
+          <t>شاحن من أنكر بمنفذ USB متوافق مع آيفون 16 و15 و14 و13 و12 بمنفذين بقوة 40.0 واط مع شحن سريع وتصميم مدمج</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>29.0 ر.س</t>
+          <t>58.99 ر.س</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة من XXZU بمنفذ USB و USB-C متوافق مع آيفون وسامسونج وهواوي، 4 منافذ، 137.0 واط، شحن سريع مع كابل قابل للسحب</t>
+          <t>شاحن سيارة من يوجرين بمنفذ USB و USB-C لآيفون 16 و15 وجالاكسي S25 و S24 بـ 3 منافذ بقوة 75 واط مع شحن سريع وكابل قابل للسحب</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>79.95 ر.س</t>
+          <t>88.98 ر.س</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>شاحن سيارة 120 واط 5 في 1 بكابلين قابلين للسحب تايب C ولايتنينج، شاحن سريع USB-C PD وUSB، متوافق مع آيفون 16/15/14/13/12، آيباد، سامسونج جالاكسي، بيكسل، شاومي</t>
+          <t>شاحن من يو جرين بمنفذ USB متوافق مع آيفون 16 و جالكسي S23 و هواوي و شاومي بمنفذين بقوة 30.0 واط مع شحن سريع و حماية متعددة</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>48.0 ر.س</t>
+          <t>59.89 ر.س</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>شاحن من يوجرين بمنفذ USB متوافق مع آيفون 13 و سامسونج S21 و هواوي Mate20 بمنفذين 24.0 واط مع شحن سريع و حماية متعددة</t>
+          <t>شاحن سيارة من يو جرين بمنفذ USB متوافق مع آيفون 16 وسامسونج S25 وماك بوك، 3 منافذ، 60 واط، شحن سريع مع كابل قابل للسحب</t>
         </is>
     